--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49C4D75-C643-4B4A-BC85-4A3ABDB7A8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70FB213-CF76-4D52-BDBC-3FE7159D2F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="39">
   <si>
     <t>Aluno</t>
   </si>
@@ -554,8 +554,12 @@
       <c r="L1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
+      <c r="M1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
@@ -671,8 +675,12 @@
       <c r="L2" s="1">
         <v>46078</v>
       </c>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="M2" s="1">
+        <v>46080</v>
+      </c>
+      <c r="N2" s="1">
+        <v>46085</v>
+      </c>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
@@ -759,6 +767,12 @@
         <v>37</v>
       </c>
       <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -876,6 +890,12 @@
       <c r="L4" t="s">
         <v>36</v>
       </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -991,6 +1011,12 @@
       <c r="L5" t="s">
         <v>36</v>
       </c>
+      <c r="M5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1106,6 +1132,12 @@
       <c r="L6" t="s">
         <v>36</v>
       </c>
+      <c r="M6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N6" t="s">
+        <v>36</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1221,6 +1253,12 @@
       <c r="L7" t="s">
         <v>36</v>
       </c>
+      <c r="M7" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1336,6 +1374,12 @@
       <c r="L8" t="s">
         <v>36</v>
       </c>
+      <c r="M8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1451,6 +1495,12 @@
       <c r="L9" t="s">
         <v>36</v>
       </c>
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1566,6 +1616,12 @@
       <c r="L10" t="s">
         <v>36</v>
       </c>
+      <c r="M10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1681,6 +1737,12 @@
       <c r="L11" t="s">
         <v>36</v>
       </c>
+      <c r="M11" t="s">
+        <v>36</v>
+      </c>
+      <c r="N11" t="s">
+        <v>36</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1796,6 +1858,12 @@
       <c r="L12" t="s">
         <v>36</v>
       </c>
+      <c r="M12" t="s">
+        <v>36</v>
+      </c>
+      <c r="N12" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1911,6 +1979,12 @@
       <c r="L13" t="s">
         <v>36</v>
       </c>
+      <c r="M13" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2026,6 +2100,12 @@
       <c r="L14" t="s">
         <v>36</v>
       </c>
+      <c r="M14" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2141,6 +2221,12 @@
       <c r="L15" t="s">
         <v>37</v>
       </c>
+      <c r="M15" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" t="s">
+        <v>37</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2256,6 +2342,12 @@
       <c r="L16" t="s">
         <v>36</v>
       </c>
+      <c r="M16" t="s">
+        <v>36</v>
+      </c>
+      <c r="N16" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2371,6 +2463,12 @@
       <c r="L17" t="s">
         <v>36</v>
       </c>
+      <c r="M17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N17" t="s">
+        <v>36</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2486,6 +2584,12 @@
       <c r="L18" t="s">
         <v>36</v>
       </c>
+      <c r="M18" t="s">
+        <v>36</v>
+      </c>
+      <c r="N18" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2601,6 +2705,12 @@
       <c r="L19" t="s">
         <v>36</v>
       </c>
+      <c r="M19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N19" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2716,6 +2826,12 @@
       <c r="L20" t="s">
         <v>36</v>
       </c>
+      <c r="M20" t="s">
+        <v>36</v>
+      </c>
+      <c r="N20" t="s">
+        <v>36</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2831,6 +2947,12 @@
       <c r="L21" t="s">
         <v>36</v>
       </c>
+      <c r="M21" t="s">
+        <v>36</v>
+      </c>
+      <c r="N21" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -2946,6 +3068,12 @@
       <c r="L22" t="s">
         <v>36</v>
       </c>
+      <c r="M22" t="s">
+        <v>36</v>
+      </c>
+      <c r="N22" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3061,6 +3189,12 @@
       <c r="L23" t="s">
         <v>36</v>
       </c>
+      <c r="M23" t="s">
+        <v>36</v>
+      </c>
+      <c r="N23" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3176,6 +3310,12 @@
       <c r="L24" t="s">
         <v>36</v>
       </c>
+      <c r="M24" t="s">
+        <v>37</v>
+      </c>
+      <c r="N24" t="s">
+        <v>36</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3291,6 +3431,12 @@
       <c r="L25" t="s">
         <v>36</v>
       </c>
+      <c r="M25" t="s">
+        <v>36</v>
+      </c>
+      <c r="N25" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3406,6 +3552,12 @@
       <c r="L26" t="s">
         <v>36</v>
       </c>
+      <c r="M26" t="s">
+        <v>36</v>
+      </c>
+      <c r="N26" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3521,6 +3673,12 @@
       <c r="L27" t="s">
         <v>36</v>
       </c>
+      <c r="M27" t="s">
+        <v>36</v>
+      </c>
+      <c r="N27" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3636,6 +3794,12 @@
       <c r="L28" t="s">
         <v>36</v>
       </c>
+      <c r="M28" t="s">
+        <v>36</v>
+      </c>
+      <c r="N28" t="s">
+        <v>36</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3751,6 +3915,12 @@
       <c r="L29" t="s">
         <v>36</v>
       </c>
+      <c r="M29" t="s">
+        <v>36</v>
+      </c>
+      <c r="N29" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -3866,6 +4036,12 @@
       <c r="L30" t="s">
         <v>36</v>
       </c>
+      <c r="M30" t="s">
+        <v>36</v>
+      </c>
+      <c r="N30" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -3981,6 +4157,12 @@
       <c r="L31" t="s">
         <v>36</v>
       </c>
+      <c r="M31" t="s">
+        <v>36</v>
+      </c>
+      <c r="N31" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4096,6 +4278,12 @@
       <c r="L32" t="s">
         <v>36</v>
       </c>
+      <c r="M32" t="s">
+        <v>36</v>
+      </c>
+      <c r="N32" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -4211,6 +4399,12 @@
       <c r="L33" t="s">
         <v>36</v>
       </c>
+      <c r="M33" t="s">
+        <v>36</v>
+      </c>
+      <c r="N33" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70FB213-CF76-4D52-BDBC-3FE7159D2F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18DEAB6-6824-4DDE-9CE8-A7DD02EE8457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="39">
   <si>
     <t>Aluno</t>
   </si>
@@ -518,10 +518,12 @@
   <dimension ref="A1:DS33"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="50" width="7.7109375" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="50" width="7.7109375" customWidth="1"/>
     <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
     <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
@@ -560,7 +562,9 @@
       <c r="N1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="O1" s="1"/>
+      <c r="O1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -681,7 +685,9 @@
       <c r="N2" s="1">
         <v>46085</v>
       </c>
-      <c r="O2" s="1"/>
+      <c r="O2" s="1">
+        <v>46087</v>
+      </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
@@ -773,6 +779,9 @@
         <v>36</v>
       </c>
       <c r="N3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O3" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -896,6 +905,9 @@
       <c r="N4" t="s">
         <v>36</v>
       </c>
+      <c r="O4" t="s">
+        <v>36</v>
+      </c>
       <c r="AU4" s="2"/>
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
@@ -1017,6 +1029,9 @@
       <c r="N5" t="s">
         <v>36</v>
       </c>
+      <c r="O5" t="s">
+        <v>36</v>
+      </c>
       <c r="AU5" s="2"/>
       <c r="AV5" s="2"/>
       <c r="AW5" s="2"/>
@@ -1138,6 +1153,9 @@
       <c r="N6" t="s">
         <v>36</v>
       </c>
+      <c r="O6" t="s">
+        <v>36</v>
+      </c>
       <c r="AU6" s="2"/>
       <c r="AV6" s="2"/>
       <c r="AW6" s="2"/>
@@ -1259,6 +1277,9 @@
       <c r="N7" t="s">
         <v>36</v>
       </c>
+      <c r="O7" t="s">
+        <v>36</v>
+      </c>
       <c r="AU7" s="2"/>
       <c r="AV7" s="2"/>
       <c r="AW7" s="2"/>
@@ -1380,6 +1401,9 @@
       <c r="N8" t="s">
         <v>36</v>
       </c>
+      <c r="O8" t="s">
+        <v>36</v>
+      </c>
       <c r="AU8" s="2"/>
       <c r="AV8" s="2"/>
       <c r="AW8" s="2"/>
@@ -1501,6 +1525,9 @@
       <c r="N9" t="s">
         <v>36</v>
       </c>
+      <c r="O9" t="s">
+        <v>36</v>
+      </c>
       <c r="AU9" s="2"/>
       <c r="AV9" s="2"/>
       <c r="AW9" s="2"/>
@@ -1622,6 +1649,9 @@
       <c r="N10" t="s">
         <v>36</v>
       </c>
+      <c r="O10" t="s">
+        <v>36</v>
+      </c>
       <c r="AU10" s="2"/>
       <c r="AV10" s="2"/>
       <c r="AW10" s="2"/>
@@ -1743,6 +1773,9 @@
       <c r="N11" t="s">
         <v>36</v>
       </c>
+      <c r="O11" t="s">
+        <v>37</v>
+      </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
       <c r="AW11" s="2"/>
@@ -1864,6 +1897,9 @@
       <c r="N12" t="s">
         <v>36</v>
       </c>
+      <c r="O12" t="s">
+        <v>36</v>
+      </c>
       <c r="AU12" s="2"/>
       <c r="AV12" s="2"/>
       <c r="AW12" s="2"/>
@@ -1985,6 +2021,9 @@
       <c r="N13" t="s">
         <v>36</v>
       </c>
+      <c r="O13" t="s">
+        <v>36</v>
+      </c>
       <c r="AU13" s="2"/>
       <c r="AV13" s="2"/>
       <c r="AW13" s="2"/>
@@ -2106,6 +2145,9 @@
       <c r="N14" t="s">
         <v>36</v>
       </c>
+      <c r="O14" t="s">
+        <v>36</v>
+      </c>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
       <c r="AW14" s="2"/>
@@ -2227,6 +2269,9 @@
       <c r="N15" t="s">
         <v>37</v>
       </c>
+      <c r="O15" t="s">
+        <v>36</v>
+      </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
       <c r="AW15" s="2"/>
@@ -2348,6 +2393,9 @@
       <c r="N16" t="s">
         <v>36</v>
       </c>
+      <c r="O16" t="s">
+        <v>36</v>
+      </c>
       <c r="AU16" s="2"/>
       <c r="AV16" s="2"/>
       <c r="AW16" s="2"/>
@@ -2469,6 +2517,9 @@
       <c r="N17" t="s">
         <v>36</v>
       </c>
+      <c r="O17" t="s">
+        <v>36</v>
+      </c>
       <c r="AU17" s="2"/>
       <c r="AV17" s="2"/>
       <c r="AW17" s="2"/>
@@ -2590,6 +2641,9 @@
       <c r="N18" t="s">
         <v>36</v>
       </c>
+      <c r="O18" t="s">
+        <v>36</v>
+      </c>
       <c r="AU18" s="2"/>
       <c r="AV18" s="2"/>
       <c r="AW18" s="2"/>
@@ -2711,6 +2765,9 @@
       <c r="N19" t="s">
         <v>36</v>
       </c>
+      <c r="O19" t="s">
+        <v>36</v>
+      </c>
       <c r="AU19" s="2"/>
       <c r="AV19" s="2"/>
       <c r="AW19" s="2"/>
@@ -2832,6 +2889,9 @@
       <c r="N20" t="s">
         <v>36</v>
       </c>
+      <c r="O20" t="s">
+        <v>36</v>
+      </c>
       <c r="AU20" s="2"/>
       <c r="AV20" s="2"/>
       <c r="AW20" s="2"/>
@@ -2953,6 +3013,9 @@
       <c r="N21" t="s">
         <v>36</v>
       </c>
+      <c r="O21" t="s">
+        <v>36</v>
+      </c>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
       <c r="AW21" s="2"/>
@@ -3074,6 +3137,9 @@
       <c r="N22" t="s">
         <v>36</v>
       </c>
+      <c r="O22" t="s">
+        <v>36</v>
+      </c>
       <c r="AU22" s="2"/>
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
@@ -3195,6 +3261,9 @@
       <c r="N23" t="s">
         <v>36</v>
       </c>
+      <c r="O23" t="s">
+        <v>36</v>
+      </c>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
@@ -3316,6 +3385,9 @@
       <c r="N24" t="s">
         <v>36</v>
       </c>
+      <c r="O24" t="s">
+        <v>36</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3437,6 +3509,9 @@
       <c r="N25" t="s">
         <v>36</v>
       </c>
+      <c r="O25" t="s">
+        <v>36</v>
+      </c>
       <c r="AU25" s="2"/>
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
@@ -3558,6 +3633,9 @@
       <c r="N26" t="s">
         <v>36</v>
       </c>
+      <c r="O26" t="s">
+        <v>36</v>
+      </c>
       <c r="AU26" s="2"/>
       <c r="AV26" s="2"/>
       <c r="AW26" s="2"/>
@@ -3679,6 +3757,9 @@
       <c r="N27" t="s">
         <v>36</v>
       </c>
+      <c r="O27" t="s">
+        <v>36</v>
+      </c>
       <c r="AU27" s="2"/>
       <c r="AV27" s="2"/>
       <c r="AW27" s="2"/>
@@ -3800,6 +3881,9 @@
       <c r="N28" t="s">
         <v>36</v>
       </c>
+      <c r="O28" t="s">
+        <v>36</v>
+      </c>
       <c r="AU28" s="2"/>
       <c r="AV28" s="2"/>
       <c r="AW28" s="2"/>
@@ -3921,6 +4005,9 @@
       <c r="N29" t="s">
         <v>36</v>
       </c>
+      <c r="O29" t="s">
+        <v>36</v>
+      </c>
       <c r="AU29" s="2"/>
       <c r="AV29" s="2"/>
       <c r="AW29" s="2"/>
@@ -4042,6 +4129,9 @@
       <c r="N30" t="s">
         <v>36</v>
       </c>
+      <c r="O30" t="s">
+        <v>36</v>
+      </c>
       <c r="AU30" s="2"/>
       <c r="AV30" s="2"/>
       <c r="AW30" s="2"/>
@@ -4163,6 +4253,9 @@
       <c r="N31" t="s">
         <v>36</v>
       </c>
+      <c r="O31" t="s">
+        <v>36</v>
+      </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
       <c r="AW31" s="2"/>
@@ -4284,6 +4377,9 @@
       <c r="N32" t="s">
         <v>36</v>
       </c>
+      <c r="O32" t="s">
+        <v>36</v>
+      </c>
       <c r="AU32" s="2"/>
       <c r="AV32" s="2"/>
       <c r="AW32" s="2"/>
@@ -4405,6 +4501,9 @@
       <c r="N33" t="s">
         <v>36</v>
       </c>
+      <c r="O33" t="s">
+        <v>36</v>
+      </c>
       <c r="AU33" s="2"/>
       <c r="AV33" s="2"/>
       <c r="AW33" s="2"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18DEAB6-6824-4DDE-9CE8-A7DD02EE8457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7D1250-C361-4BE6-A5C2-E4213AC78E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="39">
   <si>
     <t>Aluno</t>
   </si>
@@ -516,19 +516,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS33"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
@@ -565,7 +565,9 @@
       <c r="O1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="P1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
@@ -642,7 +644,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -688,7 +690,9 @@
       <c r="O2" s="1">
         <v>46087</v>
       </c>
-      <c r="P2" s="1"/>
+      <c r="P2" s="1">
+        <v>46092</v>
+      </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -736,7 +740,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -782,6 +786,9 @@
         <v>36</v>
       </c>
       <c r="O3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -860,7 +867,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -906,6 +913,9 @@
         <v>36</v>
       </c>
       <c r="O4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" t="s">
         <v>36</v>
       </c>
       <c r="AU4" s="2"/>
@@ -984,7 +994,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1030,6 +1040,9 @@
         <v>36</v>
       </c>
       <c r="O5" t="s">
+        <v>36</v>
+      </c>
+      <c r="P5" t="s">
         <v>36</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1108,7 +1121,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1154,6 +1167,9 @@
         <v>36</v>
       </c>
       <c r="O6" t="s">
+        <v>36</v>
+      </c>
+      <c r="P6" t="s">
         <v>36</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1232,7 +1248,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1278,6 +1294,9 @@
         <v>36</v>
       </c>
       <c r="O7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" t="s">
         <v>36</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1356,7 +1375,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1402,6 +1421,9 @@
         <v>36</v>
       </c>
       <c r="O8" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8" t="s">
         <v>36</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1480,7 +1502,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1526,6 +1548,9 @@
         <v>36</v>
       </c>
       <c r="O9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" t="s">
         <v>36</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1604,7 +1629,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1650,6 +1675,9 @@
         <v>36</v>
       </c>
       <c r="O10" t="s">
+        <v>36</v>
+      </c>
+      <c r="P10" t="s">
         <v>36</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1728,7 +1756,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1775,6 +1803,9 @@
       </c>
       <c r="O11" t="s">
         <v>37</v>
+      </c>
+      <c r="P11" t="s">
+        <v>36</v>
       </c>
       <c r="AU11" s="2"/>
       <c r="AV11" s="2"/>
@@ -1852,7 +1883,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -1898,6 +1929,9 @@
         <v>36</v>
       </c>
       <c r="O12" t="s">
+        <v>36</v>
+      </c>
+      <c r="P12" t="s">
         <v>36</v>
       </c>
       <c r="AU12" s="2"/>
@@ -1976,7 +2010,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2022,6 +2056,9 @@
         <v>36</v>
       </c>
       <c r="O13" t="s">
+        <v>36</v>
+      </c>
+      <c r="P13" t="s">
         <v>36</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2100,7 +2137,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2146,6 +2183,9 @@
         <v>36</v>
       </c>
       <c r="O14" t="s">
+        <v>36</v>
+      </c>
+      <c r="P14" t="s">
         <v>36</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2224,7 +2264,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2271,6 +2311,9 @@
       </c>
       <c r="O15" t="s">
         <v>36</v>
+      </c>
+      <c r="P15" t="s">
+        <v>37</v>
       </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
@@ -2348,7 +2391,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2394,6 +2437,9 @@
         <v>36</v>
       </c>
       <c r="O16" t="s">
+        <v>36</v>
+      </c>
+      <c r="P16" t="s">
         <v>36</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2472,7 +2518,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2518,6 +2564,9 @@
         <v>36</v>
       </c>
       <c r="O17" t="s">
+        <v>36</v>
+      </c>
+      <c r="P17" t="s">
         <v>36</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2596,7 +2645,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2642,6 +2691,9 @@
         <v>36</v>
       </c>
       <c r="O18" t="s">
+        <v>36</v>
+      </c>
+      <c r="P18" t="s">
         <v>36</v>
       </c>
       <c r="AU18" s="2"/>
@@ -2720,7 +2772,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -2766,6 +2818,9 @@
         <v>36</v>
       </c>
       <c r="O19" t="s">
+        <v>36</v>
+      </c>
+      <c r="P19" t="s">
         <v>36</v>
       </c>
       <c r="AU19" s="2"/>
@@ -2844,7 +2899,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -2890,6 +2945,9 @@
         <v>36</v>
       </c>
       <c r="O20" t="s">
+        <v>36</v>
+      </c>
+      <c r="P20" t="s">
         <v>36</v>
       </c>
       <c r="AU20" s="2"/>
@@ -2968,7 +3026,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3014,6 +3072,9 @@
         <v>36</v>
       </c>
       <c r="O21" t="s">
+        <v>36</v>
+      </c>
+      <c r="P21" t="s">
         <v>36</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3092,7 +3153,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3138,6 +3199,9 @@
         <v>36</v>
       </c>
       <c r="O22" t="s">
+        <v>36</v>
+      </c>
+      <c r="P22" t="s">
         <v>36</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3216,7 +3280,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3262,6 +3326,9 @@
         <v>36</v>
       </c>
       <c r="O23" t="s">
+        <v>36</v>
+      </c>
+      <c r="P23" t="s">
         <v>36</v>
       </c>
       <c r="AU23" s="2"/>
@@ -3340,7 +3407,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3386,6 +3453,9 @@
         <v>36</v>
       </c>
       <c r="O24" t="s">
+        <v>36</v>
+      </c>
+      <c r="P24" t="s">
         <v>36</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3464,7 +3534,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3510,6 +3580,9 @@
         <v>36</v>
       </c>
       <c r="O25" t="s">
+        <v>36</v>
+      </c>
+      <c r="P25" t="s">
         <v>36</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3588,7 +3661,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3634,6 +3707,9 @@
         <v>36</v>
       </c>
       <c r="O26" t="s">
+        <v>36</v>
+      </c>
+      <c r="P26" t="s">
         <v>36</v>
       </c>
       <c r="AU26" s="2"/>
@@ -3712,7 +3788,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -3758,6 +3834,9 @@
         <v>36</v>
       </c>
       <c r="O27" t="s">
+        <v>36</v>
+      </c>
+      <c r="P27" t="s">
         <v>36</v>
       </c>
       <c r="AU27" s="2"/>
@@ -3836,7 +3915,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -3882,6 +3961,9 @@
         <v>36</v>
       </c>
       <c r="O28" t="s">
+        <v>36</v>
+      </c>
+      <c r="P28" t="s">
         <v>36</v>
       </c>
       <c r="AU28" s="2"/>
@@ -3960,7 +4042,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4006,6 +4088,9 @@
         <v>36</v>
       </c>
       <c r="O29" t="s">
+        <v>36</v>
+      </c>
+      <c r="P29" t="s">
         <v>36</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4084,7 +4169,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4130,6 +4215,9 @@
         <v>36</v>
       </c>
       <c r="O30" t="s">
+        <v>36</v>
+      </c>
+      <c r="P30" t="s">
         <v>36</v>
       </c>
       <c r="AU30" s="2"/>
@@ -4208,7 +4296,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4255,6 +4343,9 @@
       </c>
       <c r="O31" t="s">
         <v>36</v>
+      </c>
+      <c r="P31" t="s">
+        <v>37</v>
       </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
@@ -4332,7 +4423,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4378,6 +4469,9 @@
         <v>36</v>
       </c>
       <c r="O32" t="s">
+        <v>36</v>
+      </c>
+      <c r="P32" t="s">
         <v>36</v>
       </c>
       <c r="AU32" s="2"/>
@@ -4456,7 +4550,7 @@
       <c r="DR32" s="5"/>
       <c r="DS32" s="5"/>
     </row>
-    <row r="33" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4502,6 +4596,9 @@
         <v>36</v>
       </c>
       <c r="O33" t="s">
+        <v>36</v>
+      </c>
+      <c r="P33" t="s">
         <v>36</v>
       </c>
       <c r="AU33" s="2"/>
@@ -4598,15 +4695,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4614,157 +4711,157 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>33</v>
       </c>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7D1250-C361-4BE6-A5C2-E4213AC78E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68A6062-687D-4F3F-A91A-CF50F214EC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="39">
   <si>
     <t>Aluno</t>
   </si>
@@ -516,19 +516,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS33"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="50" width="7.7109375" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
@@ -568,8 +568,12 @@
       <c r="P1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="Q1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -644,7 +648,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -693,8 +697,12 @@
       <c r="P2" s="1">
         <v>46092</v>
       </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
+      <c r="Q2" s="1">
+        <v>46094</v>
+      </c>
+      <c r="R2" s="1">
+        <v>46099</v>
+      </c>
       <c r="S2" s="1"/>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
@@ -740,7 +748,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -789,6 +797,12 @@
         <v>36</v>
       </c>
       <c r="P3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
         <v>36</v>
       </c>
       <c r="AU3" s="2"/>
@@ -867,7 +881,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -916,6 +930,12 @@
         <v>36</v>
       </c>
       <c r="P4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
         <v>36</v>
       </c>
       <c r="AU4" s="2"/>
@@ -994,7 +1014,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1043,6 +1063,12 @@
         <v>36</v>
       </c>
       <c r="P5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" t="s">
         <v>36</v>
       </c>
       <c r="AU5" s="2"/>
@@ -1121,7 +1147,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1170,6 +1196,12 @@
         <v>36</v>
       </c>
       <c r="P6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R6" t="s">
         <v>36</v>
       </c>
       <c r="AU6" s="2"/>
@@ -1248,7 +1280,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1297,6 +1329,12 @@
         <v>36</v>
       </c>
       <c r="P7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>36</v>
+      </c>
+      <c r="R7" t="s">
         <v>36</v>
       </c>
       <c r="AU7" s="2"/>
@@ -1375,7 +1413,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1424,6 +1462,12 @@
         <v>36</v>
       </c>
       <c r="P8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>36</v>
+      </c>
+      <c r="R8" t="s">
         <v>36</v>
       </c>
       <c r="AU8" s="2"/>
@@ -1502,7 +1546,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1551,6 +1595,12 @@
         <v>36</v>
       </c>
       <c r="P9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>36</v>
+      </c>
+      <c r="R9" t="s">
         <v>36</v>
       </c>
       <c r="AU9" s="2"/>
@@ -1629,7 +1679,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1678,6 +1728,12 @@
         <v>36</v>
       </c>
       <c r="P10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>36</v>
+      </c>
+      <c r="R10" t="s">
         <v>36</v>
       </c>
       <c r="AU10" s="2"/>
@@ -1756,7 +1812,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1805,6 +1861,12 @@
         <v>37</v>
       </c>
       <c r="P11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" t="s">
         <v>36</v>
       </c>
       <c r="AU11" s="2"/>
@@ -1883,7 +1945,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -1932,6 +1994,12 @@
         <v>36</v>
       </c>
       <c r="P12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>36</v>
+      </c>
+      <c r="R12" t="s">
         <v>36</v>
       </c>
       <c r="AU12" s="2"/>
@@ -2010,7 +2078,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2059,6 +2127,12 @@
         <v>36</v>
       </c>
       <c r="P13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>36</v>
+      </c>
+      <c r="R13" t="s">
         <v>36</v>
       </c>
       <c r="AU13" s="2"/>
@@ -2137,7 +2211,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2186,6 +2260,12 @@
         <v>36</v>
       </c>
       <c r="P14" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>36</v>
+      </c>
+      <c r="R14" t="s">
         <v>36</v>
       </c>
       <c r="AU14" s="2"/>
@@ -2264,7 +2344,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2314,6 +2394,12 @@
       </c>
       <c r="P15" t="s">
         <v>37</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>36</v>
+      </c>
+      <c r="R15" t="s">
+        <v>36</v>
       </c>
       <c r="AU15" s="2"/>
       <c r="AV15" s="2"/>
@@ -2391,7 +2477,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2440,6 +2526,12 @@
         <v>36</v>
       </c>
       <c r="P16" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>36</v>
+      </c>
+      <c r="R16" t="s">
         <v>36</v>
       </c>
       <c r="AU16" s="2"/>
@@ -2518,7 +2610,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2567,6 +2659,12 @@
         <v>36</v>
       </c>
       <c r="P17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>36</v>
+      </c>
+      <c r="R17" t="s">
         <v>36</v>
       </c>
       <c r="AU17" s="2"/>
@@ -2645,7 +2743,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2694,6 +2792,12 @@
         <v>36</v>
       </c>
       <c r="P18" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>36</v>
+      </c>
+      <c r="R18" t="s">
         <v>36</v>
       </c>
       <c r="AU18" s="2"/>
@@ -2772,7 +2876,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -2821,6 +2925,12 @@
         <v>36</v>
       </c>
       <c r="P19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>36</v>
+      </c>
+      <c r="R19" t="s">
         <v>36</v>
       </c>
       <c r="AU19" s="2"/>
@@ -2899,7 +3009,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -2948,6 +3058,12 @@
         <v>36</v>
       </c>
       <c r="P20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>36</v>
+      </c>
+      <c r="R20" t="s">
         <v>36</v>
       </c>
       <c r="AU20" s="2"/>
@@ -3026,7 +3142,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3075,6 +3191,12 @@
         <v>36</v>
       </c>
       <c r="P21" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>36</v>
+      </c>
+      <c r="R21" t="s">
         <v>36</v>
       </c>
       <c r="AU21" s="2"/>
@@ -3153,7 +3275,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3202,6 +3324,12 @@
         <v>36</v>
       </c>
       <c r="P22" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>36</v>
+      </c>
+      <c r="R22" t="s">
         <v>36</v>
       </c>
       <c r="AU22" s="2"/>
@@ -3280,7 +3408,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3329,6 +3457,12 @@
         <v>36</v>
       </c>
       <c r="P23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>36</v>
+      </c>
+      <c r="R23" t="s">
         <v>36</v>
       </c>
       <c r="AU23" s="2"/>
@@ -3407,7 +3541,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3456,6 +3590,12 @@
         <v>36</v>
       </c>
       <c r="P24" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>36</v>
+      </c>
+      <c r="R24" t="s">
         <v>36</v>
       </c>
       <c r="AU24" s="2"/>
@@ -3534,7 +3674,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3583,6 +3723,12 @@
         <v>36</v>
       </c>
       <c r="P25" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>36</v>
+      </c>
+      <c r="R25" t="s">
         <v>36</v>
       </c>
       <c r="AU25" s="2"/>
@@ -3661,7 +3807,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3710,6 +3856,12 @@
         <v>36</v>
       </c>
       <c r="P26" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>36</v>
+      </c>
+      <c r="R26" t="s">
         <v>36</v>
       </c>
       <c r="AU26" s="2"/>
@@ -3788,7 +3940,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -3837,6 +3989,12 @@
         <v>36</v>
       </c>
       <c r="P27" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>36</v>
+      </c>
+      <c r="R27" t="s">
         <v>36</v>
       </c>
       <c r="AU27" s="2"/>
@@ -3915,7 +4073,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -3964,6 +4122,12 @@
         <v>36</v>
       </c>
       <c r="P28" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>36</v>
+      </c>
+      <c r="R28" t="s">
         <v>36</v>
       </c>
       <c r="AU28" s="2"/>
@@ -4042,7 +4206,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4091,6 +4255,12 @@
         <v>36</v>
       </c>
       <c r="P29" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>36</v>
+      </c>
+      <c r="R29" t="s">
         <v>36</v>
       </c>
       <c r="AU29" s="2"/>
@@ -4169,7 +4339,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4218,6 +4388,12 @@
         <v>36</v>
       </c>
       <c r="P30" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>36</v>
+      </c>
+      <c r="R30" t="s">
         <v>36</v>
       </c>
       <c r="AU30" s="2"/>
@@ -4296,7 +4472,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4346,6 +4522,12 @@
       </c>
       <c r="P31" t="s">
         <v>37</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>36</v>
+      </c>
+      <c r="R31" t="s">
+        <v>36</v>
       </c>
       <c r="AU31" s="2"/>
       <c r="AV31" s="2"/>
@@ -4423,7 +4605,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4472,6 +4654,12 @@
         <v>36</v>
       </c>
       <c r="P32" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>36</v>
+      </c>
+      <c r="R32" t="s">
         <v>36</v>
       </c>
       <c r="AU32" s="2"/>
@@ -4550,7 +4738,7 @@
       <c r="DR32" s="5"/>
       <c r="DS32" s="5"/>
     </row>
-    <row r="33" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4599,6 +4787,12 @@
         <v>36</v>
       </c>
       <c r="P33" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>36</v>
+      </c>
+      <c r="R33" t="s">
         <v>36</v>
       </c>
       <c r="AU33" s="2"/>
@@ -4682,7 +4876,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BE3:DG3 L3:AZ10 BB3:BB22 D3:K33 BE4:BJ10 BK4:DG33 L11:BA22 BC11:BJ22 L23:BJ33">
+  <conditionalFormatting sqref="BE3:DG3 L3:AZ3 BB3:BB22 D3:K33 BE4:BJ10 BK4:DG33 BC11:BJ22 R23:BJ33 R11:BA22 R4:AZ10 L4:Q33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4695,15 +4889,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4711,157 +4905,157 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>33</v>
       </c>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68A6062-687D-4F3F-A91A-CF50F214EC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4666E274-938A-4339-8D04-94CC4D8C9800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="39">
   <si>
     <t>Aluno</t>
   </si>
@@ -516,19 +516,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS33"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="50" width="7.7109375" customWidth="1"/>
-    <col min="51" max="51" width="7.7109375" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="50" width="7.6640625" customWidth="1"/>
+    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
+    <col min="52" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
@@ -574,7 +574,9 @@
       <c r="R1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S1" s="1"/>
+      <c r="S1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -648,7 +650,7 @@
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -703,7 +705,9 @@
       <c r="R2" s="1">
         <v>46099</v>
       </c>
-      <c r="S2" s="1"/>
+      <c r="S2" s="1">
+        <v>46101</v>
+      </c>
       <c r="AU2" s="2"/>
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
@@ -748,7 +752,7 @@
       <c r="CL2" s="5"/>
       <c r="CM2" s="5"/>
     </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -881,7 +885,7 @@
       <c r="DR3" s="5"/>
       <c r="DS3" s="5"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -1014,7 +1018,7 @@
       <c r="DR4" s="5"/>
       <c r="DS4" s="5"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1147,7 +1151,7 @@
       <c r="DR5" s="5"/>
       <c r="DS5" s="5"/>
     </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1280,7 +1284,7 @@
       <c r="DR6" s="5"/>
       <c r="DS6" s="5"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1413,7 +1417,7 @@
       <c r="DR7" s="5"/>
       <c r="DS7" s="5"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1546,7 +1550,7 @@
       <c r="DR8" s="5"/>
       <c r="DS8" s="5"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1679,7 +1683,7 @@
       <c r="DR9" s="5"/>
       <c r="DS9" s="5"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1812,7 +1816,7 @@
       <c r="DR10" s="5"/>
       <c r="DS10" s="5"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1945,7 +1949,7 @@
       <c r="DR11" s="5"/>
       <c r="DS11" s="5"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2078,7 +2082,7 @@
       <c r="DR12" s="5"/>
       <c r="DS12" s="5"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2211,7 +2215,7 @@
       <c r="DR13" s="5"/>
       <c r="DS13" s="5"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2344,7 +2348,7 @@
       <c r="DR14" s="5"/>
       <c r="DS14" s="5"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2477,7 +2481,7 @@
       <c r="DR15" s="5"/>
       <c r="DS15" s="5"/>
     </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2610,7 +2614,7 @@
       <c r="DR16" s="5"/>
       <c r="DS16" s="5"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2743,7 +2747,7 @@
       <c r="DR17" s="5"/>
       <c r="DS17" s="5"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2876,7 +2880,7 @@
       <c r="DR18" s="5"/>
       <c r="DS18" s="5"/>
     </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -3009,7 +3013,7 @@
       <c r="DR19" s="5"/>
       <c r="DS19" s="5"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3142,7 +3146,7 @@
       <c r="DR20" s="5"/>
       <c r="DS20" s="5"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3275,7 +3279,7 @@
       <c r="DR21" s="5"/>
       <c r="DS21" s="5"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3408,7 +3412,7 @@
       <c r="DR22" s="5"/>
       <c r="DS22" s="5"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3541,7 +3545,7 @@
       <c r="DR23" s="5"/>
       <c r="DS23" s="5"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3674,7 +3678,7 @@
       <c r="DR24" s="5"/>
       <c r="DS24" s="5"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3807,7 +3811,7 @@
       <c r="DR25" s="5"/>
       <c r="DS25" s="5"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3940,7 +3944,7 @@
       <c r="DR26" s="5"/>
       <c r="DS26" s="5"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -4073,7 +4077,7 @@
       <c r="DR27" s="5"/>
       <c r="DS27" s="5"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4206,7 +4210,7 @@
       <c r="DR28" s="5"/>
       <c r="DS28" s="5"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4339,7 +4343,7 @@
       <c r="DR29" s="5"/>
       <c r="DS29" s="5"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4472,7 +4476,7 @@
       <c r="DR30" s="5"/>
       <c r="DS30" s="5"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4605,7 +4609,7 @@
       <c r="DR31" s="5"/>
       <c r="DS31" s="5"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4738,7 +4742,7 @@
       <c r="DR32" s="5"/>
       <c r="DS32" s="5"/>
     </row>
-    <row r="33" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4876,7 +4880,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BE3:DG3 L3:AZ3 BB3:BB22 D3:K33 BE4:BJ10 BK4:DG33 BC11:BJ22 R23:BJ33 R11:BA22 R4:AZ10 L4:Q33">
+  <conditionalFormatting sqref="L3:AZ3 BE3:DG3 BB3:BB22 D3:K33 R4:AZ10 BE4:BJ10 L4:Q33 BK4:DG33 R11:BA22 BC11:BJ22 R23:BJ33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4889,15 +4893,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4905,157 +4909,157 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>33</v>
       </c>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4666E274-938A-4339-8D04-94CC4D8C9800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4307C40D-2089-4346-95F3-4598631A2AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="39">
   <si>
     <t>Aluno</t>
   </si>
@@ -515,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DS33"/>
+  <dimension ref="A1:DQ33"/>
   <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
@@ -523,12 +523,14 @@
     <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="50" width="7.6640625" customWidth="1"/>
-    <col min="51" max="51" width="7.6640625" style="5" customWidth="1"/>
-    <col min="52" max="106" width="7.6640625" customWidth="1"/>
+    <col min="16" max="19" width="7.6640625" customWidth="1"/>
+    <col min="20" max="20" width="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="48" width="7.6640625" customWidth="1"/>
+    <col min="49" max="49" width="7.6640625" style="5" customWidth="1"/>
+    <col min="50" max="104" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:121" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
@@ -577,7 +579,9 @@
       <c r="S1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="T1" s="1"/>
+      <c r="T1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -602,12 +606,12 @@
       <c r="AP1" s="1"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
-      <c r="AS1" s="1"/>
-      <c r="AT1" s="1"/>
+      <c r="AS1" s="3"/>
+      <c r="AT1" s="3"/>
       <c r="AU1" s="3"/>
-      <c r="AV1" s="3"/>
-      <c r="AW1" s="3"/>
-      <c r="AX1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="4"/>
+      <c r="AX1" s="4"/>
       <c r="AY1" s="4"/>
       <c r="AZ1" s="4"/>
       <c r="BA1" s="4"/>
@@ -641,16 +645,14 @@
       <c r="CC1" s="4"/>
       <c r="CD1" s="4"/>
       <c r="CE1" s="4"/>
-      <c r="CF1" s="4"/>
+      <c r="CF1" s="1"/>
       <c r="CG1" s="4"/>
-      <c r="CH1" s="1"/>
+      <c r="CH1" s="4"/>
       <c r="CI1" s="4"/>
       <c r="CJ1" s="4"/>
       <c r="CK1" s="4"/>
-      <c r="CL1" s="4"/>
-      <c r="CM1" s="4"/>
-    </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -708,9 +710,25 @@
       <c r="S2" s="1">
         <v>46101</v>
       </c>
+      <c r="T2" s="1">
+        <v>46106</v>
+      </c>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AS2" s="2"/>
+      <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
-      <c r="AW2" s="2"/>
+      <c r="AX2" s="5"/>
+      <c r="AY2" s="5"/>
       <c r="AZ2" s="5"/>
       <c r="BA2" s="5"/>
       <c r="BB2" s="5"/>
@@ -749,10 +767,8 @@
       <c r="CI2" s="5"/>
       <c r="CJ2" s="5"/>
       <c r="CK2" s="5"/>
-      <c r="CL2" s="5"/>
-      <c r="CM2" s="5"/>
-    </row>
-    <row r="3" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -809,9 +825,17 @@
       <c r="R3" t="s">
         <v>36</v>
       </c>
+      <c r="S3" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS3" s="2"/>
+      <c r="AT3" s="2"/>
       <c r="AU3" s="2"/>
-      <c r="AV3" s="2"/>
-      <c r="AW3" s="2"/>
+      <c r="AX3" s="5"/>
+      <c r="AY3" s="5"/>
       <c r="AZ3" s="5"/>
       <c r="BA3" s="5"/>
       <c r="BB3" s="5"/>
@@ -882,10 +906,8 @@
       <c r="DO3" s="5"/>
       <c r="DP3" s="5"/>
       <c r="DQ3" s="5"/>
-      <c r="DR3" s="5"/>
-      <c r="DS3" s="5"/>
-    </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -942,9 +964,17 @@
       <c r="R4" t="s">
         <v>36</v>
       </c>
+      <c r="S4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS4" s="2"/>
+      <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
-      <c r="AV4" s="2"/>
-      <c r="AW4" s="2"/>
+      <c r="AX4" s="5"/>
+      <c r="AY4" s="5"/>
       <c r="AZ4" s="5"/>
       <c r="BA4" s="5"/>
       <c r="BB4" s="5"/>
@@ -1015,10 +1045,8 @@
       <c r="DO4" s="5"/>
       <c r="DP4" s="5"/>
       <c r="DQ4" s="5"/>
-      <c r="DR4" s="5"/>
-      <c r="DS4" s="5"/>
-    </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1075,9 +1103,17 @@
       <c r="R5" t="s">
         <v>36</v>
       </c>
+      <c r="S5" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS5" s="2"/>
+      <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
+      <c r="AX5" s="5"/>
+      <c r="AY5" s="5"/>
       <c r="AZ5" s="5"/>
       <c r="BA5" s="5"/>
       <c r="BB5" s="5"/>
@@ -1148,10 +1184,8 @@
       <c r="DO5" s="5"/>
       <c r="DP5" s="5"/>
       <c r="DQ5" s="5"/>
-      <c r="DR5" s="5"/>
-      <c r="DS5" s="5"/>
-    </row>
-    <row r="6" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1208,9 +1242,17 @@
       <c r="R6" t="s">
         <v>36</v>
       </c>
+      <c r="S6" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS6" s="2"/>
+      <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
+      <c r="AX6" s="5"/>
+      <c r="AY6" s="5"/>
       <c r="AZ6" s="5"/>
       <c r="BA6" s="5"/>
       <c r="BB6" s="5"/>
@@ -1244,9 +1286,9 @@
       <c r="CD6" s="5"/>
       <c r="CE6" s="5"/>
       <c r="CF6" s="5"/>
-      <c r="CG6" s="5"/>
+      <c r="CG6" s="7"/>
       <c r="CH6" s="5"/>
-      <c r="CI6" s="7"/>
+      <c r="CI6" s="5"/>
       <c r="CJ6" s="5"/>
       <c r="CK6" s="5"/>
       <c r="CL6" s="5"/>
@@ -1281,10 +1323,8 @@
       <c r="DO6" s="5"/>
       <c r="DP6" s="5"/>
       <c r="DQ6" s="5"/>
-      <c r="DR6" s="5"/>
-      <c r="DS6" s="5"/>
-    </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1341,9 +1381,17 @@
       <c r="R7" t="s">
         <v>36</v>
       </c>
+      <c r="S7" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS7" s="2"/>
+      <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
+      <c r="AX7" s="5"/>
+      <c r="AY7" s="5"/>
       <c r="AZ7" s="5"/>
       <c r="BA7" s="5"/>
       <c r="BB7" s="5"/>
@@ -1377,9 +1425,9 @@
       <c r="CD7" s="5"/>
       <c r="CE7" s="5"/>
       <c r="CF7" s="5"/>
-      <c r="CG7" s="5"/>
+      <c r="CG7" s="6"/>
       <c r="CH7" s="5"/>
-      <c r="CI7" s="6"/>
+      <c r="CI7" s="5"/>
       <c r="CJ7" s="5"/>
       <c r="CK7" s="5"/>
       <c r="CL7" s="5"/>
@@ -1414,10 +1462,8 @@
       <c r="DO7" s="5"/>
       <c r="DP7" s="5"/>
       <c r="DQ7" s="5"/>
-      <c r="DR7" s="5"/>
-      <c r="DS7" s="5"/>
-    </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1474,9 +1520,17 @@
       <c r="R8" t="s">
         <v>36</v>
       </c>
+      <c r="S8" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS8" s="2"/>
+      <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
-      <c r="AV8" s="2"/>
-      <c r="AW8" s="2"/>
+      <c r="AX8" s="5"/>
+      <c r="AY8" s="5"/>
       <c r="AZ8" s="5"/>
       <c r="BA8" s="5"/>
       <c r="BB8" s="5"/>
@@ -1547,10 +1601,8 @@
       <c r="DO8" s="5"/>
       <c r="DP8" s="5"/>
       <c r="DQ8" s="5"/>
-      <c r="DR8" s="5"/>
-      <c r="DS8" s="5"/>
-    </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1607,9 +1659,17 @@
       <c r="R9" t="s">
         <v>36</v>
       </c>
+      <c r="S9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS9" s="2"/>
+      <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
-      <c r="AV9" s="2"/>
-      <c r="AW9" s="2"/>
+      <c r="AX9" s="5"/>
+      <c r="AY9" s="5"/>
       <c r="AZ9" s="5"/>
       <c r="BA9" s="5"/>
       <c r="BB9" s="5"/>
@@ -1680,10 +1740,8 @@
       <c r="DO9" s="5"/>
       <c r="DP9" s="5"/>
       <c r="DQ9" s="5"/>
-      <c r="DR9" s="5"/>
-      <c r="DS9" s="5"/>
-    </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1740,9 +1798,17 @@
       <c r="R10" t="s">
         <v>36</v>
       </c>
+      <c r="S10" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS10" s="2"/>
+      <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
-      <c r="AV10" s="2"/>
-      <c r="AW10" s="2"/>
+      <c r="AX10" s="5"/>
+      <c r="AY10" s="5"/>
       <c r="AZ10" s="5"/>
       <c r="BA10" s="5"/>
       <c r="BB10" s="5"/>
@@ -1813,10 +1879,8 @@
       <c r="DO10" s="5"/>
       <c r="DP10" s="5"/>
       <c r="DQ10" s="5"/>
-      <c r="DR10" s="5"/>
-      <c r="DS10" s="5"/>
-    </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1873,9 +1937,17 @@
       <c r="R11" t="s">
         <v>36</v>
       </c>
+      <c r="S11" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS11" s="2"/>
+      <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
-      <c r="AV11" s="2"/>
-      <c r="AW11" s="2"/>
+      <c r="AX11" s="5"/>
+      <c r="AY11" s="5"/>
       <c r="AZ11" s="5"/>
       <c r="BA11" s="5"/>
       <c r="BB11" s="5"/>
@@ -1946,10 +2018,8 @@
       <c r="DO11" s="5"/>
       <c r="DP11" s="5"/>
       <c r="DQ11" s="5"/>
-      <c r="DR11" s="5"/>
-      <c r="DS11" s="5"/>
-    </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2006,9 +2076,17 @@
       <c r="R12" t="s">
         <v>36</v>
       </c>
+      <c r="S12" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS12" s="2"/>
+      <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
-      <c r="AV12" s="2"/>
-      <c r="AW12" s="2"/>
+      <c r="AX12" s="5"/>
+      <c r="AY12" s="5"/>
       <c r="AZ12" s="5"/>
       <c r="BA12" s="5"/>
       <c r="BB12" s="5"/>
@@ -2079,10 +2157,8 @@
       <c r="DO12" s="5"/>
       <c r="DP12" s="5"/>
       <c r="DQ12" s="5"/>
-      <c r="DR12" s="5"/>
-      <c r="DS12" s="5"/>
-    </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2139,9 +2215,17 @@
       <c r="R13" t="s">
         <v>36</v>
       </c>
+      <c r="S13" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS13" s="2"/>
+      <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
-      <c r="AV13" s="2"/>
-      <c r="AW13" s="2"/>
+      <c r="AX13" s="5"/>
+      <c r="AY13" s="5"/>
       <c r="AZ13" s="5"/>
       <c r="BA13" s="5"/>
       <c r="BB13" s="5"/>
@@ -2212,10 +2296,8 @@
       <c r="DO13" s="5"/>
       <c r="DP13" s="5"/>
       <c r="DQ13" s="5"/>
-      <c r="DR13" s="5"/>
-      <c r="DS13" s="5"/>
-    </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2272,9 +2354,17 @@
       <c r="R14" t="s">
         <v>36</v>
       </c>
+      <c r="S14" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS14" s="2"/>
+      <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
-      <c r="AV14" s="2"/>
-      <c r="AW14" s="2"/>
+      <c r="AX14" s="5"/>
+      <c r="AY14" s="5"/>
       <c r="AZ14" s="5"/>
       <c r="BA14" s="5"/>
       <c r="BB14" s="5"/>
@@ -2345,10 +2435,8 @@
       <c r="DO14" s="5"/>
       <c r="DP14" s="5"/>
       <c r="DQ14" s="5"/>
-      <c r="DR14" s="5"/>
-      <c r="DS14" s="5"/>
-    </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2405,9 +2493,17 @@
       <c r="R15" t="s">
         <v>36</v>
       </c>
+      <c r="S15" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" t="s">
+        <v>37</v>
+      </c>
+      <c r="AS15" s="2"/>
+      <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
-      <c r="AV15" s="2"/>
-      <c r="AW15" s="2"/>
+      <c r="AX15" s="5"/>
+      <c r="AY15" s="5"/>
       <c r="AZ15" s="5"/>
       <c r="BA15" s="5"/>
       <c r="BB15" s="5"/>
@@ -2478,10 +2574,8 @@
       <c r="DO15" s="5"/>
       <c r="DP15" s="5"/>
       <c r="DQ15" s="5"/>
-      <c r="DR15" s="5"/>
-      <c r="DS15" s="5"/>
-    </row>
-    <row r="16" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2538,9 +2632,17 @@
       <c r="R16" t="s">
         <v>36</v>
       </c>
+      <c r="S16" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS16" s="2"/>
+      <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
-      <c r="AV16" s="2"/>
-      <c r="AW16" s="2"/>
+      <c r="AX16" s="5"/>
+      <c r="AY16" s="5"/>
       <c r="AZ16" s="5"/>
       <c r="BA16" s="5"/>
       <c r="BB16" s="5"/>
@@ -2611,10 +2713,8 @@
       <c r="DO16" s="5"/>
       <c r="DP16" s="5"/>
       <c r="DQ16" s="5"/>
-      <c r="DR16" s="5"/>
-      <c r="DS16" s="5"/>
-    </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2671,9 +2771,17 @@
       <c r="R17" t="s">
         <v>36</v>
       </c>
+      <c r="S17" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" t="s">
+        <v>37</v>
+      </c>
+      <c r="AS17" s="2"/>
+      <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
-      <c r="AV17" s="2"/>
-      <c r="AW17" s="2"/>
+      <c r="AX17" s="5"/>
+      <c r="AY17" s="5"/>
       <c r="AZ17" s="5"/>
       <c r="BA17" s="5"/>
       <c r="BB17" s="5"/>
@@ -2744,10 +2852,8 @@
       <c r="DO17" s="5"/>
       <c r="DP17" s="5"/>
       <c r="DQ17" s="5"/>
-      <c r="DR17" s="5"/>
-      <c r="DS17" s="5"/>
-    </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2804,9 +2910,17 @@
       <c r="R18" t="s">
         <v>36</v>
       </c>
+      <c r="S18" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS18" s="2"/>
+      <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
-      <c r="AV18" s="2"/>
-      <c r="AW18" s="2"/>
+      <c r="AX18" s="5"/>
+      <c r="AY18" s="5"/>
       <c r="AZ18" s="5"/>
       <c r="BA18" s="5"/>
       <c r="BB18" s="5"/>
@@ -2877,10 +2991,8 @@
       <c r="DO18" s="5"/>
       <c r="DP18" s="5"/>
       <c r="DQ18" s="5"/>
-      <c r="DR18" s="5"/>
-      <c r="DS18" s="5"/>
-    </row>
-    <row r="19" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -2937,9 +3049,17 @@
       <c r="R19" t="s">
         <v>36</v>
       </c>
+      <c r="S19" t="s">
+        <v>36</v>
+      </c>
+      <c r="T19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS19" s="2"/>
+      <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
-      <c r="AV19" s="2"/>
-      <c r="AW19" s="2"/>
+      <c r="AX19" s="5"/>
+      <c r="AY19" s="5"/>
       <c r="AZ19" s="5"/>
       <c r="BA19" s="5"/>
       <c r="BB19" s="5"/>
@@ -3010,10 +3130,8 @@
       <c r="DO19" s="5"/>
       <c r="DP19" s="5"/>
       <c r="DQ19" s="5"/>
-      <c r="DR19" s="5"/>
-      <c r="DS19" s="5"/>
-    </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3070,9 +3188,17 @@
       <c r="R20" t="s">
         <v>36</v>
       </c>
+      <c r="S20" t="s">
+        <v>36</v>
+      </c>
+      <c r="T20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS20" s="2"/>
+      <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
-      <c r="AV20" s="2"/>
-      <c r="AW20" s="2"/>
+      <c r="AX20" s="5"/>
+      <c r="AY20" s="5"/>
       <c r="AZ20" s="5"/>
       <c r="BA20" s="5"/>
       <c r="BB20" s="5"/>
@@ -3143,10 +3269,8 @@
       <c r="DO20" s="5"/>
       <c r="DP20" s="5"/>
       <c r="DQ20" s="5"/>
-      <c r="DR20" s="5"/>
-      <c r="DS20" s="5"/>
-    </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3203,9 +3327,17 @@
       <c r="R21" t="s">
         <v>36</v>
       </c>
+      <c r="S21" t="s">
+        <v>36</v>
+      </c>
+      <c r="T21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS21" s="2"/>
+      <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
-      <c r="AV21" s="2"/>
-      <c r="AW21" s="2"/>
+      <c r="AX21" s="5"/>
+      <c r="AY21" s="5"/>
       <c r="AZ21" s="5"/>
       <c r="BA21" s="5"/>
       <c r="BB21" s="5"/>
@@ -3276,10 +3408,8 @@
       <c r="DO21" s="5"/>
       <c r="DP21" s="5"/>
       <c r="DQ21" s="5"/>
-      <c r="DR21" s="5"/>
-      <c r="DS21" s="5"/>
-    </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3336,9 +3466,17 @@
       <c r="R22" t="s">
         <v>36</v>
       </c>
+      <c r="S22" t="s">
+        <v>36</v>
+      </c>
+      <c r="T22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS22" s="2"/>
+      <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
-      <c r="AV22" s="2"/>
-      <c r="AW22" s="2"/>
+      <c r="AX22" s="5"/>
+      <c r="AY22" s="5"/>
       <c r="AZ22" s="5"/>
       <c r="BA22" s="5"/>
       <c r="BB22" s="5"/>
@@ -3409,10 +3547,8 @@
       <c r="DO22" s="5"/>
       <c r="DP22" s="5"/>
       <c r="DQ22" s="5"/>
-      <c r="DR22" s="5"/>
-      <c r="DS22" s="5"/>
-    </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3469,9 +3605,17 @@
       <c r="R23" t="s">
         <v>36</v>
       </c>
+      <c r="S23" t="s">
+        <v>36</v>
+      </c>
+      <c r="T23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS23" s="2"/>
+      <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
-      <c r="AV23" s="2"/>
-      <c r="AW23" s="2"/>
+      <c r="AX23" s="5"/>
+      <c r="AY23" s="5"/>
       <c r="AZ23" s="5"/>
       <c r="BA23" s="5"/>
       <c r="BB23" s="5"/>
@@ -3542,10 +3686,8 @@
       <c r="DO23" s="5"/>
       <c r="DP23" s="5"/>
       <c r="DQ23" s="5"/>
-      <c r="DR23" s="5"/>
-      <c r="DS23" s="5"/>
-    </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3602,9 +3744,17 @@
       <c r="R24" t="s">
         <v>36</v>
       </c>
+      <c r="S24" t="s">
+        <v>36</v>
+      </c>
+      <c r="T24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS24" s="2"/>
+      <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
-      <c r="AV24" s="2"/>
-      <c r="AW24" s="2"/>
+      <c r="AX24" s="5"/>
+      <c r="AY24" s="5"/>
       <c r="AZ24" s="5"/>
       <c r="BA24" s="5"/>
       <c r="BB24" s="5"/>
@@ -3675,10 +3825,8 @@
       <c r="DO24" s="5"/>
       <c r="DP24" s="5"/>
       <c r="DQ24" s="5"/>
-      <c r="DR24" s="5"/>
-      <c r="DS24" s="5"/>
-    </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3735,9 +3883,17 @@
       <c r="R25" t="s">
         <v>36</v>
       </c>
+      <c r="S25" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS25" s="2"/>
+      <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
-      <c r="AV25" s="2"/>
-      <c r="AW25" s="2"/>
+      <c r="AX25" s="5"/>
+      <c r="AY25" s="5"/>
       <c r="AZ25" s="5"/>
       <c r="BA25" s="5"/>
       <c r="BB25" s="5"/>
@@ -3808,10 +3964,8 @@
       <c r="DO25" s="5"/>
       <c r="DP25" s="5"/>
       <c r="DQ25" s="5"/>
-      <c r="DR25" s="5"/>
-      <c r="DS25" s="5"/>
-    </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -3868,9 +4022,17 @@
       <c r="R26" t="s">
         <v>36</v>
       </c>
+      <c r="S26" t="s">
+        <v>36</v>
+      </c>
+      <c r="T26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS26" s="2"/>
+      <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
-      <c r="AV26" s="2"/>
-      <c r="AW26" s="2"/>
+      <c r="AX26" s="5"/>
+      <c r="AY26" s="5"/>
       <c r="AZ26" s="5"/>
       <c r="BA26" s="5"/>
       <c r="BB26" s="5"/>
@@ -3941,10 +4103,8 @@
       <c r="DO26" s="5"/>
       <c r="DP26" s="5"/>
       <c r="DQ26" s="5"/>
-      <c r="DR26" s="5"/>
-      <c r="DS26" s="5"/>
-    </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -4001,9 +4161,17 @@
       <c r="R27" t="s">
         <v>36</v>
       </c>
+      <c r="S27" t="s">
+        <v>36</v>
+      </c>
+      <c r="T27" t="s">
+        <v>37</v>
+      </c>
+      <c r="AS27" s="2"/>
+      <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
-      <c r="AV27" s="2"/>
-      <c r="AW27" s="2"/>
+      <c r="AX27" s="5"/>
+      <c r="AY27" s="5"/>
       <c r="AZ27" s="5"/>
       <c r="BA27" s="5"/>
       <c r="BB27" s="5"/>
@@ -4074,10 +4242,8 @@
       <c r="DO27" s="5"/>
       <c r="DP27" s="5"/>
       <c r="DQ27" s="5"/>
-      <c r="DR27" s="5"/>
-      <c r="DS27" s="5"/>
-    </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4134,9 +4300,17 @@
       <c r="R28" t="s">
         <v>36</v>
       </c>
+      <c r="S28" t="s">
+        <v>36</v>
+      </c>
+      <c r="T28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS28" s="2"/>
+      <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
-      <c r="AV28" s="2"/>
-      <c r="AW28" s="2"/>
+      <c r="AX28" s="5"/>
+      <c r="AY28" s="5"/>
       <c r="AZ28" s="5"/>
       <c r="BA28" s="5"/>
       <c r="BB28" s="5"/>
@@ -4207,10 +4381,8 @@
       <c r="DO28" s="5"/>
       <c r="DP28" s="5"/>
       <c r="DQ28" s="5"/>
-      <c r="DR28" s="5"/>
-      <c r="DS28" s="5"/>
-    </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4267,9 +4439,17 @@
       <c r="R29" t="s">
         <v>36</v>
       </c>
+      <c r="S29" t="s">
+        <v>36</v>
+      </c>
+      <c r="T29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS29" s="2"/>
+      <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
-      <c r="AV29" s="2"/>
-      <c r="AW29" s="2"/>
+      <c r="AX29" s="5"/>
+      <c r="AY29" s="5"/>
       <c r="AZ29" s="5"/>
       <c r="BA29" s="5"/>
       <c r="BB29" s="5"/>
@@ -4340,10 +4520,8 @@
       <c r="DO29" s="5"/>
       <c r="DP29" s="5"/>
       <c r="DQ29" s="5"/>
-      <c r="DR29" s="5"/>
-      <c r="DS29" s="5"/>
-    </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4400,9 +4578,17 @@
       <c r="R30" t="s">
         <v>36</v>
       </c>
+      <c r="S30" t="s">
+        <v>36</v>
+      </c>
+      <c r="T30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS30" s="2"/>
+      <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
-      <c r="AV30" s="2"/>
-      <c r="AW30" s="2"/>
+      <c r="AX30" s="5"/>
+      <c r="AY30" s="5"/>
       <c r="AZ30" s="5"/>
       <c r="BA30" s="5"/>
       <c r="BB30" s="5"/>
@@ -4473,10 +4659,8 @@
       <c r="DO30" s="5"/>
       <c r="DP30" s="5"/>
       <c r="DQ30" s="5"/>
-      <c r="DR30" s="5"/>
-      <c r="DS30" s="5"/>
-    </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4533,9 +4717,17 @@
       <c r="R31" t="s">
         <v>36</v>
       </c>
+      <c r="S31" t="s">
+        <v>36</v>
+      </c>
+      <c r="T31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS31" s="2"/>
+      <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
-      <c r="AV31" s="2"/>
-      <c r="AW31" s="2"/>
+      <c r="AX31" s="5"/>
+      <c r="AY31" s="5"/>
       <c r="AZ31" s="5"/>
       <c r="BA31" s="5"/>
       <c r="BB31" s="5"/>
@@ -4606,10 +4798,8 @@
       <c r="DO31" s="5"/>
       <c r="DP31" s="5"/>
       <c r="DQ31" s="5"/>
-      <c r="DR31" s="5"/>
-      <c r="DS31" s="5"/>
-    </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4666,9 +4856,17 @@
       <c r="R32" t="s">
         <v>36</v>
       </c>
+      <c r="S32" t="s">
+        <v>36</v>
+      </c>
+      <c r="T32" t="s">
+        <v>37</v>
+      </c>
+      <c r="AS32" s="2"/>
+      <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
-      <c r="AV32" s="2"/>
-      <c r="AW32" s="2"/>
+      <c r="AX32" s="5"/>
+      <c r="AY32" s="5"/>
       <c r="AZ32" s="5"/>
       <c r="BA32" s="5"/>
       <c r="BB32" s="5"/>
@@ -4739,10 +4937,8 @@
       <c r="DO32" s="5"/>
       <c r="DP32" s="5"/>
       <c r="DQ32" s="5"/>
-      <c r="DR32" s="5"/>
-      <c r="DS32" s="5"/>
-    </row>
-    <row r="33" spans="1:123" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4799,9 +4995,17 @@
       <c r="R33" t="s">
         <v>36</v>
       </c>
+      <c r="S33" t="s">
+        <v>36</v>
+      </c>
+      <c r="T33" t="s">
+        <v>37</v>
+      </c>
+      <c r="AS33" s="2"/>
+      <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>
-      <c r="AV33" s="2"/>
-      <c r="AW33" s="2"/>
+      <c r="AX33" s="5"/>
+      <c r="AY33" s="5"/>
       <c r="AZ33" s="5"/>
       <c r="BA33" s="5"/>
       <c r="BB33" s="5"/>
@@ -4872,15 +5076,13 @@
       <c r="DO33" s="5"/>
       <c r="DP33" s="5"/>
       <c r="DQ33" s="5"/>
-      <c r="DR33" s="5"/>
-      <c r="DS33" s="5"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="L3:AZ3 BE3:DG3 BB3:BB22 D3:K33 R4:AZ10 BE4:BJ10 L4:Q33 BK4:DG33 R11:BA22 BC11:BJ22 R23:BJ33">
+  <conditionalFormatting sqref="BC3:DE3 AZ3:AZ22 D3:K33 BC4:BH10 L4:Q33 BI4:DE33 BA11:BH22 L3:AX3 R4:AX10 R11:AY22 R23:BH33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4307C40D-2089-4346-95F3-4598631A2AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7554B5A6-0B55-4400-873C-2354EE8F2958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14160" yWindow="4335" windowWidth="14460" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="39">
   <si>
     <t>Aluno</t>
   </si>
@@ -516,21 +516,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DQ33"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="7.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="7.7109375" customWidth="1"/>
     <col min="20" max="20" width="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="48" width="7.6640625" customWidth="1"/>
-    <col min="49" max="49" width="7.6640625" style="5" customWidth="1"/>
-    <col min="50" max="104" width="7.6640625" customWidth="1"/>
+    <col min="21" max="48" width="7.7109375" customWidth="1"/>
+    <col min="49" max="49" width="7.7109375" style="5" customWidth="1"/>
+    <col min="50" max="104" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:121" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
@@ -582,7 +582,9 @@
       <c r="T1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U1" s="1"/>
+      <c r="U1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
@@ -652,7 +654,7 @@
       <c r="CJ1" s="4"/>
       <c r="CK1" s="4"/>
     </row>
-    <row r="2" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -713,7 +715,9 @@
       <c r="T2" s="1">
         <v>46106</v>
       </c>
-      <c r="U2" s="1"/>
+      <c r="U2" s="1">
+        <v>46108</v>
+      </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -768,7 +772,7 @@
       <c r="CJ2" s="5"/>
       <c r="CK2" s="5"/>
     </row>
-    <row r="3" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>0</v>
@@ -829,6 +833,9 @@
         <v>36</v>
       </c>
       <c r="T3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -907,7 +914,7 @@
       <c r="DP3" s="5"/>
       <c r="DQ3" s="5"/>
     </row>
-    <row r="4" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>0</v>
@@ -969,6 +976,9 @@
       </c>
       <c r="T4" t="s">
         <v>36</v>
+      </c>
+      <c r="U4" t="s">
+        <v>37</v>
       </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
@@ -1046,7 +1056,7 @@
       <c r="DP4" s="5"/>
       <c r="DQ4" s="5"/>
     </row>
-    <row r="5" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>0</v>
@@ -1107,6 +1117,9 @@
         <v>36</v>
       </c>
       <c r="T5" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" t="s">
         <v>36</v>
       </c>
       <c r="AS5" s="2"/>
@@ -1185,7 +1198,7 @@
       <c r="DP5" s="5"/>
       <c r="DQ5" s="5"/>
     </row>
-    <row r="6" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>0</v>
@@ -1246,6 +1259,9 @@
         <v>36</v>
       </c>
       <c r="T6" t="s">
+        <v>36</v>
+      </c>
+      <c r="U6" t="s">
         <v>36</v>
       </c>
       <c r="AS6" s="2"/>
@@ -1324,7 +1340,7 @@
       <c r="DP6" s="5"/>
       <c r="DQ6" s="5"/>
     </row>
-    <row r="7" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>0</v>
@@ -1386,6 +1402,9 @@
       </c>
       <c r="T7" t="s">
         <v>36</v>
+      </c>
+      <c r="U7" t="s">
+        <v>37</v>
       </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
@@ -1463,7 +1482,7 @@
       <c r="DP7" s="5"/>
       <c r="DQ7" s="5"/>
     </row>
-    <row r="8" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>0</v>
@@ -1524,6 +1543,9 @@
         <v>36</v>
       </c>
       <c r="T8" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" t="s">
         <v>36</v>
       </c>
       <c r="AS8" s="2"/>
@@ -1602,7 +1624,7 @@
       <c r="DP8" s="5"/>
       <c r="DQ8" s="5"/>
     </row>
-    <row r="9" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>0</v>
@@ -1663,6 +1685,9 @@
         <v>36</v>
       </c>
       <c r="T9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U9" t="s">
         <v>36</v>
       </c>
       <c r="AS9" s="2"/>
@@ -1741,7 +1766,7 @@
       <c r="DP9" s="5"/>
       <c r="DQ9" s="5"/>
     </row>
-    <row r="10" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>0</v>
@@ -1802,6 +1827,9 @@
         <v>36</v>
       </c>
       <c r="T10" t="s">
+        <v>36</v>
+      </c>
+      <c r="U10" t="s">
         <v>36</v>
       </c>
       <c r="AS10" s="2"/>
@@ -1880,7 +1908,7 @@
       <c r="DP10" s="5"/>
       <c r="DQ10" s="5"/>
     </row>
-    <row r="11" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>0</v>
@@ -1941,6 +1969,9 @@
         <v>36</v>
       </c>
       <c r="T11" t="s">
+        <v>36</v>
+      </c>
+      <c r="U11" t="s">
         <v>36</v>
       </c>
       <c r="AS11" s="2"/>
@@ -2019,7 +2050,7 @@
       <c r="DP11" s="5"/>
       <c r="DQ11" s="5"/>
     </row>
-    <row r="12" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>0</v>
@@ -2080,6 +2111,9 @@
         <v>36</v>
       </c>
       <c r="T12" t="s">
+        <v>36</v>
+      </c>
+      <c r="U12" t="s">
         <v>36</v>
       </c>
       <c r="AS12" s="2"/>
@@ -2158,7 +2192,7 @@
       <c r="DP12" s="5"/>
       <c r="DQ12" s="5"/>
     </row>
-    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>0</v>
@@ -2219,6 +2253,9 @@
         <v>36</v>
       </c>
       <c r="T13" t="s">
+        <v>36</v>
+      </c>
+      <c r="U13" t="s">
         <v>36</v>
       </c>
       <c r="AS13" s="2"/>
@@ -2297,7 +2334,7 @@
       <c r="DP13" s="5"/>
       <c r="DQ13" s="5"/>
     </row>
-    <row r="14" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>0</v>
@@ -2358,6 +2395,9 @@
         <v>36</v>
       </c>
       <c r="T14" t="s">
+        <v>36</v>
+      </c>
+      <c r="U14" t="s">
         <v>36</v>
       </c>
       <c r="AS14" s="2"/>
@@ -2436,7 +2476,7 @@
       <c r="DP14" s="5"/>
       <c r="DQ14" s="5"/>
     </row>
-    <row r="15" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>0</v>
@@ -2498,6 +2538,9 @@
       </c>
       <c r="T15" t="s">
         <v>37</v>
+      </c>
+      <c r="U15" t="s">
+        <v>36</v>
       </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
@@ -2575,7 +2618,7 @@
       <c r="DP15" s="5"/>
       <c r="DQ15" s="5"/>
     </row>
-    <row r="16" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>0</v>
@@ -2636,6 +2679,9 @@
         <v>36</v>
       </c>
       <c r="T16" t="s">
+        <v>36</v>
+      </c>
+      <c r="U16" t="s">
         <v>36</v>
       </c>
       <c r="AS16" s="2"/>
@@ -2714,7 +2760,7 @@
       <c r="DP16" s="5"/>
       <c r="DQ16" s="5"/>
     </row>
-    <row r="17" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>0</v>
@@ -2775,6 +2821,9 @@
         <v>36</v>
       </c>
       <c r="T17" t="s">
+        <v>37</v>
+      </c>
+      <c r="U17" t="s">
         <v>37</v>
       </c>
       <c r="AS17" s="2"/>
@@ -2853,7 +2902,7 @@
       <c r="DP17" s="5"/>
       <c r="DQ17" s="5"/>
     </row>
-    <row r="18" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>0</v>
@@ -2914,6 +2963,9 @@
         <v>36</v>
       </c>
       <c r="T18" t="s">
+        <v>36</v>
+      </c>
+      <c r="U18" t="s">
         <v>36</v>
       </c>
       <c r="AS18" s="2"/>
@@ -2992,7 +3044,7 @@
       <c r="DP18" s="5"/>
       <c r="DQ18" s="5"/>
     </row>
-    <row r="19" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>0</v>
@@ -3053,6 +3105,9 @@
         <v>36</v>
       </c>
       <c r="T19" t="s">
+        <v>36</v>
+      </c>
+      <c r="U19" t="s">
         <v>36</v>
       </c>
       <c r="AS19" s="2"/>
@@ -3131,7 +3186,7 @@
       <c r="DP19" s="5"/>
       <c r="DQ19" s="5"/>
     </row>
-    <row r="20" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>0</v>
@@ -3192,6 +3247,9 @@
         <v>36</v>
       </c>
       <c r="T20" t="s">
+        <v>36</v>
+      </c>
+      <c r="U20" t="s">
         <v>36</v>
       </c>
       <c r="AS20" s="2"/>
@@ -3270,7 +3328,7 @@
       <c r="DP20" s="5"/>
       <c r="DQ20" s="5"/>
     </row>
-    <row r="21" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>0</v>
@@ -3331,6 +3389,9 @@
         <v>36</v>
       </c>
       <c r="T21" t="s">
+        <v>36</v>
+      </c>
+      <c r="U21" t="s">
         <v>36</v>
       </c>
       <c r="AS21" s="2"/>
@@ -3409,7 +3470,7 @@
       <c r="DP21" s="5"/>
       <c r="DQ21" s="5"/>
     </row>
-    <row r="22" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>0</v>
@@ -3470,6 +3531,9 @@
         <v>36</v>
       </c>
       <c r="T22" t="s">
+        <v>36</v>
+      </c>
+      <c r="U22" t="s">
         <v>36</v>
       </c>
       <c r="AS22" s="2"/>
@@ -3548,7 +3612,7 @@
       <c r="DP22" s="5"/>
       <c r="DQ22" s="5"/>
     </row>
-    <row r="23" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>0</v>
@@ -3610,6 +3674,9 @@
       </c>
       <c r="T23" t="s">
         <v>36</v>
+      </c>
+      <c r="U23" t="s">
+        <v>37</v>
       </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
@@ -3687,7 +3754,7 @@
       <c r="DP23" s="5"/>
       <c r="DQ23" s="5"/>
     </row>
-    <row r="24" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>0</v>
@@ -3748,6 +3815,9 @@
         <v>36</v>
       </c>
       <c r="T24" t="s">
+        <v>36</v>
+      </c>
+      <c r="U24" t="s">
         <v>36</v>
       </c>
       <c r="AS24" s="2"/>
@@ -3826,7 +3896,7 @@
       <c r="DP24" s="5"/>
       <c r="DQ24" s="5"/>
     </row>
-    <row r="25" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>0</v>
@@ -3887,6 +3957,9 @@
         <v>36</v>
       </c>
       <c r="T25" t="s">
+        <v>36</v>
+      </c>
+      <c r="U25" t="s">
         <v>36</v>
       </c>
       <c r="AS25" s="2"/>
@@ -3965,7 +4038,7 @@
       <c r="DP25" s="5"/>
       <c r="DQ25" s="5"/>
     </row>
-    <row r="26" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>0</v>
@@ -4026,6 +4099,9 @@
         <v>36</v>
       </c>
       <c r="T26" t="s">
+        <v>36</v>
+      </c>
+      <c r="U26" t="s">
         <v>36</v>
       </c>
       <c r="AS26" s="2"/>
@@ -4104,7 +4180,7 @@
       <c r="DP26" s="5"/>
       <c r="DQ26" s="5"/>
     </row>
-    <row r="27" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>0</v>
@@ -4165,6 +4241,9 @@
         <v>36</v>
       </c>
       <c r="T27" t="s">
+        <v>37</v>
+      </c>
+      <c r="U27" t="s">
         <v>37</v>
       </c>
       <c r="AS27" s="2"/>
@@ -4243,7 +4322,7 @@
       <c r="DP27" s="5"/>
       <c r="DQ27" s="5"/>
     </row>
-    <row r="28" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>0</v>
@@ -4304,6 +4383,9 @@
         <v>36</v>
       </c>
       <c r="T28" t="s">
+        <v>36</v>
+      </c>
+      <c r="U28" t="s">
         <v>36</v>
       </c>
       <c r="AS28" s="2"/>
@@ -4382,7 +4464,7 @@
       <c r="DP28" s="5"/>
       <c r="DQ28" s="5"/>
     </row>
-    <row r="29" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>0</v>
@@ -4443,6 +4525,9 @@
         <v>36</v>
       </c>
       <c r="T29" t="s">
+        <v>36</v>
+      </c>
+      <c r="U29" t="s">
         <v>36</v>
       </c>
       <c r="AS29" s="2"/>
@@ -4521,7 +4606,7 @@
       <c r="DP29" s="5"/>
       <c r="DQ29" s="5"/>
     </row>
-    <row r="30" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>0</v>
@@ -4582,6 +4667,9 @@
         <v>36</v>
       </c>
       <c r="T30" t="s">
+        <v>36</v>
+      </c>
+      <c r="U30" t="s">
         <v>36</v>
       </c>
       <c r="AS30" s="2"/>
@@ -4660,7 +4748,7 @@
       <c r="DP30" s="5"/>
       <c r="DQ30" s="5"/>
     </row>
-    <row r="31" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>0</v>
@@ -4722,6 +4810,9 @@
       </c>
       <c r="T31" t="s">
         <v>36</v>
+      </c>
+      <c r="U31" t="s">
+        <v>37</v>
       </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
@@ -4799,7 +4890,7 @@
       <c r="DP31" s="5"/>
       <c r="DQ31" s="5"/>
     </row>
-    <row r="32" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>0</v>
@@ -4860,6 +4951,9 @@
         <v>36</v>
       </c>
       <c r="T32" t="s">
+        <v>37</v>
+      </c>
+      <c r="U32" t="s">
         <v>37</v>
       </c>
       <c r="AS32" s="2"/>
@@ -4938,7 +5032,7 @@
       <c r="DP32" s="5"/>
       <c r="DQ32" s="5"/>
     </row>
-    <row r="33" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>0</v>
@@ -4999,6 +5093,9 @@
         <v>36</v>
       </c>
       <c r="T33" t="s">
+        <v>37</v>
+      </c>
+      <c r="U33" t="s">
         <v>37</v>
       </c>
       <c r="AS33" s="2"/>
@@ -5082,7 +5179,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BC3:DE3 AZ3:AZ22 D3:K33 BC4:BH10 L4:Q33 BI4:DE33 BA11:BH22 L3:AX3 R4:AX10 R11:AY22 R23:BH33">
+  <conditionalFormatting sqref="BC3:DE3 AZ3:AZ22 BC4:BH10 BI4:DE33 BA11:BH22 V23:BH33 V11:AY22 V3:AX10 D3:U33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -5095,15 +5192,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -5111,157 +5208,157 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>33</v>
       </c>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7554B5A6-0B55-4400-873C-2354EE8F2958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98762AA9-6E5A-4F63-8079-1D0F393744EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14160" yWindow="4335" windowWidth="14460" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="40">
   <si>
     <t>Aluno</t>
   </si>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>P/5</t>
+  </si>
+  <si>
+    <t>aniver</t>
   </si>
 </sst>
 </file>
@@ -585,8 +588,12 @@
       <c r="U1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
+      <c r="V1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
@@ -718,8 +725,12 @@
       <c r="U2" s="1">
         <v>46108</v>
       </c>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
+      <c r="V2" s="1">
+        <v>46120</v>
+      </c>
+      <c r="W2" s="1">
+        <v>46122</v>
+      </c>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
@@ -836,6 +847,12 @@
         <v>36</v>
       </c>
       <c r="U3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V3" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -980,6 +997,12 @@
       <c r="U4" t="s">
         <v>37</v>
       </c>
+      <c r="V4" t="s">
+        <v>39</v>
+      </c>
+      <c r="W4" t="s">
+        <v>36</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1122,6 +1145,12 @@
       <c r="U5" t="s">
         <v>36</v>
       </c>
+      <c r="V5" t="s">
+        <v>39</v>
+      </c>
+      <c r="W5" t="s">
+        <v>36</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -1264,6 +1293,12 @@
       <c r="U6" t="s">
         <v>36</v>
       </c>
+      <c r="V6" t="s">
+        <v>39</v>
+      </c>
+      <c r="W6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -1406,6 +1441,12 @@
       <c r="U7" t="s">
         <v>37</v>
       </c>
+      <c r="V7" t="s">
+        <v>39</v>
+      </c>
+      <c r="W7" t="s">
+        <v>36</v>
+      </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -1548,6 +1589,12 @@
       <c r="U8" t="s">
         <v>36</v>
       </c>
+      <c r="V8" t="s">
+        <v>39</v>
+      </c>
+      <c r="W8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -1690,6 +1737,12 @@
       <c r="U9" t="s">
         <v>36</v>
       </c>
+      <c r="V9" t="s">
+        <v>39</v>
+      </c>
+      <c r="W9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -1832,6 +1885,12 @@
       <c r="U10" t="s">
         <v>36</v>
       </c>
+      <c r="V10" t="s">
+        <v>39</v>
+      </c>
+      <c r="W10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -1974,6 +2033,12 @@
       <c r="U11" t="s">
         <v>36</v>
       </c>
+      <c r="V11" t="s">
+        <v>39</v>
+      </c>
+      <c r="W11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -2116,6 +2181,12 @@
       <c r="U12" t="s">
         <v>36</v>
       </c>
+      <c r="V12" t="s">
+        <v>39</v>
+      </c>
+      <c r="W12" t="s">
+        <v>36</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -2258,6 +2329,12 @@
       <c r="U13" t="s">
         <v>36</v>
       </c>
+      <c r="V13" t="s">
+        <v>39</v>
+      </c>
+      <c r="W13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -2400,6 +2477,12 @@
       <c r="U14" t="s">
         <v>36</v>
       </c>
+      <c r="V14" t="s">
+        <v>39</v>
+      </c>
+      <c r="W14" t="s">
+        <v>37</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -2542,6 +2625,12 @@
       <c r="U15" t="s">
         <v>36</v>
       </c>
+      <c r="V15" t="s">
+        <v>39</v>
+      </c>
+      <c r="W15" t="s">
+        <v>36</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -2684,6 +2773,12 @@
       <c r="U16" t="s">
         <v>36</v>
       </c>
+      <c r="V16" t="s">
+        <v>39</v>
+      </c>
+      <c r="W16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -2826,6 +2921,12 @@
       <c r="U17" t="s">
         <v>37</v>
       </c>
+      <c r="V17" t="s">
+        <v>39</v>
+      </c>
+      <c r="W17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -2968,6 +3069,12 @@
       <c r="U18" t="s">
         <v>36</v>
       </c>
+      <c r="V18" t="s">
+        <v>39</v>
+      </c>
+      <c r="W18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -3110,6 +3217,12 @@
       <c r="U19" t="s">
         <v>36</v>
       </c>
+      <c r="V19" t="s">
+        <v>39</v>
+      </c>
+      <c r="W19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -3252,6 +3365,12 @@
       <c r="U20" t="s">
         <v>36</v>
       </c>
+      <c r="V20" t="s">
+        <v>39</v>
+      </c>
+      <c r="W20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -3394,6 +3513,12 @@
       <c r="U21" t="s">
         <v>36</v>
       </c>
+      <c r="V21" t="s">
+        <v>39</v>
+      </c>
+      <c r="W21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -3536,6 +3661,12 @@
       <c r="U22" t="s">
         <v>36</v>
       </c>
+      <c r="V22" t="s">
+        <v>39</v>
+      </c>
+      <c r="W22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -3678,6 +3809,12 @@
       <c r="U23" t="s">
         <v>37</v>
       </c>
+      <c r="V23" t="s">
+        <v>39</v>
+      </c>
+      <c r="W23" t="s">
+        <v>37</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -3820,6 +3957,12 @@
       <c r="U24" t="s">
         <v>36</v>
       </c>
+      <c r="V24" t="s">
+        <v>39</v>
+      </c>
+      <c r="W24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -3962,6 +4105,12 @@
       <c r="U25" t="s">
         <v>36</v>
       </c>
+      <c r="V25" t="s">
+        <v>39</v>
+      </c>
+      <c r="W25" t="s">
+        <v>36</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -4104,6 +4253,12 @@
       <c r="U26" t="s">
         <v>36</v>
       </c>
+      <c r="V26" t="s">
+        <v>39</v>
+      </c>
+      <c r="W26" t="s">
+        <v>36</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -4246,6 +4401,12 @@
       <c r="U27" t="s">
         <v>37</v>
       </c>
+      <c r="V27" t="s">
+        <v>39</v>
+      </c>
+      <c r="W27" t="s">
+        <v>36</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -4388,6 +4549,12 @@
       <c r="U28" t="s">
         <v>36</v>
       </c>
+      <c r="V28" t="s">
+        <v>39</v>
+      </c>
+      <c r="W28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -4530,6 +4697,12 @@
       <c r="U29" t="s">
         <v>36</v>
       </c>
+      <c r="V29" t="s">
+        <v>39</v>
+      </c>
+      <c r="W29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -4672,6 +4845,12 @@
       <c r="U30" t="s">
         <v>36</v>
       </c>
+      <c r="V30" t="s">
+        <v>39</v>
+      </c>
+      <c r="W30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -4814,6 +4993,12 @@
       <c r="U31" t="s">
         <v>37</v>
       </c>
+      <c r="V31" t="s">
+        <v>39</v>
+      </c>
+      <c r="W31" t="s">
+        <v>36</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -4956,6 +5141,12 @@
       <c r="U32" t="s">
         <v>37</v>
       </c>
+      <c r="V32" t="s">
+        <v>39</v>
+      </c>
+      <c r="W32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -5098,6 +5289,12 @@
       <c r="U33" t="s">
         <v>37</v>
       </c>
+      <c r="V33" t="s">
+        <v>39</v>
+      </c>
+      <c r="W33" t="s">
+        <v>36</v>
+      </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>
@@ -5179,7 +5376,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BC3:DE3 AZ3:AZ22 BC4:BH10 BI4:DE33 BA11:BH22 V23:BH33 V11:AY22 V3:AX10 D3:U33">
+  <conditionalFormatting sqref="BC3:DE3 V3:AX3 AZ3:AZ22 D3:U33 BC4:BH10 BI4:DE33 W11:AY22 BA11:BH22 W23:BH33 W4:AX10 V4:V33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98762AA9-6E5A-4F63-8079-1D0F393744EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8DB494-BC1C-4031-97D0-B4A6CC3011D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="40">
   <si>
     <t>Aluno</t>
   </si>
@@ -594,9 +594,15 @@
       <c r="W1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="X1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
@@ -731,9 +737,15 @@
       <c r="W2" s="1">
         <v>46122</v>
       </c>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
+      <c r="X2" s="1">
+        <v>46127</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>46129</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>46134</v>
+      </c>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
@@ -853,6 +865,15 @@
         <v>39</v>
       </c>
       <c r="W3" t="s">
+        <v>36</v>
+      </c>
+      <c r="X3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -1003,6 +1024,15 @@
       <c r="W4" t="s">
         <v>36</v>
       </c>
+      <c r="X4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>36</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1151,6 +1181,15 @@
       <c r="W5" t="s">
         <v>36</v>
       </c>
+      <c r="X5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>36</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -1299,6 +1338,15 @@
       <c r="W6" t="s">
         <v>36</v>
       </c>
+      <c r="X6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -1447,6 +1495,15 @@
       <c r="W7" t="s">
         <v>36</v>
       </c>
+      <c r="X7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>36</v>
+      </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -1595,6 +1652,15 @@
       <c r="W8" t="s">
         <v>36</v>
       </c>
+      <c r="X8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -1743,6 +1809,15 @@
       <c r="W9" t="s">
         <v>36</v>
       </c>
+      <c r="X9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -1891,6 +1966,15 @@
       <c r="W10" t="s">
         <v>36</v>
       </c>
+      <c r="X10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -2039,6 +2123,15 @@
       <c r="W11" t="s">
         <v>36</v>
       </c>
+      <c r="X11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -2187,6 +2280,15 @@
       <c r="W12" t="s">
         <v>36</v>
       </c>
+      <c r="X12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>37</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -2335,6 +2437,15 @@
       <c r="W13" t="s">
         <v>36</v>
       </c>
+      <c r="X13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -2483,6 +2594,15 @@
       <c r="W14" t="s">
         <v>37</v>
       </c>
+      <c r="X14" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>36</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -2631,6 +2751,15 @@
       <c r="W15" t="s">
         <v>36</v>
       </c>
+      <c r="X15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>36</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -2779,6 +2908,15 @@
       <c r="W16" t="s">
         <v>36</v>
       </c>
+      <c r="X16" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -2927,6 +3065,15 @@
       <c r="W17" t="s">
         <v>36</v>
       </c>
+      <c r="X17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -3075,6 +3222,15 @@
       <c r="W18" t="s">
         <v>36</v>
       </c>
+      <c r="X18" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -3223,6 +3379,15 @@
       <c r="W19" t="s">
         <v>36</v>
       </c>
+      <c r="X19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -3371,6 +3536,15 @@
       <c r="W20" t="s">
         <v>36</v>
       </c>
+      <c r="X20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -3519,6 +3693,15 @@
       <c r="W21" t="s">
         <v>36</v>
       </c>
+      <c r="X21" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -3667,6 +3850,15 @@
       <c r="W22" t="s">
         <v>36</v>
       </c>
+      <c r="X22" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -3815,6 +4007,15 @@
       <c r="W23" t="s">
         <v>37</v>
       </c>
+      <c r="X23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>36</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -3963,6 +4164,15 @@
       <c r="W24" t="s">
         <v>36</v>
       </c>
+      <c r="X24" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -4111,6 +4321,15 @@
       <c r="W25" t="s">
         <v>36</v>
       </c>
+      <c r="X25" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>36</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -4259,6 +4478,15 @@
       <c r="W26" t="s">
         <v>36</v>
       </c>
+      <c r="X26" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>36</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -4407,6 +4635,15 @@
       <c r="W27" t="s">
         <v>36</v>
       </c>
+      <c r="X27" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>36</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -4555,6 +4792,15 @@
       <c r="W28" t="s">
         <v>36</v>
       </c>
+      <c r="X28" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -4703,6 +4949,15 @@
       <c r="W29" t="s">
         <v>36</v>
       </c>
+      <c r="X29" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -4851,6 +5106,15 @@
       <c r="W30" t="s">
         <v>36</v>
       </c>
+      <c r="X30" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -4999,6 +5263,15 @@
       <c r="W31" t="s">
         <v>36</v>
       </c>
+      <c r="X31" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>36</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -5147,6 +5420,15 @@
       <c r="W32" t="s">
         <v>36</v>
       </c>
+      <c r="X32" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -5295,6 +5577,15 @@
       <c r="W33" t="s">
         <v>36</v>
       </c>
+      <c r="X33" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>36</v>
+      </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>
@@ -5376,7 +5667,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BC3:DE3 V3:AX3 AZ3:AZ22 D3:U33 BC4:BH10 BI4:DE33 W11:AY22 BA11:BH22 W23:BH33 W4:AX10 V4:V33">
+  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 W4:AX10 BC4:BH10 V4:V33 BI4:DE33 W11:AY22 BA11:BH22 W23:BH33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8DB494-BC1C-4031-97D0-B4A6CC3011D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6057910D-985A-4779-8D1D-5C38E16656BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="40">
   <si>
     <t>Aluno</t>
   </si>
@@ -603,7 +603,9 @@
       <c r="Z1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AA1" s="1"/>
+      <c r="AA1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
@@ -746,7 +748,9 @@
       <c r="Z2" s="1">
         <v>46134</v>
       </c>
-      <c r="AA2" s="1"/>
+      <c r="AA2" s="1">
+        <v>46136</v>
+      </c>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
@@ -874,6 +878,9 @@
         <v>36</v>
       </c>
       <c r="Z3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -1033,6 +1040,9 @@
       <c r="Z4" t="s">
         <v>36</v>
       </c>
+      <c r="AA4" t="s">
+        <v>36</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1190,6 +1200,9 @@
       <c r="Z5" t="s">
         <v>36</v>
       </c>
+      <c r="AA5" t="s">
+        <v>36</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -1347,6 +1360,9 @@
       <c r="Z6" t="s">
         <v>36</v>
       </c>
+      <c r="AA6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -1504,6 +1520,9 @@
       <c r="Z7" t="s">
         <v>36</v>
       </c>
+      <c r="AA7" t="s">
+        <v>36</v>
+      </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -1661,6 +1680,9 @@
       <c r="Z8" t="s">
         <v>36</v>
       </c>
+      <c r="AA8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -1818,6 +1840,9 @@
       <c r="Z9" t="s">
         <v>36</v>
       </c>
+      <c r="AA9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -1975,6 +2000,9 @@
       <c r="Z10" t="s">
         <v>36</v>
       </c>
+      <c r="AA10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -2132,6 +2160,9 @@
       <c r="Z11" t="s">
         <v>36</v>
       </c>
+      <c r="AA11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -2289,6 +2320,9 @@
       <c r="Z12" t="s">
         <v>37</v>
       </c>
+      <c r="AA12" t="s">
+        <v>36</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -2446,6 +2480,9 @@
       <c r="Z13" t="s">
         <v>36</v>
       </c>
+      <c r="AA13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -2603,6 +2640,9 @@
       <c r="Z14" t="s">
         <v>36</v>
       </c>
+      <c r="AA14" t="s">
+        <v>37</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -2760,6 +2800,9 @@
       <c r="Z15" t="s">
         <v>36</v>
       </c>
+      <c r="AA15" t="s">
+        <v>36</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -2917,6 +2960,9 @@
       <c r="Z16" t="s">
         <v>36</v>
       </c>
+      <c r="AA16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -3074,6 +3120,9 @@
       <c r="Z17" t="s">
         <v>36</v>
       </c>
+      <c r="AA17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -3231,6 +3280,9 @@
       <c r="Z18" t="s">
         <v>36</v>
       </c>
+      <c r="AA18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -3388,6 +3440,9 @@
       <c r="Z19" t="s">
         <v>36</v>
       </c>
+      <c r="AA19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -3545,6 +3600,9 @@
       <c r="Z20" t="s">
         <v>36</v>
       </c>
+      <c r="AA20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -3702,6 +3760,9 @@
       <c r="Z21" t="s">
         <v>36</v>
       </c>
+      <c r="AA21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -3859,6 +3920,9 @@
       <c r="Z22" t="s">
         <v>36</v>
       </c>
+      <c r="AA22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -4016,6 +4080,9 @@
       <c r="Z23" t="s">
         <v>36</v>
       </c>
+      <c r="AA23" t="s">
+        <v>36</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -4173,6 +4240,9 @@
       <c r="Z24" t="s">
         <v>36</v>
       </c>
+      <c r="AA24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -4330,6 +4400,9 @@
       <c r="Z25" t="s">
         <v>36</v>
       </c>
+      <c r="AA25" t="s">
+        <v>36</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -4487,6 +4560,9 @@
       <c r="Z26" t="s">
         <v>36</v>
       </c>
+      <c r="AA26" t="s">
+        <v>36</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -4644,6 +4720,9 @@
       <c r="Z27" t="s">
         <v>36</v>
       </c>
+      <c r="AA27" t="s">
+        <v>36</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -4801,6 +4880,9 @@
       <c r="Z28" t="s">
         <v>36</v>
       </c>
+      <c r="AA28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -4958,6 +5040,9 @@
       <c r="Z29" t="s">
         <v>36</v>
       </c>
+      <c r="AA29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -5115,6 +5200,9 @@
       <c r="Z30" t="s">
         <v>36</v>
       </c>
+      <c r="AA30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -5272,6 +5360,9 @@
       <c r="Z31" t="s">
         <v>36</v>
       </c>
+      <c r="AA31" t="s">
+        <v>36</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -5429,6 +5520,9 @@
       <c r="Z32" t="s">
         <v>36</v>
       </c>
+      <c r="AA32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -5586,6 +5680,9 @@
       <c r="Z33" t="s">
         <v>36</v>
       </c>
+      <c r="AA33" t="s">
+        <v>36</v>
+      </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>
@@ -5667,7 +5764,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 W4:AX10 BC4:BH10 V4:V33 BI4:DE33 W11:AY22 BA11:BH22 W23:BH33">
+  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 AB4:AX10 BC4:BH10 V4:AA33 BI4:DE33 AB11:AY22 BA11:BH22 AB23:BH33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8DB494-BC1C-4031-97D0-B4A6CC3011D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C283B25D-36BC-4A34-8DFB-657515AB8A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="40">
   <si>
     <t>Aluno</t>
   </si>
@@ -603,7 +603,9 @@
       <c r="Z1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AA1" s="1"/>
+      <c r="AA1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
@@ -746,7 +748,9 @@
       <c r="Z2" s="1">
         <v>46134</v>
       </c>
-      <c r="AA2" s="1"/>
+      <c r="AA2" s="1">
+        <v>46136</v>
+      </c>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
@@ -874,6 +878,9 @@
         <v>36</v>
       </c>
       <c r="Z3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -1033,6 +1040,9 @@
       <c r="Z4" t="s">
         <v>36</v>
       </c>
+      <c r="AA4" t="s">
+        <v>36</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1190,6 +1200,9 @@
       <c r="Z5" t="s">
         <v>36</v>
       </c>
+      <c r="AA5" t="s">
+        <v>36</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -1347,6 +1360,9 @@
       <c r="Z6" t="s">
         <v>36</v>
       </c>
+      <c r="AA6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -1504,6 +1520,9 @@
       <c r="Z7" t="s">
         <v>36</v>
       </c>
+      <c r="AA7" t="s">
+        <v>36</v>
+      </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -1661,6 +1680,9 @@
       <c r="Z8" t="s">
         <v>36</v>
       </c>
+      <c r="AA8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -1818,6 +1840,9 @@
       <c r="Z9" t="s">
         <v>36</v>
       </c>
+      <c r="AA9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -1975,6 +2000,9 @@
       <c r="Z10" t="s">
         <v>36</v>
       </c>
+      <c r="AA10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -2132,6 +2160,9 @@
       <c r="Z11" t="s">
         <v>36</v>
       </c>
+      <c r="AA11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -2289,6 +2320,9 @@
       <c r="Z12" t="s">
         <v>37</v>
       </c>
+      <c r="AA12" t="s">
+        <v>36</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -2446,6 +2480,9 @@
       <c r="Z13" t="s">
         <v>36</v>
       </c>
+      <c r="AA13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -2603,6 +2640,9 @@
       <c r="Z14" t="s">
         <v>36</v>
       </c>
+      <c r="AA14" t="s">
+        <v>37</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -2760,6 +2800,9 @@
       <c r="Z15" t="s">
         <v>36</v>
       </c>
+      <c r="AA15" t="s">
+        <v>36</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -2917,6 +2960,9 @@
       <c r="Z16" t="s">
         <v>36</v>
       </c>
+      <c r="AA16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -3074,6 +3120,9 @@
       <c r="Z17" t="s">
         <v>36</v>
       </c>
+      <c r="AA17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -3231,6 +3280,9 @@
       <c r="Z18" t="s">
         <v>36</v>
       </c>
+      <c r="AA18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -3388,6 +3440,9 @@
       <c r="Z19" t="s">
         <v>36</v>
       </c>
+      <c r="AA19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -3545,6 +3600,9 @@
       <c r="Z20" t="s">
         <v>36</v>
       </c>
+      <c r="AA20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -3702,6 +3760,9 @@
       <c r="Z21" t="s">
         <v>36</v>
       </c>
+      <c r="AA21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -3859,6 +3920,9 @@
       <c r="Z22" t="s">
         <v>36</v>
       </c>
+      <c r="AA22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -4016,6 +4080,9 @@
       <c r="Z23" t="s">
         <v>36</v>
       </c>
+      <c r="AA23" t="s">
+        <v>36</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -4173,6 +4240,9 @@
       <c r="Z24" t="s">
         <v>36</v>
       </c>
+      <c r="AA24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -4330,6 +4400,9 @@
       <c r="Z25" t="s">
         <v>36</v>
       </c>
+      <c r="AA25" t="s">
+        <v>36</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -4487,6 +4560,9 @@
       <c r="Z26" t="s">
         <v>36</v>
       </c>
+      <c r="AA26" t="s">
+        <v>36</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -4644,6 +4720,9 @@
       <c r="Z27" t="s">
         <v>36</v>
       </c>
+      <c r="AA27" t="s">
+        <v>36</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -4801,6 +4880,9 @@
       <c r="Z28" t="s">
         <v>36</v>
       </c>
+      <c r="AA28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -4958,6 +5040,9 @@
       <c r="Z29" t="s">
         <v>36</v>
       </c>
+      <c r="AA29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -5115,6 +5200,9 @@
       <c r="Z30" t="s">
         <v>36</v>
       </c>
+      <c r="AA30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -5272,6 +5360,9 @@
       <c r="Z31" t="s">
         <v>36</v>
       </c>
+      <c r="AA31" t="s">
+        <v>36</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -5429,6 +5520,9 @@
       <c r="Z32" t="s">
         <v>36</v>
       </c>
+      <c r="AA32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -5586,6 +5680,9 @@
       <c r="Z33" t="s">
         <v>36</v>
       </c>
+      <c r="AA33" t="s">
+        <v>36</v>
+      </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C283B25D-36BC-4A34-8DFB-657515AB8A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3257808-2EFB-40E3-A6D1-7CF8714B86DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="41">
   <si>
     <t>Aluno</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>aniver</t>
+  </si>
+  <si>
+    <t>SEG</t>
   </si>
 </sst>
 </file>
@@ -525,10 +528,9 @@
     <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="7.7109375" customWidth="1"/>
-    <col min="20" max="20" width="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="48" width="7.7109375" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="48" width="7.7109375" customWidth="1"/>
     <col min="49" max="49" width="7.7109375" style="5" customWidth="1"/>
     <col min="50" max="104" width="7.7109375" customWidth="1"/>
   </cols>
@@ -606,7 +608,9 @@
       <c r="AA1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AB1" s="1"/>
+      <c r="AB1" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
@@ -751,7 +755,9 @@
       <c r="AA2" s="1">
         <v>46136</v>
       </c>
-      <c r="AB2" s="1"/>
+      <c r="AB2" s="1">
+        <v>46141</v>
+      </c>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
@@ -881,6 +887,9 @@
         <v>36</v>
       </c>
       <c r="AA3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -1043,6 +1052,9 @@
       <c r="AA4" t="s">
         <v>36</v>
       </c>
+      <c r="AB4" t="s">
+        <v>36</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1203,6 +1215,9 @@
       <c r="AA5" t="s">
         <v>36</v>
       </c>
+      <c r="AB5" t="s">
+        <v>36</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -1363,6 +1378,9 @@
       <c r="AA6" t="s">
         <v>36</v>
       </c>
+      <c r="AB6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -1523,6 +1541,9 @@
       <c r="AA7" t="s">
         <v>36</v>
       </c>
+      <c r="AB7" t="s">
+        <v>36</v>
+      </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -1683,6 +1704,9 @@
       <c r="AA8" t="s">
         <v>36</v>
       </c>
+      <c r="AB8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -1843,6 +1867,9 @@
       <c r="AA9" t="s">
         <v>36</v>
       </c>
+      <c r="AB9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -2003,6 +2030,9 @@
       <c r="AA10" t="s">
         <v>36</v>
       </c>
+      <c r="AB10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -2163,6 +2193,9 @@
       <c r="AA11" t="s">
         <v>36</v>
       </c>
+      <c r="AB11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -2323,6 +2356,9 @@
       <c r="AA12" t="s">
         <v>36</v>
       </c>
+      <c r="AB12" t="s">
+        <v>36</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -2483,6 +2519,9 @@
       <c r="AA13" t="s">
         <v>36</v>
       </c>
+      <c r="AB13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -2643,6 +2682,9 @@
       <c r="AA14" t="s">
         <v>37</v>
       </c>
+      <c r="AB14" t="s">
+        <v>36</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -2803,6 +2845,9 @@
       <c r="AA15" t="s">
         <v>36</v>
       </c>
+      <c r="AB15" t="s">
+        <v>36</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -2963,6 +3008,9 @@
       <c r="AA16" t="s">
         <v>36</v>
       </c>
+      <c r="AB16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -3123,6 +3171,9 @@
       <c r="AA17" t="s">
         <v>36</v>
       </c>
+      <c r="AB17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -3283,6 +3334,9 @@
       <c r="AA18" t="s">
         <v>36</v>
       </c>
+      <c r="AB18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -3443,6 +3497,9 @@
       <c r="AA19" t="s">
         <v>36</v>
       </c>
+      <c r="AB19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -3603,6 +3660,9 @@
       <c r="AA20" t="s">
         <v>36</v>
       </c>
+      <c r="AB20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -3763,6 +3823,9 @@
       <c r="AA21" t="s">
         <v>36</v>
       </c>
+      <c r="AB21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -3923,6 +3986,9 @@
       <c r="AA22" t="s">
         <v>36</v>
       </c>
+      <c r="AB22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -4083,6 +4149,9 @@
       <c r="AA23" t="s">
         <v>36</v>
       </c>
+      <c r="AB23" t="s">
+        <v>36</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -4243,6 +4312,9 @@
       <c r="AA24" t="s">
         <v>36</v>
       </c>
+      <c r="AB24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -4403,6 +4475,9 @@
       <c r="AA25" t="s">
         <v>36</v>
       </c>
+      <c r="AB25" t="s">
+        <v>36</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -4563,6 +4638,9 @@
       <c r="AA26" t="s">
         <v>36</v>
       </c>
+      <c r="AB26" t="s">
+        <v>36</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -4723,6 +4801,9 @@
       <c r="AA27" t="s">
         <v>36</v>
       </c>
+      <c r="AB27" t="s">
+        <v>36</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -4883,6 +4964,9 @@
       <c r="AA28" t="s">
         <v>36</v>
       </c>
+      <c r="AB28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -5043,6 +5127,9 @@
       <c r="AA29" t="s">
         <v>36</v>
       </c>
+      <c r="AB29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -5203,6 +5290,9 @@
       <c r="AA30" t="s">
         <v>36</v>
       </c>
+      <c r="AB30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -5363,6 +5453,9 @@
       <c r="AA31" t="s">
         <v>36</v>
       </c>
+      <c r="AB31" t="s">
+        <v>36</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -5523,6 +5616,9 @@
       <c r="AA32" t="s">
         <v>36</v>
       </c>
+      <c r="AB32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -5683,6 +5779,9 @@
       <c r="AA33" t="s">
         <v>36</v>
       </c>
+      <c r="AB33" t="s">
+        <v>36</v>
+      </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3257808-2EFB-40E3-A6D1-7CF8714B86DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF857BD-92D5-4E48-8EC7-536E538F7F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t>SEG</t>
+  </si>
+  <si>
+    <t>feriado</t>
   </si>
 </sst>
 </file>
@@ -611,9 +614,15 @@
       <c r="AB1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
+      <c r="AC1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1"/>
@@ -758,9 +767,15 @@
       <c r="AB2" s="1">
         <v>46141</v>
       </c>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
+      <c r="AC2" s="1">
+        <v>46143</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>46148</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>46150</v>
+      </c>
       <c r="AS2" s="2"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
@@ -890,6 +905,12 @@
         <v>36</v>
       </c>
       <c r="AB3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -1055,6 +1076,12 @@
       <c r="AB4" t="s">
         <v>36</v>
       </c>
+      <c r="AC4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>37</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1218,6 +1245,12 @@
       <c r="AB5" t="s">
         <v>36</v>
       </c>
+      <c r="AC5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>36</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -1381,6 +1414,12 @@
       <c r="AB6" t="s">
         <v>36</v>
       </c>
+      <c r="AC6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -1544,6 +1583,12 @@
       <c r="AB7" t="s">
         <v>36</v>
       </c>
+      <c r="AC7" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>36</v>
+      </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -1707,6 +1752,12 @@
       <c r="AB8" t="s">
         <v>36</v>
       </c>
+      <c r="AC8" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -1870,6 +1921,12 @@
       <c r="AB9" t="s">
         <v>36</v>
       </c>
+      <c r="AC9" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -2033,6 +2090,12 @@
       <c r="AB10" t="s">
         <v>36</v>
       </c>
+      <c r="AC10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -2196,6 +2259,12 @@
       <c r="AB11" t="s">
         <v>36</v>
       </c>
+      <c r="AC11" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -2359,6 +2428,12 @@
       <c r="AB12" t="s">
         <v>36</v>
       </c>
+      <c r="AC12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>36</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -2522,6 +2597,12 @@
       <c r="AB13" t="s">
         <v>36</v>
       </c>
+      <c r="AC13" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -2685,6 +2766,12 @@
       <c r="AB14" t="s">
         <v>36</v>
       </c>
+      <c r="AC14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>37</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -2848,6 +2935,12 @@
       <c r="AB15" t="s">
         <v>36</v>
       </c>
+      <c r="AC15" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>36</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -3011,6 +3104,12 @@
       <c r="AB16" t="s">
         <v>36</v>
       </c>
+      <c r="AC16" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -3174,6 +3273,12 @@
       <c r="AB17" t="s">
         <v>36</v>
       </c>
+      <c r="AC17" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -3337,6 +3442,12 @@
       <c r="AB18" t="s">
         <v>36</v>
       </c>
+      <c r="AC18" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -3500,6 +3611,12 @@
       <c r="AB19" t="s">
         <v>36</v>
       </c>
+      <c r="AC19" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -3663,6 +3780,12 @@
       <c r="AB20" t="s">
         <v>36</v>
       </c>
+      <c r="AC20" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -3826,6 +3949,12 @@
       <c r="AB21" t="s">
         <v>36</v>
       </c>
+      <c r="AC21" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -3989,6 +4118,12 @@
       <c r="AB22" t="s">
         <v>36</v>
       </c>
+      <c r="AC22" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -4152,6 +4287,12 @@
       <c r="AB23" t="s">
         <v>36</v>
       </c>
+      <c r="AC23" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>36</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -4315,6 +4456,12 @@
       <c r="AB24" t="s">
         <v>36</v>
       </c>
+      <c r="AC24" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -4478,6 +4625,12 @@
       <c r="AB25" t="s">
         <v>36</v>
       </c>
+      <c r="AC25" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>36</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -4641,6 +4794,12 @@
       <c r="AB26" t="s">
         <v>36</v>
       </c>
+      <c r="AC26" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>36</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -4804,6 +4963,12 @@
       <c r="AB27" t="s">
         <v>36</v>
       </c>
+      <c r="AC27" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>36</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -4967,6 +5132,12 @@
       <c r="AB28" t="s">
         <v>36</v>
       </c>
+      <c r="AC28" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -5130,6 +5301,12 @@
       <c r="AB29" t="s">
         <v>36</v>
       </c>
+      <c r="AC29" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -5293,6 +5470,12 @@
       <c r="AB30" t="s">
         <v>36</v>
       </c>
+      <c r="AC30" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -5456,6 +5639,12 @@
       <c r="AB31" t="s">
         <v>36</v>
       </c>
+      <c r="AC31" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>36</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -5619,6 +5808,12 @@
       <c r="AB32" t="s">
         <v>36</v>
       </c>
+      <c r="AC32" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -5782,6 +5977,12 @@
       <c r="AB33" t="s">
         <v>36</v>
       </c>
+      <c r="AC33" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>36</v>
+      </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>
@@ -5863,7 +6064,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 W4:AX10 BC4:BH10 V4:V33 BI4:DE33 W11:AY22 BA11:BH22 W23:BH33">
+  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 BC4:BH10 BI4:DE33 BA11:BH22 AD23:BH33 AD11:AY22 AD4:AX10 V4:AC33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF857BD-92D5-4E48-8EC7-536E538F7F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CD823C-1161-495F-BF41-AD48EC5653B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -223,7 +223,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -232,6 +232,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1080,7 +1081,7 @@
         <v>41</v>
       </c>
       <c r="AD4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
@@ -1248,7 +1249,7 @@
       <c r="AC5" t="s">
         <v>41</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AD5" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS5" s="2"/>
@@ -6064,7 +6065,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 BC4:BH10 BI4:DE33 BA11:BH22 AD23:BH33 AD11:AY22 AD4:AX10 V4:AC33">
+  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 AD4:AX10 BC4:BH10 V4:AC33 BI4:DE33 AD11:AY22 BA11:BH22 AD23:BH33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CD823C-1161-495F-BF41-AD48EC5653B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087DB32B-50C1-453A-8097-5DE13EE30AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -223,7 +223,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -232,7 +232,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -624,8 +623,12 @@
       <c r="AE1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
+      <c r="AF1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
@@ -777,6 +780,12 @@
       <c r="AE2" s="1">
         <v>46150</v>
       </c>
+      <c r="AF2" s="1">
+        <v>46155</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>46157</v>
+      </c>
       <c r="AS2" s="2"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
@@ -912,6 +921,9 @@
         <v>41</v>
       </c>
       <c r="AD3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -1083,6 +1095,9 @@
       <c r="AD4" t="s">
         <v>36</v>
       </c>
+      <c r="AE4" t="s">
+        <v>36</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1249,8 +1264,11 @@
       <c r="AC5" t="s">
         <v>41</v>
       </c>
-      <c r="AD5" s="8" t="s">
-        <v>36</v>
+      <c r="AD5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>37</v>
       </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
@@ -1421,6 +1439,9 @@
       <c r="AD6" t="s">
         <v>36</v>
       </c>
+      <c r="AE6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -1590,6 +1611,9 @@
       <c r="AD7" t="s">
         <v>36</v>
       </c>
+      <c r="AE7" t="s">
+        <v>36</v>
+      </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -1759,6 +1783,9 @@
       <c r="AD8" t="s">
         <v>36</v>
       </c>
+      <c r="AE8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -1928,6 +1955,9 @@
       <c r="AD9" t="s">
         <v>36</v>
       </c>
+      <c r="AE9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -2097,6 +2127,9 @@
       <c r="AD10" t="s">
         <v>36</v>
       </c>
+      <c r="AE10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -2266,6 +2299,9 @@
       <c r="AD11" t="s">
         <v>36</v>
       </c>
+      <c r="AE11" t="s">
+        <v>37</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -2435,6 +2471,9 @@
       <c r="AD12" t="s">
         <v>36</v>
       </c>
+      <c r="AE12" t="s">
+        <v>36</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -2604,6 +2643,9 @@
       <c r="AD13" t="s">
         <v>36</v>
       </c>
+      <c r="AE13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -2773,6 +2815,9 @@
       <c r="AD14" t="s">
         <v>37</v>
       </c>
+      <c r="AE14" t="s">
+        <v>36</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -2942,6 +2987,9 @@
       <c r="AD15" t="s">
         <v>36</v>
       </c>
+      <c r="AE15" t="s">
+        <v>36</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -3111,6 +3159,9 @@
       <c r="AD16" t="s">
         <v>36</v>
       </c>
+      <c r="AE16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -3280,6 +3331,9 @@
       <c r="AD17" t="s">
         <v>36</v>
       </c>
+      <c r="AE17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -3449,6 +3503,9 @@
       <c r="AD18" t="s">
         <v>36</v>
       </c>
+      <c r="AE18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -3618,6 +3675,9 @@
       <c r="AD19" t="s">
         <v>36</v>
       </c>
+      <c r="AE19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -3787,6 +3847,9 @@
       <c r="AD20" t="s">
         <v>36</v>
       </c>
+      <c r="AE20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -3956,6 +4019,9 @@
       <c r="AD21" t="s">
         <v>36</v>
       </c>
+      <c r="AE21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -4125,6 +4191,9 @@
       <c r="AD22" t="s">
         <v>36</v>
       </c>
+      <c r="AE22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -4294,6 +4363,9 @@
       <c r="AD23" t="s">
         <v>36</v>
       </c>
+      <c r="AE23" t="s">
+        <v>37</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -4463,6 +4535,9 @@
       <c r="AD24" t="s">
         <v>36</v>
       </c>
+      <c r="AE24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -4632,6 +4707,9 @@
       <c r="AD25" t="s">
         <v>36</v>
       </c>
+      <c r="AE25" t="s">
+        <v>36</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -4801,6 +4879,9 @@
       <c r="AD26" t="s">
         <v>36</v>
       </c>
+      <c r="AE26" t="s">
+        <v>36</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -4970,6 +5051,9 @@
       <c r="AD27" t="s">
         <v>36</v>
       </c>
+      <c r="AE27" t="s">
+        <v>36</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -5139,6 +5223,9 @@
       <c r="AD28" t="s">
         <v>36</v>
       </c>
+      <c r="AE28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -5308,6 +5395,9 @@
       <c r="AD29" t="s">
         <v>36</v>
       </c>
+      <c r="AE29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -5477,6 +5567,9 @@
       <c r="AD30" t="s">
         <v>36</v>
       </c>
+      <c r="AE30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -5646,6 +5739,9 @@
       <c r="AD31" t="s">
         <v>36</v>
       </c>
+      <c r="AE31" t="s">
+        <v>37</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -5815,6 +5911,9 @@
       <c r="AD32" t="s">
         <v>36</v>
       </c>
+      <c r="AE32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -5984,6 +6083,9 @@
       <c r="AD33" t="s">
         <v>36</v>
       </c>
+      <c r="AE33" t="s">
+        <v>36</v>
+      </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
       <c r="AU33" s="2"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087DB32B-50C1-453A-8097-5DE13EE30AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC49F3D-C031-4355-86F7-D1D4CAED1040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -167,7 +167,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,16 +201,309 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -218,12 +511,160 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -232,10 +673,52 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="43">
+    <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase2" xfId="24" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase3" xfId="28" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase4" xfId="32" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase5" xfId="36" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase6" xfId="40" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase1" xfId="21" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase2" xfId="25" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase3" xfId="29" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase4" xfId="33" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase5" xfId="37" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase6" xfId="41" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase1" xfId="22" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase2" xfId="26" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase3" xfId="30" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase4" xfId="34" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase5" xfId="38" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase6" xfId="42" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bom" xfId="7" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="12" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Célula de Verificação" xfId="14" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Célula Vinculada" xfId="13" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Ênfase1" xfId="19" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Ênfase2" xfId="23" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Ênfase3" xfId="27" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Ênfase4" xfId="31" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Ênfase5" xfId="35" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Ênfase6" xfId="39" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="10" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Neutro" xfId="9" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Nota" xfId="16" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
+    <cellStyle name="Ruim" xfId="8" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Saída" xfId="11" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de Aviso" xfId="15" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto Explicativo" xfId="17" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="2" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 1" xfId="3" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="4" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="5" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -525,20 +1008,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DQ33"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="48" width="7.7109375" customWidth="1"/>
-    <col min="49" max="49" width="7.7109375" style="5" customWidth="1"/>
-    <col min="50" max="104" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="48" width="7.6640625" customWidth="1"/>
+    <col min="49" max="49" width="7.6640625" style="5" customWidth="1"/>
+    <col min="50" max="104" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:121" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
@@ -686,7 +1169,7 @@
       <c r="CJ1" s="4"/>
       <c r="CK1" s="4"/>
     </row>
-    <row r="2" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -830,10 +1313,10 @@
       <c r="CJ2" s="5"/>
       <c r="CK2" s="5"/>
     </row>
-    <row r="3" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
-        <v>0</v>
+        <v>25129175</v>
       </c>
       <c r="B3" t="str">
         <f>alunos!B2</f>
@@ -924,6 +1407,12 @@
         <v>36</v>
       </c>
       <c r="AE3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -1002,10 +1491,10 @@
       <c r="DP3" s="5"/>
       <c r="DQ3" s="5"/>
     </row>
-    <row r="4" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
-        <v>0</v>
+        <v>25129085</v>
       </c>
       <c r="B4" t="str">
         <f>alunos!B3</f>
@@ -1096,6 +1585,12 @@
         <v>36</v>
       </c>
       <c r="AE4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG4" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS4" s="2"/>
@@ -1174,10 +1669,10 @@
       <c r="DP4" s="5"/>
       <c r="DQ4" s="5"/>
     </row>
-    <row r="5" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
-        <v>0</v>
+        <v>25129021</v>
       </c>
       <c r="B5" t="str">
         <f>alunos!B4</f>
@@ -1269,6 +1764,12 @@
       </c>
       <c r="AE5" t="s">
         <v>37</v>
+      </c>
+      <c r="AF5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG5" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
@@ -1346,10 +1847,10 @@
       <c r="DP5" s="5"/>
       <c r="DQ5" s="5"/>
     </row>
-    <row r="6" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
-        <v>0</v>
+        <v>25129019</v>
       </c>
       <c r="B6" t="str">
         <f>alunos!B5</f>
@@ -1440,6 +1941,12 @@
         <v>36</v>
       </c>
       <c r="AE6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG6" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS6" s="2"/>
@@ -1518,10 +2025,10 @@
       <c r="DP6" s="5"/>
       <c r="DQ6" s="5"/>
     </row>
-    <row r="7" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
-        <v>0</v>
+        <v>25129023</v>
       </c>
       <c r="B7" t="str">
         <f>alunos!B6</f>
@@ -1612,6 +2119,12 @@
         <v>36</v>
       </c>
       <c r="AE7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG7" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS7" s="2"/>
@@ -1690,10 +2203,10 @@
       <c r="DP7" s="5"/>
       <c r="DQ7" s="5"/>
     </row>
-    <row r="8" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
-        <v>0</v>
+        <v>25129105</v>
       </c>
       <c r="B8" t="str">
         <f>alunos!B7</f>
@@ -1784,6 +2297,12 @@
         <v>36</v>
       </c>
       <c r="AE8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG8" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS8" s="2"/>
@@ -1862,10 +2381,10 @@
       <c r="DP8" s="5"/>
       <c r="DQ8" s="5"/>
     </row>
-    <row r="9" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
-        <v>0</v>
+        <v>25129083</v>
       </c>
       <c r="B9" t="str">
         <f>alunos!B8</f>
@@ -1956,6 +2475,12 @@
         <v>36</v>
       </c>
       <c r="AE9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG9" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS9" s="2"/>
@@ -2034,10 +2559,10 @@
       <c r="DP9" s="5"/>
       <c r="DQ9" s="5"/>
     </row>
-    <row r="10" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
-        <v>0</v>
+        <v>25129047</v>
       </c>
       <c r="B10" t="str">
         <f>alunos!B9</f>
@@ -2128,6 +2653,12 @@
         <v>36</v>
       </c>
       <c r="AE10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG10" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS10" s="2"/>
@@ -2206,10 +2737,10 @@
       <c r="DP10" s="5"/>
       <c r="DQ10" s="5"/>
     </row>
-    <row r="11" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
-        <v>0</v>
+        <v>25129101</v>
       </c>
       <c r="B11" t="str">
         <f>alunos!B10</f>
@@ -2301,6 +2832,12 @@
       </c>
       <c r="AE11" t="s">
         <v>37</v>
+      </c>
+      <c r="AF11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG11" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
@@ -2378,10 +2915,10 @@
       <c r="DP11" s="5"/>
       <c r="DQ11" s="5"/>
     </row>
-    <row r="12" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
-        <v>0</v>
+        <v>25129081</v>
       </c>
       <c r="B12" t="str">
         <f>alunos!B11</f>
@@ -2472,6 +3009,12 @@
         <v>36</v>
       </c>
       <c r="AE12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG12" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS12" s="2"/>
@@ -2550,10 +3093,10 @@
       <c r="DP12" s="5"/>
       <c r="DQ12" s="5"/>
     </row>
-    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
-        <v>0</v>
+        <v>25129160</v>
       </c>
       <c r="B13" t="str">
         <f>alunos!B12</f>
@@ -2644,6 +3187,12 @@
         <v>36</v>
       </c>
       <c r="AE13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG13" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS13" s="2"/>
@@ -2722,10 +3271,10 @@
       <c r="DP13" s="5"/>
       <c r="DQ13" s="5"/>
     </row>
-    <row r="14" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
-        <v>0</v>
+        <v>25129079</v>
       </c>
       <c r="B14" t="str">
         <f>alunos!B13</f>
@@ -2816,6 +3365,12 @@
         <v>37</v>
       </c>
       <c r="AE14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG14" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS14" s="2"/>
@@ -2894,10 +3449,10 @@
       <c r="DP14" s="5"/>
       <c r="DQ14" s="5"/>
     </row>
-    <row r="15" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
-        <v>0</v>
+        <v>25129208</v>
       </c>
       <c r="B15" t="str">
         <f>alunos!B14</f>
@@ -2988,6 +3543,12 @@
         <v>36</v>
       </c>
       <c r="AE15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF15" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG15" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS15" s="2"/>
@@ -3066,10 +3627,10 @@
       <c r="DP15" s="5"/>
       <c r="DQ15" s="5"/>
     </row>
-    <row r="16" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
-        <v>0</v>
+        <v>25129025</v>
       </c>
       <c r="B16" t="str">
         <f>alunos!B15</f>
@@ -3160,6 +3721,12 @@
         <v>36</v>
       </c>
       <c r="AE16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG16" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS16" s="2"/>
@@ -3238,10 +3805,10 @@
       <c r="DP16" s="5"/>
       <c r="DQ16" s="5"/>
     </row>
-    <row r="17" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
-        <v>0</v>
+        <v>25129121</v>
       </c>
       <c r="B17" t="str">
         <f>alunos!B16</f>
@@ -3332,6 +3899,12 @@
         <v>36</v>
       </c>
       <c r="AE17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG17" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS17" s="2"/>
@@ -3410,10 +3983,10 @@
       <c r="DP17" s="5"/>
       <c r="DQ17" s="5"/>
     </row>
-    <row r="18" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
-        <v>0</v>
+        <v>25129073</v>
       </c>
       <c r="B18" t="str">
         <f>alunos!B17</f>
@@ -3504,6 +4077,12 @@
         <v>36</v>
       </c>
       <c r="AE18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG18" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS18" s="2"/>
@@ -3582,10 +4161,10 @@
       <c r="DP18" s="5"/>
       <c r="DQ18" s="5"/>
     </row>
-    <row r="19" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
-        <v>0</v>
+        <v>25129125</v>
       </c>
       <c r="B19" t="str">
         <f>alunos!B18</f>
@@ -3676,6 +4255,12 @@
         <v>36</v>
       </c>
       <c r="AE19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG19" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS19" s="2"/>
@@ -3754,10 +4339,10 @@
       <c r="DP19" s="5"/>
       <c r="DQ19" s="5"/>
     </row>
-    <row r="20" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
-        <v>0</v>
+        <v>25129027</v>
       </c>
       <c r="B20" t="str">
         <f>alunos!B19</f>
@@ -3848,6 +4433,12 @@
         <v>36</v>
       </c>
       <c r="AE20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF20" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG20" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS20" s="2"/>
@@ -3926,10 +4517,10 @@
       <c r="DP20" s="5"/>
       <c r="DQ20" s="5"/>
     </row>
-    <row r="21" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
-        <v>0</v>
+        <v>25129210</v>
       </c>
       <c r="B21" t="str">
         <f>alunos!B20</f>
@@ -4020,6 +4611,12 @@
         <v>36</v>
       </c>
       <c r="AE21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF21" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG21" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS21" s="2"/>
@@ -4098,10 +4695,10 @@
       <c r="DP21" s="5"/>
       <c r="DQ21" s="5"/>
     </row>
-    <row r="22" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
-        <v>0</v>
+        <v>25129029</v>
       </c>
       <c r="B22" t="str">
         <f>alunos!B21</f>
@@ -4192,6 +4789,12 @@
         <v>36</v>
       </c>
       <c r="AE22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF22" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG22" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS22" s="2"/>
@@ -4270,10 +4873,10 @@
       <c r="DP22" s="5"/>
       <c r="DQ22" s="5"/>
     </row>
-    <row r="23" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
-        <v>0</v>
+        <v>25129127</v>
       </c>
       <c r="B23" t="str">
         <f>alunos!B22</f>
@@ -4365,6 +4968,12 @@
       </c>
       <c r="AE23" t="s">
         <v>37</v>
+      </c>
+      <c r="AF23" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG23" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
@@ -4442,10 +5051,10 @@
       <c r="DP23" s="5"/>
       <c r="DQ23" s="5"/>
     </row>
-    <row r="24" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
-        <v>0</v>
+        <v>25129235</v>
       </c>
       <c r="B24" t="str">
         <f>alunos!B23</f>
@@ -4536,6 +5145,12 @@
         <v>36</v>
       </c>
       <c r="AE24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG24" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS24" s="2"/>
@@ -4614,10 +5229,10 @@
       <c r="DP24" s="5"/>
       <c r="DQ24" s="5"/>
     </row>
-    <row r="25" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
-        <v>0</v>
+        <v>25129031</v>
       </c>
       <c r="B25" t="str">
         <f>alunos!B24</f>
@@ -4708,6 +5323,12 @@
         <v>36</v>
       </c>
       <c r="AE25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG25" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS25" s="2"/>
@@ -4786,10 +5407,10 @@
       <c r="DP25" s="5"/>
       <c r="DQ25" s="5"/>
     </row>
-    <row r="26" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
-        <v>0</v>
+        <v>25129033</v>
       </c>
       <c r="B26" t="str">
         <f>alunos!B25</f>
@@ -4880,6 +5501,12 @@
         <v>36</v>
       </c>
       <c r="AE26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF26" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG26" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS26" s="2"/>
@@ -4958,10 +5585,10 @@
       <c r="DP26" s="5"/>
       <c r="DQ26" s="5"/>
     </row>
-    <row r="27" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
-        <v>0</v>
+        <v>25129162</v>
       </c>
       <c r="B27" t="str">
         <f>alunos!B26</f>
@@ -5052,6 +5679,12 @@
         <v>36</v>
       </c>
       <c r="AE27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF27" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG27" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS27" s="2"/>
@@ -5130,10 +5763,10 @@
       <c r="DP27" s="5"/>
       <c r="DQ27" s="5"/>
     </row>
-    <row r="28" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
-        <v>0</v>
+        <v>25129035</v>
       </c>
       <c r="B28" t="str">
         <f>alunos!B27</f>
@@ -5224,6 +5857,12 @@
         <v>36</v>
       </c>
       <c r="AE28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG28" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS28" s="2"/>
@@ -5302,10 +5941,10 @@
       <c r="DP28" s="5"/>
       <c r="DQ28" s="5"/>
     </row>
-    <row r="29" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
-        <v>0</v>
+        <v>25129039</v>
       </c>
       <c r="B29" t="str">
         <f>alunos!B28</f>
@@ -5396,6 +6035,12 @@
         <v>36</v>
       </c>
       <c r="AE29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF29" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG29" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS29" s="2"/>
@@ -5474,10 +6119,10 @@
       <c r="DP29" s="5"/>
       <c r="DQ29" s="5"/>
     </row>
-    <row r="30" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
-        <v>0</v>
+        <v>25129041</v>
       </c>
       <c r="B30" t="str">
         <f>alunos!B29</f>
@@ -5568,6 +6213,12 @@
         <v>36</v>
       </c>
       <c r="AE30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF30" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG30" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS30" s="2"/>
@@ -5646,10 +6297,10 @@
       <c r="DP30" s="5"/>
       <c r="DQ30" s="5"/>
     </row>
-    <row r="31" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
-        <v>0</v>
+        <v>25129043</v>
       </c>
       <c r="B31" t="str">
         <f>alunos!B30</f>
@@ -5741,6 +6392,12 @@
       </c>
       <c r="AE31" t="s">
         <v>37</v>
+      </c>
+      <c r="AF31" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG31" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
@@ -5818,10 +6475,10 @@
       <c r="DP31" s="5"/>
       <c r="DQ31" s="5"/>
     </row>
-    <row r="32" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
-        <v>0</v>
+        <v>25129189</v>
       </c>
       <c r="B32" t="str">
         <f>alunos!B31</f>
@@ -5912,6 +6569,12 @@
         <v>36</v>
       </c>
       <c r="AE32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF32" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG32" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS32" s="2"/>
@@ -5990,10 +6653,10 @@
       <c r="DP32" s="5"/>
       <c r="DQ32" s="5"/>
     </row>
-    <row r="33" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
-        <v>0</v>
+        <v>25129069</v>
       </c>
       <c r="B33" t="str">
         <f>alunos!B32</f>
@@ -6084,6 +6747,12 @@
         <v>36</v>
       </c>
       <c r="AE33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF33" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG33" s="8" t="s">
         <v>36</v>
       </c>
       <c r="AS33" s="2"/>
@@ -6167,7 +6836,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 AD4:AX10 BC4:BH10 V4:AC33 BI4:DE33 AD11:AY22 BA11:BH22 AD23:BH33">
+  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 BC4:BH10 BI4:DE33 BA11:BH22 AH23:BH33 AH11:AY22 AH4:AX10 V4:AG33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6180,15 +6849,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6196,157 +6865,250 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>25129175</v>
+      </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>25129085</v>
+      </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>25129021</v>
+      </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>25129019</v>
+      </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>25129023</v>
+      </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>25129105</v>
+      </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>25129083</v>
+      </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>25129047</v>
+      </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>25129101</v>
+      </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>25129081</v>
+      </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>25129160</v>
+      </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>25129079</v>
+      </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>25129208</v>
+      </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>25129025</v>
+      </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>25129121</v>
+      </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>25129073</v>
+      </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>25129125</v>
+      </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>25129027</v>
+      </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>25129210</v>
+      </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>25129029</v>
+      </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>25129127</v>
+      </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>25129235</v>
+      </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>25129031</v>
+      </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>25129033</v>
+      </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25129162</v>
+      </c>
       <c r="B26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>25129035</v>
+      </c>
       <c r="B27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>25129039</v>
+      </c>
       <c r="B28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>25129041</v>
+      </c>
       <c r="B29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>25129043</v>
+      </c>
       <c r="B30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>25129189</v>
+      </c>
       <c r="B31" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>25129069</v>
+      </c>
       <c r="B32" t="s">
         <v>33</v>
       </c>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC49F3D-C031-4355-86F7-D1D4CAED1040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72676F3-982D-476C-AEB0-71AF8D442AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="41">
   <si>
     <t>Aluno</t>
   </si>
@@ -155,9 +155,6 @@
   </si>
   <si>
     <t>aniver</t>
-  </si>
-  <si>
-    <t>SEG</t>
   </si>
   <si>
     <t>feriado</t>
@@ -664,7 +661,7 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -673,7 +670,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1008,20 +1004,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DQ33"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="48" width="7.6640625" customWidth="1"/>
-    <col min="49" max="49" width="7.6640625" style="5" customWidth="1"/>
-    <col min="50" max="104" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="48" width="7.7109375" customWidth="1"/>
+    <col min="49" max="49" width="7.7109375" style="5" customWidth="1"/>
+    <col min="50" max="104" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:121" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
@@ -1095,25 +1091,29 @@
         <v>35</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AE1" s="1" t="s">
         <v>35</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
+      <c r="AH1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="AJ1" s="1"/>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
@@ -1169,7 +1169,7 @@
       <c r="CJ1" s="4"/>
       <c r="CK1" s="4"/>
     </row>
-    <row r="2" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1269,6 +1269,10 @@
       <c r="AG2" s="1">
         <v>46157</v>
       </c>
+      <c r="AH2" s="1">
+        <v>46162</v>
+      </c>
+      <c r="AI2" s="1"/>
       <c r="AS2" s="2"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
@@ -1313,7 +1317,7 @@
       <c r="CJ2" s="5"/>
       <c r="CK2" s="5"/>
     </row>
-    <row r="3" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25129175</v>
@@ -1401,7 +1405,7 @@
         <v>36</v>
       </c>
       <c r="AC3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD3" t="s">
         <v>36</v>
@@ -1413,6 +1417,9 @@
         <v>36</v>
       </c>
       <c r="AG3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -1491,7 +1498,7 @@
       <c r="DP3" s="5"/>
       <c r="DQ3" s="5"/>
     </row>
-    <row r="4" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129085</v>
@@ -1579,7 +1586,7 @@
         <v>36</v>
       </c>
       <c r="AC4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD4" t="s">
         <v>36</v>
@@ -1587,10 +1594,13 @@
       <c r="AE4" t="s">
         <v>36</v>
       </c>
-      <c r="AF4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG4" s="8" t="s">
+      <c r="AF4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH4" t="s">
         <v>36</v>
       </c>
       <c r="AS4" s="2"/>
@@ -1669,7 +1679,7 @@
       <c r="DP4" s="5"/>
       <c r="DQ4" s="5"/>
     </row>
-    <row r="5" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129021</v>
@@ -1757,7 +1767,7 @@
         <v>36</v>
       </c>
       <c r="AC5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD5" t="s">
         <v>36</v>
@@ -1765,10 +1775,13 @@
       <c r="AE5" t="s">
         <v>37</v>
       </c>
-      <c r="AF5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG5" s="8" t="s">
+      <c r="AF5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH5" t="s">
         <v>36</v>
       </c>
       <c r="AS5" s="2"/>
@@ -1847,7 +1860,7 @@
       <c r="DP5" s="5"/>
       <c r="DQ5" s="5"/>
     </row>
-    <row r="6" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129019</v>
@@ -1935,7 +1948,7 @@
         <v>36</v>
       </c>
       <c r="AC6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD6" t="s">
         <v>36</v>
@@ -1943,10 +1956,13 @@
       <c r="AE6" t="s">
         <v>36</v>
       </c>
-      <c r="AF6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG6" s="8" t="s">
+      <c r="AF6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH6" t="s">
         <v>36</v>
       </c>
       <c r="AS6" s="2"/>
@@ -2025,7 +2041,7 @@
       <c r="DP6" s="5"/>
       <c r="DQ6" s="5"/>
     </row>
-    <row r="7" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129023</v>
@@ -2113,7 +2129,7 @@
         <v>36</v>
       </c>
       <c r="AC7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD7" t="s">
         <v>36</v>
@@ -2121,10 +2137,13 @@
       <c r="AE7" t="s">
         <v>36</v>
       </c>
-      <c r="AF7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG7" s="8" t="s">
+      <c r="AF7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH7" t="s">
         <v>36</v>
       </c>
       <c r="AS7" s="2"/>
@@ -2203,7 +2222,7 @@
       <c r="DP7" s="5"/>
       <c r="DQ7" s="5"/>
     </row>
-    <row r="8" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129105</v>
@@ -2291,7 +2310,7 @@
         <v>36</v>
       </c>
       <c r="AC8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD8" t="s">
         <v>36</v>
@@ -2299,10 +2318,13 @@
       <c r="AE8" t="s">
         <v>36</v>
       </c>
-      <c r="AF8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG8" s="8" t="s">
+      <c r="AF8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH8" t="s">
         <v>36</v>
       </c>
       <c r="AS8" s="2"/>
@@ -2381,7 +2403,7 @@
       <c r="DP8" s="5"/>
       <c r="DQ8" s="5"/>
     </row>
-    <row r="9" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129083</v>
@@ -2469,7 +2491,7 @@
         <v>36</v>
       </c>
       <c r="AC9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD9" t="s">
         <v>36</v>
@@ -2477,10 +2499,13 @@
       <c r="AE9" t="s">
         <v>36</v>
       </c>
-      <c r="AF9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG9" s="8" t="s">
+      <c r="AF9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH9" t="s">
         <v>36</v>
       </c>
       <c r="AS9" s="2"/>
@@ -2559,7 +2584,7 @@
       <c r="DP9" s="5"/>
       <c r="DQ9" s="5"/>
     </row>
-    <row r="10" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129047</v>
@@ -2647,7 +2672,7 @@
         <v>36</v>
       </c>
       <c r="AC10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD10" t="s">
         <v>36</v>
@@ -2655,10 +2680,13 @@
       <c r="AE10" t="s">
         <v>36</v>
       </c>
-      <c r="AF10" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG10" s="8" t="s">
+      <c r="AF10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH10" t="s">
         <v>36</v>
       </c>
       <c r="AS10" s="2"/>
@@ -2737,7 +2765,7 @@
       <c r="DP10" s="5"/>
       <c r="DQ10" s="5"/>
     </row>
-    <row r="11" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129101</v>
@@ -2825,7 +2853,7 @@
         <v>36</v>
       </c>
       <c r="AC11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD11" t="s">
         <v>36</v>
@@ -2833,10 +2861,13 @@
       <c r="AE11" t="s">
         <v>37</v>
       </c>
-      <c r="AF11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG11" s="8" t="s">
+      <c r="AF11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH11" t="s">
         <v>36</v>
       </c>
       <c r="AS11" s="2"/>
@@ -2915,7 +2946,7 @@
       <c r="DP11" s="5"/>
       <c r="DQ11" s="5"/>
     </row>
-    <row r="12" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129081</v>
@@ -3003,7 +3034,7 @@
         <v>36</v>
       </c>
       <c r="AC12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD12" t="s">
         <v>36</v>
@@ -3011,10 +3042,13 @@
       <c r="AE12" t="s">
         <v>36</v>
       </c>
-      <c r="AF12" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG12" s="8" t="s">
+      <c r="AF12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH12" t="s">
         <v>36</v>
       </c>
       <c r="AS12" s="2"/>
@@ -3093,7 +3127,7 @@
       <c r="DP12" s="5"/>
       <c r="DQ12" s="5"/>
     </row>
-    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129160</v>
@@ -3181,7 +3215,7 @@
         <v>36</v>
       </c>
       <c r="AC13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD13" t="s">
         <v>36</v>
@@ -3189,10 +3223,13 @@
       <c r="AE13" t="s">
         <v>36</v>
       </c>
-      <c r="AF13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG13" s="8" t="s">
+      <c r="AF13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH13" t="s">
         <v>36</v>
       </c>
       <c r="AS13" s="2"/>
@@ -3271,7 +3308,7 @@
       <c r="DP13" s="5"/>
       <c r="DQ13" s="5"/>
     </row>
-    <row r="14" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129079</v>
@@ -3359,7 +3396,7 @@
         <v>36</v>
       </c>
       <c r="AC14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD14" t="s">
         <v>37</v>
@@ -3367,10 +3404,13 @@
       <c r="AE14" t="s">
         <v>36</v>
       </c>
-      <c r="AF14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG14" s="8" t="s">
+      <c r="AF14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH14" t="s">
         <v>36</v>
       </c>
       <c r="AS14" s="2"/>
@@ -3449,7 +3489,7 @@
       <c r="DP14" s="5"/>
       <c r="DQ14" s="5"/>
     </row>
-    <row r="15" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129208</v>
@@ -3537,7 +3577,7 @@
         <v>36</v>
       </c>
       <c r="AC15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD15" t="s">
         <v>36</v>
@@ -3545,11 +3585,14 @@
       <c r="AE15" t="s">
         <v>36</v>
       </c>
-      <c r="AF15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG15" s="8" t="s">
-        <v>36</v>
+      <c r="AF15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>38</v>
       </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
@@ -3627,7 +3670,7 @@
       <c r="DP15" s="5"/>
       <c r="DQ15" s="5"/>
     </row>
-    <row r="16" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129025</v>
@@ -3715,7 +3758,7 @@
         <v>36</v>
       </c>
       <c r="AC16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD16" t="s">
         <v>36</v>
@@ -3723,10 +3766,13 @@
       <c r="AE16" t="s">
         <v>36</v>
       </c>
-      <c r="AF16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG16" s="8" t="s">
+      <c r="AF16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH16" t="s">
         <v>36</v>
       </c>
       <c r="AS16" s="2"/>
@@ -3805,7 +3851,7 @@
       <c r="DP16" s="5"/>
       <c r="DQ16" s="5"/>
     </row>
-    <row r="17" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129121</v>
@@ -3893,7 +3939,7 @@
         <v>36</v>
       </c>
       <c r="AC17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD17" t="s">
         <v>36</v>
@@ -3901,10 +3947,13 @@
       <c r="AE17" t="s">
         <v>36</v>
       </c>
-      <c r="AF17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG17" s="8" t="s">
+      <c r="AF17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH17" t="s">
         <v>36</v>
       </c>
       <c r="AS17" s="2"/>
@@ -3983,7 +4032,7 @@
       <c r="DP17" s="5"/>
       <c r="DQ17" s="5"/>
     </row>
-    <row r="18" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129073</v>
@@ -4071,7 +4120,7 @@
         <v>36</v>
       </c>
       <c r="AC18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD18" t="s">
         <v>36</v>
@@ -4079,10 +4128,13 @@
       <c r="AE18" t="s">
         <v>36</v>
       </c>
-      <c r="AF18" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG18" s="8" t="s">
+      <c r="AF18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH18" t="s">
         <v>36</v>
       </c>
       <c r="AS18" s="2"/>
@@ -4161,7 +4213,7 @@
       <c r="DP18" s="5"/>
       <c r="DQ18" s="5"/>
     </row>
-    <row r="19" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129125</v>
@@ -4249,7 +4301,7 @@
         <v>36</v>
       </c>
       <c r="AC19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD19" t="s">
         <v>36</v>
@@ -4257,10 +4309,13 @@
       <c r="AE19" t="s">
         <v>36</v>
       </c>
-      <c r="AF19" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG19" s="8" t="s">
+      <c r="AF19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH19" t="s">
         <v>36</v>
       </c>
       <c r="AS19" s="2"/>
@@ -4339,7 +4394,7 @@
       <c r="DP19" s="5"/>
       <c r="DQ19" s="5"/>
     </row>
-    <row r="20" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25129027</v>
@@ -4427,7 +4482,7 @@
         <v>36</v>
       </c>
       <c r="AC20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD20" t="s">
         <v>36</v>
@@ -4435,10 +4490,13 @@
       <c r="AE20" t="s">
         <v>36</v>
       </c>
-      <c r="AF20" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG20" s="8" t="s">
+      <c r="AF20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH20" t="s">
         <v>36</v>
       </c>
       <c r="AS20" s="2"/>
@@ -4517,7 +4575,7 @@
       <c r="DP20" s="5"/>
       <c r="DQ20" s="5"/>
     </row>
-    <row r="21" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129210</v>
@@ -4605,7 +4663,7 @@
         <v>36</v>
       </c>
       <c r="AC21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD21" t="s">
         <v>36</v>
@@ -4613,10 +4671,13 @@
       <c r="AE21" t="s">
         <v>36</v>
       </c>
-      <c r="AF21" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG21" s="8" t="s">
+      <c r="AF21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH21" t="s">
         <v>36</v>
       </c>
       <c r="AS21" s="2"/>
@@ -4695,7 +4756,7 @@
       <c r="DP21" s="5"/>
       <c r="DQ21" s="5"/>
     </row>
-    <row r="22" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129029</v>
@@ -4783,7 +4844,7 @@
         <v>36</v>
       </c>
       <c r="AC22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD22" t="s">
         <v>36</v>
@@ -4791,10 +4852,13 @@
       <c r="AE22" t="s">
         <v>36</v>
       </c>
-      <c r="AF22" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG22" s="8" t="s">
+      <c r="AF22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH22" t="s">
         <v>36</v>
       </c>
       <c r="AS22" s="2"/>
@@ -4873,7 +4937,7 @@
       <c r="DP22" s="5"/>
       <c r="DQ22" s="5"/>
     </row>
-    <row r="23" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25129127</v>
@@ -4961,7 +5025,7 @@
         <v>36</v>
       </c>
       <c r="AC23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD23" t="s">
         <v>36</v>
@@ -4969,10 +5033,13 @@
       <c r="AE23" t="s">
         <v>37</v>
       </c>
-      <c r="AF23" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG23" s="8" t="s">
+      <c r="AF23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH23" t="s">
         <v>36</v>
       </c>
       <c r="AS23" s="2"/>
@@ -5051,7 +5118,7 @@
       <c r="DP23" s="5"/>
       <c r="DQ23" s="5"/>
     </row>
-    <row r="24" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129235</v>
@@ -5139,7 +5206,7 @@
         <v>36</v>
       </c>
       <c r="AC24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD24" t="s">
         <v>36</v>
@@ -5147,10 +5214,13 @@
       <c r="AE24" t="s">
         <v>36</v>
       </c>
-      <c r="AF24" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG24" s="8" t="s">
+      <c r="AF24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH24" t="s">
         <v>36</v>
       </c>
       <c r="AS24" s="2"/>
@@ -5229,7 +5299,7 @@
       <c r="DP24" s="5"/>
       <c r="DQ24" s="5"/>
     </row>
-    <row r="25" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129031</v>
@@ -5317,7 +5387,7 @@
         <v>36</v>
       </c>
       <c r="AC25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD25" t="s">
         <v>36</v>
@@ -5325,10 +5395,13 @@
       <c r="AE25" t="s">
         <v>36</v>
       </c>
-      <c r="AF25" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG25" s="8" t="s">
+      <c r="AF25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH25" t="s">
         <v>36</v>
       </c>
       <c r="AS25" s="2"/>
@@ -5407,7 +5480,7 @@
       <c r="DP25" s="5"/>
       <c r="DQ25" s="5"/>
     </row>
-    <row r="26" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129033</v>
@@ -5495,7 +5568,7 @@
         <v>36</v>
       </c>
       <c r="AC26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD26" t="s">
         <v>36</v>
@@ -5503,10 +5576,13 @@
       <c r="AE26" t="s">
         <v>36</v>
       </c>
-      <c r="AF26" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG26" s="8" t="s">
+      <c r="AF26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH26" t="s">
         <v>36</v>
       </c>
       <c r="AS26" s="2"/>
@@ -5585,7 +5661,7 @@
       <c r="DP26" s="5"/>
       <c r="DQ26" s="5"/>
     </row>
-    <row r="27" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129162</v>
@@ -5673,7 +5749,7 @@
         <v>36</v>
       </c>
       <c r="AC27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD27" t="s">
         <v>36</v>
@@ -5681,10 +5757,13 @@
       <c r="AE27" t="s">
         <v>36</v>
       </c>
-      <c r="AF27" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG27" s="8" t="s">
+      <c r="AF27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH27" t="s">
         <v>36</v>
       </c>
       <c r="AS27" s="2"/>
@@ -5763,7 +5842,7 @@
       <c r="DP27" s="5"/>
       <c r="DQ27" s="5"/>
     </row>
-    <row r="28" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129035</v>
@@ -5851,7 +5930,7 @@
         <v>36</v>
       </c>
       <c r="AC28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD28" t="s">
         <v>36</v>
@@ -5859,10 +5938,13 @@
       <c r="AE28" t="s">
         <v>36</v>
       </c>
-      <c r="AF28" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG28" s="8" t="s">
+      <c r="AF28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH28" t="s">
         <v>36</v>
       </c>
       <c r="AS28" s="2"/>
@@ -5941,7 +6023,7 @@
       <c r="DP28" s="5"/>
       <c r="DQ28" s="5"/>
     </row>
-    <row r="29" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129039</v>
@@ -6029,7 +6111,7 @@
         <v>36</v>
       </c>
       <c r="AC29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD29" t="s">
         <v>36</v>
@@ -6037,10 +6119,13 @@
       <c r="AE29" t="s">
         <v>36</v>
       </c>
-      <c r="AF29" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG29" s="8" t="s">
+      <c r="AF29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH29" t="s">
         <v>36</v>
       </c>
       <c r="AS29" s="2"/>
@@ -6119,7 +6204,7 @@
       <c r="DP29" s="5"/>
       <c r="DQ29" s="5"/>
     </row>
-    <row r="30" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129041</v>
@@ -6207,7 +6292,7 @@
         <v>36</v>
       </c>
       <c r="AC30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD30" t="s">
         <v>36</v>
@@ -6215,10 +6300,13 @@
       <c r="AE30" t="s">
         <v>36</v>
       </c>
-      <c r="AF30" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG30" s="8" t="s">
+      <c r="AF30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH30" t="s">
         <v>36</v>
       </c>
       <c r="AS30" s="2"/>
@@ -6297,7 +6385,7 @@
       <c r="DP30" s="5"/>
       <c r="DQ30" s="5"/>
     </row>
-    <row r="31" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129043</v>
@@ -6385,7 +6473,7 @@
         <v>36</v>
       </c>
       <c r="AC31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD31" t="s">
         <v>36</v>
@@ -6393,10 +6481,13 @@
       <c r="AE31" t="s">
         <v>37</v>
       </c>
-      <c r="AF31" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG31" s="8" t="s">
+      <c r="AF31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH31" t="s">
         <v>36</v>
       </c>
       <c r="AS31" s="2"/>
@@ -6475,7 +6566,7 @@
       <c r="DP31" s="5"/>
       <c r="DQ31" s="5"/>
     </row>
-    <row r="32" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>25129189</v>
@@ -6563,7 +6654,7 @@
         <v>36</v>
       </c>
       <c r="AC32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD32" t="s">
         <v>36</v>
@@ -6571,10 +6662,13 @@
       <c r="AE32" t="s">
         <v>36</v>
       </c>
-      <c r="AF32" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG32" s="8" t="s">
+      <c r="AF32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH32" t="s">
         <v>36</v>
       </c>
       <c r="AS32" s="2"/>
@@ -6653,7 +6747,7 @@
       <c r="DP32" s="5"/>
       <c r="DQ32" s="5"/>
     </row>
-    <row r="33" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>25129069</v>
@@ -6741,7 +6835,7 @@
         <v>36</v>
       </c>
       <c r="AC33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AD33" t="s">
         <v>36</v>
@@ -6749,10 +6843,13 @@
       <c r="AE33" t="s">
         <v>36</v>
       </c>
-      <c r="AF33" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="AG33" s="8" t="s">
+      <c r="AF33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH33" t="s">
         <v>36</v>
       </c>
       <c r="AS33" s="2"/>
@@ -6836,7 +6933,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 BC4:BH10 BI4:DE33 BA11:BH22 AH23:BH33 AH11:AY22 AH4:AX10 V4:AG33">
+  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 AH4:AX10 BC4:BH10 V4:AG33 BI4:DE33 AH11:AY22 BA11:BH22 AH23:BH33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -6849,15 +6946,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -6865,7 +6962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25129175</v>
       </c>
@@ -6873,7 +6970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129085</v>
       </c>
@@ -6881,7 +6978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129021</v>
       </c>
@@ -6889,7 +6986,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129019</v>
       </c>
@@ -6897,7 +6994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129023</v>
       </c>
@@ -6905,7 +7002,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129105</v>
       </c>
@@ -6913,7 +7010,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129083</v>
       </c>
@@ -6921,7 +7018,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129047</v>
       </c>
@@ -6929,7 +7026,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129101</v>
       </c>
@@ -6937,7 +7034,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129081</v>
       </c>
@@ -6945,7 +7042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129160</v>
       </c>
@@ -6953,7 +7050,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129079</v>
       </c>
@@ -6961,7 +7058,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129208</v>
       </c>
@@ -6969,7 +7066,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129025</v>
       </c>
@@ -6977,7 +7074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129121</v>
       </c>
@@ -6985,7 +7082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129073</v>
       </c>
@@ -6993,7 +7090,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129125</v>
       </c>
@@ -7001,7 +7098,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25129027</v>
       </c>
@@ -7009,7 +7106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129210</v>
       </c>
@@ -7017,7 +7114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129029</v>
       </c>
@@ -7025,7 +7122,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25129127</v>
       </c>
@@ -7033,7 +7130,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129235</v>
       </c>
@@ -7041,7 +7138,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129031</v>
       </c>
@@ -7049,7 +7146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129033</v>
       </c>
@@ -7057,7 +7154,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129162</v>
       </c>
@@ -7065,7 +7162,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129035</v>
       </c>
@@ -7073,7 +7170,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129039</v>
       </c>
@@ -7081,7 +7178,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129041</v>
       </c>
@@ -7089,7 +7186,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129043</v>
       </c>
@@ -7097,7 +7194,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>25129189</v>
       </c>
@@ -7105,7 +7202,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>25129069</v>
       </c>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72676F3-982D-476C-AEB0-71AF8D442AF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFD0E2D-0F69-4F73-A38C-11AA4BFEF4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="41">
   <si>
     <t>Aluno</t>
   </si>
@@ -164,7 +164,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,6 +314,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -661,7 +669,7 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -670,6 +678,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1114,7 +1123,9 @@
       <c r="AI1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AJ1" s="1"/>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
@@ -1272,7 +1283,12 @@
       <c r="AH2" s="1">
         <v>46162</v>
       </c>
-      <c r="AI2" s="1"/>
+      <c r="AI2" s="1">
+        <v>46164</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>46169</v>
+      </c>
       <c r="AS2" s="2"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
@@ -1420,6 +1436,12 @@
         <v>36</v>
       </c>
       <c r="AH3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -1603,6 +1625,12 @@
       <c r="AH4" t="s">
         <v>36</v>
       </c>
+      <c r="AI4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>36</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1784,6 +1812,12 @@
       <c r="AH5" t="s">
         <v>36</v>
       </c>
+      <c r="AI5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>36</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -1965,6 +1999,12 @@
       <c r="AH6" t="s">
         <v>36</v>
       </c>
+      <c r="AI6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -2146,6 +2186,13 @@
       <c r="AH7" t="s">
         <v>36</v>
       </c>
+      <c r="AI7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL7" s="8"/>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -2327,6 +2374,12 @@
       <c r="AH8" t="s">
         <v>36</v>
       </c>
+      <c r="AI8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -2508,6 +2561,12 @@
       <c r="AH9" t="s">
         <v>36</v>
       </c>
+      <c r="AI9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -2689,6 +2748,12 @@
       <c r="AH10" t="s">
         <v>36</v>
       </c>
+      <c r="AI10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -2870,6 +2935,12 @@
       <c r="AH11" t="s">
         <v>36</v>
       </c>
+      <c r="AI11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -3051,6 +3122,12 @@
       <c r="AH12" t="s">
         <v>36</v>
       </c>
+      <c r="AI12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>36</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -3232,6 +3309,12 @@
       <c r="AH13" t="s">
         <v>36</v>
       </c>
+      <c r="AI13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -3413,6 +3496,12 @@
       <c r="AH14" t="s">
         <v>36</v>
       </c>
+      <c r="AI14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>36</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -3594,6 +3683,12 @@
       <c r="AH15" t="s">
         <v>38</v>
       </c>
+      <c r="AI15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>36</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -3775,6 +3870,12 @@
       <c r="AH16" t="s">
         <v>36</v>
       </c>
+      <c r="AI16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -3956,6 +4057,12 @@
       <c r="AH17" t="s">
         <v>36</v>
       </c>
+      <c r="AI17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -4137,6 +4244,12 @@
       <c r="AH18" t="s">
         <v>36</v>
       </c>
+      <c r="AI18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -4318,6 +4431,12 @@
       <c r="AH19" t="s">
         <v>36</v>
       </c>
+      <c r="AI19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -4499,6 +4618,12 @@
       <c r="AH20" t="s">
         <v>36</v>
       </c>
+      <c r="AI20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -4680,6 +4805,12 @@
       <c r="AH21" t="s">
         <v>36</v>
       </c>
+      <c r="AI21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -4861,6 +4992,12 @@
       <c r="AH22" t="s">
         <v>36</v>
       </c>
+      <c r="AI22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -5042,6 +5179,12 @@
       <c r="AH23" t="s">
         <v>36</v>
       </c>
+      <c r="AI23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>36</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -5223,6 +5366,12 @@
       <c r="AH24" t="s">
         <v>36</v>
       </c>
+      <c r="AI24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -5404,6 +5553,12 @@
       <c r="AH25" t="s">
         <v>36</v>
       </c>
+      <c r="AI25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>36</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -5585,6 +5740,12 @@
       <c r="AH26" t="s">
         <v>36</v>
       </c>
+      <c r="AI26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>36</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -5766,6 +5927,12 @@
       <c r="AH27" t="s">
         <v>36</v>
       </c>
+      <c r="AI27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>36</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -5947,6 +6114,12 @@
       <c r="AH28" t="s">
         <v>36</v>
       </c>
+      <c r="AI28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -6128,6 +6301,12 @@
       <c r="AH29" t="s">
         <v>36</v>
       </c>
+      <c r="AI29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -6309,6 +6488,12 @@
       <c r="AH30" t="s">
         <v>36</v>
       </c>
+      <c r="AI30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -6490,6 +6675,12 @@
       <c r="AH31" t="s">
         <v>36</v>
       </c>
+      <c r="AI31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>36</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -6671,6 +6862,12 @@
       <c r="AH32" t="s">
         <v>36</v>
       </c>
+      <c r="AI32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -6850,6 +7047,12 @@
         <v>36</v>
       </c>
       <c r="AH33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ33" t="s">
         <v>36</v>
       </c>
       <c r="AS33" s="2"/>
@@ -6933,7 +7136,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="V3:AX3 BC3:DE3 AZ3:AZ22 D3:U33 AH4:AX10 BC4:BH10 V4:AG33 BI4:DE33 AH11:AY22 BA11:BH22 AH23:BH33">
+  <conditionalFormatting sqref="BC3:DE3 AZ3:AZ22 D3:U33 BC4:BH10 BI4:DE33 BA11:BH22 V3:AX3 AK23:BH33 AK11:AY22 AK4:AX10 V4:AJ33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFD0E2D-0F69-4F73-A38C-11AA4BFEF4A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7588DD3C-BA6E-4544-B733-948560CB0DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="41">
   <si>
     <t>Aluno</t>
   </si>
@@ -164,7 +164,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,14 +314,6 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -678,7 +670,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1126,11 +1118,21 @@
       <c r="AJ1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
+      <c r="AK1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="AP1" s="1"/>
       <c r="AQ1" s="1"/>
       <c r="AR1" s="1"/>
@@ -1289,6 +1291,21 @@
       <c r="AJ2" s="1">
         <v>46169</v>
       </c>
+      <c r="AK2" s="1">
+        <v>46171</v>
+      </c>
+      <c r="AL2" s="1">
+        <v>46176</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>46178</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>46182</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>46184</v>
+      </c>
       <c r="AS2" s="2"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
@@ -1443,6 +1460,15 @@
       </c>
       <c r="AJ3" t="s">
         <v>36</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>40</v>
       </c>
       <c r="AS3" s="2"/>
       <c r="AT3" s="2"/>
@@ -1631,6 +1657,15 @@
       <c r="AJ4" t="s">
         <v>36</v>
       </c>
+      <c r="AK4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>40</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1818,6 +1853,15 @@
       <c r="AJ5" t="s">
         <v>36</v>
       </c>
+      <c r="AK5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>40</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -2005,6 +2049,15 @@
       <c r="AJ6" t="s">
         <v>36</v>
       </c>
+      <c r="AK6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>40</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -2192,7 +2245,15 @@
       <c r="AJ7" t="s">
         <v>36</v>
       </c>
-      <c r="AL7" s="8"/>
+      <c r="AK7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>40</v>
+      </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -2380,6 +2441,15 @@
       <c r="AJ8" t="s">
         <v>36</v>
       </c>
+      <c r="AK8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>40</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -2567,6 +2637,15 @@
       <c r="AJ9" t="s">
         <v>36</v>
       </c>
+      <c r="AK9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>40</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -2754,6 +2833,15 @@
       <c r="AJ10" t="s">
         <v>36</v>
       </c>
+      <c r="AK10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>40</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -2941,6 +3029,15 @@
       <c r="AJ11" t="s">
         <v>36</v>
       </c>
+      <c r="AK11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>40</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -3128,6 +3225,15 @@
       <c r="AJ12" t="s">
         <v>36</v>
       </c>
+      <c r="AK12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>40</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -3315,6 +3421,15 @@
       <c r="AJ13" t="s">
         <v>36</v>
       </c>
+      <c r="AK13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>40</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -3502,6 +3617,15 @@
       <c r="AJ14" t="s">
         <v>36</v>
       </c>
+      <c r="AK14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>40</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -3689,6 +3813,15 @@
       <c r="AJ15" t="s">
         <v>36</v>
       </c>
+      <c r="AK15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>40</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -3876,6 +4009,15 @@
       <c r="AJ16" t="s">
         <v>36</v>
       </c>
+      <c r="AK16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>40</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -4063,6 +4205,15 @@
       <c r="AJ17" t="s">
         <v>36</v>
       </c>
+      <c r="AK17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>40</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -4250,6 +4401,15 @@
       <c r="AJ18" t="s">
         <v>36</v>
       </c>
+      <c r="AK18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>40</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -4437,6 +4597,15 @@
       <c r="AJ19" t="s">
         <v>36</v>
       </c>
+      <c r="AK19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>40</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -4624,6 +4793,15 @@
       <c r="AJ20" t="s">
         <v>36</v>
       </c>
+      <c r="AK20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>40</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -4811,6 +4989,15 @@
       <c r="AJ21" t="s">
         <v>36</v>
       </c>
+      <c r="AK21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>40</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -4998,6 +5185,15 @@
       <c r="AJ22" t="s">
         <v>36</v>
       </c>
+      <c r="AK22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>40</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -5185,6 +5381,15 @@
       <c r="AJ23" t="s">
         <v>36</v>
       </c>
+      <c r="AK23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>40</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -5372,6 +5577,15 @@
       <c r="AJ24" t="s">
         <v>36</v>
       </c>
+      <c r="AK24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>40</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -5559,6 +5773,15 @@
       <c r="AJ25" t="s">
         <v>36</v>
       </c>
+      <c r="AK25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>40</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -5746,6 +5969,15 @@
       <c r="AJ26" t="s">
         <v>36</v>
       </c>
+      <c r="AK26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>40</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -5933,6 +6165,15 @@
       <c r="AJ27" t="s">
         <v>36</v>
       </c>
+      <c r="AK27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>40</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -6120,6 +6361,15 @@
       <c r="AJ28" t="s">
         <v>36</v>
       </c>
+      <c r="AK28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>40</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -6307,6 +6557,15 @@
       <c r="AJ29" t="s">
         <v>36</v>
       </c>
+      <c r="AK29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>40</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -6494,6 +6753,15 @@
       <c r="AJ30" t="s">
         <v>36</v>
       </c>
+      <c r="AK30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>40</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -6681,6 +6949,15 @@
       <c r="AJ31" t="s">
         <v>36</v>
       </c>
+      <c r="AK31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>40</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -6868,6 +7145,15 @@
       <c r="AJ32" t="s">
         <v>36</v>
       </c>
+      <c r="AK32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>40</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -7054,6 +7340,15 @@
       </c>
       <c r="AJ33" t="s">
         <v>36</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>40</v>
       </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
@@ -7136,7 +7431,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BC3:DE3 AZ3:AZ22 D3:U33 BC4:BH10 BI4:DE33 BA11:BH22 V3:AX3 AK23:BH33 AK11:AY22 AK4:AX10 V4:AJ33">
+  <conditionalFormatting sqref="BC3:DE3 AZ3:AZ22 BC4:BH10 BI4:DE33 BA11:BH22 AL3:AX3 D3:AK33 AN4:AX10 AN23:BH33 AN11:AY22 AL4:AM33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7588DD3C-BA6E-4544-B733-948560CB0DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B4FD5D-C083-49FD-8E8D-8EF7B51607F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t>feriado</t>
+  </si>
+  <si>
+    <t>2F / P</t>
   </si>
 </sst>
 </file>
@@ -661,7 +664,7 @@
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -670,7 +673,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -1301,10 +1303,10 @@
         <v>46178</v>
       </c>
       <c r="AN2" s="1">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="AO2" s="1">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="AS2" s="2"/>
       <c r="AT2" s="2"/>
@@ -1469,6 +1471,9 @@
       </c>
       <c r="AM3" t="s">
         <v>40</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>36</v>
       </c>
       <c r="AS3" s="2"/>
       <c r="AT3" s="2"/>
@@ -1666,6 +1671,9 @@
       <c r="AM4" t="s">
         <v>40</v>
       </c>
+      <c r="AN4" t="s">
+        <v>36</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1862,6 +1870,9 @@
       <c r="AM5" t="s">
         <v>40</v>
       </c>
+      <c r="AN5" t="s">
+        <v>36</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -2058,6 +2069,9 @@
       <c r="AM6" t="s">
         <v>40</v>
       </c>
+      <c r="AN6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -2248,11 +2262,14 @@
       <c r="AK7" t="s">
         <v>36</v>
       </c>
-      <c r="AL7" s="8" t="s">
+      <c r="AL7" t="s">
         <v>37</v>
       </c>
       <c r="AM7" t="s">
         <v>40</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>36</v>
       </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
@@ -2450,6 +2467,9 @@
       <c r="AM8" t="s">
         <v>40</v>
       </c>
+      <c r="AN8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -2646,6 +2666,9 @@
       <c r="AM9" t="s">
         <v>40</v>
       </c>
+      <c r="AN9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -2842,6 +2865,9 @@
       <c r="AM10" t="s">
         <v>40</v>
       </c>
+      <c r="AN10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -3038,6 +3064,9 @@
       <c r="AM11" t="s">
         <v>40</v>
       </c>
+      <c r="AN11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -3234,6 +3263,9 @@
       <c r="AM12" t="s">
         <v>40</v>
       </c>
+      <c r="AN12" t="s">
+        <v>36</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -3430,6 +3462,9 @@
       <c r="AM13" t="s">
         <v>40</v>
       </c>
+      <c r="AN13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -3626,6 +3661,9 @@
       <c r="AM14" t="s">
         <v>40</v>
       </c>
+      <c r="AN14" t="s">
+        <v>36</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -3822,6 +3860,9 @@
       <c r="AM15" t="s">
         <v>40</v>
       </c>
+      <c r="AN15" t="s">
+        <v>37</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -4018,6 +4059,9 @@
       <c r="AM16" t="s">
         <v>40</v>
       </c>
+      <c r="AN16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -4214,6 +4258,9 @@
       <c r="AM17" t="s">
         <v>40</v>
       </c>
+      <c r="AN17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -4410,6 +4457,9 @@
       <c r="AM18" t="s">
         <v>40</v>
       </c>
+      <c r="AN18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -4606,6 +4656,9 @@
       <c r="AM19" t="s">
         <v>40</v>
       </c>
+      <c r="AN19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -4802,6 +4855,9 @@
       <c r="AM20" t="s">
         <v>40</v>
       </c>
+      <c r="AN20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -4998,6 +5054,9 @@
       <c r="AM21" t="s">
         <v>40</v>
       </c>
+      <c r="AN21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -5194,6 +5253,9 @@
       <c r="AM22" t="s">
         <v>40</v>
       </c>
+      <c r="AN22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -5390,6 +5452,9 @@
       <c r="AM23" t="s">
         <v>40</v>
       </c>
+      <c r="AN23" t="s">
+        <v>36</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -5586,6 +5651,9 @@
       <c r="AM24" t="s">
         <v>40</v>
       </c>
+      <c r="AN24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -5782,6 +5850,9 @@
       <c r="AM25" t="s">
         <v>40</v>
       </c>
+      <c r="AN25" t="s">
+        <v>36</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -5978,6 +6049,9 @@
       <c r="AM26" t="s">
         <v>40</v>
       </c>
+      <c r="AN26" t="s">
+        <v>41</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -6174,6 +6248,9 @@
       <c r="AM27" t="s">
         <v>40</v>
       </c>
+      <c r="AN27" t="s">
+        <v>36</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -6370,6 +6447,9 @@
       <c r="AM28" t="s">
         <v>40</v>
       </c>
+      <c r="AN28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -6566,6 +6646,9 @@
       <c r="AM29" t="s">
         <v>40</v>
       </c>
+      <c r="AN29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -6762,6 +6845,9 @@
       <c r="AM30" t="s">
         <v>40</v>
       </c>
+      <c r="AN30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -6958,6 +7044,9 @@
       <c r="AM31" t="s">
         <v>40</v>
       </c>
+      <c r="AN31" t="s">
+        <v>36</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -7154,6 +7243,9 @@
       <c r="AM32" t="s">
         <v>40</v>
       </c>
+      <c r="AN32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -7349,6 +7441,9 @@
       </c>
       <c r="AM33" t="s">
         <v>40</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>37</v>
       </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
@@ -7431,7 +7526,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="BC3:DE3 AZ3:AZ22 BC4:BH10 BI4:DE33 BA11:BH22 AL3:AX3 D3:AK33 AN4:AX10 AN23:BH33 AN11:AY22 AL4:AM33">
+  <conditionalFormatting sqref="AL3:AX3 BC3:DE3 AZ3:AZ22 D3:AK33 AO4:AX10 BC4:BH10 AL4:AM33 BI4:DE33 AN15:AY15 BA11:BH22 AO11:AY14 AN4:AN14 AO23:BH25 AO16:AY22 AN16:AN25 AN26:BH33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B4FD5D-C083-49FD-8E8D-8EF7B51607F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B87D5DB-58E4-4FBF-95A4-4F2007607712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -1475,6 +1475,9 @@
       <c r="AN3" t="s">
         <v>36</v>
       </c>
+      <c r="AO3" t="s">
+        <v>36</v>
+      </c>
       <c r="AS3" s="2"/>
       <c r="AT3" s="2"/>
       <c r="AU3" s="2"/>
@@ -1674,6 +1677,9 @@
       <c r="AN4" t="s">
         <v>36</v>
       </c>
+      <c r="AO4" t="s">
+        <v>37</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1873,6 +1879,9 @@
       <c r="AN5" t="s">
         <v>36</v>
       </c>
+      <c r="AO5" t="s">
+        <v>36</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -2072,6 +2081,9 @@
       <c r="AN6" t="s">
         <v>36</v>
       </c>
+      <c r="AO6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -2271,6 +2283,9 @@
       <c r="AN7" t="s">
         <v>36</v>
       </c>
+      <c r="AO7" t="s">
+        <v>36</v>
+      </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -2470,6 +2485,9 @@
       <c r="AN8" t="s">
         <v>36</v>
       </c>
+      <c r="AO8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -2669,6 +2687,9 @@
       <c r="AN9" t="s">
         <v>36</v>
       </c>
+      <c r="AO9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -2868,6 +2889,9 @@
       <c r="AN10" t="s">
         <v>36</v>
       </c>
+      <c r="AO10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -3067,6 +3091,9 @@
       <c r="AN11" t="s">
         <v>36</v>
       </c>
+      <c r="AO11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -3266,6 +3293,9 @@
       <c r="AN12" t="s">
         <v>36</v>
       </c>
+      <c r="AO12" t="s">
+        <v>36</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -3465,6 +3495,9 @@
       <c r="AN13" t="s">
         <v>36</v>
       </c>
+      <c r="AO13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -3664,6 +3697,9 @@
       <c r="AN14" t="s">
         <v>36</v>
       </c>
+      <c r="AO14" t="s">
+        <v>37</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -3863,6 +3899,9 @@
       <c r="AN15" t="s">
         <v>37</v>
       </c>
+      <c r="AO15" t="s">
+        <v>36</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -4062,6 +4101,9 @@
       <c r="AN16" t="s">
         <v>36</v>
       </c>
+      <c r="AO16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -4261,6 +4303,9 @@
       <c r="AN17" t="s">
         <v>36</v>
       </c>
+      <c r="AO17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -4460,6 +4505,9 @@
       <c r="AN18" t="s">
         <v>36</v>
       </c>
+      <c r="AO18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -4659,6 +4707,9 @@
       <c r="AN19" t="s">
         <v>36</v>
       </c>
+      <c r="AO19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -4858,6 +4909,9 @@
       <c r="AN20" t="s">
         <v>36</v>
       </c>
+      <c r="AO20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -5057,6 +5111,9 @@
       <c r="AN21" t="s">
         <v>36</v>
       </c>
+      <c r="AO21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -5256,6 +5313,9 @@
       <c r="AN22" t="s">
         <v>36</v>
       </c>
+      <c r="AO22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -5455,6 +5515,9 @@
       <c r="AN23" t="s">
         <v>36</v>
       </c>
+      <c r="AO23" t="s">
+        <v>36</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -5654,6 +5717,9 @@
       <c r="AN24" t="s">
         <v>36</v>
       </c>
+      <c r="AO24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -5853,6 +5919,9 @@
       <c r="AN25" t="s">
         <v>36</v>
       </c>
+      <c r="AO25" t="s">
+        <v>36</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -6052,6 +6121,9 @@
       <c r="AN26" t="s">
         <v>41</v>
       </c>
+      <c r="AO26" t="s">
+        <v>36</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -6251,6 +6323,9 @@
       <c r="AN27" t="s">
         <v>36</v>
       </c>
+      <c r="AO27" t="s">
+        <v>36</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -6450,6 +6525,9 @@
       <c r="AN28" t="s">
         <v>36</v>
       </c>
+      <c r="AO28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -6649,6 +6727,9 @@
       <c r="AN29" t="s">
         <v>36</v>
       </c>
+      <c r="AO29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -6848,6 +6929,9 @@
       <c r="AN30" t="s">
         <v>36</v>
       </c>
+      <c r="AO30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -7047,6 +7131,9 @@
       <c r="AN31" t="s">
         <v>36</v>
       </c>
+      <c r="AO31" t="s">
+        <v>36</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -7246,6 +7333,9 @@
       <c r="AN32" t="s">
         <v>36</v>
       </c>
+      <c r="AO32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -7444,6 +7534,9 @@
       </c>
       <c r="AN33" t="s">
         <v>37</v>
+      </c>
+      <c r="AO33" t="s">
+        <v>36</v>
       </c>
       <c r="AS33" s="2"/>
       <c r="AT33" s="2"/>
@@ -7526,7 +7619,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="AL3:AX3 BC3:DE3 AZ3:AZ22 D3:AK33 AO4:AX10 BC4:BH10 AL4:AM33 BI4:DE33 AN15:AY15 BA11:BH22 AO11:AY14 AN4:AN14 AO23:BH25 AO16:AY22 AN16:AN25 AN26:BH33">
+  <conditionalFormatting sqref="AL3:AX3 BC3:DE3 AZ3:AZ22 D3:AK33 AO4:AX4 BC4:BH10 BI4:DE33 AO14:AY14 BA11:BH22 AL4:AN33 AP11:AY13 AP5:AX10 AO5:AO13 AP23:BH33 AP15:AY22 AO15:AO33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B87D5DB-58E4-4FBF-95A4-4F2007607712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF3A3D3-9DC1-4159-A8BC-CBBA093CA97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="42">
   <si>
     <t>Aluno</t>
   </si>
@@ -1015,7 +1015,11 @@
     <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="22" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="48" width="7.7109375" customWidth="1"/>
+    <col min="29" max="39" width="7.7109375" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.7109375" customWidth="1"/>
+    <col min="42" max="43" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="48" width="7.7109375" customWidth="1"/>
     <col min="49" max="49" width="7.7109375" style="5" customWidth="1"/>
     <col min="50" max="104" width="7.7109375" customWidth="1"/>
   </cols>
@@ -1135,8 +1139,12 @@
       <c r="AO1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
+      <c r="AP1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="AR1" s="1"/>
       <c r="AS1" s="3"/>
       <c r="AT1" s="3"/>
@@ -1308,6 +1316,12 @@
       <c r="AO2" s="1">
         <v>46185</v>
       </c>
+      <c r="AP2" s="1">
+        <v>46190</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>46191</v>
+      </c>
       <c r="AS2" s="2"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="2"/>
@@ -1476,6 +1490,9 @@
         <v>36</v>
       </c>
       <c r="AO3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP3" t="s">
         <v>36</v>
       </c>
       <c r="AS3" s="2"/>
@@ -1680,6 +1697,9 @@
       <c r="AO4" t="s">
         <v>37</v>
       </c>
+      <c r="AP4" t="s">
+        <v>36</v>
+      </c>
       <c r="AS4" s="2"/>
       <c r="AT4" s="2"/>
       <c r="AU4" s="2"/>
@@ -1882,6 +1902,9 @@
       <c r="AO5" t="s">
         <v>36</v>
       </c>
+      <c r="AP5" t="s">
+        <v>36</v>
+      </c>
       <c r="AS5" s="2"/>
       <c r="AT5" s="2"/>
       <c r="AU5" s="2"/>
@@ -2084,6 +2107,9 @@
       <c r="AO6" t="s">
         <v>36</v>
       </c>
+      <c r="AP6" t="s">
+        <v>36</v>
+      </c>
       <c r="AS6" s="2"/>
       <c r="AT6" s="2"/>
       <c r="AU6" s="2"/>
@@ -2286,6 +2312,9 @@
       <c r="AO7" t="s">
         <v>36</v>
       </c>
+      <c r="AP7" t="s">
+        <v>36</v>
+      </c>
       <c r="AS7" s="2"/>
       <c r="AT7" s="2"/>
       <c r="AU7" s="2"/>
@@ -2488,6 +2517,9 @@
       <c r="AO8" t="s">
         <v>36</v>
       </c>
+      <c r="AP8" t="s">
+        <v>36</v>
+      </c>
       <c r="AS8" s="2"/>
       <c r="AT8" s="2"/>
       <c r="AU8" s="2"/>
@@ -2690,6 +2722,9 @@
       <c r="AO9" t="s">
         <v>36</v>
       </c>
+      <c r="AP9" t="s">
+        <v>36</v>
+      </c>
       <c r="AS9" s="2"/>
       <c r="AT9" s="2"/>
       <c r="AU9" s="2"/>
@@ -2892,6 +2927,9 @@
       <c r="AO10" t="s">
         <v>36</v>
       </c>
+      <c r="AP10" t="s">
+        <v>36</v>
+      </c>
       <c r="AS10" s="2"/>
       <c r="AT10" s="2"/>
       <c r="AU10" s="2"/>
@@ -3094,6 +3132,9 @@
       <c r="AO11" t="s">
         <v>36</v>
       </c>
+      <c r="AP11" t="s">
+        <v>36</v>
+      </c>
       <c r="AS11" s="2"/>
       <c r="AT11" s="2"/>
       <c r="AU11" s="2"/>
@@ -3296,6 +3337,9 @@
       <c r="AO12" t="s">
         <v>36</v>
       </c>
+      <c r="AP12" t="s">
+        <v>36</v>
+      </c>
       <c r="AS12" s="2"/>
       <c r="AT12" s="2"/>
       <c r="AU12" s="2"/>
@@ -3498,6 +3542,9 @@
       <c r="AO13" t="s">
         <v>36</v>
       </c>
+      <c r="AP13" t="s">
+        <v>36</v>
+      </c>
       <c r="AS13" s="2"/>
       <c r="AT13" s="2"/>
       <c r="AU13" s="2"/>
@@ -3700,6 +3747,9 @@
       <c r="AO14" t="s">
         <v>37</v>
       </c>
+      <c r="AP14" t="s">
+        <v>36</v>
+      </c>
       <c r="AS14" s="2"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
@@ -3902,6 +3952,9 @@
       <c r="AO15" t="s">
         <v>36</v>
       </c>
+      <c r="AP15" t="s">
+        <v>36</v>
+      </c>
       <c r="AS15" s="2"/>
       <c r="AT15" s="2"/>
       <c r="AU15" s="2"/>
@@ -4104,6 +4157,9 @@
       <c r="AO16" t="s">
         <v>36</v>
       </c>
+      <c r="AP16" t="s">
+        <v>36</v>
+      </c>
       <c r="AS16" s="2"/>
       <c r="AT16" s="2"/>
       <c r="AU16" s="2"/>
@@ -4306,6 +4362,9 @@
       <c r="AO17" t="s">
         <v>36</v>
       </c>
+      <c r="AP17" t="s">
+        <v>36</v>
+      </c>
       <c r="AS17" s="2"/>
       <c r="AT17" s="2"/>
       <c r="AU17" s="2"/>
@@ -4508,6 +4567,9 @@
       <c r="AO18" t="s">
         <v>36</v>
       </c>
+      <c r="AP18" t="s">
+        <v>36</v>
+      </c>
       <c r="AS18" s="2"/>
       <c r="AT18" s="2"/>
       <c r="AU18" s="2"/>
@@ -4710,6 +4772,9 @@
       <c r="AO19" t="s">
         <v>36</v>
       </c>
+      <c r="AP19" t="s">
+        <v>36</v>
+      </c>
       <c r="AS19" s="2"/>
       <c r="AT19" s="2"/>
       <c r="AU19" s="2"/>
@@ -4912,6 +4977,9 @@
       <c r="AO20" t="s">
         <v>36</v>
       </c>
+      <c r="AP20" t="s">
+        <v>36</v>
+      </c>
       <c r="AS20" s="2"/>
       <c r="AT20" s="2"/>
       <c r="AU20" s="2"/>
@@ -5114,6 +5182,9 @@
       <c r="AO21" t="s">
         <v>36</v>
       </c>
+      <c r="AP21" t="s">
+        <v>36</v>
+      </c>
       <c r="AS21" s="2"/>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
@@ -5316,6 +5387,9 @@
       <c r="AO22" t="s">
         <v>36</v>
       </c>
+      <c r="AP22" t="s">
+        <v>36</v>
+      </c>
       <c r="AS22" s="2"/>
       <c r="AT22" s="2"/>
       <c r="AU22" s="2"/>
@@ -5518,6 +5592,9 @@
       <c r="AO23" t="s">
         <v>36</v>
       </c>
+      <c r="AP23" t="s">
+        <v>37</v>
+      </c>
       <c r="AS23" s="2"/>
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
@@ -5720,6 +5797,9 @@
       <c r="AO24" t="s">
         <v>36</v>
       </c>
+      <c r="AP24" t="s">
+        <v>36</v>
+      </c>
       <c r="AS24" s="2"/>
       <c r="AT24" s="2"/>
       <c r="AU24" s="2"/>
@@ -5922,6 +6002,9 @@
       <c r="AO25" t="s">
         <v>36</v>
       </c>
+      <c r="AP25" t="s">
+        <v>37</v>
+      </c>
       <c r="AS25" s="2"/>
       <c r="AT25" s="2"/>
       <c r="AU25" s="2"/>
@@ -6124,6 +6207,9 @@
       <c r="AO26" t="s">
         <v>36</v>
       </c>
+      <c r="AP26" t="s">
+        <v>36</v>
+      </c>
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
@@ -6326,6 +6412,9 @@
       <c r="AO27" t="s">
         <v>36</v>
       </c>
+      <c r="AP27" t="s">
+        <v>37</v>
+      </c>
       <c r="AS27" s="2"/>
       <c r="AT27" s="2"/>
       <c r="AU27" s="2"/>
@@ -6528,6 +6617,9 @@
       <c r="AO28" t="s">
         <v>36</v>
       </c>
+      <c r="AP28" t="s">
+        <v>36</v>
+      </c>
       <c r="AS28" s="2"/>
       <c r="AT28" s="2"/>
       <c r="AU28" s="2"/>
@@ -6730,6 +6822,9 @@
       <c r="AO29" t="s">
         <v>36</v>
       </c>
+      <c r="AP29" t="s">
+        <v>36</v>
+      </c>
       <c r="AS29" s="2"/>
       <c r="AT29" s="2"/>
       <c r="AU29" s="2"/>
@@ -6932,6 +7027,9 @@
       <c r="AO30" t="s">
         <v>36</v>
       </c>
+      <c r="AP30" t="s">
+        <v>36</v>
+      </c>
       <c r="AS30" s="2"/>
       <c r="AT30" s="2"/>
       <c r="AU30" s="2"/>
@@ -7134,6 +7232,9 @@
       <c r="AO31" t="s">
         <v>36</v>
       </c>
+      <c r="AP31" t="s">
+        <v>37</v>
+      </c>
       <c r="AS31" s="2"/>
       <c r="AT31" s="2"/>
       <c r="AU31" s="2"/>
@@ -7336,6 +7437,9 @@
       <c r="AO32" t="s">
         <v>36</v>
       </c>
+      <c r="AP32" t="s">
+        <v>36</v>
+      </c>
       <c r="AS32" s="2"/>
       <c r="AT32" s="2"/>
       <c r="AU32" s="2"/>
@@ -7536,6 +7640,9 @@
         <v>37</v>
       </c>
       <c r="AO33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP33" t="s">
         <v>36</v>
       </c>
       <c r="AS33" s="2"/>
@@ -7619,7 +7726,7 @@
     <sortCondition ref="B3:B33"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="AL3:AX3 BC3:DE3 AZ3:AZ22 D3:AK33 AO4:AX4 BC4:BH10 BI4:DE33 AO14:AY14 BA11:BH22 AL4:AN33 AP11:AY13 AP5:AX10 AO5:AO13 AP23:BH33 AP15:AY22 AO15:AO33">
+  <conditionalFormatting sqref="AL3:AX3 BC3:DE3 AZ3:AZ22 D3:AK33 AO4:AX4 BC4:BH10 AL4:AN33 BI4:DE33 AP5:AX10 AO5:AO13 AP11:AY13 BA11:BH22 AO14:AY14 AP15:AY22 AO15:AO33 AP23:BH33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF3A3D3-9DC1-4159-A8BC-CBBA093CA97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70268E72-F10B-45C2-B1ED-0B608903AC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -1007,24 +1007,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DQ33"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="39" width="7.7109375" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.7109375" customWidth="1"/>
-    <col min="42" max="43" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="48" width="7.7109375" customWidth="1"/>
-    <col min="49" max="49" width="7.7109375" style="5" customWidth="1"/>
-    <col min="50" max="104" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="44" max="48" width="7.6640625" customWidth="1"/>
+    <col min="49" max="49" width="7.6640625" style="5" customWidth="1"/>
+    <col min="50" max="104" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:121" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
@@ -1192,7 +1194,7 @@
       <c r="CJ1" s="4"/>
       <c r="CK1" s="4"/>
     </row>
-    <row r="2" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1320,7 +1322,7 @@
         <v>46190</v>
       </c>
       <c r="AQ2" s="1">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="AS2" s="2"/>
       <c r="AT2" s="2"/>
@@ -1366,7 +1368,7 @@
       <c r="CJ2" s="5"/>
       <c r="CK2" s="5"/>
     </row>
-    <row r="3" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25129175</v>
@@ -1571,7 +1573,7 @@
       <c r="DP3" s="5"/>
       <c r="DQ3" s="5"/>
     </row>
-    <row r="4" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129085</v>
@@ -1776,7 +1778,7 @@
       <c r="DP4" s="5"/>
       <c r="DQ4" s="5"/>
     </row>
-    <row r="5" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129021</v>
@@ -1981,7 +1983,7 @@
       <c r="DP5" s="5"/>
       <c r="DQ5" s="5"/>
     </row>
-    <row r="6" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129019</v>
@@ -2186,7 +2188,7 @@
       <c r="DP6" s="5"/>
       <c r="DQ6" s="5"/>
     </row>
-    <row r="7" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129023</v>
@@ -2391,7 +2393,7 @@
       <c r="DP7" s="5"/>
       <c r="DQ7" s="5"/>
     </row>
-    <row r="8" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129105</v>
@@ -2596,7 +2598,7 @@
       <c r="DP8" s="5"/>
       <c r="DQ8" s="5"/>
     </row>
-    <row r="9" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129083</v>
@@ -2801,7 +2803,7 @@
       <c r="DP9" s="5"/>
       <c r="DQ9" s="5"/>
     </row>
-    <row r="10" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129047</v>
@@ -3006,7 +3008,7 @@
       <c r="DP10" s="5"/>
       <c r="DQ10" s="5"/>
     </row>
-    <row r="11" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129101</v>
@@ -3211,7 +3213,7 @@
       <c r="DP11" s="5"/>
       <c r="DQ11" s="5"/>
     </row>
-    <row r="12" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129081</v>
@@ -3416,7 +3418,7 @@
       <c r="DP12" s="5"/>
       <c r="DQ12" s="5"/>
     </row>
-    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129160</v>
@@ -3621,7 +3623,7 @@
       <c r="DP13" s="5"/>
       <c r="DQ13" s="5"/>
     </row>
-    <row r="14" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129079</v>
@@ -3826,7 +3828,7 @@
       <c r="DP14" s="5"/>
       <c r="DQ14" s="5"/>
     </row>
-    <row r="15" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129208</v>
@@ -4031,7 +4033,7 @@
       <c r="DP15" s="5"/>
       <c r="DQ15" s="5"/>
     </row>
-    <row r="16" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129025</v>
@@ -4236,7 +4238,7 @@
       <c r="DP16" s="5"/>
       <c r="DQ16" s="5"/>
     </row>
-    <row r="17" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129121</v>
@@ -4441,7 +4443,7 @@
       <c r="DP17" s="5"/>
       <c r="DQ17" s="5"/>
     </row>
-    <row r="18" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129073</v>
@@ -4646,7 +4648,7 @@
       <c r="DP18" s="5"/>
       <c r="DQ18" s="5"/>
     </row>
-    <row r="19" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129125</v>
@@ -4851,7 +4853,7 @@
       <c r="DP19" s="5"/>
       <c r="DQ19" s="5"/>
     </row>
-    <row r="20" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25129027</v>
@@ -5056,7 +5058,7 @@
       <c r="DP20" s="5"/>
       <c r="DQ20" s="5"/>
     </row>
-    <row r="21" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129210</v>
@@ -5261,7 +5263,7 @@
       <c r="DP21" s="5"/>
       <c r="DQ21" s="5"/>
     </row>
-    <row r="22" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129029</v>
@@ -5466,7 +5468,7 @@
       <c r="DP22" s="5"/>
       <c r="DQ22" s="5"/>
     </row>
-    <row r="23" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25129127</v>
@@ -5671,7 +5673,7 @@
       <c r="DP23" s="5"/>
       <c r="DQ23" s="5"/>
     </row>
-    <row r="24" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129235</v>
@@ -5876,7 +5878,7 @@
       <c r="DP24" s="5"/>
       <c r="DQ24" s="5"/>
     </row>
-    <row r="25" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129031</v>
@@ -6081,7 +6083,7 @@
       <c r="DP25" s="5"/>
       <c r="DQ25" s="5"/>
     </row>
-    <row r="26" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129033</v>
@@ -6286,7 +6288,7 @@
       <c r="DP26" s="5"/>
       <c r="DQ26" s="5"/>
     </row>
-    <row r="27" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129162</v>
@@ -6491,7 +6493,7 @@
       <c r="DP27" s="5"/>
       <c r="DQ27" s="5"/>
     </row>
-    <row r="28" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129035</v>
@@ -6696,7 +6698,7 @@
       <c r="DP28" s="5"/>
       <c r="DQ28" s="5"/>
     </row>
-    <row r="29" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129039</v>
@@ -6901,7 +6903,7 @@
       <c r="DP29" s="5"/>
       <c r="DQ29" s="5"/>
     </row>
-    <row r="30" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129041</v>
@@ -7106,7 +7108,7 @@
       <c r="DP30" s="5"/>
       <c r="DQ30" s="5"/>
     </row>
-    <row r="31" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129043</v>
@@ -7311,7 +7313,7 @@
       <c r="DP31" s="5"/>
       <c r="DQ31" s="5"/>
     </row>
-    <row r="32" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>alunos!A31</f>
         <v>25129189</v>
@@ -7516,7 +7518,7 @@
       <c r="DP32" s="5"/>
       <c r="DQ32" s="5"/>
     </row>
-    <row r="33" spans="1:121" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:121" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>alunos!A32</f>
         <v>25129069</v>
@@ -7739,15 +7741,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7755,7 +7757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>25129175</v>
       </c>
@@ -7763,7 +7765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>25129085</v>
       </c>
@@ -7771,7 +7773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>25129021</v>
       </c>
@@ -7779,7 +7781,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>25129019</v>
       </c>
@@ -7787,7 +7789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>25129023</v>
       </c>
@@ -7795,7 +7797,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>25129105</v>
       </c>
@@ -7803,7 +7805,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>25129083</v>
       </c>
@@ -7811,7 +7813,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>25129047</v>
       </c>
@@ -7819,7 +7821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>25129101</v>
       </c>
@@ -7827,7 +7829,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>25129081</v>
       </c>
@@ -7835,7 +7837,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>25129160</v>
       </c>
@@ -7843,7 +7845,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>25129079</v>
       </c>
@@ -7851,7 +7853,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>25129208</v>
       </c>
@@ -7859,7 +7861,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>25129025</v>
       </c>
@@ -7867,7 +7869,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>25129121</v>
       </c>
@@ -7875,7 +7877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>25129073</v>
       </c>
@@ -7883,7 +7885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>25129125</v>
       </c>
@@ -7891,7 +7893,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>25129027</v>
       </c>
@@ -7899,7 +7901,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>25129210</v>
       </c>
@@ -7907,7 +7909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>25129029</v>
       </c>
@@ -7915,7 +7917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>25129127</v>
       </c>
@@ -7923,7 +7925,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>25129235</v>
       </c>
@@ -7931,7 +7933,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>25129031</v>
       </c>
@@ -7939,7 +7941,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>25129033</v>
       </c>
@@ -7947,7 +7949,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25129162</v>
       </c>
@@ -7955,7 +7957,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>25129035</v>
       </c>
@@ -7963,7 +7965,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>25129039</v>
       </c>
@@ -7971,7 +7973,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>25129041</v>
       </c>
@@ -7979,7 +7981,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>25129043</v>
       </c>
@@ -7987,7 +7989,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>25129189</v>
       </c>
@@ -7995,7 +7997,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>25129069</v>
       </c>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70268E72-F10B-45C2-B1ED-0B608903AC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF5A711-86D3-43DC-B5A3-792427697A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -162,22 +162,21 @@
   <si>
     <t>2F / P</t>
   </si>
+  <si>
+    <t>FÉRIAS</t>
+  </si>
+  <si>
+    <t>férias</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -619,105 +618,99 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="43">
-    <cellStyle name="20% - Ênfase1" xfId="20" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase2" xfId="24" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase3" xfId="28" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase4" xfId="32" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase5" xfId="36" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Ênfase6" xfId="40" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase1" xfId="21" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase2" xfId="25" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase3" xfId="29" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase4" xfId="33" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase5" xfId="37" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Ênfase6" xfId="41" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase1" xfId="22" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase2" xfId="26" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase3" xfId="30" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase4" xfId="34" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase5" xfId="38" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Ênfase6" xfId="42" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Bom" xfId="7" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Cálculo" xfId="12" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Célula de Verificação" xfId="14" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Célula Vinculada" xfId="13" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Ênfase1" xfId="19" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Ênfase2" xfId="23" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Ênfase3" xfId="27" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Ênfase4" xfId="31" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Ênfase5" xfId="35" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Ênfase6" xfId="39" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Entrada" xfId="10" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Neutro" xfId="9" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="42">
+    <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Ênfase6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Ênfase6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Ênfase6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bom" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Célula Vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Ênfase1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Ênfase2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Ênfase3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Ênfase4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Ênfase5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Ênfase6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Neutro" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Nota" xfId="16" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
-    <cellStyle name="Ruim" xfId="8" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Saída" xfId="11" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Texto de Aviso" xfId="15" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="Texto Explicativo" xfId="17" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Título" xfId="2" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Título 1" xfId="3" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Título 2" xfId="4" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Título 3" xfId="5" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Título 4" xfId="6" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Nota" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Ruim" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Saída" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de Aviso" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto Explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -1007,26 +1000,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DQ33"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="44" max="48" width="7.6640625" customWidth="1"/>
-    <col min="49" max="49" width="7.6640625" style="5" customWidth="1"/>
-    <col min="50" max="104" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="37" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="43" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="48" width="7.7109375" customWidth="1"/>
+    <col min="49" max="49" width="7.7109375" style="3" customWidth="1"/>
+    <col min="50" max="104" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:121" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
@@ -1147,54 +1139,58 @@
       <c r="AQ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AR1" s="1"/>
-      <c r="AS1" s="3"/>
-      <c r="AT1" s="3"/>
-      <c r="AU1" s="3"/>
+      <c r="AR1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
       <c r="AV1" s="1"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
-      <c r="AY1" s="4"/>
-      <c r="AZ1" s="4"/>
-      <c r="BA1" s="4"/>
-      <c r="BB1" s="4"/>
-      <c r="BC1" s="4"/>
-      <c r="BD1" s="4"/>
-      <c r="BE1" s="4"/>
-      <c r="BF1" s="4"/>
-      <c r="BG1" s="4"/>
-      <c r="BH1" s="4"/>
-      <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
-      <c r="BL1" s="4"/>
-      <c r="BM1" s="4"/>
-      <c r="BN1" s="4"/>
-      <c r="BO1" s="4"/>
-      <c r="BP1" s="4"/>
-      <c r="BQ1" s="4"/>
-      <c r="BR1" s="4"/>
-      <c r="BS1" s="4"/>
-      <c r="BT1" s="4"/>
-      <c r="BU1" s="4"/>
-      <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="4"/>
-      <c r="BY1" s="4"/>
-      <c r="BZ1" s="4"/>
-      <c r="CA1" s="4"/>
-      <c r="CB1" s="4"/>
-      <c r="CC1" s="4"/>
-      <c r="CD1" s="4"/>
-      <c r="CE1" s="4"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="2"/>
+      <c r="BU1" s="2"/>
+      <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
+      <c r="BY1" s="2"/>
+      <c r="BZ1" s="2"/>
+      <c r="CA1" s="2"/>
+      <c r="CB1" s="2"/>
+      <c r="CC1" s="2"/>
+      <c r="CD1" s="2"/>
+      <c r="CE1" s="2"/>
       <c r="CF1" s="1"/>
-      <c r="CG1" s="4"/>
-      <c r="CH1" s="4"/>
-      <c r="CI1" s="4"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
+      <c r="CG1" s="2"/>
+      <c r="CH1" s="2"/>
+      <c r="CI1" s="2"/>
+      <c r="CJ1" s="2"/>
+      <c r="CK1" s="2"/>
     </row>
-    <row r="2" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1324,51 +1320,58 @@
       <c r="AQ2" s="1">
         <v>46192</v>
       </c>
-      <c r="AS2" s="2"/>
-      <c r="AT2" s="2"/>
-      <c r="AU2" s="2"/>
-      <c r="AX2" s="5"/>
-      <c r="AY2" s="5"/>
-      <c r="AZ2" s="5"/>
-      <c r="BA2" s="5"/>
-      <c r="BB2" s="5"/>
-      <c r="BC2" s="5"/>
-      <c r="BD2" s="5"/>
-      <c r="BE2" s="5"/>
-      <c r="BF2" s="5"/>
-      <c r="BG2" s="5"/>
-      <c r="BH2" s="5"/>
-      <c r="BI2" s="5"/>
-      <c r="BJ2" s="5"/>
-      <c r="BK2" s="5"/>
-      <c r="BL2" s="5"/>
-      <c r="BM2" s="5"/>
-      <c r="BN2" s="5"/>
-      <c r="BO2" s="5"/>
-      <c r="BP2" s="5"/>
-      <c r="BQ2" s="5"/>
-      <c r="BR2" s="5"/>
-      <c r="BS2" s="5"/>
-      <c r="BT2" s="5"/>
-      <c r="BU2" s="5"/>
-      <c r="BV2" s="5"/>
-      <c r="BW2" s="5"/>
-      <c r="BX2" s="5"/>
-      <c r="BY2" s="5"/>
-      <c r="BZ2" s="5"/>
-      <c r="CA2" s="5"/>
-      <c r="CB2" s="5"/>
-      <c r="CC2" s="5"/>
-      <c r="CD2" s="5"/>
-      <c r="CE2" s="5"/>
-      <c r="CF2" s="5"/>
-      <c r="CG2" s="5"/>
-      <c r="CH2" s="5"/>
-      <c r="CI2" s="5"/>
-      <c r="CJ2" s="5"/>
-      <c r="CK2" s="5"/>
+      <c r="AR2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>46227</v>
+      </c>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="3"/>
+      <c r="BU2" s="3"/>
+      <c r="BV2" s="3"/>
+      <c r="BW2" s="3"/>
+      <c r="BX2" s="3"/>
+      <c r="BY2" s="3"/>
+      <c r="BZ2" s="3"/>
+      <c r="CA2" s="3"/>
+      <c r="CB2" s="3"/>
+      <c r="CC2" s="3"/>
+      <c r="CD2" s="3"/>
+      <c r="CE2" s="3"/>
+      <c r="CF2" s="3"/>
+      <c r="CG2" s="3"/>
+      <c r="CH2" s="3"/>
+      <c r="CI2" s="3"/>
+      <c r="CJ2" s="3"/>
+      <c r="CK2" s="3"/>
     </row>
-    <row r="3" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>alunos!A2</f>
         <v>25129175</v>
@@ -1497,83 +1500,66 @@
       <c r="AP3" t="s">
         <v>36</v>
       </c>
-      <c r="AS3" s="2"/>
-      <c r="AT3" s="2"/>
-      <c r="AU3" s="2"/>
-      <c r="AX3" s="5"/>
-      <c r="AY3" s="5"/>
-      <c r="AZ3" s="5"/>
-      <c r="BA3" s="5"/>
-      <c r="BB3" s="5"/>
-      <c r="BC3" s="5"/>
-      <c r="BD3" s="5"/>
-      <c r="BE3" s="5"/>
-      <c r="BF3" s="5"/>
-      <c r="BG3" s="5"/>
-      <c r="BH3" s="5"/>
-      <c r="BI3" s="5"/>
-      <c r="BJ3" s="5"/>
-      <c r="BK3" s="5"/>
-      <c r="BL3" s="5"/>
-      <c r="BM3" s="5"/>
-      <c r="BN3" s="5"/>
-      <c r="BO3" s="5"/>
-      <c r="BP3" s="5"/>
-      <c r="BQ3" s="5"/>
-      <c r="BR3" s="5"/>
-      <c r="BS3" s="5"/>
-      <c r="BT3" s="5"/>
-      <c r="BU3" s="5"/>
-      <c r="BV3" s="5"/>
-      <c r="BW3" s="5"/>
-      <c r="BX3" s="5"/>
-      <c r="BY3" s="5"/>
-      <c r="BZ3" s="5"/>
-      <c r="CA3" s="5"/>
-      <c r="CB3" s="5"/>
-      <c r="CC3" s="5"/>
-      <c r="CD3" s="5"/>
-      <c r="CE3" s="5"/>
-      <c r="CF3" s="5"/>
-      <c r="CG3" s="5"/>
-      <c r="CH3" s="5"/>
-      <c r="CI3" s="5"/>
-      <c r="CJ3" s="5"/>
-      <c r="CK3" s="5"/>
-      <c r="CL3" s="5"/>
-      <c r="CM3" s="5"/>
-      <c r="CN3" s="5"/>
-      <c r="CO3" s="5"/>
-      <c r="CP3" s="5"/>
-      <c r="CQ3" s="5"/>
-      <c r="CR3" s="5"/>
-      <c r="CS3" s="5"/>
-      <c r="CT3" s="5"/>
-      <c r="CU3" s="5"/>
-      <c r="CV3" s="5"/>
-      <c r="CW3" s="5"/>
-      <c r="CX3" s="5"/>
-      <c r="CY3" s="5"/>
-      <c r="CZ3" s="5"/>
-      <c r="DA3" s="5"/>
-      <c r="DB3" s="5"/>
-      <c r="DC3" s="5"/>
-      <c r="DD3" s="5"/>
-      <c r="DE3" s="5"/>
-      <c r="DF3" s="5"/>
-      <c r="DG3" s="5"/>
-      <c r="DH3" s="5"/>
-      <c r="DI3" s="5"/>
-      <c r="DJ3" s="5"/>
-      <c r="DK3" s="5"/>
-      <c r="DL3" s="5"/>
-      <c r="DM3" s="5"/>
-      <c r="DN3" s="5"/>
-      <c r="DO3" s="5"/>
-      <c r="DP3" s="5"/>
-      <c r="DQ3" s="5"/>
+      <c r="AQ3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW3"/>
+      <c r="BV3" s="3"/>
+      <c r="BW3" s="3"/>
+      <c r="BX3" s="3"/>
+      <c r="BY3" s="3"/>
+      <c r="BZ3" s="3"/>
+      <c r="CA3" s="3"/>
+      <c r="CB3" s="3"/>
+      <c r="CC3" s="3"/>
+      <c r="CD3" s="3"/>
+      <c r="CE3" s="3"/>
+      <c r="CF3" s="3"/>
+      <c r="CG3" s="3"/>
+      <c r="CH3" s="3"/>
+      <c r="CI3" s="3"/>
+      <c r="CJ3" s="3"/>
+      <c r="CK3" s="3"/>
+      <c r="CL3" s="3"/>
+      <c r="CM3" s="3"/>
+      <c r="CN3" s="3"/>
+      <c r="CO3" s="3"/>
+      <c r="CP3" s="3"/>
+      <c r="CQ3" s="3"/>
+      <c r="CR3" s="3"/>
+      <c r="CS3" s="3"/>
+      <c r="CT3" s="3"/>
+      <c r="CU3" s="3"/>
+      <c r="CV3" s="3"/>
+      <c r="CW3" s="3"/>
+      <c r="CX3" s="3"/>
+      <c r="CY3" s="3"/>
+      <c r="CZ3" s="3"/>
+      <c r="DA3" s="3"/>
+      <c r="DB3" s="3"/>
+      <c r="DC3" s="3"/>
+      <c r="DD3" s="3"/>
+      <c r="DE3" s="3"/>
+      <c r="DF3" s="3"/>
+      <c r="DG3" s="3"/>
+      <c r="DH3" s="3"/>
+      <c r="DI3" s="3"/>
+      <c r="DJ3" s="3"/>
+      <c r="DK3" s="3"/>
+      <c r="DL3" s="3"/>
+      <c r="DM3" s="3"/>
+      <c r="DN3" s="3"/>
+      <c r="DO3" s="3"/>
+      <c r="DP3" s="3"/>
+      <c r="DQ3" s="3"/>
     </row>
-    <row r="4" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>alunos!A3</f>
         <v>25129085</v>
@@ -1702,83 +1688,66 @@
       <c r="AP4" t="s">
         <v>36</v>
       </c>
-      <c r="AS4" s="2"/>
-      <c r="AT4" s="2"/>
-      <c r="AU4" s="2"/>
-      <c r="AX4" s="5"/>
-      <c r="AY4" s="5"/>
-      <c r="AZ4" s="5"/>
-      <c r="BA4" s="5"/>
-      <c r="BB4" s="5"/>
-      <c r="BC4" s="5"/>
-      <c r="BD4" s="5"/>
-      <c r="BE4" s="5"/>
-      <c r="BF4" s="5"/>
-      <c r="BG4" s="5"/>
-      <c r="BH4" s="5"/>
-      <c r="BI4" s="5"/>
-      <c r="BJ4" s="5"/>
-      <c r="BK4" s="5"/>
-      <c r="BL4" s="5"/>
-      <c r="BM4" s="5"/>
-      <c r="BN4" s="5"/>
-      <c r="BO4" s="5"/>
-      <c r="BP4" s="5"/>
-      <c r="BQ4" s="5"/>
-      <c r="BR4" s="5"/>
-      <c r="BS4" s="5"/>
-      <c r="BT4" s="5"/>
-      <c r="BU4" s="5"/>
-      <c r="BV4" s="5"/>
-      <c r="BW4" s="5"/>
-      <c r="BX4" s="5"/>
-      <c r="BY4" s="5"/>
-      <c r="BZ4" s="5"/>
-      <c r="CA4" s="5"/>
-      <c r="CB4" s="5"/>
-      <c r="CC4" s="5"/>
-      <c r="CD4" s="5"/>
-      <c r="CE4" s="5"/>
-      <c r="CF4" s="5"/>
-      <c r="CG4" s="5"/>
-      <c r="CH4" s="5"/>
-      <c r="CI4" s="5"/>
-      <c r="CJ4" s="5"/>
-      <c r="CK4" s="5"/>
-      <c r="CL4" s="5"/>
-      <c r="CM4" s="5"/>
-      <c r="CN4" s="5"/>
-      <c r="CO4" s="5"/>
-      <c r="CP4" s="5"/>
-      <c r="CQ4" s="5"/>
-      <c r="CR4" s="5"/>
-      <c r="CS4" s="5"/>
-      <c r="CT4" s="5"/>
-      <c r="CU4" s="5"/>
-      <c r="CV4" s="5"/>
-      <c r="CW4" s="5"/>
-      <c r="CX4" s="5"/>
-      <c r="CY4" s="5"/>
-      <c r="CZ4" s="5"/>
-      <c r="DA4" s="5"/>
-      <c r="DB4" s="5"/>
-      <c r="DC4" s="5"/>
-      <c r="DD4" s="5"/>
-      <c r="DE4" s="5"/>
-      <c r="DF4" s="5"/>
-      <c r="DG4" s="5"/>
-      <c r="DH4" s="5"/>
-      <c r="DI4" s="5"/>
-      <c r="DJ4" s="5"/>
-      <c r="DK4" s="5"/>
-      <c r="DL4" s="5"/>
-      <c r="DM4" s="5"/>
-      <c r="DN4" s="5"/>
-      <c r="DO4" s="5"/>
-      <c r="DP4" s="5"/>
-      <c r="DQ4" s="5"/>
+      <c r="AQ4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW4"/>
+      <c r="BV4" s="3"/>
+      <c r="BW4" s="3"/>
+      <c r="BX4" s="3"/>
+      <c r="BY4" s="3"/>
+      <c r="BZ4" s="3"/>
+      <c r="CA4" s="3"/>
+      <c r="CB4" s="3"/>
+      <c r="CC4" s="3"/>
+      <c r="CD4" s="3"/>
+      <c r="CE4" s="3"/>
+      <c r="CF4" s="3"/>
+      <c r="CG4" s="3"/>
+      <c r="CH4" s="3"/>
+      <c r="CI4" s="3"/>
+      <c r="CJ4" s="3"/>
+      <c r="CK4" s="3"/>
+      <c r="CL4" s="3"/>
+      <c r="CM4" s="3"/>
+      <c r="CN4" s="3"/>
+      <c r="CO4" s="3"/>
+      <c r="CP4" s="3"/>
+      <c r="CQ4" s="3"/>
+      <c r="CR4" s="3"/>
+      <c r="CS4" s="3"/>
+      <c r="CT4" s="3"/>
+      <c r="CU4" s="3"/>
+      <c r="CV4" s="3"/>
+      <c r="CW4" s="3"/>
+      <c r="CX4" s="3"/>
+      <c r="CY4" s="3"/>
+      <c r="CZ4" s="3"/>
+      <c r="DA4" s="3"/>
+      <c r="DB4" s="3"/>
+      <c r="DC4" s="3"/>
+      <c r="DD4" s="3"/>
+      <c r="DE4" s="3"/>
+      <c r="DF4" s="3"/>
+      <c r="DG4" s="3"/>
+      <c r="DH4" s="3"/>
+      <c r="DI4" s="3"/>
+      <c r="DJ4" s="3"/>
+      <c r="DK4" s="3"/>
+      <c r="DL4" s="3"/>
+      <c r="DM4" s="3"/>
+      <c r="DN4" s="3"/>
+      <c r="DO4" s="3"/>
+      <c r="DP4" s="3"/>
+      <c r="DQ4" s="3"/>
     </row>
-    <row r="5" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>alunos!A4</f>
         <v>25129021</v>
@@ -1907,83 +1876,66 @@
       <c r="AP5" t="s">
         <v>36</v>
       </c>
-      <c r="AS5" s="2"/>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AX5" s="5"/>
-      <c r="AY5" s="5"/>
-      <c r="AZ5" s="5"/>
-      <c r="BA5" s="5"/>
-      <c r="BB5" s="5"/>
-      <c r="BC5" s="5"/>
-      <c r="BD5" s="5"/>
-      <c r="BE5" s="5"/>
-      <c r="BF5" s="5"/>
-      <c r="BG5" s="5"/>
-      <c r="BH5" s="5"/>
-      <c r="BI5" s="5"/>
-      <c r="BJ5" s="5"/>
-      <c r="BK5" s="5"/>
-      <c r="BL5" s="5"/>
-      <c r="BM5" s="5"/>
-      <c r="BN5" s="5"/>
-      <c r="BO5" s="5"/>
-      <c r="BP5" s="5"/>
-      <c r="BQ5" s="5"/>
-      <c r="BR5" s="5"/>
-      <c r="BS5" s="5"/>
-      <c r="BT5" s="5"/>
-      <c r="BU5" s="5"/>
-      <c r="BV5" s="5"/>
-      <c r="BW5" s="5"/>
-      <c r="BX5" s="5"/>
-      <c r="BY5" s="5"/>
-      <c r="BZ5" s="5"/>
-      <c r="CA5" s="5"/>
-      <c r="CB5" s="5"/>
-      <c r="CC5" s="5"/>
-      <c r="CD5" s="5"/>
-      <c r="CE5" s="5"/>
-      <c r="CF5" s="5"/>
-      <c r="CG5" s="5"/>
-      <c r="CH5" s="5"/>
-      <c r="CI5" s="5"/>
-      <c r="CJ5" s="5"/>
-      <c r="CK5" s="5"/>
-      <c r="CL5" s="5"/>
-      <c r="CM5" s="5"/>
-      <c r="CN5" s="5"/>
-      <c r="CO5" s="5"/>
-      <c r="CP5" s="5"/>
-      <c r="CQ5" s="5"/>
-      <c r="CR5" s="5"/>
-      <c r="CS5" s="5"/>
-      <c r="CT5" s="5"/>
-      <c r="CU5" s="5"/>
-      <c r="CV5" s="5"/>
-      <c r="CW5" s="5"/>
-      <c r="CX5" s="5"/>
-      <c r="CY5" s="5"/>
-      <c r="CZ5" s="5"/>
-      <c r="DA5" s="5"/>
-      <c r="DB5" s="5"/>
-      <c r="DC5" s="5"/>
-      <c r="DD5" s="5"/>
-      <c r="DE5" s="5"/>
-      <c r="DF5" s="5"/>
-      <c r="DG5" s="5"/>
-      <c r="DH5" s="5"/>
-      <c r="DI5" s="5"/>
-      <c r="DJ5" s="5"/>
-      <c r="DK5" s="5"/>
-      <c r="DL5" s="5"/>
-      <c r="DM5" s="5"/>
-      <c r="DN5" s="5"/>
-      <c r="DO5" s="5"/>
-      <c r="DP5" s="5"/>
-      <c r="DQ5" s="5"/>
+      <c r="AQ5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW5"/>
+      <c r="BV5" s="3"/>
+      <c r="BW5" s="3"/>
+      <c r="BX5" s="3"/>
+      <c r="BY5" s="3"/>
+      <c r="BZ5" s="3"/>
+      <c r="CA5" s="3"/>
+      <c r="CB5" s="3"/>
+      <c r="CC5" s="3"/>
+      <c r="CD5" s="3"/>
+      <c r="CE5" s="3"/>
+      <c r="CF5" s="3"/>
+      <c r="CG5" s="3"/>
+      <c r="CH5" s="3"/>
+      <c r="CI5" s="3"/>
+      <c r="CJ5" s="3"/>
+      <c r="CK5" s="3"/>
+      <c r="CL5" s="3"/>
+      <c r="CM5" s="3"/>
+      <c r="CN5" s="3"/>
+      <c r="CO5" s="3"/>
+      <c r="CP5" s="3"/>
+      <c r="CQ5" s="3"/>
+      <c r="CR5" s="3"/>
+      <c r="CS5" s="3"/>
+      <c r="CT5" s="3"/>
+      <c r="CU5" s="3"/>
+      <c r="CV5" s="3"/>
+      <c r="CW5" s="3"/>
+      <c r="CX5" s="3"/>
+      <c r="CY5" s="3"/>
+      <c r="CZ5" s="3"/>
+      <c r="DA5" s="3"/>
+      <c r="DB5" s="3"/>
+      <c r="DC5" s="3"/>
+      <c r="DD5" s="3"/>
+      <c r="DE5" s="3"/>
+      <c r="DF5" s="3"/>
+      <c r="DG5" s="3"/>
+      <c r="DH5" s="3"/>
+      <c r="DI5" s="3"/>
+      <c r="DJ5" s="3"/>
+      <c r="DK5" s="3"/>
+      <c r="DL5" s="3"/>
+      <c r="DM5" s="3"/>
+      <c r="DN5" s="3"/>
+      <c r="DO5" s="3"/>
+      <c r="DP5" s="3"/>
+      <c r="DQ5" s="3"/>
     </row>
-    <row r="6" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>alunos!A5</f>
         <v>25129019</v>
@@ -2112,83 +2064,52 @@
       <c r="AP6" t="s">
         <v>36</v>
       </c>
-      <c r="AS6" s="2"/>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AX6" s="5"/>
-      <c r="AY6" s="5"/>
-      <c r="AZ6" s="5"/>
-      <c r="BA6" s="5"/>
-      <c r="BB6" s="5"/>
-      <c r="BC6" s="5"/>
-      <c r="BD6" s="5"/>
-      <c r="BE6" s="5"/>
-      <c r="BF6" s="5"/>
-      <c r="BG6" s="5"/>
-      <c r="BH6" s="5"/>
-      <c r="BI6" s="5"/>
-      <c r="BJ6" s="5"/>
-      <c r="BK6" s="5"/>
-      <c r="BL6" s="5"/>
-      <c r="BM6" s="5"/>
-      <c r="BN6" s="5"/>
-      <c r="BO6" s="5"/>
-      <c r="BP6" s="5"/>
-      <c r="BQ6" s="5"/>
-      <c r="BR6" s="5"/>
-      <c r="BS6" s="5"/>
-      <c r="BT6" s="5"/>
-      <c r="BU6" s="5"/>
-      <c r="BV6" s="5"/>
-      <c r="BW6" s="5"/>
-      <c r="BX6" s="5"/>
-      <c r="BY6" s="5"/>
-      <c r="BZ6" s="5"/>
-      <c r="CA6" s="5"/>
-      <c r="CB6" s="5"/>
-      <c r="CC6" s="5"/>
-      <c r="CD6" s="5"/>
-      <c r="CE6" s="5"/>
-      <c r="CF6" s="5"/>
-      <c r="CG6" s="7"/>
-      <c r="CH6" s="5"/>
-      <c r="CI6" s="5"/>
-      <c r="CJ6" s="5"/>
-      <c r="CK6" s="5"/>
-      <c r="CL6" s="5"/>
-      <c r="CM6" s="5"/>
-      <c r="CN6" s="5"/>
-      <c r="CO6" s="5"/>
-      <c r="CP6" s="5"/>
-      <c r="CQ6" s="5"/>
-      <c r="CR6" s="5"/>
-      <c r="CS6" s="5"/>
-      <c r="CT6" s="5"/>
-      <c r="CU6" s="5"/>
-      <c r="CV6" s="5"/>
-      <c r="CW6" s="5"/>
-      <c r="CX6" s="5"/>
-      <c r="CY6" s="5"/>
-      <c r="CZ6" s="5"/>
-      <c r="DA6" s="5"/>
-      <c r="DB6" s="5"/>
-      <c r="DC6" s="5"/>
-      <c r="DD6" s="5"/>
-      <c r="DE6" s="5"/>
-      <c r="DF6" s="5"/>
-      <c r="DG6" s="5"/>
-      <c r="DH6" s="5"/>
-      <c r="DI6" s="5"/>
-      <c r="DJ6" s="5"/>
-      <c r="DK6" s="5"/>
-      <c r="DL6" s="5"/>
-      <c r="DM6" s="5"/>
-      <c r="DN6" s="5"/>
-      <c r="DO6" s="5"/>
-      <c r="DP6" s="5"/>
-      <c r="DQ6" s="5"/>
+      <c r="AQ6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW6"/>
+      <c r="CJ6" s="3"/>
+      <c r="CK6" s="3"/>
+      <c r="CL6" s="3"/>
+      <c r="CM6" s="3"/>
+      <c r="CN6" s="3"/>
+      <c r="CO6" s="3"/>
+      <c r="CP6" s="3"/>
+      <c r="CQ6" s="3"/>
+      <c r="CR6" s="3"/>
+      <c r="CS6" s="3"/>
+      <c r="CT6" s="3"/>
+      <c r="CU6" s="3"/>
+      <c r="CV6" s="3"/>
+      <c r="CW6" s="3"/>
+      <c r="CX6" s="3"/>
+      <c r="CY6" s="3"/>
+      <c r="CZ6" s="3"/>
+      <c r="DA6" s="3"/>
+      <c r="DB6" s="3"/>
+      <c r="DC6" s="3"/>
+      <c r="DD6" s="3"/>
+      <c r="DE6" s="3"/>
+      <c r="DF6" s="3"/>
+      <c r="DG6" s="3"/>
+      <c r="DH6" s="3"/>
+      <c r="DI6" s="3"/>
+      <c r="DJ6" s="3"/>
+      <c r="DK6" s="3"/>
+      <c r="DL6" s="3"/>
+      <c r="DM6" s="3"/>
+      <c r="DN6" s="3"/>
+      <c r="DO6" s="3"/>
+      <c r="DP6" s="3"/>
+      <c r="DQ6" s="3"/>
     </row>
-    <row r="7" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>alunos!A6</f>
         <v>25129023</v>
@@ -2317,83 +2238,52 @@
       <c r="AP7" t="s">
         <v>36</v>
       </c>
-      <c r="AS7" s="2"/>
-      <c r="AT7" s="2"/>
-      <c r="AU7" s="2"/>
-      <c r="AX7" s="5"/>
-      <c r="AY7" s="5"/>
-      <c r="AZ7" s="5"/>
-      <c r="BA7" s="5"/>
-      <c r="BB7" s="5"/>
-      <c r="BC7" s="5"/>
-      <c r="BD7" s="5"/>
-      <c r="BE7" s="5"/>
-      <c r="BF7" s="5"/>
-      <c r="BG7" s="5"/>
-      <c r="BH7" s="5"/>
-      <c r="BI7" s="5"/>
-      <c r="BJ7" s="5"/>
-      <c r="BK7" s="5"/>
-      <c r="BL7" s="5"/>
-      <c r="BM7" s="5"/>
-      <c r="BN7" s="5"/>
-      <c r="BO7" s="5"/>
-      <c r="BP7" s="5"/>
-      <c r="BQ7" s="5"/>
-      <c r="BR7" s="5"/>
-      <c r="BS7" s="5"/>
-      <c r="BT7" s="5"/>
-      <c r="BU7" s="5"/>
-      <c r="BV7" s="5"/>
-      <c r="BW7" s="5"/>
-      <c r="BX7" s="5"/>
-      <c r="BY7" s="5"/>
-      <c r="BZ7" s="5"/>
-      <c r="CA7" s="5"/>
-      <c r="CB7" s="5"/>
-      <c r="CC7" s="5"/>
-      <c r="CD7" s="5"/>
-      <c r="CE7" s="5"/>
-      <c r="CF7" s="5"/>
-      <c r="CG7" s="6"/>
-      <c r="CH7" s="5"/>
-      <c r="CI7" s="5"/>
-      <c r="CJ7" s="5"/>
-      <c r="CK7" s="5"/>
-      <c r="CL7" s="5"/>
-      <c r="CM7" s="5"/>
-      <c r="CN7" s="5"/>
-      <c r="CO7" s="5"/>
-      <c r="CP7" s="5"/>
-      <c r="CQ7" s="5"/>
-      <c r="CR7" s="5"/>
-      <c r="CS7" s="5"/>
-      <c r="CT7" s="5"/>
-      <c r="CU7" s="5"/>
-      <c r="CV7" s="5"/>
-      <c r="CW7" s="5"/>
-      <c r="CX7" s="5"/>
-      <c r="CY7" s="5"/>
-      <c r="CZ7" s="5"/>
-      <c r="DA7" s="5"/>
-      <c r="DB7" s="5"/>
-      <c r="DC7" s="5"/>
-      <c r="DD7" s="5"/>
-      <c r="DE7" s="5"/>
-      <c r="DF7" s="5"/>
-      <c r="DG7" s="5"/>
-      <c r="DH7" s="5"/>
-      <c r="DI7" s="5"/>
-      <c r="DJ7" s="5"/>
-      <c r="DK7" s="5"/>
-      <c r="DL7" s="5"/>
-      <c r="DM7" s="5"/>
-      <c r="DN7" s="5"/>
-      <c r="DO7" s="5"/>
-      <c r="DP7" s="5"/>
-      <c r="DQ7" s="5"/>
+      <c r="AQ7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW7"/>
+      <c r="CJ7" s="3"/>
+      <c r="CK7" s="3"/>
+      <c r="CL7" s="3"/>
+      <c r="CM7" s="3"/>
+      <c r="CN7" s="3"/>
+      <c r="CO7" s="3"/>
+      <c r="CP7" s="3"/>
+      <c r="CQ7" s="3"/>
+      <c r="CR7" s="3"/>
+      <c r="CS7" s="3"/>
+      <c r="CT7" s="3"/>
+      <c r="CU7" s="3"/>
+      <c r="CV7" s="3"/>
+      <c r="CW7" s="3"/>
+      <c r="CX7" s="3"/>
+      <c r="CY7" s="3"/>
+      <c r="CZ7" s="3"/>
+      <c r="DA7" s="3"/>
+      <c r="DB7" s="3"/>
+      <c r="DC7" s="3"/>
+      <c r="DD7" s="3"/>
+      <c r="DE7" s="3"/>
+      <c r="DF7" s="3"/>
+      <c r="DG7" s="3"/>
+      <c r="DH7" s="3"/>
+      <c r="DI7" s="3"/>
+      <c r="DJ7" s="3"/>
+      <c r="DK7" s="3"/>
+      <c r="DL7" s="3"/>
+      <c r="DM7" s="3"/>
+      <c r="DN7" s="3"/>
+      <c r="DO7" s="3"/>
+      <c r="DP7" s="3"/>
+      <c r="DQ7" s="3"/>
     </row>
-    <row r="8" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>alunos!A7</f>
         <v>25129105</v>
@@ -2522,83 +2412,52 @@
       <c r="AP8" t="s">
         <v>36</v>
       </c>
-      <c r="AS8" s="2"/>
-      <c r="AT8" s="2"/>
-      <c r="AU8" s="2"/>
-      <c r="AX8" s="5"/>
-      <c r="AY8" s="5"/>
-      <c r="AZ8" s="5"/>
-      <c r="BA8" s="5"/>
-      <c r="BB8" s="5"/>
-      <c r="BC8" s="5"/>
-      <c r="BD8" s="5"/>
-      <c r="BE8" s="5"/>
-      <c r="BF8" s="5"/>
-      <c r="BG8" s="5"/>
-      <c r="BH8" s="5"/>
-      <c r="BI8" s="5"/>
-      <c r="BJ8" s="5"/>
-      <c r="BK8" s="5"/>
-      <c r="BL8" s="5"/>
-      <c r="BM8" s="5"/>
-      <c r="BN8" s="5"/>
-      <c r="BO8" s="5"/>
-      <c r="BP8" s="5"/>
-      <c r="BQ8" s="5"/>
-      <c r="BR8" s="5"/>
-      <c r="BS8" s="5"/>
-      <c r="BT8" s="5"/>
-      <c r="BU8" s="5"/>
-      <c r="BV8" s="5"/>
-      <c r="BW8" s="5"/>
-      <c r="BX8" s="5"/>
-      <c r="BY8" s="5"/>
-      <c r="BZ8" s="5"/>
-      <c r="CA8" s="5"/>
-      <c r="CB8" s="5"/>
-      <c r="CC8" s="5"/>
-      <c r="CD8" s="5"/>
-      <c r="CE8" s="5"/>
-      <c r="CF8" s="5"/>
-      <c r="CG8" s="5"/>
-      <c r="CH8" s="5"/>
-      <c r="CI8" s="5"/>
-      <c r="CJ8" s="5"/>
-      <c r="CK8" s="5"/>
-      <c r="CL8" s="5"/>
-      <c r="CM8" s="5"/>
-      <c r="CN8" s="5"/>
-      <c r="CO8" s="5"/>
-      <c r="CP8" s="5"/>
-      <c r="CQ8" s="5"/>
-      <c r="CR8" s="5"/>
-      <c r="CS8" s="5"/>
-      <c r="CT8" s="5"/>
-      <c r="CU8" s="5"/>
-      <c r="CV8" s="5"/>
-      <c r="CW8" s="5"/>
-      <c r="CX8" s="5"/>
-      <c r="CY8" s="5"/>
-      <c r="CZ8" s="5"/>
-      <c r="DA8" s="5"/>
-      <c r="DB8" s="5"/>
-      <c r="DC8" s="5"/>
-      <c r="DD8" s="5"/>
-      <c r="DE8" s="5"/>
-      <c r="DF8" s="5"/>
-      <c r="DG8" s="5"/>
-      <c r="DH8" s="5"/>
-      <c r="DI8" s="5"/>
-      <c r="DJ8" s="5"/>
-      <c r="DK8" s="5"/>
-      <c r="DL8" s="5"/>
-      <c r="DM8" s="5"/>
-      <c r="DN8" s="5"/>
-      <c r="DO8" s="5"/>
-      <c r="DP8" s="5"/>
-      <c r="DQ8" s="5"/>
+      <c r="AQ8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW8"/>
+      <c r="CJ8" s="3"/>
+      <c r="CK8" s="3"/>
+      <c r="CL8" s="3"/>
+      <c r="CM8" s="3"/>
+      <c r="CN8" s="3"/>
+      <c r="CO8" s="3"/>
+      <c r="CP8" s="3"/>
+      <c r="CQ8" s="3"/>
+      <c r="CR8" s="3"/>
+      <c r="CS8" s="3"/>
+      <c r="CT8" s="3"/>
+      <c r="CU8" s="3"/>
+      <c r="CV8" s="3"/>
+      <c r="CW8" s="3"/>
+      <c r="CX8" s="3"/>
+      <c r="CY8" s="3"/>
+      <c r="CZ8" s="3"/>
+      <c r="DA8" s="3"/>
+      <c r="DB8" s="3"/>
+      <c r="DC8" s="3"/>
+      <c r="DD8" s="3"/>
+      <c r="DE8" s="3"/>
+      <c r="DF8" s="3"/>
+      <c r="DG8" s="3"/>
+      <c r="DH8" s="3"/>
+      <c r="DI8" s="3"/>
+      <c r="DJ8" s="3"/>
+      <c r="DK8" s="3"/>
+      <c r="DL8" s="3"/>
+      <c r="DM8" s="3"/>
+      <c r="DN8" s="3"/>
+      <c r="DO8" s="3"/>
+      <c r="DP8" s="3"/>
+      <c r="DQ8" s="3"/>
     </row>
-    <row r="9" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>alunos!A8</f>
         <v>25129083</v>
@@ -2727,83 +2586,52 @@
       <c r="AP9" t="s">
         <v>36</v>
       </c>
-      <c r="AS9" s="2"/>
-      <c r="AT9" s="2"/>
-      <c r="AU9" s="2"/>
-      <c r="AX9" s="5"/>
-      <c r="AY9" s="5"/>
-      <c r="AZ9" s="5"/>
-      <c r="BA9" s="5"/>
-      <c r="BB9" s="5"/>
-      <c r="BC9" s="5"/>
-      <c r="BD9" s="5"/>
-      <c r="BE9" s="5"/>
-      <c r="BF9" s="5"/>
-      <c r="BG9" s="5"/>
-      <c r="BH9" s="5"/>
-      <c r="BI9" s="5"/>
-      <c r="BJ9" s="5"/>
-      <c r="BK9" s="5"/>
-      <c r="BL9" s="5"/>
-      <c r="BM9" s="5"/>
-      <c r="BN9" s="5"/>
-      <c r="BO9" s="5"/>
-      <c r="BP9" s="5"/>
-      <c r="BQ9" s="5"/>
-      <c r="BR9" s="5"/>
-      <c r="BS9" s="5"/>
-      <c r="BT9" s="5"/>
-      <c r="BU9" s="5"/>
-      <c r="BV9" s="5"/>
-      <c r="BW9" s="5"/>
-      <c r="BX9" s="5"/>
-      <c r="BY9" s="5"/>
-      <c r="BZ9" s="5"/>
-      <c r="CA9" s="5"/>
-      <c r="CB9" s="5"/>
-      <c r="CC9" s="5"/>
-      <c r="CD9" s="5"/>
-      <c r="CE9" s="5"/>
-      <c r="CF9" s="5"/>
-      <c r="CG9" s="5"/>
-      <c r="CH9" s="5"/>
-      <c r="CI9" s="5"/>
-      <c r="CJ9" s="5"/>
-      <c r="CK9" s="5"/>
-      <c r="CL9" s="5"/>
-      <c r="CM9" s="5"/>
-      <c r="CN9" s="5"/>
-      <c r="CO9" s="5"/>
-      <c r="CP9" s="5"/>
-      <c r="CQ9" s="5"/>
-      <c r="CR9" s="5"/>
-      <c r="CS9" s="5"/>
-      <c r="CT9" s="5"/>
-      <c r="CU9" s="5"/>
-      <c r="CV9" s="5"/>
-      <c r="CW9" s="5"/>
-      <c r="CX9" s="5"/>
-      <c r="CY9" s="5"/>
-      <c r="CZ9" s="5"/>
-      <c r="DA9" s="5"/>
-      <c r="DB9" s="5"/>
-      <c r="DC9" s="5"/>
-      <c r="DD9" s="5"/>
-      <c r="DE9" s="5"/>
-      <c r="DF9" s="5"/>
-      <c r="DG9" s="5"/>
-      <c r="DH9" s="5"/>
-      <c r="DI9" s="5"/>
-      <c r="DJ9" s="5"/>
-      <c r="DK9" s="5"/>
-      <c r="DL9" s="5"/>
-      <c r="DM9" s="5"/>
-      <c r="DN9" s="5"/>
-      <c r="DO9" s="5"/>
-      <c r="DP9" s="5"/>
-      <c r="DQ9" s="5"/>
+      <c r="AQ9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW9"/>
+      <c r="CJ9" s="3"/>
+      <c r="CK9" s="3"/>
+      <c r="CL9" s="3"/>
+      <c r="CM9" s="3"/>
+      <c r="CN9" s="3"/>
+      <c r="CO9" s="3"/>
+      <c r="CP9" s="3"/>
+      <c r="CQ9" s="3"/>
+      <c r="CR9" s="3"/>
+      <c r="CS9" s="3"/>
+      <c r="CT9" s="3"/>
+      <c r="CU9" s="3"/>
+      <c r="CV9" s="3"/>
+      <c r="CW9" s="3"/>
+      <c r="CX9" s="3"/>
+      <c r="CY9" s="3"/>
+      <c r="CZ9" s="3"/>
+      <c r="DA9" s="3"/>
+      <c r="DB9" s="3"/>
+      <c r="DC9" s="3"/>
+      <c r="DD9" s="3"/>
+      <c r="DE9" s="3"/>
+      <c r="DF9" s="3"/>
+      <c r="DG9" s="3"/>
+      <c r="DH9" s="3"/>
+      <c r="DI9" s="3"/>
+      <c r="DJ9" s="3"/>
+      <c r="DK9" s="3"/>
+      <c r="DL9" s="3"/>
+      <c r="DM9" s="3"/>
+      <c r="DN9" s="3"/>
+      <c r="DO9" s="3"/>
+      <c r="DP9" s="3"/>
+      <c r="DQ9" s="3"/>
     </row>
-    <row r="10" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>alunos!A9</f>
         <v>25129047</v>
@@ -2932,83 +2760,52 @@
       <c r="AP10" t="s">
         <v>36</v>
       </c>
-      <c r="AS10" s="2"/>
-      <c r="AT10" s="2"/>
-      <c r="AU10" s="2"/>
-      <c r="AX10" s="5"/>
-      <c r="AY10" s="5"/>
-      <c r="AZ10" s="5"/>
-      <c r="BA10" s="5"/>
-      <c r="BB10" s="5"/>
-      <c r="BC10" s="5"/>
-      <c r="BD10" s="5"/>
-      <c r="BE10" s="5"/>
-      <c r="BF10" s="5"/>
-      <c r="BG10" s="5"/>
-      <c r="BH10" s="5"/>
-      <c r="BI10" s="5"/>
-      <c r="BJ10" s="5"/>
-      <c r="BK10" s="5"/>
-      <c r="BL10" s="5"/>
-      <c r="BM10" s="5"/>
-      <c r="BN10" s="5"/>
-      <c r="BO10" s="5"/>
-      <c r="BP10" s="5"/>
-      <c r="BQ10" s="5"/>
-      <c r="BR10" s="5"/>
-      <c r="BS10" s="5"/>
-      <c r="BT10" s="5"/>
-      <c r="BU10" s="5"/>
-      <c r="BV10" s="5"/>
-      <c r="BW10" s="5"/>
-      <c r="BX10" s="5"/>
-      <c r="BY10" s="5"/>
-      <c r="BZ10" s="5"/>
-      <c r="CA10" s="5"/>
-      <c r="CB10" s="5"/>
-      <c r="CC10" s="5"/>
-      <c r="CD10" s="5"/>
-      <c r="CE10" s="5"/>
-      <c r="CF10" s="5"/>
-      <c r="CG10" s="5"/>
-      <c r="CH10" s="5"/>
-      <c r="CI10" s="5"/>
-      <c r="CJ10" s="5"/>
-      <c r="CK10" s="5"/>
-      <c r="CL10" s="5"/>
-      <c r="CM10" s="5"/>
-      <c r="CN10" s="5"/>
-      <c r="CO10" s="5"/>
-      <c r="CP10" s="5"/>
-      <c r="CQ10" s="5"/>
-      <c r="CR10" s="5"/>
-      <c r="CS10" s="5"/>
-      <c r="CT10" s="5"/>
-      <c r="CU10" s="5"/>
-      <c r="CV10" s="5"/>
-      <c r="CW10" s="5"/>
-      <c r="CX10" s="5"/>
-      <c r="CY10" s="5"/>
-      <c r="CZ10" s="5"/>
-      <c r="DA10" s="5"/>
-      <c r="DB10" s="5"/>
-      <c r="DC10" s="5"/>
-      <c r="DD10" s="5"/>
-      <c r="DE10" s="5"/>
-      <c r="DF10" s="5"/>
-      <c r="DG10" s="5"/>
-      <c r="DH10" s="5"/>
-      <c r="DI10" s="5"/>
-      <c r="DJ10" s="5"/>
-      <c r="DK10" s="5"/>
-      <c r="DL10" s="5"/>
-      <c r="DM10" s="5"/>
-      <c r="DN10" s="5"/>
-      <c r="DO10" s="5"/>
-      <c r="DP10" s="5"/>
-      <c r="DQ10" s="5"/>
+      <c r="AQ10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW10"/>
+      <c r="CJ10" s="3"/>
+      <c r="CK10" s="3"/>
+      <c r="CL10" s="3"/>
+      <c r="CM10" s="3"/>
+      <c r="CN10" s="3"/>
+      <c r="CO10" s="3"/>
+      <c r="CP10" s="3"/>
+      <c r="CQ10" s="3"/>
+      <c r="CR10" s="3"/>
+      <c r="CS10" s="3"/>
+      <c r="CT10" s="3"/>
+      <c r="CU10" s="3"/>
+      <c r="CV10" s="3"/>
+      <c r="CW10" s="3"/>
+      <c r="CX10" s="3"/>
+      <c r="CY10" s="3"/>
+      <c r="CZ10" s="3"/>
+      <c r="DA10" s="3"/>
+      <c r="DB10" s="3"/>
+      <c r="DC10" s="3"/>
+      <c r="DD10" s="3"/>
+      <c r="DE10" s="3"/>
+      <c r="DF10" s="3"/>
+      <c r="DG10" s="3"/>
+      <c r="DH10" s="3"/>
+      <c r="DI10" s="3"/>
+      <c r="DJ10" s="3"/>
+      <c r="DK10" s="3"/>
+      <c r="DL10" s="3"/>
+      <c r="DM10" s="3"/>
+      <c r="DN10" s="3"/>
+      <c r="DO10" s="3"/>
+      <c r="DP10" s="3"/>
+      <c r="DQ10" s="3"/>
     </row>
-    <row r="11" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>alunos!A10</f>
         <v>25129101</v>
@@ -3137,83 +2934,52 @@
       <c r="AP11" t="s">
         <v>36</v>
       </c>
-      <c r="AS11" s="2"/>
-      <c r="AT11" s="2"/>
-      <c r="AU11" s="2"/>
-      <c r="AX11" s="5"/>
-      <c r="AY11" s="5"/>
-      <c r="AZ11" s="5"/>
-      <c r="BA11" s="5"/>
-      <c r="BB11" s="5"/>
-      <c r="BC11" s="5"/>
-      <c r="BD11" s="5"/>
-      <c r="BE11" s="5"/>
-      <c r="BF11" s="5"/>
-      <c r="BG11" s="5"/>
-      <c r="BH11" s="5"/>
-      <c r="BI11" s="5"/>
-      <c r="BJ11" s="5"/>
-      <c r="BK11" s="5"/>
-      <c r="BL11" s="5"/>
-      <c r="BM11" s="5"/>
-      <c r="BN11" s="5"/>
-      <c r="BO11" s="5"/>
-      <c r="BP11" s="5"/>
-      <c r="BQ11" s="5"/>
-      <c r="BR11" s="5"/>
-      <c r="BS11" s="5"/>
-      <c r="BT11" s="5"/>
-      <c r="BU11" s="5"/>
-      <c r="BV11" s="5"/>
-      <c r="BW11" s="5"/>
-      <c r="BX11" s="5"/>
-      <c r="BY11" s="5"/>
-      <c r="BZ11" s="5"/>
-      <c r="CA11" s="5"/>
-      <c r="CB11" s="5"/>
-      <c r="CC11" s="5"/>
-      <c r="CD11" s="5"/>
-      <c r="CE11" s="5"/>
-      <c r="CF11" s="5"/>
-      <c r="CG11" s="5"/>
-      <c r="CH11" s="5"/>
-      <c r="CI11" s="5"/>
-      <c r="CJ11" s="5"/>
-      <c r="CK11" s="5"/>
-      <c r="CL11" s="5"/>
-      <c r="CM11" s="5"/>
-      <c r="CN11" s="5"/>
-      <c r="CO11" s="5"/>
-      <c r="CP11" s="5"/>
-      <c r="CQ11" s="5"/>
-      <c r="CR11" s="5"/>
-      <c r="CS11" s="5"/>
-      <c r="CT11" s="5"/>
-      <c r="CU11" s="5"/>
-      <c r="CV11" s="5"/>
-      <c r="CW11" s="5"/>
-      <c r="CX11" s="5"/>
-      <c r="CY11" s="5"/>
-      <c r="CZ11" s="5"/>
-      <c r="DA11" s="5"/>
-      <c r="DB11" s="5"/>
-      <c r="DC11" s="5"/>
-      <c r="DD11" s="5"/>
-      <c r="DE11" s="5"/>
-      <c r="DF11" s="5"/>
-      <c r="DG11" s="5"/>
-      <c r="DH11" s="5"/>
-      <c r="DI11" s="5"/>
-      <c r="DJ11" s="5"/>
-      <c r="DK11" s="5"/>
-      <c r="DL11" s="5"/>
-      <c r="DM11" s="5"/>
-      <c r="DN11" s="5"/>
-      <c r="DO11" s="5"/>
-      <c r="DP11" s="5"/>
-      <c r="DQ11" s="5"/>
+      <c r="AQ11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW11"/>
+      <c r="CJ11" s="3"/>
+      <c r="CK11" s="3"/>
+      <c r="CL11" s="3"/>
+      <c r="CM11" s="3"/>
+      <c r="CN11" s="3"/>
+      <c r="CO11" s="3"/>
+      <c r="CP11" s="3"/>
+      <c r="CQ11" s="3"/>
+      <c r="CR11" s="3"/>
+      <c r="CS11" s="3"/>
+      <c r="CT11" s="3"/>
+      <c r="CU11" s="3"/>
+      <c r="CV11" s="3"/>
+      <c r="CW11" s="3"/>
+      <c r="CX11" s="3"/>
+      <c r="CY11" s="3"/>
+      <c r="CZ11" s="3"/>
+      <c r="DA11" s="3"/>
+      <c r="DB11" s="3"/>
+      <c r="DC11" s="3"/>
+      <c r="DD11" s="3"/>
+      <c r="DE11" s="3"/>
+      <c r="DF11" s="3"/>
+      <c r="DG11" s="3"/>
+      <c r="DH11" s="3"/>
+      <c r="DI11" s="3"/>
+      <c r="DJ11" s="3"/>
+      <c r="DK11" s="3"/>
+      <c r="DL11" s="3"/>
+      <c r="DM11" s="3"/>
+      <c r="DN11" s="3"/>
+      <c r="DO11" s="3"/>
+      <c r="DP11" s="3"/>
+      <c r="DQ11" s="3"/>
     </row>
-    <row r="12" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>alunos!A11</f>
         <v>25129081</v>
@@ -3342,83 +3108,52 @@
       <c r="AP12" t="s">
         <v>36</v>
       </c>
-      <c r="AS12" s="2"/>
-      <c r="AT12" s="2"/>
-      <c r="AU12" s="2"/>
-      <c r="AX12" s="5"/>
-      <c r="AY12" s="5"/>
-      <c r="AZ12" s="5"/>
-      <c r="BA12" s="5"/>
-      <c r="BB12" s="5"/>
-      <c r="BC12" s="5"/>
-      <c r="BD12" s="5"/>
-      <c r="BE12" s="5"/>
-      <c r="BF12" s="5"/>
-      <c r="BG12" s="5"/>
-      <c r="BH12" s="5"/>
-      <c r="BI12" s="5"/>
-      <c r="BJ12" s="5"/>
-      <c r="BK12" s="5"/>
-      <c r="BL12" s="5"/>
-      <c r="BM12" s="5"/>
-      <c r="BN12" s="5"/>
-      <c r="BO12" s="5"/>
-      <c r="BP12" s="5"/>
-      <c r="BQ12" s="5"/>
-      <c r="BR12" s="5"/>
-      <c r="BS12" s="5"/>
-      <c r="BT12" s="5"/>
-      <c r="BU12" s="5"/>
-      <c r="BV12" s="5"/>
-      <c r="BW12" s="5"/>
-      <c r="BX12" s="5"/>
-      <c r="BY12" s="5"/>
-      <c r="BZ12" s="5"/>
-      <c r="CA12" s="5"/>
-      <c r="CB12" s="5"/>
-      <c r="CC12" s="5"/>
-      <c r="CD12" s="5"/>
-      <c r="CE12" s="5"/>
-      <c r="CF12" s="5"/>
-      <c r="CG12" s="5"/>
-      <c r="CH12" s="5"/>
-      <c r="CI12" s="5"/>
-      <c r="CJ12" s="5"/>
-      <c r="CK12" s="5"/>
-      <c r="CL12" s="5"/>
-      <c r="CM12" s="5"/>
-      <c r="CN12" s="5"/>
-      <c r="CO12" s="5"/>
-      <c r="CP12" s="5"/>
-      <c r="CQ12" s="5"/>
-      <c r="CR12" s="5"/>
-      <c r="CS12" s="5"/>
-      <c r="CT12" s="5"/>
-      <c r="CU12" s="5"/>
-      <c r="CV12" s="5"/>
-      <c r="CW12" s="5"/>
-      <c r="CX12" s="5"/>
-      <c r="CY12" s="5"/>
-      <c r="CZ12" s="5"/>
-      <c r="DA12" s="5"/>
-      <c r="DB12" s="5"/>
-      <c r="DC12" s="5"/>
-      <c r="DD12" s="5"/>
-      <c r="DE12" s="5"/>
-      <c r="DF12" s="5"/>
-      <c r="DG12" s="5"/>
-      <c r="DH12" s="5"/>
-      <c r="DI12" s="5"/>
-      <c r="DJ12" s="5"/>
-      <c r="DK12" s="5"/>
-      <c r="DL12" s="5"/>
-      <c r="DM12" s="5"/>
-      <c r="DN12" s="5"/>
-      <c r="DO12" s="5"/>
-      <c r="DP12" s="5"/>
-      <c r="DQ12" s="5"/>
+      <c r="AQ12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW12"/>
+      <c r="CJ12" s="3"/>
+      <c r="CK12" s="3"/>
+      <c r="CL12" s="3"/>
+      <c r="CM12" s="3"/>
+      <c r="CN12" s="3"/>
+      <c r="CO12" s="3"/>
+      <c r="CP12" s="3"/>
+      <c r="CQ12" s="3"/>
+      <c r="CR12" s="3"/>
+      <c r="CS12" s="3"/>
+      <c r="CT12" s="3"/>
+      <c r="CU12" s="3"/>
+      <c r="CV12" s="3"/>
+      <c r="CW12" s="3"/>
+      <c r="CX12" s="3"/>
+      <c r="CY12" s="3"/>
+      <c r="CZ12" s="3"/>
+      <c r="DA12" s="3"/>
+      <c r="DB12" s="3"/>
+      <c r="DC12" s="3"/>
+      <c r="DD12" s="3"/>
+      <c r="DE12" s="3"/>
+      <c r="DF12" s="3"/>
+      <c r="DG12" s="3"/>
+      <c r="DH12" s="3"/>
+      <c r="DI12" s="3"/>
+      <c r="DJ12" s="3"/>
+      <c r="DK12" s="3"/>
+      <c r="DL12" s="3"/>
+      <c r="DM12" s="3"/>
+      <c r="DN12" s="3"/>
+      <c r="DO12" s="3"/>
+      <c r="DP12" s="3"/>
+      <c r="DQ12" s="3"/>
     </row>
-    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>alunos!A12</f>
         <v>25129160</v>
@@ -3547,83 +3282,52 @@
       <c r="AP13" t="s">
         <v>36</v>
       </c>
-      <c r="AS13" s="2"/>
-      <c r="AT13" s="2"/>
-      <c r="AU13" s="2"/>
-      <c r="AX13" s="5"/>
-      <c r="AY13" s="5"/>
-      <c r="AZ13" s="5"/>
-      <c r="BA13" s="5"/>
-      <c r="BB13" s="5"/>
-      <c r="BC13" s="5"/>
-      <c r="BD13" s="5"/>
-      <c r="BE13" s="5"/>
-      <c r="BF13" s="5"/>
-      <c r="BG13" s="5"/>
-      <c r="BH13" s="5"/>
-      <c r="BI13" s="5"/>
-      <c r="BJ13" s="5"/>
-      <c r="BK13" s="5"/>
-      <c r="BL13" s="5"/>
-      <c r="BM13" s="5"/>
-      <c r="BN13" s="5"/>
-      <c r="BO13" s="5"/>
-      <c r="BP13" s="5"/>
-      <c r="BQ13" s="5"/>
-      <c r="BR13" s="5"/>
-      <c r="BS13" s="5"/>
-      <c r="BT13" s="5"/>
-      <c r="BU13" s="5"/>
-      <c r="BV13" s="5"/>
-      <c r="BW13" s="5"/>
-      <c r="BX13" s="5"/>
-      <c r="BY13" s="5"/>
-      <c r="BZ13" s="5"/>
-      <c r="CA13" s="5"/>
-      <c r="CB13" s="5"/>
-      <c r="CC13" s="5"/>
-      <c r="CD13" s="5"/>
-      <c r="CE13" s="5"/>
-      <c r="CF13" s="5"/>
-      <c r="CG13" s="5"/>
-      <c r="CH13" s="5"/>
-      <c r="CI13" s="5"/>
-      <c r="CJ13" s="5"/>
-      <c r="CK13" s="5"/>
-      <c r="CL13" s="5"/>
-      <c r="CM13" s="5"/>
-      <c r="CN13" s="5"/>
-      <c r="CO13" s="5"/>
-      <c r="CP13" s="5"/>
-      <c r="CQ13" s="5"/>
-      <c r="CR13" s="5"/>
-      <c r="CS13" s="5"/>
-      <c r="CT13" s="5"/>
-      <c r="CU13" s="5"/>
-      <c r="CV13" s="5"/>
-      <c r="CW13" s="5"/>
-      <c r="CX13" s="5"/>
-      <c r="CY13" s="5"/>
-      <c r="CZ13" s="5"/>
-      <c r="DA13" s="5"/>
-      <c r="DB13" s="5"/>
-      <c r="DC13" s="5"/>
-      <c r="DD13" s="5"/>
-      <c r="DE13" s="5"/>
-      <c r="DF13" s="5"/>
-      <c r="DG13" s="5"/>
-      <c r="DH13" s="5"/>
-      <c r="DI13" s="5"/>
-      <c r="DJ13" s="5"/>
-      <c r="DK13" s="5"/>
-      <c r="DL13" s="5"/>
-      <c r="DM13" s="5"/>
-      <c r="DN13" s="5"/>
-      <c r="DO13" s="5"/>
-      <c r="DP13" s="5"/>
-      <c r="DQ13" s="5"/>
+      <c r="AQ13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW13"/>
+      <c r="CJ13" s="3"/>
+      <c r="CK13" s="3"/>
+      <c r="CL13" s="3"/>
+      <c r="CM13" s="3"/>
+      <c r="CN13" s="3"/>
+      <c r="CO13" s="3"/>
+      <c r="CP13" s="3"/>
+      <c r="CQ13" s="3"/>
+      <c r="CR13" s="3"/>
+      <c r="CS13" s="3"/>
+      <c r="CT13" s="3"/>
+      <c r="CU13" s="3"/>
+      <c r="CV13" s="3"/>
+      <c r="CW13" s="3"/>
+      <c r="CX13" s="3"/>
+      <c r="CY13" s="3"/>
+      <c r="CZ13" s="3"/>
+      <c r="DA13" s="3"/>
+      <c r="DB13" s="3"/>
+      <c r="DC13" s="3"/>
+      <c r="DD13" s="3"/>
+      <c r="DE13" s="3"/>
+      <c r="DF13" s="3"/>
+      <c r="DG13" s="3"/>
+      <c r="DH13" s="3"/>
+      <c r="DI13" s="3"/>
+      <c r="DJ13" s="3"/>
+      <c r="DK13" s="3"/>
+      <c r="DL13" s="3"/>
+      <c r="DM13" s="3"/>
+      <c r="DN13" s="3"/>
+      <c r="DO13" s="3"/>
+      <c r="DP13" s="3"/>
+      <c r="DQ13" s="3"/>
     </row>
-    <row r="14" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>alunos!A13</f>
         <v>25129079</v>
@@ -3752,83 +3456,52 @@
       <c r="AP14" t="s">
         <v>36</v>
       </c>
-      <c r="AS14" s="2"/>
-      <c r="AT14" s="2"/>
-      <c r="AU14" s="2"/>
-      <c r="AX14" s="5"/>
-      <c r="AY14" s="5"/>
-      <c r="AZ14" s="5"/>
-      <c r="BA14" s="5"/>
-      <c r="BB14" s="5"/>
-      <c r="BC14" s="5"/>
-      <c r="BD14" s="5"/>
-      <c r="BE14" s="5"/>
-      <c r="BF14" s="5"/>
-      <c r="BG14" s="5"/>
-      <c r="BH14" s="5"/>
-      <c r="BI14" s="5"/>
-      <c r="BJ14" s="5"/>
-      <c r="BK14" s="5"/>
-      <c r="BL14" s="5"/>
-      <c r="BM14" s="5"/>
-      <c r="BN14" s="5"/>
-      <c r="BO14" s="5"/>
-      <c r="BP14" s="5"/>
-      <c r="BQ14" s="5"/>
-      <c r="BR14" s="5"/>
-      <c r="BS14" s="5"/>
-      <c r="BT14" s="5"/>
-      <c r="BU14" s="5"/>
-      <c r="BV14" s="5"/>
-      <c r="BW14" s="5"/>
-      <c r="BX14" s="5"/>
-      <c r="BY14" s="5"/>
-      <c r="BZ14" s="5"/>
-      <c r="CA14" s="5"/>
-      <c r="CB14" s="5"/>
-      <c r="CC14" s="5"/>
-      <c r="CD14" s="5"/>
-      <c r="CE14" s="5"/>
-      <c r="CF14" s="5"/>
-      <c r="CG14" s="5"/>
-      <c r="CH14" s="5"/>
-      <c r="CI14" s="5"/>
-      <c r="CJ14" s="5"/>
-      <c r="CK14" s="5"/>
-      <c r="CL14" s="5"/>
-      <c r="CM14" s="5"/>
-      <c r="CN14" s="5"/>
-      <c r="CO14" s="5"/>
-      <c r="CP14" s="5"/>
-      <c r="CQ14" s="5"/>
-      <c r="CR14" s="5"/>
-      <c r="CS14" s="5"/>
-      <c r="CT14" s="5"/>
-      <c r="CU14" s="5"/>
-      <c r="CV14" s="5"/>
-      <c r="CW14" s="5"/>
-      <c r="CX14" s="5"/>
-      <c r="CY14" s="5"/>
-      <c r="CZ14" s="5"/>
-      <c r="DA14" s="5"/>
-      <c r="DB14" s="5"/>
-      <c r="DC14" s="5"/>
-      <c r="DD14" s="5"/>
-      <c r="DE14" s="5"/>
-      <c r="DF14" s="5"/>
-      <c r="DG14" s="5"/>
-      <c r="DH14" s="5"/>
-      <c r="DI14" s="5"/>
-      <c r="DJ14" s="5"/>
-      <c r="DK14" s="5"/>
-      <c r="DL14" s="5"/>
-      <c r="DM14" s="5"/>
-      <c r="DN14" s="5"/>
-      <c r="DO14" s="5"/>
-      <c r="DP14" s="5"/>
-      <c r="DQ14" s="5"/>
+      <c r="AQ14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW14"/>
+      <c r="CJ14" s="3"/>
+      <c r="CK14" s="3"/>
+      <c r="CL14" s="3"/>
+      <c r="CM14" s="3"/>
+      <c r="CN14" s="3"/>
+      <c r="CO14" s="3"/>
+      <c r="CP14" s="3"/>
+      <c r="CQ14" s="3"/>
+      <c r="CR14" s="3"/>
+      <c r="CS14" s="3"/>
+      <c r="CT14" s="3"/>
+      <c r="CU14" s="3"/>
+      <c r="CV14" s="3"/>
+      <c r="CW14" s="3"/>
+      <c r="CX14" s="3"/>
+      <c r="CY14" s="3"/>
+      <c r="CZ14" s="3"/>
+      <c r="DA14" s="3"/>
+      <c r="DB14" s="3"/>
+      <c r="DC14" s="3"/>
+      <c r="DD14" s="3"/>
+      <c r="DE14" s="3"/>
+      <c r="DF14" s="3"/>
+      <c r="DG14" s="3"/>
+      <c r="DH14" s="3"/>
+      <c r="DI14" s="3"/>
+      <c r="DJ14" s="3"/>
+      <c r="DK14" s="3"/>
+      <c r="DL14" s="3"/>
+      <c r="DM14" s="3"/>
+      <c r="DN14" s="3"/>
+      <c r="DO14" s="3"/>
+      <c r="DP14" s="3"/>
+      <c r="DQ14" s="3"/>
     </row>
-    <row r="15" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>alunos!A14</f>
         <v>25129208</v>
@@ -3957,83 +3630,52 @@
       <c r="AP15" t="s">
         <v>36</v>
       </c>
-      <c r="AS15" s="2"/>
-      <c r="AT15" s="2"/>
-      <c r="AU15" s="2"/>
-      <c r="AX15" s="5"/>
-      <c r="AY15" s="5"/>
-      <c r="AZ15" s="5"/>
-      <c r="BA15" s="5"/>
-      <c r="BB15" s="5"/>
-      <c r="BC15" s="5"/>
-      <c r="BD15" s="5"/>
-      <c r="BE15" s="5"/>
-      <c r="BF15" s="5"/>
-      <c r="BG15" s="5"/>
-      <c r="BH15" s="5"/>
-      <c r="BI15" s="5"/>
-      <c r="BJ15" s="5"/>
-      <c r="BK15" s="5"/>
-      <c r="BL15" s="5"/>
-      <c r="BM15" s="5"/>
-      <c r="BN15" s="5"/>
-      <c r="BO15" s="5"/>
-      <c r="BP15" s="5"/>
-      <c r="BQ15" s="5"/>
-      <c r="BR15" s="5"/>
-      <c r="BS15" s="5"/>
-      <c r="BT15" s="5"/>
-      <c r="BU15" s="5"/>
-      <c r="BV15" s="5"/>
-      <c r="BW15" s="5"/>
-      <c r="BX15" s="5"/>
-      <c r="BY15" s="5"/>
-      <c r="BZ15" s="5"/>
-      <c r="CA15" s="5"/>
-      <c r="CB15" s="5"/>
-      <c r="CC15" s="5"/>
-      <c r="CD15" s="5"/>
-      <c r="CE15" s="5"/>
-      <c r="CF15" s="5"/>
-      <c r="CG15" s="5"/>
-      <c r="CH15" s="5"/>
-      <c r="CI15" s="5"/>
-      <c r="CJ15" s="5"/>
-      <c r="CK15" s="5"/>
-      <c r="CL15" s="5"/>
-      <c r="CM15" s="5"/>
-      <c r="CN15" s="5"/>
-      <c r="CO15" s="5"/>
-      <c r="CP15" s="5"/>
-      <c r="CQ15" s="5"/>
-      <c r="CR15" s="5"/>
-      <c r="CS15" s="5"/>
-      <c r="CT15" s="5"/>
-      <c r="CU15" s="5"/>
-      <c r="CV15" s="5"/>
-      <c r="CW15" s="5"/>
-      <c r="CX15" s="5"/>
-      <c r="CY15" s="5"/>
-      <c r="CZ15" s="5"/>
-      <c r="DA15" s="5"/>
-      <c r="DB15" s="5"/>
-      <c r="DC15" s="5"/>
-      <c r="DD15" s="5"/>
-      <c r="DE15" s="5"/>
-      <c r="DF15" s="5"/>
-      <c r="DG15" s="5"/>
-      <c r="DH15" s="5"/>
-      <c r="DI15" s="5"/>
-      <c r="DJ15" s="5"/>
-      <c r="DK15" s="5"/>
-      <c r="DL15" s="5"/>
-      <c r="DM15" s="5"/>
-      <c r="DN15" s="5"/>
-      <c r="DO15" s="5"/>
-      <c r="DP15" s="5"/>
-      <c r="DQ15" s="5"/>
+      <c r="AQ15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS15" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW15"/>
+      <c r="CJ15" s="3"/>
+      <c r="CK15" s="3"/>
+      <c r="CL15" s="3"/>
+      <c r="CM15" s="3"/>
+      <c r="CN15" s="3"/>
+      <c r="CO15" s="3"/>
+      <c r="CP15" s="3"/>
+      <c r="CQ15" s="3"/>
+      <c r="CR15" s="3"/>
+      <c r="CS15" s="3"/>
+      <c r="CT15" s="3"/>
+      <c r="CU15" s="3"/>
+      <c r="CV15" s="3"/>
+      <c r="CW15" s="3"/>
+      <c r="CX15" s="3"/>
+      <c r="CY15" s="3"/>
+      <c r="CZ15" s="3"/>
+      <c r="DA15" s="3"/>
+      <c r="DB15" s="3"/>
+      <c r="DC15" s="3"/>
+      <c r="DD15" s="3"/>
+      <c r="DE15" s="3"/>
+      <c r="DF15" s="3"/>
+      <c r="DG15" s="3"/>
+      <c r="DH15" s="3"/>
+      <c r="DI15" s="3"/>
+      <c r="DJ15" s="3"/>
+      <c r="DK15" s="3"/>
+      <c r="DL15" s="3"/>
+      <c r="DM15" s="3"/>
+      <c r="DN15" s="3"/>
+      <c r="DO15" s="3"/>
+      <c r="DP15" s="3"/>
+      <c r="DQ15" s="3"/>
     </row>
-    <row r="16" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>alunos!A15</f>
         <v>25129025</v>
@@ -4162,83 +3804,52 @@
       <c r="AP16" t="s">
         <v>36</v>
       </c>
-      <c r="AS16" s="2"/>
-      <c r="AT16" s="2"/>
-      <c r="AU16" s="2"/>
-      <c r="AX16" s="5"/>
-      <c r="AY16" s="5"/>
-      <c r="AZ16" s="5"/>
-      <c r="BA16" s="5"/>
-      <c r="BB16" s="5"/>
-      <c r="BC16" s="5"/>
-      <c r="BD16" s="5"/>
-      <c r="BE16" s="5"/>
-      <c r="BF16" s="5"/>
-      <c r="BG16" s="5"/>
-      <c r="BH16" s="5"/>
-      <c r="BI16" s="5"/>
-      <c r="BJ16" s="5"/>
-      <c r="BK16" s="5"/>
-      <c r="BL16" s="5"/>
-      <c r="BM16" s="5"/>
-      <c r="BN16" s="5"/>
-      <c r="BO16" s="5"/>
-      <c r="BP16" s="5"/>
-      <c r="BQ16" s="5"/>
-      <c r="BR16" s="5"/>
-      <c r="BS16" s="5"/>
-      <c r="BT16" s="5"/>
-      <c r="BU16" s="5"/>
-      <c r="BV16" s="5"/>
-      <c r="BW16" s="5"/>
-      <c r="BX16" s="5"/>
-      <c r="BY16" s="5"/>
-      <c r="BZ16" s="5"/>
-      <c r="CA16" s="5"/>
-      <c r="CB16" s="5"/>
-      <c r="CC16" s="5"/>
-      <c r="CD16" s="5"/>
-      <c r="CE16" s="5"/>
-      <c r="CF16" s="5"/>
-      <c r="CG16" s="5"/>
-      <c r="CH16" s="5"/>
-      <c r="CI16" s="5"/>
-      <c r="CJ16" s="5"/>
-      <c r="CK16" s="5"/>
-      <c r="CL16" s="5"/>
-      <c r="CM16" s="5"/>
-      <c r="CN16" s="5"/>
-      <c r="CO16" s="5"/>
-      <c r="CP16" s="5"/>
-      <c r="CQ16" s="5"/>
-      <c r="CR16" s="5"/>
-      <c r="CS16" s="5"/>
-      <c r="CT16" s="5"/>
-      <c r="CU16" s="5"/>
-      <c r="CV16" s="5"/>
-      <c r="CW16" s="5"/>
-      <c r="CX16" s="5"/>
-      <c r="CY16" s="5"/>
-      <c r="CZ16" s="5"/>
-      <c r="DA16" s="5"/>
-      <c r="DB16" s="5"/>
-      <c r="DC16" s="5"/>
-      <c r="DD16" s="5"/>
-      <c r="DE16" s="5"/>
-      <c r="DF16" s="5"/>
-      <c r="DG16" s="5"/>
-      <c r="DH16" s="5"/>
-      <c r="DI16" s="5"/>
-      <c r="DJ16" s="5"/>
-      <c r="DK16" s="5"/>
-      <c r="DL16" s="5"/>
-      <c r="DM16" s="5"/>
-      <c r="DN16" s="5"/>
-      <c r="DO16" s="5"/>
-      <c r="DP16" s="5"/>
-      <c r="DQ16" s="5"/>
+      <c r="AQ16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW16"/>
+      <c r="CJ16" s="3"/>
+      <c r="CK16" s="3"/>
+      <c r="CL16" s="3"/>
+      <c r="CM16" s="3"/>
+      <c r="CN16" s="3"/>
+      <c r="CO16" s="3"/>
+      <c r="CP16" s="3"/>
+      <c r="CQ16" s="3"/>
+      <c r="CR16" s="3"/>
+      <c r="CS16" s="3"/>
+      <c r="CT16" s="3"/>
+      <c r="CU16" s="3"/>
+      <c r="CV16" s="3"/>
+      <c r="CW16" s="3"/>
+      <c r="CX16" s="3"/>
+      <c r="CY16" s="3"/>
+      <c r="CZ16" s="3"/>
+      <c r="DA16" s="3"/>
+      <c r="DB16" s="3"/>
+      <c r="DC16" s="3"/>
+      <c r="DD16" s="3"/>
+      <c r="DE16" s="3"/>
+      <c r="DF16" s="3"/>
+      <c r="DG16" s="3"/>
+      <c r="DH16" s="3"/>
+      <c r="DI16" s="3"/>
+      <c r="DJ16" s="3"/>
+      <c r="DK16" s="3"/>
+      <c r="DL16" s="3"/>
+      <c r="DM16" s="3"/>
+      <c r="DN16" s="3"/>
+      <c r="DO16" s="3"/>
+      <c r="DP16" s="3"/>
+      <c r="DQ16" s="3"/>
     </row>
-    <row r="17" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>alunos!A16</f>
         <v>25129121</v>
@@ -4367,83 +3978,52 @@
       <c r="AP17" t="s">
         <v>36</v>
       </c>
-      <c r="AS17" s="2"/>
-      <c r="AT17" s="2"/>
-      <c r="AU17" s="2"/>
-      <c r="AX17" s="5"/>
-      <c r="AY17" s="5"/>
-      <c r="AZ17" s="5"/>
-      <c r="BA17" s="5"/>
-      <c r="BB17" s="5"/>
-      <c r="BC17" s="5"/>
-      <c r="BD17" s="5"/>
-      <c r="BE17" s="5"/>
-      <c r="BF17" s="5"/>
-      <c r="BG17" s="5"/>
-      <c r="BH17" s="5"/>
-      <c r="BI17" s="5"/>
-      <c r="BJ17" s="5"/>
-      <c r="BK17" s="5"/>
-      <c r="BL17" s="5"/>
-      <c r="BM17" s="5"/>
-      <c r="BN17" s="5"/>
-      <c r="BO17" s="5"/>
-      <c r="BP17" s="5"/>
-      <c r="BQ17" s="5"/>
-      <c r="BR17" s="5"/>
-      <c r="BS17" s="5"/>
-      <c r="BT17" s="5"/>
-      <c r="BU17" s="5"/>
-      <c r="BV17" s="5"/>
-      <c r="BW17" s="5"/>
-      <c r="BX17" s="5"/>
-      <c r="BY17" s="5"/>
-      <c r="BZ17" s="5"/>
-      <c r="CA17" s="5"/>
-      <c r="CB17" s="5"/>
-      <c r="CC17" s="5"/>
-      <c r="CD17" s="5"/>
-      <c r="CE17" s="5"/>
-      <c r="CF17" s="5"/>
-      <c r="CG17" s="5"/>
-      <c r="CH17" s="5"/>
-      <c r="CI17" s="5"/>
-      <c r="CJ17" s="5"/>
-      <c r="CK17" s="5"/>
-      <c r="CL17" s="5"/>
-      <c r="CM17" s="5"/>
-      <c r="CN17" s="5"/>
-      <c r="CO17" s="5"/>
-      <c r="CP17" s="5"/>
-      <c r="CQ17" s="5"/>
-      <c r="CR17" s="5"/>
-      <c r="CS17" s="5"/>
-      <c r="CT17" s="5"/>
-      <c r="CU17" s="5"/>
-      <c r="CV17" s="5"/>
-      <c r="CW17" s="5"/>
-      <c r="CX17" s="5"/>
-      <c r="CY17" s="5"/>
-      <c r="CZ17" s="5"/>
-      <c r="DA17" s="5"/>
-      <c r="DB17" s="5"/>
-      <c r="DC17" s="5"/>
-      <c r="DD17" s="5"/>
-      <c r="DE17" s="5"/>
-      <c r="DF17" s="5"/>
-      <c r="DG17" s="5"/>
-      <c r="DH17" s="5"/>
-      <c r="DI17" s="5"/>
-      <c r="DJ17" s="5"/>
-      <c r="DK17" s="5"/>
-      <c r="DL17" s="5"/>
-      <c r="DM17" s="5"/>
-      <c r="DN17" s="5"/>
-      <c r="DO17" s="5"/>
-      <c r="DP17" s="5"/>
-      <c r="DQ17" s="5"/>
+      <c r="AQ17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW17"/>
+      <c r="CJ17" s="3"/>
+      <c r="CK17" s="3"/>
+      <c r="CL17" s="3"/>
+      <c r="CM17" s="3"/>
+      <c r="CN17" s="3"/>
+      <c r="CO17" s="3"/>
+      <c r="CP17" s="3"/>
+      <c r="CQ17" s="3"/>
+      <c r="CR17" s="3"/>
+      <c r="CS17" s="3"/>
+      <c r="CT17" s="3"/>
+      <c r="CU17" s="3"/>
+      <c r="CV17" s="3"/>
+      <c r="CW17" s="3"/>
+      <c r="CX17" s="3"/>
+      <c r="CY17" s="3"/>
+      <c r="CZ17" s="3"/>
+      <c r="DA17" s="3"/>
+      <c r="DB17" s="3"/>
+      <c r="DC17" s="3"/>
+      <c r="DD17" s="3"/>
+      <c r="DE17" s="3"/>
+      <c r="DF17" s="3"/>
+      <c r="DG17" s="3"/>
+      <c r="DH17" s="3"/>
+      <c r="DI17" s="3"/>
+      <c r="DJ17" s="3"/>
+      <c r="DK17" s="3"/>
+      <c r="DL17" s="3"/>
+      <c r="DM17" s="3"/>
+      <c r="DN17" s="3"/>
+      <c r="DO17" s="3"/>
+      <c r="DP17" s="3"/>
+      <c r="DQ17" s="3"/>
     </row>
-    <row r="18" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>alunos!A17</f>
         <v>25129073</v>
@@ -4572,83 +4152,52 @@
       <c r="AP18" t="s">
         <v>36</v>
       </c>
-      <c r="AS18" s="2"/>
-      <c r="AT18" s="2"/>
-      <c r="AU18" s="2"/>
-      <c r="AX18" s="5"/>
-      <c r="AY18" s="5"/>
-      <c r="AZ18" s="5"/>
-      <c r="BA18" s="5"/>
-      <c r="BB18" s="5"/>
-      <c r="BC18" s="5"/>
-      <c r="BD18" s="5"/>
-      <c r="BE18" s="5"/>
-      <c r="BF18" s="5"/>
-      <c r="BG18" s="5"/>
-      <c r="BH18" s="5"/>
-      <c r="BI18" s="5"/>
-      <c r="BJ18" s="5"/>
-      <c r="BK18" s="5"/>
-      <c r="BL18" s="5"/>
-      <c r="BM18" s="5"/>
-      <c r="BN18" s="5"/>
-      <c r="BO18" s="5"/>
-      <c r="BP18" s="5"/>
-      <c r="BQ18" s="5"/>
-      <c r="BR18" s="5"/>
-      <c r="BS18" s="5"/>
-      <c r="BT18" s="5"/>
-      <c r="BU18" s="5"/>
-      <c r="BV18" s="5"/>
-      <c r="BW18" s="5"/>
-      <c r="BX18" s="5"/>
-      <c r="BY18" s="5"/>
-      <c r="BZ18" s="5"/>
-      <c r="CA18" s="5"/>
-      <c r="CB18" s="5"/>
-      <c r="CC18" s="5"/>
-      <c r="CD18" s="5"/>
-      <c r="CE18" s="5"/>
-      <c r="CF18" s="5"/>
-      <c r="CG18" s="5"/>
-      <c r="CH18" s="5"/>
-      <c r="CI18" s="5"/>
-      <c r="CJ18" s="5"/>
-      <c r="CK18" s="5"/>
-      <c r="CL18" s="5"/>
-      <c r="CM18" s="5"/>
-      <c r="CN18" s="5"/>
-      <c r="CO18" s="5"/>
-      <c r="CP18" s="5"/>
-      <c r="CQ18" s="5"/>
-      <c r="CR18" s="5"/>
-      <c r="CS18" s="5"/>
-      <c r="CT18" s="5"/>
-      <c r="CU18" s="5"/>
-      <c r="CV18" s="5"/>
-      <c r="CW18" s="5"/>
-      <c r="CX18" s="5"/>
-      <c r="CY18" s="5"/>
-      <c r="CZ18" s="5"/>
-      <c r="DA18" s="5"/>
-      <c r="DB18" s="5"/>
-      <c r="DC18" s="5"/>
-      <c r="DD18" s="5"/>
-      <c r="DE18" s="5"/>
-      <c r="DF18" s="5"/>
-      <c r="DG18" s="5"/>
-      <c r="DH18" s="5"/>
-      <c r="DI18" s="5"/>
-      <c r="DJ18" s="5"/>
-      <c r="DK18" s="5"/>
-      <c r="DL18" s="5"/>
-      <c r="DM18" s="5"/>
-      <c r="DN18" s="5"/>
-      <c r="DO18" s="5"/>
-      <c r="DP18" s="5"/>
-      <c r="DQ18" s="5"/>
+      <c r="AQ18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW18"/>
+      <c r="CJ18" s="3"/>
+      <c r="CK18" s="3"/>
+      <c r="CL18" s="3"/>
+      <c r="CM18" s="3"/>
+      <c r="CN18" s="3"/>
+      <c r="CO18" s="3"/>
+      <c r="CP18" s="3"/>
+      <c r="CQ18" s="3"/>
+      <c r="CR18" s="3"/>
+      <c r="CS18" s="3"/>
+      <c r="CT18" s="3"/>
+      <c r="CU18" s="3"/>
+      <c r="CV18" s="3"/>
+      <c r="CW18" s="3"/>
+      <c r="CX18" s="3"/>
+      <c r="CY18" s="3"/>
+      <c r="CZ18" s="3"/>
+      <c r="DA18" s="3"/>
+      <c r="DB18" s="3"/>
+      <c r="DC18" s="3"/>
+      <c r="DD18" s="3"/>
+      <c r="DE18" s="3"/>
+      <c r="DF18" s="3"/>
+      <c r="DG18" s="3"/>
+      <c r="DH18" s="3"/>
+      <c r="DI18" s="3"/>
+      <c r="DJ18" s="3"/>
+      <c r="DK18" s="3"/>
+      <c r="DL18" s="3"/>
+      <c r="DM18" s="3"/>
+      <c r="DN18" s="3"/>
+      <c r="DO18" s="3"/>
+      <c r="DP18" s="3"/>
+      <c r="DQ18" s="3"/>
     </row>
-    <row r="19" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>alunos!A18</f>
         <v>25129125</v>
@@ -4777,83 +4326,52 @@
       <c r="AP19" t="s">
         <v>36</v>
       </c>
-      <c r="AS19" s="2"/>
-      <c r="AT19" s="2"/>
-      <c r="AU19" s="2"/>
-      <c r="AX19" s="5"/>
-      <c r="AY19" s="5"/>
-      <c r="AZ19" s="5"/>
-      <c r="BA19" s="5"/>
-      <c r="BB19" s="5"/>
-      <c r="BC19" s="5"/>
-      <c r="BD19" s="5"/>
-      <c r="BE19" s="5"/>
-      <c r="BF19" s="5"/>
-      <c r="BG19" s="5"/>
-      <c r="BH19" s="5"/>
-      <c r="BI19" s="5"/>
-      <c r="BJ19" s="5"/>
-      <c r="BK19" s="5"/>
-      <c r="BL19" s="5"/>
-      <c r="BM19" s="5"/>
-      <c r="BN19" s="5"/>
-      <c r="BO19" s="5"/>
-      <c r="BP19" s="5"/>
-      <c r="BQ19" s="5"/>
-      <c r="BR19" s="5"/>
-      <c r="BS19" s="5"/>
-      <c r="BT19" s="5"/>
-      <c r="BU19" s="5"/>
-      <c r="BV19" s="5"/>
-      <c r="BW19" s="5"/>
-      <c r="BX19" s="5"/>
-      <c r="BY19" s="5"/>
-      <c r="BZ19" s="5"/>
-      <c r="CA19" s="5"/>
-      <c r="CB19" s="5"/>
-      <c r="CC19" s="5"/>
-      <c r="CD19" s="5"/>
-      <c r="CE19" s="5"/>
-      <c r="CF19" s="5"/>
-      <c r="CG19" s="5"/>
-      <c r="CH19" s="5"/>
-      <c r="CI19" s="5"/>
-      <c r="CJ19" s="5"/>
-      <c r="CK19" s="5"/>
-      <c r="CL19" s="5"/>
-      <c r="CM19" s="5"/>
-      <c r="CN19" s="5"/>
-      <c r="CO19" s="5"/>
-      <c r="CP19" s="5"/>
-      <c r="CQ19" s="5"/>
-      <c r="CR19" s="5"/>
-      <c r="CS19" s="5"/>
-      <c r="CT19" s="5"/>
-      <c r="CU19" s="5"/>
-      <c r="CV19" s="5"/>
-      <c r="CW19" s="5"/>
-      <c r="CX19" s="5"/>
-      <c r="CY19" s="5"/>
-      <c r="CZ19" s="5"/>
-      <c r="DA19" s="5"/>
-      <c r="DB19" s="5"/>
-      <c r="DC19" s="5"/>
-      <c r="DD19" s="5"/>
-      <c r="DE19" s="5"/>
-      <c r="DF19" s="5"/>
-      <c r="DG19" s="5"/>
-      <c r="DH19" s="5"/>
-      <c r="DI19" s="5"/>
-      <c r="DJ19" s="5"/>
-      <c r="DK19" s="5"/>
-      <c r="DL19" s="5"/>
-      <c r="DM19" s="5"/>
-      <c r="DN19" s="5"/>
-      <c r="DO19" s="5"/>
-      <c r="DP19" s="5"/>
-      <c r="DQ19" s="5"/>
+      <c r="AQ19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW19"/>
+      <c r="CJ19" s="3"/>
+      <c r="CK19" s="3"/>
+      <c r="CL19" s="3"/>
+      <c r="CM19" s="3"/>
+      <c r="CN19" s="3"/>
+      <c r="CO19" s="3"/>
+      <c r="CP19" s="3"/>
+      <c r="CQ19" s="3"/>
+      <c r="CR19" s="3"/>
+      <c r="CS19" s="3"/>
+      <c r="CT19" s="3"/>
+      <c r="CU19" s="3"/>
+      <c r="CV19" s="3"/>
+      <c r="CW19" s="3"/>
+      <c r="CX19" s="3"/>
+      <c r="CY19" s="3"/>
+      <c r="CZ19" s="3"/>
+      <c r="DA19" s="3"/>
+      <c r="DB19" s="3"/>
+      <c r="DC19" s="3"/>
+      <c r="DD19" s="3"/>
+      <c r="DE19" s="3"/>
+      <c r="DF19" s="3"/>
+      <c r="DG19" s="3"/>
+      <c r="DH19" s="3"/>
+      <c r="DI19" s="3"/>
+      <c r="DJ19" s="3"/>
+      <c r="DK19" s="3"/>
+      <c r="DL19" s="3"/>
+      <c r="DM19" s="3"/>
+      <c r="DN19" s="3"/>
+      <c r="DO19" s="3"/>
+      <c r="DP19" s="3"/>
+      <c r="DQ19" s="3"/>
     </row>
-    <row r="20" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>alunos!A19</f>
         <v>25129027</v>
@@ -4982,83 +4500,52 @@
       <c r="AP20" t="s">
         <v>36</v>
       </c>
-      <c r="AS20" s="2"/>
-      <c r="AT20" s="2"/>
-      <c r="AU20" s="2"/>
-      <c r="AX20" s="5"/>
-      <c r="AY20" s="5"/>
-      <c r="AZ20" s="5"/>
-      <c r="BA20" s="5"/>
-      <c r="BB20" s="5"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="5"/>
-      <c r="BE20" s="5"/>
-      <c r="BF20" s="5"/>
-      <c r="BG20" s="5"/>
-      <c r="BH20" s="5"/>
-      <c r="BI20" s="5"/>
-      <c r="BJ20" s="5"/>
-      <c r="BK20" s="5"/>
-      <c r="BL20" s="5"/>
-      <c r="BM20" s="5"/>
-      <c r="BN20" s="5"/>
-      <c r="BO20" s="5"/>
-      <c r="BP20" s="5"/>
-      <c r="BQ20" s="5"/>
-      <c r="BR20" s="5"/>
-      <c r="BS20" s="5"/>
-      <c r="BT20" s="5"/>
-      <c r="BU20" s="5"/>
-      <c r="BV20" s="5"/>
-      <c r="BW20" s="5"/>
-      <c r="BX20" s="5"/>
-      <c r="BY20" s="5"/>
-      <c r="BZ20" s="5"/>
-      <c r="CA20" s="5"/>
-      <c r="CB20" s="5"/>
-      <c r="CC20" s="5"/>
-      <c r="CD20" s="5"/>
-      <c r="CE20" s="5"/>
-      <c r="CF20" s="5"/>
-      <c r="CG20" s="5"/>
-      <c r="CH20" s="5"/>
-      <c r="CI20" s="5"/>
-      <c r="CJ20" s="5"/>
-      <c r="CK20" s="5"/>
-      <c r="CL20" s="5"/>
-      <c r="CM20" s="5"/>
-      <c r="CN20" s="5"/>
-      <c r="CO20" s="5"/>
-      <c r="CP20" s="5"/>
-      <c r="CQ20" s="5"/>
-      <c r="CR20" s="5"/>
-      <c r="CS20" s="5"/>
-      <c r="CT20" s="5"/>
-      <c r="CU20" s="5"/>
-      <c r="CV20" s="5"/>
-      <c r="CW20" s="5"/>
-      <c r="CX20" s="5"/>
-      <c r="CY20" s="5"/>
-      <c r="CZ20" s="5"/>
-      <c r="DA20" s="5"/>
-      <c r="DB20" s="5"/>
-      <c r="DC20" s="5"/>
-      <c r="DD20" s="5"/>
-      <c r="DE20" s="5"/>
-      <c r="DF20" s="5"/>
-      <c r="DG20" s="5"/>
-      <c r="DH20" s="5"/>
-      <c r="DI20" s="5"/>
-      <c r="DJ20" s="5"/>
-      <c r="DK20" s="5"/>
-      <c r="DL20" s="5"/>
-      <c r="DM20" s="5"/>
-      <c r="DN20" s="5"/>
-      <c r="DO20" s="5"/>
-      <c r="DP20" s="5"/>
-      <c r="DQ20" s="5"/>
+      <c r="AQ20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW20"/>
+      <c r="CJ20" s="3"/>
+      <c r="CK20" s="3"/>
+      <c r="CL20" s="3"/>
+      <c r="CM20" s="3"/>
+      <c r="CN20" s="3"/>
+      <c r="CO20" s="3"/>
+      <c r="CP20" s="3"/>
+      <c r="CQ20" s="3"/>
+      <c r="CR20" s="3"/>
+      <c r="CS20" s="3"/>
+      <c r="CT20" s="3"/>
+      <c r="CU20" s="3"/>
+      <c r="CV20" s="3"/>
+      <c r="CW20" s="3"/>
+      <c r="CX20" s="3"/>
+      <c r="CY20" s="3"/>
+      <c r="CZ20" s="3"/>
+      <c r="DA20" s="3"/>
+      <c r="DB20" s="3"/>
+      <c r="DC20" s="3"/>
+      <c r="DD20" s="3"/>
+      <c r="DE20" s="3"/>
+      <c r="DF20" s="3"/>
+      <c r="DG20" s="3"/>
+      <c r="DH20" s="3"/>
+      <c r="DI20" s="3"/>
+      <c r="DJ20" s="3"/>
+      <c r="DK20" s="3"/>
+      <c r="DL20" s="3"/>
+      <c r="DM20" s="3"/>
+      <c r="DN20" s="3"/>
+      <c r="DO20" s="3"/>
+      <c r="DP20" s="3"/>
+      <c r="DQ20" s="3"/>
     </row>
-    <row r="21" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>alunos!A20</f>
         <v>25129210</v>
@@ -5187,83 +4674,52 @@
       <c r="AP21" t="s">
         <v>36</v>
       </c>
-      <c r="AS21" s="2"/>
-      <c r="AT21" s="2"/>
-      <c r="AU21" s="2"/>
-      <c r="AX21" s="5"/>
-      <c r="AY21" s="5"/>
-      <c r="AZ21" s="5"/>
-      <c r="BA21" s="5"/>
-      <c r="BB21" s="5"/>
-      <c r="BC21" s="5"/>
-      <c r="BD21" s="5"/>
-      <c r="BE21" s="5"/>
-      <c r="BF21" s="5"/>
-      <c r="BG21" s="5"/>
-      <c r="BH21" s="5"/>
-      <c r="BI21" s="5"/>
-      <c r="BJ21" s="5"/>
-      <c r="BK21" s="5"/>
-      <c r="BL21" s="5"/>
-      <c r="BM21" s="5"/>
-      <c r="BN21" s="5"/>
-      <c r="BO21" s="5"/>
-      <c r="BP21" s="5"/>
-      <c r="BQ21" s="5"/>
-      <c r="BR21" s="5"/>
-      <c r="BS21" s="5"/>
-      <c r="BT21" s="5"/>
-      <c r="BU21" s="5"/>
-      <c r="BV21" s="5"/>
-      <c r="BW21" s="5"/>
-      <c r="BX21" s="5"/>
-      <c r="BY21" s="5"/>
-      <c r="BZ21" s="5"/>
-      <c r="CA21" s="5"/>
-      <c r="CB21" s="5"/>
-      <c r="CC21" s="5"/>
-      <c r="CD21" s="5"/>
-      <c r="CE21" s="5"/>
-      <c r="CF21" s="5"/>
-      <c r="CG21" s="5"/>
-      <c r="CH21" s="5"/>
-      <c r="CI21" s="5"/>
-      <c r="CJ21" s="5"/>
-      <c r="CK21" s="5"/>
-      <c r="CL21" s="5"/>
-      <c r="CM21" s="5"/>
-      <c r="CN21" s="5"/>
-      <c r="CO21" s="5"/>
-      <c r="CP21" s="5"/>
-      <c r="CQ21" s="5"/>
-      <c r="CR21" s="5"/>
-      <c r="CS21" s="5"/>
-      <c r="CT21" s="5"/>
-      <c r="CU21" s="5"/>
-      <c r="CV21" s="5"/>
-      <c r="CW21" s="5"/>
-      <c r="CX21" s="5"/>
-      <c r="CY21" s="5"/>
-      <c r="CZ21" s="5"/>
-      <c r="DA21" s="5"/>
-      <c r="DB21" s="5"/>
-      <c r="DC21" s="5"/>
-      <c r="DD21" s="5"/>
-      <c r="DE21" s="5"/>
-      <c r="DF21" s="5"/>
-      <c r="DG21" s="5"/>
-      <c r="DH21" s="5"/>
-      <c r="DI21" s="5"/>
-      <c r="DJ21" s="5"/>
-      <c r="DK21" s="5"/>
-      <c r="DL21" s="5"/>
-      <c r="DM21" s="5"/>
-      <c r="DN21" s="5"/>
-      <c r="DO21" s="5"/>
-      <c r="DP21" s="5"/>
-      <c r="DQ21" s="5"/>
+      <c r="AQ21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW21"/>
+      <c r="CJ21" s="3"/>
+      <c r="CK21" s="3"/>
+      <c r="CL21" s="3"/>
+      <c r="CM21" s="3"/>
+      <c r="CN21" s="3"/>
+      <c r="CO21" s="3"/>
+      <c r="CP21" s="3"/>
+      <c r="CQ21" s="3"/>
+      <c r="CR21" s="3"/>
+      <c r="CS21" s="3"/>
+      <c r="CT21" s="3"/>
+      <c r="CU21" s="3"/>
+      <c r="CV21" s="3"/>
+      <c r="CW21" s="3"/>
+      <c r="CX21" s="3"/>
+      <c r="CY21" s="3"/>
+      <c r="CZ21" s="3"/>
+      <c r="DA21" s="3"/>
+      <c r="DB21" s="3"/>
+      <c r="DC21" s="3"/>
+      <c r="DD21" s="3"/>
+      <c r="DE21" s="3"/>
+      <c r="DF21" s="3"/>
+      <c r="DG21" s="3"/>
+      <c r="DH21" s="3"/>
+      <c r="DI21" s="3"/>
+      <c r="DJ21" s="3"/>
+      <c r="DK21" s="3"/>
+      <c r="DL21" s="3"/>
+      <c r="DM21" s="3"/>
+      <c r="DN21" s="3"/>
+      <c r="DO21" s="3"/>
+      <c r="DP21" s="3"/>
+      <c r="DQ21" s="3"/>
     </row>
-    <row r="22" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>alunos!A21</f>
         <v>25129029</v>
@@ -5392,83 +4848,52 @@
       <c r="AP22" t="s">
         <v>36</v>
       </c>
-      <c r="AS22" s="2"/>
-      <c r="AT22" s="2"/>
-      <c r="AU22" s="2"/>
-      <c r="AX22" s="5"/>
-      <c r="AY22" s="5"/>
-      <c r="AZ22" s="5"/>
-      <c r="BA22" s="5"/>
-      <c r="BB22" s="5"/>
-      <c r="BC22" s="5"/>
-      <c r="BD22" s="5"/>
-      <c r="BE22" s="5"/>
-      <c r="BF22" s="5"/>
-      <c r="BG22" s="5"/>
-      <c r="BH22" s="5"/>
-      <c r="BI22" s="5"/>
-      <c r="BJ22" s="5"/>
-      <c r="BK22" s="5"/>
-      <c r="BL22" s="5"/>
-      <c r="BM22" s="5"/>
-      <c r="BN22" s="5"/>
-      <c r="BO22" s="5"/>
-      <c r="BP22" s="5"/>
-      <c r="BQ22" s="5"/>
-      <c r="BR22" s="5"/>
-      <c r="BS22" s="5"/>
-      <c r="BT22" s="5"/>
-      <c r="BU22" s="5"/>
-      <c r="BV22" s="5"/>
-      <c r="BW22" s="5"/>
-      <c r="BX22" s="5"/>
-      <c r="BY22" s="5"/>
-      <c r="BZ22" s="5"/>
-      <c r="CA22" s="5"/>
-      <c r="CB22" s="5"/>
-      <c r="CC22" s="5"/>
-      <c r="CD22" s="5"/>
-      <c r="CE22" s="5"/>
-      <c r="CF22" s="5"/>
-      <c r="CG22" s="5"/>
-      <c r="CH22" s="5"/>
-      <c r="CI22" s="5"/>
-      <c r="CJ22" s="5"/>
-      <c r="CK22" s="5"/>
-      <c r="CL22" s="5"/>
-      <c r="CM22" s="5"/>
-      <c r="CN22" s="5"/>
-      <c r="CO22" s="5"/>
-      <c r="CP22" s="5"/>
-      <c r="CQ22" s="5"/>
-      <c r="CR22" s="5"/>
-      <c r="CS22" s="5"/>
-      <c r="CT22" s="5"/>
-      <c r="CU22" s="5"/>
-      <c r="CV22" s="5"/>
-      <c r="CW22" s="5"/>
-      <c r="CX22" s="5"/>
-      <c r="CY22" s="5"/>
-      <c r="CZ22" s="5"/>
-      <c r="DA22" s="5"/>
-      <c r="DB22" s="5"/>
-      <c r="DC22" s="5"/>
-      <c r="DD22" s="5"/>
-      <c r="DE22" s="5"/>
-      <c r="DF22" s="5"/>
-      <c r="DG22" s="5"/>
-      <c r="DH22" s="5"/>
-      <c r="DI22" s="5"/>
-      <c r="DJ22" s="5"/>
-      <c r="DK22" s="5"/>
-      <c r="DL22" s="5"/>
-      <c r="DM22" s="5"/>
-      <c r="DN22" s="5"/>
-      <c r="DO22" s="5"/>
-      <c r="DP22" s="5"/>
-      <c r="DQ22" s="5"/>
+      <c r="AQ22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW22"/>
+      <c r="CJ22" s="3"/>
+      <c r="CK22" s="3"/>
+      <c r="CL22" s="3"/>
+      <c r="CM22" s="3"/>
+      <c r="CN22" s="3"/>
+      <c r="CO22" s="3"/>
+      <c r="CP22" s="3"/>
+      <c r="CQ22" s="3"/>
+      <c r="CR22" s="3"/>
+      <c r="CS22" s="3"/>
+      <c r="CT22" s="3"/>
+      <c r="CU22" s="3"/>
+      <c r="CV22" s="3"/>
+      <c r="CW22" s="3"/>
+      <c r="CX22" s="3"/>
+      <c r="CY22" s="3"/>
+      <c r="CZ22" s="3"/>
+      <c r="DA22" s="3"/>
+      <c r="DB22" s="3"/>
+      <c r="DC22" s="3"/>
+      <c r="DD22" s="3"/>
+      <c r="DE22" s="3"/>
+      <c r="DF22" s="3"/>
+      <c r="DG22" s="3"/>
+      <c r="DH22" s="3"/>
+      <c r="DI22" s="3"/>
+      <c r="DJ22" s="3"/>
+      <c r="DK22" s="3"/>
+      <c r="DL22" s="3"/>
+      <c r="DM22" s="3"/>
+      <c r="DN22" s="3"/>
+      <c r="DO22" s="3"/>
+      <c r="DP22" s="3"/>
+      <c r="DQ22" s="3"/>
     </row>
-    <row r="23" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>alunos!A22</f>
         <v>25129127</v>
@@ -5597,83 +5022,52 @@
       <c r="AP23" t="s">
         <v>37</v>
       </c>
-      <c r="AS23" s="2"/>
-      <c r="AT23" s="2"/>
-      <c r="AU23" s="2"/>
-      <c r="AX23" s="5"/>
-      <c r="AY23" s="5"/>
-      <c r="AZ23" s="5"/>
-      <c r="BA23" s="5"/>
-      <c r="BB23" s="5"/>
-      <c r="BC23" s="5"/>
-      <c r="BD23" s="5"/>
-      <c r="BE23" s="5"/>
-      <c r="BF23" s="5"/>
-      <c r="BG23" s="5"/>
-      <c r="BH23" s="5"/>
-      <c r="BI23" s="5"/>
-      <c r="BJ23" s="5"/>
-      <c r="BK23" s="5"/>
-      <c r="BL23" s="5"/>
-      <c r="BM23" s="5"/>
-      <c r="BN23" s="5"/>
-      <c r="BO23" s="5"/>
-      <c r="BP23" s="5"/>
-      <c r="BQ23" s="5"/>
-      <c r="BR23" s="5"/>
-      <c r="BS23" s="5"/>
-      <c r="BT23" s="5"/>
-      <c r="BU23" s="5"/>
-      <c r="BV23" s="5"/>
-      <c r="BW23" s="5"/>
-      <c r="BX23" s="5"/>
-      <c r="BY23" s="5"/>
-      <c r="BZ23" s="5"/>
-      <c r="CA23" s="5"/>
-      <c r="CB23" s="5"/>
-      <c r="CC23" s="5"/>
-      <c r="CD23" s="5"/>
-      <c r="CE23" s="5"/>
-      <c r="CF23" s="5"/>
-      <c r="CG23" s="5"/>
-      <c r="CH23" s="5"/>
-      <c r="CI23" s="5"/>
-      <c r="CJ23" s="5"/>
-      <c r="CK23" s="5"/>
-      <c r="CL23" s="5"/>
-      <c r="CM23" s="5"/>
-      <c r="CN23" s="5"/>
-      <c r="CO23" s="5"/>
-      <c r="CP23" s="5"/>
-      <c r="CQ23" s="5"/>
-      <c r="CR23" s="5"/>
-      <c r="CS23" s="5"/>
-      <c r="CT23" s="5"/>
-      <c r="CU23" s="5"/>
-      <c r="CV23" s="5"/>
-      <c r="CW23" s="5"/>
-      <c r="CX23" s="5"/>
-      <c r="CY23" s="5"/>
-      <c r="CZ23" s="5"/>
-      <c r="DA23" s="5"/>
-      <c r="DB23" s="5"/>
-      <c r="DC23" s="5"/>
-      <c r="DD23" s="5"/>
-      <c r="DE23" s="5"/>
-      <c r="DF23" s="5"/>
-      <c r="DG23" s="5"/>
-      <c r="DH23" s="5"/>
-      <c r="DI23" s="5"/>
-      <c r="DJ23" s="5"/>
-      <c r="DK23" s="5"/>
-      <c r="DL23" s="5"/>
-      <c r="DM23" s="5"/>
-      <c r="DN23" s="5"/>
-      <c r="DO23" s="5"/>
-      <c r="DP23" s="5"/>
-      <c r="DQ23" s="5"/>
+      <c r="AQ23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW23"/>
+      <c r="CJ23" s="3"/>
+      <c r="CK23" s="3"/>
+      <c r="CL23" s="3"/>
+      <c r="CM23" s="3"/>
+      <c r="CN23" s="3"/>
+      <c r="CO23" s="3"/>
+      <c r="CP23" s="3"/>
+      <c r="CQ23" s="3"/>
+      <c r="CR23" s="3"/>
+      <c r="CS23" s="3"/>
+      <c r="CT23" s="3"/>
+      <c r="CU23" s="3"/>
+      <c r="CV23" s="3"/>
+      <c r="CW23" s="3"/>
+      <c r="CX23" s="3"/>
+      <c r="CY23" s="3"/>
+      <c r="CZ23" s="3"/>
+      <c r="DA23" s="3"/>
+      <c r="DB23" s="3"/>
+      <c r="DC23" s="3"/>
+      <c r="DD23" s="3"/>
+      <c r="DE23" s="3"/>
+      <c r="DF23" s="3"/>
+      <c r="DG23" s="3"/>
+      <c r="DH23" s="3"/>
+      <c r="DI23" s="3"/>
+      <c r="DJ23" s="3"/>
+      <c r="DK23" s="3"/>
+      <c r="DL23" s="3"/>
+      <c r="DM23" s="3"/>
+      <c r="DN23" s="3"/>
+      <c r="DO23" s="3"/>
+      <c r="DP23" s="3"/>
+      <c r="DQ23" s="3"/>
     </row>
-    <row r="24" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>alunos!A23</f>
         <v>25129235</v>
@@ -5802,83 +5196,52 @@
       <c r="AP24" t="s">
         <v>36</v>
       </c>
-      <c r="AS24" s="2"/>
-      <c r="AT24" s="2"/>
-      <c r="AU24" s="2"/>
-      <c r="AX24" s="5"/>
-      <c r="AY24" s="5"/>
-      <c r="AZ24" s="5"/>
-      <c r="BA24" s="5"/>
-      <c r="BB24" s="5"/>
-      <c r="BC24" s="5"/>
-      <c r="BD24" s="5"/>
-      <c r="BE24" s="5"/>
-      <c r="BF24" s="5"/>
-      <c r="BG24" s="5"/>
-      <c r="BH24" s="5"/>
-      <c r="BI24" s="5"/>
-      <c r="BJ24" s="5"/>
-      <c r="BK24" s="5"/>
-      <c r="BL24" s="5"/>
-      <c r="BM24" s="5"/>
-      <c r="BN24" s="5"/>
-      <c r="BO24" s="5"/>
-      <c r="BP24" s="5"/>
-      <c r="BQ24" s="5"/>
-      <c r="BR24" s="5"/>
-      <c r="BS24" s="5"/>
-      <c r="BT24" s="5"/>
-      <c r="BU24" s="5"/>
-      <c r="BV24" s="5"/>
-      <c r="BW24" s="5"/>
-      <c r="BX24" s="5"/>
-      <c r="BY24" s="5"/>
-      <c r="BZ24" s="5"/>
-      <c r="CA24" s="5"/>
-      <c r="CB24" s="5"/>
-      <c r="CC24" s="5"/>
-      <c r="CD24" s="5"/>
-      <c r="CE24" s="5"/>
-      <c r="CF24" s="5"/>
-      <c r="CG24" s="5"/>
-      <c r="CH24" s="5"/>
-      <c r="CI24" s="5"/>
-      <c r="CJ24" s="5"/>
-      <c r="CK24" s="5"/>
-      <c r="CL24" s="5"/>
-      <c r="CM24" s="5"/>
-      <c r="CN24" s="5"/>
-      <c r="CO24" s="5"/>
-      <c r="CP24" s="5"/>
-      <c r="CQ24" s="5"/>
-      <c r="CR24" s="5"/>
-      <c r="CS24" s="5"/>
-      <c r="CT24" s="5"/>
-      <c r="CU24" s="5"/>
-      <c r="CV24" s="5"/>
-      <c r="CW24" s="5"/>
-      <c r="CX24" s="5"/>
-      <c r="CY24" s="5"/>
-      <c r="CZ24" s="5"/>
-      <c r="DA24" s="5"/>
-      <c r="DB24" s="5"/>
-      <c r="DC24" s="5"/>
-      <c r="DD24" s="5"/>
-      <c r="DE24" s="5"/>
-      <c r="DF24" s="5"/>
-      <c r="DG24" s="5"/>
-      <c r="DH24" s="5"/>
-      <c r="DI24" s="5"/>
-      <c r="DJ24" s="5"/>
-      <c r="DK24" s="5"/>
-      <c r="DL24" s="5"/>
-      <c r="DM24" s="5"/>
-      <c r="DN24" s="5"/>
-      <c r="DO24" s="5"/>
-      <c r="DP24" s="5"/>
-      <c r="DQ24" s="5"/>
+      <c r="AQ24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW24"/>
+      <c r="CJ24" s="3"/>
+      <c r="CK24" s="3"/>
+      <c r="CL24" s="3"/>
+      <c r="CM24" s="3"/>
+      <c r="CN24" s="3"/>
+      <c r="CO24" s="3"/>
+      <c r="CP24" s="3"/>
+      <c r="CQ24" s="3"/>
+      <c r="CR24" s="3"/>
+      <c r="CS24" s="3"/>
+      <c r="CT24" s="3"/>
+      <c r="CU24" s="3"/>
+      <c r="CV24" s="3"/>
+      <c r="CW24" s="3"/>
+      <c r="CX24" s="3"/>
+      <c r="CY24" s="3"/>
+      <c r="CZ24" s="3"/>
+      <c r="DA24" s="3"/>
+      <c r="DB24" s="3"/>
+      <c r="DC24" s="3"/>
+      <c r="DD24" s="3"/>
+      <c r="DE24" s="3"/>
+      <c r="DF24" s="3"/>
+      <c r="DG24" s="3"/>
+      <c r="DH24" s="3"/>
+      <c r="DI24" s="3"/>
+      <c r="DJ24" s="3"/>
+      <c r="DK24" s="3"/>
+      <c r="DL24" s="3"/>
+      <c r="DM24" s="3"/>
+      <c r="DN24" s="3"/>
+      <c r="DO24" s="3"/>
+      <c r="DP24" s="3"/>
+      <c r="DQ24" s="3"/>
     </row>
-    <row r="25" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>alunos!A24</f>
         <v>25129031</v>
@@ -6007,83 +5370,52 @@
       <c r="AP25" t="s">
         <v>37</v>
       </c>
-      <c r="AS25" s="2"/>
-      <c r="AT25" s="2"/>
-      <c r="AU25" s="2"/>
-      <c r="AX25" s="5"/>
-      <c r="AY25" s="5"/>
-      <c r="AZ25" s="5"/>
-      <c r="BA25" s="5"/>
-      <c r="BB25" s="5"/>
-      <c r="BC25" s="5"/>
-      <c r="BD25" s="5"/>
-      <c r="BE25" s="5"/>
-      <c r="BF25" s="5"/>
-      <c r="BG25" s="5"/>
-      <c r="BH25" s="5"/>
-      <c r="BI25" s="5"/>
-      <c r="BJ25" s="5"/>
-      <c r="BK25" s="5"/>
-      <c r="BL25" s="5"/>
-      <c r="BM25" s="5"/>
-      <c r="BN25" s="5"/>
-      <c r="BO25" s="5"/>
-      <c r="BP25" s="5"/>
-      <c r="BQ25" s="5"/>
-      <c r="BR25" s="5"/>
-      <c r="BS25" s="5"/>
-      <c r="BT25" s="5"/>
-      <c r="BU25" s="5"/>
-      <c r="BV25" s="5"/>
-      <c r="BW25" s="5"/>
-      <c r="BX25" s="5"/>
-      <c r="BY25" s="5"/>
-      <c r="BZ25" s="5"/>
-      <c r="CA25" s="5"/>
-      <c r="CB25" s="5"/>
-      <c r="CC25" s="5"/>
-      <c r="CD25" s="5"/>
-      <c r="CE25" s="5"/>
-      <c r="CF25" s="5"/>
-      <c r="CG25" s="5"/>
-      <c r="CH25" s="5"/>
-      <c r="CI25" s="5"/>
-      <c r="CJ25" s="5"/>
-      <c r="CK25" s="5"/>
-      <c r="CL25" s="5"/>
-      <c r="CM25" s="5"/>
-      <c r="CN25" s="5"/>
-      <c r="CO25" s="5"/>
-      <c r="CP25" s="5"/>
-      <c r="CQ25" s="5"/>
-      <c r="CR25" s="5"/>
-      <c r="CS25" s="5"/>
-      <c r="CT25" s="5"/>
-      <c r="CU25" s="5"/>
-      <c r="CV25" s="5"/>
-      <c r="CW25" s="5"/>
-      <c r="CX25" s="5"/>
-      <c r="CY25" s="5"/>
-      <c r="CZ25" s="5"/>
-      <c r="DA25" s="5"/>
-      <c r="DB25" s="5"/>
-      <c r="DC25" s="5"/>
-      <c r="DD25" s="5"/>
-      <c r="DE25" s="5"/>
-      <c r="DF25" s="5"/>
-      <c r="DG25" s="5"/>
-      <c r="DH25" s="5"/>
-      <c r="DI25" s="5"/>
-      <c r="DJ25" s="5"/>
-      <c r="DK25" s="5"/>
-      <c r="DL25" s="5"/>
-      <c r="DM25" s="5"/>
-      <c r="DN25" s="5"/>
-      <c r="DO25" s="5"/>
-      <c r="DP25" s="5"/>
-      <c r="DQ25" s="5"/>
+      <c r="AQ25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW25"/>
+      <c r="CJ25" s="3"/>
+      <c r="CK25" s="3"/>
+      <c r="CL25" s="3"/>
+      <c r="CM25" s="3"/>
+      <c r="CN25" s="3"/>
+      <c r="CO25" s="3"/>
+      <c r="CP25" s="3"/>
+      <c r="CQ25" s="3"/>
+      <c r="CR25" s="3"/>
+      <c r="CS25" s="3"/>
+      <c r="CT25" s="3"/>
+      <c r="CU25" s="3"/>
+      <c r="CV25" s="3"/>
+      <c r="CW25" s="3"/>
+      <c r="CX25" s="3"/>
+      <c r="CY25" s="3"/>
+      <c r="CZ25" s="3"/>
+      <c r="DA25" s="3"/>
+      <c r="DB25" s="3"/>
+      <c r="DC25" s="3"/>
+      <c r="DD25" s="3"/>
+      <c r="DE25" s="3"/>
+      <c r="DF25" s="3"/>
+      <c r="DG25" s="3"/>
+      <c r="DH25" s="3"/>
+      <c r="DI25" s="3"/>
+      <c r="DJ25" s="3"/>
+      <c r="DK25" s="3"/>
+      <c r="DL25" s="3"/>
+      <c r="DM25" s="3"/>
+      <c r="DN25" s="3"/>
+      <c r="DO25" s="3"/>
+      <c r="DP25" s="3"/>
+      <c r="DQ25" s="3"/>
     </row>
-    <row r="26" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>alunos!A25</f>
         <v>25129033</v>
@@ -6212,83 +5544,52 @@
       <c r="AP26" t="s">
         <v>36</v>
       </c>
-      <c r="AS26" s="2"/>
-      <c r="AT26" s="2"/>
-      <c r="AU26" s="2"/>
-      <c r="AX26" s="5"/>
-      <c r="AY26" s="5"/>
-      <c r="AZ26" s="5"/>
-      <c r="BA26" s="5"/>
-      <c r="BB26" s="5"/>
-      <c r="BC26" s="5"/>
-      <c r="BD26" s="5"/>
-      <c r="BE26" s="5"/>
-      <c r="BF26" s="5"/>
-      <c r="BG26" s="5"/>
-      <c r="BH26" s="5"/>
-      <c r="BI26" s="5"/>
-      <c r="BJ26" s="5"/>
-      <c r="BK26" s="5"/>
-      <c r="BL26" s="5"/>
-      <c r="BM26" s="5"/>
-      <c r="BN26" s="5"/>
-      <c r="BO26" s="5"/>
-      <c r="BP26" s="5"/>
-      <c r="BQ26" s="5"/>
-      <c r="BR26" s="5"/>
-      <c r="BS26" s="5"/>
-      <c r="BT26" s="5"/>
-      <c r="BU26" s="5"/>
-      <c r="BV26" s="5"/>
-      <c r="BW26" s="5"/>
-      <c r="BX26" s="5"/>
-      <c r="BY26" s="5"/>
-      <c r="BZ26" s="5"/>
-      <c r="CA26" s="5"/>
-      <c r="CB26" s="5"/>
-      <c r="CC26" s="5"/>
-      <c r="CD26" s="5"/>
-      <c r="CE26" s="5"/>
-      <c r="CF26" s="5"/>
-      <c r="CG26" s="5"/>
-      <c r="CH26" s="5"/>
-      <c r="CI26" s="5"/>
-      <c r="CJ26" s="5"/>
-      <c r="CK26" s="5"/>
-      <c r="CL26" s="5"/>
-      <c r="CM26" s="5"/>
-      <c r="CN26" s="5"/>
-      <c r="CO26" s="5"/>
-      <c r="CP26" s="5"/>
-      <c r="CQ26" s="5"/>
-      <c r="CR26" s="5"/>
-      <c r="CS26" s="5"/>
-      <c r="CT26" s="5"/>
-      <c r="CU26" s="5"/>
-      <c r="CV26" s="5"/>
-      <c r="CW26" s="5"/>
-      <c r="CX26" s="5"/>
-      <c r="CY26" s="5"/>
-      <c r="CZ26" s="5"/>
-      <c r="DA26" s="5"/>
-      <c r="DB26" s="5"/>
-      <c r="DC26" s="5"/>
-      <c r="DD26" s="5"/>
-      <c r="DE26" s="5"/>
-      <c r="DF26" s="5"/>
-      <c r="DG26" s="5"/>
-      <c r="DH26" s="5"/>
-      <c r="DI26" s="5"/>
-      <c r="DJ26" s="5"/>
-      <c r="DK26" s="5"/>
-      <c r="DL26" s="5"/>
-      <c r="DM26" s="5"/>
-      <c r="DN26" s="5"/>
-      <c r="DO26" s="5"/>
-      <c r="DP26" s="5"/>
-      <c r="DQ26" s="5"/>
+      <c r="AQ26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW26"/>
+      <c r="CJ26" s="3"/>
+      <c r="CK26" s="3"/>
+      <c r="CL26" s="3"/>
+      <c r="CM26" s="3"/>
+      <c r="CN26" s="3"/>
+      <c r="CO26" s="3"/>
+      <c r="CP26" s="3"/>
+      <c r="CQ26" s="3"/>
+      <c r="CR26" s="3"/>
+      <c r="CS26" s="3"/>
+      <c r="CT26" s="3"/>
+      <c r="CU26" s="3"/>
+      <c r="CV26" s="3"/>
+      <c r="CW26" s="3"/>
+      <c r="CX26" s="3"/>
+      <c r="CY26" s="3"/>
+      <c r="CZ26" s="3"/>
+      <c r="DA26" s="3"/>
+      <c r="DB26" s="3"/>
+      <c r="DC26" s="3"/>
+      <c r="DD26" s="3"/>
+      <c r="DE26" s="3"/>
+      <c r="DF26" s="3"/>
+      <c r="DG26" s="3"/>
+      <c r="DH26" s="3"/>
+      <c r="DI26" s="3"/>
+      <c r="DJ26" s="3"/>
+      <c r="DK26" s="3"/>
+      <c r="DL26" s="3"/>
+      <c r="DM26" s="3"/>
+      <c r="DN26" s="3"/>
+      <c r="DO26" s="3"/>
+      <c r="DP26" s="3"/>
+      <c r="DQ26" s="3"/>
     </row>
-    <row r="27" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>alunos!A26</f>
         <v>25129162</v>
@@ -6417,83 +5718,52 @@
       <c r="AP27" t="s">
         <v>37</v>
       </c>
-      <c r="AS27" s="2"/>
-      <c r="AT27" s="2"/>
-      <c r="AU27" s="2"/>
-      <c r="AX27" s="5"/>
-      <c r="AY27" s="5"/>
-      <c r="AZ27" s="5"/>
-      <c r="BA27" s="5"/>
-      <c r="BB27" s="5"/>
-      <c r="BC27" s="5"/>
-      <c r="BD27" s="5"/>
-      <c r="BE27" s="5"/>
-      <c r="BF27" s="5"/>
-      <c r="BG27" s="5"/>
-      <c r="BH27" s="5"/>
-      <c r="BI27" s="5"/>
-      <c r="BJ27" s="5"/>
-      <c r="BK27" s="5"/>
-      <c r="BL27" s="5"/>
-      <c r="BM27" s="5"/>
-      <c r="BN27" s="5"/>
-      <c r="BO27" s="5"/>
-      <c r="BP27" s="5"/>
-      <c r="BQ27" s="5"/>
-      <c r="BR27" s="5"/>
-      <c r="BS27" s="5"/>
-      <c r="BT27" s="5"/>
-      <c r="BU27" s="5"/>
-      <c r="BV27" s="5"/>
-      <c r="BW27" s="5"/>
-      <c r="BX27" s="5"/>
-      <c r="BY27" s="5"/>
-      <c r="BZ27" s="5"/>
-      <c r="CA27" s="5"/>
-      <c r="CB27" s="5"/>
-      <c r="CC27" s="5"/>
-      <c r="CD27" s="5"/>
-      <c r="CE27" s="5"/>
-      <c r="CF27" s="5"/>
-      <c r="CG27" s="5"/>
-      <c r="CH27" s="5"/>
-      <c r="CI27" s="5"/>
-      <c r="CJ27" s="5"/>
-      <c r="CK27" s="5"/>
-      <c r="CL27" s="5"/>
-      <c r="CM27" s="5"/>
-      <c r="CN27" s="5"/>
-      <c r="CO27" s="5"/>
-      <c r="CP27" s="5"/>
-      <c r="CQ27" s="5"/>
-      <c r="CR27" s="5"/>
-      <c r="CS27" s="5"/>
-      <c r="CT27" s="5"/>
-      <c r="CU27" s="5"/>
-      <c r="CV27" s="5"/>
-      <c r="CW27" s="5"/>
-      <c r="CX27" s="5"/>
-      <c r="CY27" s="5"/>
-      <c r="CZ27" s="5"/>
-      <c r="DA27" s="5"/>
-      <c r="DB27" s="5"/>
-      <c r="DC27" s="5"/>
-      <c r="DD27" s="5"/>
-      <c r="DE27" s="5"/>
-      <c r="DF27" s="5"/>
-      <c r="DG27" s="5"/>
-      <c r="DH27" s="5"/>
-      <c r="DI27" s="5"/>
-      <c r="DJ27" s="5"/>
-      <c r="DK27" s="5"/>
-      <c r="DL27" s="5"/>
-      <c r="DM27" s="5"/>
-      <c r="DN27" s="5"/>
-      <c r="DO27" s="5"/>
-      <c r="DP27" s="5"/>
-      <c r="DQ27" s="5"/>
+      <c r="AQ27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS27" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW27"/>
+      <c r="CJ27" s="3"/>
+      <c r="CK27" s="3"/>
+      <c r="CL27" s="3"/>
+      <c r="CM27" s="3"/>
+      <c r="CN27" s="3"/>
+      <c r="CO27" s="3"/>
+      <c r="CP27" s="3"/>
+      <c r="CQ27" s="3"/>
+      <c r="CR27" s="3"/>
+      <c r="CS27" s="3"/>
+      <c r="CT27" s="3"/>
+      <c r="CU27" s="3"/>
+      <c r="CV27" s="3"/>
+      <c r="CW27" s="3"/>
+      <c r="CX27" s="3"/>
+      <c r="CY27" s="3"/>
+      <c r="CZ27" s="3"/>
+      <c r="DA27" s="3"/>
+      <c r="DB27" s="3"/>
+      <c r="DC27" s="3"/>
+      <c r="DD27" s="3"/>
+      <c r="DE27" s="3"/>
+      <c r="DF27" s="3"/>
+      <c r="DG27" s="3"/>
+      <c r="DH27" s="3"/>
+      <c r="DI27" s="3"/>
+      <c r="DJ27" s="3"/>
+      <c r="DK27" s="3"/>
+      <c r="DL27" s="3"/>
+      <c r="DM27" s="3"/>
+      <c r="DN27" s="3"/>
+      <c r="DO27" s="3"/>
+      <c r="DP27" s="3"/>
+      <c r="DQ27" s="3"/>
     </row>
-    <row r="28" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>alunos!A27</f>
         <v>25129035</v>
@@ -6622,83 +5892,52 @@
       <c r="AP28" t="s">
         <v>36</v>
       </c>
-      <c r="AS28" s="2"/>
-      <c r="AT28" s="2"/>
-      <c r="AU28" s="2"/>
-      <c r="AX28" s="5"/>
-      <c r="AY28" s="5"/>
-      <c r="AZ28" s="5"/>
-      <c r="BA28" s="5"/>
-      <c r="BB28" s="5"/>
-      <c r="BC28" s="5"/>
-      <c r="BD28" s="5"/>
-      <c r="BE28" s="5"/>
-      <c r="BF28" s="5"/>
-      <c r="BG28" s="5"/>
-      <c r="BH28" s="5"/>
-      <c r="BI28" s="5"/>
-      <c r="BJ28" s="5"/>
-      <c r="BK28" s="5"/>
-      <c r="BL28" s="5"/>
-      <c r="BM28" s="5"/>
-      <c r="BN28" s="5"/>
-      <c r="BO28" s="5"/>
-      <c r="BP28" s="5"/>
-      <c r="BQ28" s="5"/>
-      <c r="BR28" s="5"/>
-      <c r="BS28" s="5"/>
-      <c r="BT28" s="5"/>
-      <c r="BU28" s="5"/>
-      <c r="BV28" s="5"/>
-      <c r="BW28" s="5"/>
-      <c r="BX28" s="5"/>
-      <c r="BY28" s="5"/>
-      <c r="BZ28" s="5"/>
-      <c r="CA28" s="5"/>
-      <c r="CB28" s="5"/>
-      <c r="CC28" s="5"/>
-      <c r="CD28" s="5"/>
-      <c r="CE28" s="5"/>
-      <c r="CF28" s="5"/>
-      <c r="CG28" s="5"/>
-      <c r="CH28" s="5"/>
-      <c r="CI28" s="5"/>
-      <c r="CJ28" s="5"/>
-      <c r="CK28" s="5"/>
-      <c r="CL28" s="5"/>
-      <c r="CM28" s="5"/>
-      <c r="CN28" s="5"/>
-      <c r="CO28" s="5"/>
-      <c r="CP28" s="5"/>
-      <c r="CQ28" s="5"/>
-      <c r="CR28" s="5"/>
-      <c r="CS28" s="5"/>
-      <c r="CT28" s="5"/>
-      <c r="CU28" s="5"/>
-      <c r="CV28" s="5"/>
-      <c r="CW28" s="5"/>
-      <c r="CX28" s="5"/>
-      <c r="CY28" s="5"/>
-      <c r="CZ28" s="5"/>
-      <c r="DA28" s="5"/>
-      <c r="DB28" s="5"/>
-      <c r="DC28" s="5"/>
-      <c r="DD28" s="5"/>
-      <c r="DE28" s="5"/>
-      <c r="DF28" s="5"/>
-      <c r="DG28" s="5"/>
-      <c r="DH28" s="5"/>
-      <c r="DI28" s="5"/>
-      <c r="DJ28" s="5"/>
-      <c r="DK28" s="5"/>
-      <c r="DL28" s="5"/>
-      <c r="DM28" s="5"/>
-      <c r="DN28" s="5"/>
-      <c r="DO28" s="5"/>
-      <c r="DP28" s="5"/>
-      <c r="DQ28" s="5"/>
+      <c r="AQ28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW28"/>
+      <c r="CJ28" s="3"/>
+      <c r="CK28" s="3"/>
+      <c r="CL28" s="3"/>
+      <c r="CM28" s="3"/>
+      <c r="CN28" s="3"/>
+      <c r="CO28" s="3"/>
+      <c r="CP28" s="3"/>
+      <c r="CQ28" s="3"/>
+      <c r="CR28" s="3"/>
+      <c r="CS28" s="3"/>
+      <c r="CT28" s="3"/>
+      <c r="CU28" s="3"/>
+      <c r="CV28" s="3"/>
+      <c r="CW28" s="3"/>
+      <c r="CX28" s="3"/>
+      <c r="CY28" s="3"/>
+      <c r="CZ28" s="3"/>
+      <c r="DA28" s="3"/>
+      <c r="DB28" s="3"/>
+      <c r="DC28" s="3"/>
+      <c r="DD28" s="3"/>
+      <c r="DE28" s="3"/>
+      <c r="DF28" s="3"/>
+      <c r="DG28" s="3"/>
+      <c r="DH28" s="3"/>
+      <c r="DI28" s="3"/>
+      <c r="DJ28" s="3"/>
+      <c r="DK28" s="3"/>
+      <c r="DL28" s="3"/>
+      <c r="DM28" s="3"/>
+      <c r="DN28" s="3"/>
+      <c r="DO28" s="3"/>
+      <c r="DP28" s="3"/>
+      <c r="DQ28" s="3"/>
     </row>
-    <row r="29" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>alunos!A28</f>
         <v>25129039</v>
@@ -6827,83 +6066,52 @@
       <c r="AP29" t="s">
         <v>36</v>
       </c>
-      <c r="AS29" s="2"/>
-      <c r="AT29" s="2"/>
-      <c r="AU29" s="2"/>
-      <c r="AX29" s="5"/>
-      <c r="AY29" s="5"/>
-      <c r="AZ29" s="5"/>
-      <c r="BA29" s="5"/>
-      <c r="BB29" s="5"/>
-      <c r="BC29" s="5"/>
-      <c r="BD29" s="5"/>
-      <c r="BE29" s="5"/>
-      <c r="BF29" s="5"/>
-      <c r="BG29" s="5"/>
-      <c r="BH29" s="5"/>
-      <c r="BI29" s="5"/>
-      <c r="BJ29" s="5"/>
-      <c r="BK29" s="5"/>
-      <c r="BL29" s="5"/>
-      <c r="BM29" s="5"/>
-      <c r="BN29" s="5"/>
-      <c r="BO29" s="5"/>
-      <c r="BP29" s="5"/>
-      <c r="BQ29" s="5"/>
-      <c r="BR29" s="5"/>
-      <c r="BS29" s="5"/>
-      <c r="BT29" s="5"/>
-      <c r="BU29" s="5"/>
-      <c r="BV29" s="5"/>
-      <c r="BW29" s="5"/>
-      <c r="BX29" s="5"/>
-      <c r="BY29" s="5"/>
-      <c r="BZ29" s="5"/>
-      <c r="CA29" s="5"/>
-      <c r="CB29" s="5"/>
-      <c r="CC29" s="5"/>
-      <c r="CD29" s="5"/>
-      <c r="CE29" s="5"/>
-      <c r="CF29" s="5"/>
-      <c r="CG29" s="5"/>
-      <c r="CH29" s="5"/>
-      <c r="CI29" s="5"/>
-      <c r="CJ29" s="5"/>
-      <c r="CK29" s="5"/>
-      <c r="CL29" s="5"/>
-      <c r="CM29" s="5"/>
-      <c r="CN29" s="5"/>
-      <c r="CO29" s="5"/>
-      <c r="CP29" s="5"/>
-      <c r="CQ29" s="5"/>
-      <c r="CR29" s="5"/>
-      <c r="CS29" s="5"/>
-      <c r="CT29" s="5"/>
-      <c r="CU29" s="5"/>
-      <c r="CV29" s="5"/>
-      <c r="CW29" s="5"/>
-      <c r="CX29" s="5"/>
-      <c r="CY29" s="5"/>
-      <c r="CZ29" s="5"/>
-      <c r="DA29" s="5"/>
-      <c r="DB29" s="5"/>
-      <c r="DC29" s="5"/>
-      <c r="DD29" s="5"/>
-      <c r="DE29" s="5"/>
-      <c r="DF29" s="5"/>
-      <c r="DG29" s="5"/>
-      <c r="DH29" s="5"/>
-      <c r="DI29" s="5"/>
-      <c r="DJ29" s="5"/>
-      <c r="DK29" s="5"/>
-      <c r="DL29" s="5"/>
-      <c r="DM29" s="5"/>
-      <c r="DN29" s="5"/>
-      <c r="DO29" s="5"/>
-      <c r="DP29" s="5"/>
-      <c r="DQ29" s="5"/>
+      <c r="AQ29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR29" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW29"/>
+      <c r="CJ29" s="3"/>
+      <c r="CK29" s="3"/>
+      <c r="CL29" s="3"/>
+      <c r="CM29" s="3"/>
+      <c r="CN29" s="3"/>
+      <c r="CO29" s="3"/>
+      <c r="CP29" s="3"/>
+      <c r="CQ29" s="3"/>
+      <c r="CR29" s="3"/>
+      <c r="CS29" s="3"/>
+      <c r="CT29" s="3"/>
+      <c r="CU29" s="3"/>
+      <c r="CV29" s="3"/>
+      <c r="CW29" s="3"/>
+      <c r="CX29" s="3"/>
+      <c r="CY29" s="3"/>
+      <c r="CZ29" s="3"/>
+      <c r="DA29" s="3"/>
+      <c r="DB29" s="3"/>
+      <c r="DC29" s="3"/>
+      <c r="DD29" s="3"/>
+      <c r="DE29" s="3"/>
+      <c r="DF29" s="3"/>
+      <c r="DG29" s="3"/>
+      <c r="DH29" s="3"/>
+      <c r="DI29" s="3"/>
+      <c r="DJ29" s="3"/>
+      <c r="DK29" s="3"/>
+      <c r="DL29" s="3"/>
+      <c r="DM29" s="3"/>
+      <c r="DN29" s="3"/>
+      <c r="DO29" s="3"/>
+      <c r="DP29" s="3"/>
+      <c r="DQ29" s="3"/>
     </row>
-    <row r="30" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>alunos!A29</f>
         <v>25129041</v>
@@ -7032,83 +6240,52 @@
       <c r="AP30" t="s">
         <v>36</v>
       </c>
-      <c r="AS30" s="2"/>
-      <c r="AT30" s="2"/>
-      <c r="AU30" s="2"/>
-      <c r="AX30" s="5"/>
-      <c r="AY30" s="5"/>
-      <c r="AZ30" s="5"/>
-      <c r="BA30" s="5"/>
-      <c r="BB30" s="5"/>
-      <c r="BC30" s="5"/>
-      <c r="BD30" s="5"/>
-      <c r="BE30" s="5"/>
-      <c r="BF30" s="5"/>
-      <c r="BG30" s="5"/>
-      <c r="BH30" s="5"/>
-      <c r="BI30" s="5"/>
-      <c r="BJ30" s="5"/>
-      <c r="BK30" s="5"/>
-      <c r="BL30" s="5"/>
-      <c r="BM30" s="5"/>
-      <c r="BN30" s="5"/>
-      <c r="BO30" s="5"/>
-      <c r="BP30" s="5"/>
-      <c r="BQ30" s="5"/>
-      <c r="BR30" s="5"/>
-      <c r="BS30" s="5"/>
-      <c r="BT30" s="5"/>
-      <c r="BU30" s="5"/>
-      <c r="BV30" s="5"/>
-      <c r="BW30" s="5"/>
-      <c r="BX30" s="5"/>
-      <c r="BY30" s="5"/>
-      <c r="BZ30" s="5"/>
-      <c r="CA30" s="5"/>
-      <c r="CB30" s="5"/>
-      <c r="CC30" s="5"/>
-      <c r="CD30" s="5"/>
-      <c r="CE30" s="5"/>
-      <c r="CF30" s="5"/>
-      <c r="CG30" s="5"/>
-      <c r="CH30" s="5"/>
-      <c r="CI30" s="5"/>
-      <c r="CJ30" s="5"/>
-      <c r="CK30" s="5"/>
-      <c r="CL30" s="5"/>
-      <c r="CM30" s="5"/>
-      <c r="CN30" s="5"/>
-      <c r="CO30" s="5"/>
-      <c r="CP30" s="5"/>
-      <c r="CQ30" s="5"/>
-      <c r="CR30" s="5"/>
-      <c r="CS30" s="5"/>
-      <c r="CT30" s="5"/>
-      <c r="CU30" s="5"/>
-      <c r="CV30" s="5"/>
-      <c r="CW30" s="5"/>
-      <c r="CX30" s="5"/>
-      <c r="CY30" s="5"/>
-      <c r="CZ30" s="5"/>
-      <c r="DA30" s="5"/>
-      <c r="DB30" s="5"/>
-      <c r="DC30" s="5"/>
-      <c r="DD30" s="5"/>
-      <c r="DE30" s="5"/>
-      <c r="DF30" s="5"/>
-      <c r="DG30" s="5"/>
-      <c r="DH30" s="5"/>
-      <c r="DI30" s="5"/>
-      <c r="DJ30" s="5"/>
-      <c r="DK30" s="5"/>
-      <c r="DL30" s="5"/>
-      <c r="DM30" s="5"/>
-      <c r="DN30" s="5"/>
-      <c r="DO30" s="5"/>
-      <c r="DP30" s="5"/>
-      <c r="DQ30" s="5"/>
+      <c r="AQ30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR30" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW30"/>
+      <c r="CJ30" s="3"/>
+      <c r="CK30" s="3"/>
+      <c r="CL30" s="3"/>
+      <c r="CM30" s="3"/>
+      <c r="CN30" s="3"/>
+      <c r="CO30" s="3"/>
+      <c r="CP30" s="3"/>
+      <c r="CQ30" s="3"/>
+      <c r="CR30" s="3"/>
+      <c r="CS30" s="3"/>
+      <c r="CT30" s="3"/>
+      <c r="CU30" s="3"/>
+      <c r="CV30" s="3"/>
+      <c r="CW30" s="3"/>
+      <c r="CX30" s="3"/>
+      <c r="CY30" s="3"/>
+      <c r="CZ30" s="3"/>
+      <c r="DA30" s="3"/>
+      <c r="DB30" s="3"/>
+      <c r="DC30" s="3"/>
+      <c r="DD30" s="3"/>
+      <c r="DE30" s="3"/>
+      <c r="DF30" s="3"/>
+      <c r="DG30" s="3"/>
+      <c r="DH30" s="3"/>
+      <c r="DI30" s="3"/>
+      <c r="DJ30" s="3"/>
+      <c r="DK30" s="3"/>
+      <c r="DL30" s="3"/>
+      <c r="DM30" s="3"/>
+      <c r="DN30" s="3"/>
+      <c r="DO30" s="3"/>
+      <c r="DP30" s="3"/>
+      <c r="DQ30" s="3"/>
     </row>
-    <row r="31" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>alunos!A30</f>
         <v>25129043</v>
@@ -7237,83 +6414,52 @@
       <c r="AP31" t="s">
         <v>37</v>
       </c>
-      <c r="AS31" s="2"/>
-      <c r="AT31" s="2"/>
-      <c r="AU31" s="2"/>
-      <c r="AX31" s="5"/>
-      <c r="AY31" s="5"/>
-      <c r="AZ31" s="5"/>
-      <c r="BA31" s="5"/>
-      <c r="BB31" s="5"/>
-      <c r="BC31" s="5"/>
-      <c r="BD31" s="5"/>
-      <c r="BE31" s="5"/>
-      <c r="BF31" s="5"/>
-      <c r="BG31" s="5"/>
-      <c r="BH31" s="5"/>
-      <c r="BI31" s="5"/>
-      <c r="BJ31" s="5"/>
-      <c r="BK31" s="5"/>
-      <c r="BL31" s="5"/>
-      <c r="BM31" s="5"/>
-      <c r="BN31" s="5"/>
-      <c r="BO31" s="5"/>
-      <c r="BP31" s="5"/>
-      <c r="BQ31" s="5"/>
-      <c r="BR31" s="5"/>
-      <c r="BS31" s="5"/>
-      <c r="BT31" s="5"/>
-      <c r="BU31" s="5"/>
-      <c r="BV31" s="5"/>
-      <c r="BW31" s="5"/>
-      <c r="BX31" s="5"/>
-      <c r="BY31" s="5"/>
-      <c r="BZ31" s="5"/>
-      <c r="CA31" s="5"/>
-      <c r="CB31" s="5"/>
-      <c r="CC31" s="5"/>
-      <c r="CD31" s="5"/>
-      <c r="CE31" s="5"/>
-      <c r="CF31" s="5"/>
-      <c r="CG31" s="5"/>
-      <c r="CH31" s="5"/>
-      <c r="CI31" s="5"/>
-      <c r="CJ31" s="5"/>
-      <c r="CK31" s="5"/>
-      <c r="CL31" s="5"/>
-      <c r="CM31" s="5"/>
-      <c r="CN31" s="5"/>
-      <c r="CO31" s="5"/>
-      <c r="CP31" s="5"/>
-      <c r="CQ31" s="5"/>
-      <c r="CR31" s="5"/>
-      <c r="CS31" s="5"/>
-      <c r="CT31" s="5"/>
-      <c r="CU31" s="5"/>
-      <c r="CV31" s="5"/>
-      <c r="CW31" s="5"/>
-      <c r="CX31" s="5"/>
-      <c r="CY31" s="5"/>
-      <c r="CZ31" s="5"/>
-      <c r="DA31" s="5"/>
-      <c r="DB31" s="5"/>
-      <c r="DC31" s="5"/>
-      <c r="DD31" s="5"/>
-      <c r="DE31" s="5"/>
-      <c r="DF31" s="5"/>
-      <c r="DG31" s="5"/>
-      <c r="DH31" s="5"/>
-      <c r="DI31" s="5"/>
-      <c r="DJ31" s="5"/>
-      <c r="DK31" s="5"/>
-      <c r="DL31" s="5"/>
-      <c r="DM31" s="5"/>
-      <c r="DN31" s="5"/>
-      <c r="DO31" s="5"/>
-      <c r="DP31" s="5"/>
-      <c r="DQ31" s="5"/>
+      <c r="AQ31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS31" t="s">
+        <v>37</v>
+      </c>
+      <c r="AW31"/>
+      <c r="CJ31" s="3"/>
+      <c r="CK31" s="3"/>
+      <c r="CL31" s="3"/>
+      <c r="CM31" s="3"/>
+      <c r="CN31" s="3"/>
+      <c r="CO31" s="3"/>
+      <c r="CP31" s="3"/>
+      <c r="CQ31" s="3"/>
+      <c r="CR31" s="3"/>
+      <c r="CS31" s="3"/>
+      <c r="CT31" s="3"/>
+      <c r="CU31" s="3"/>
+      <c r="CV31" s="3"/>
+      <c r="CW31" s="3"/>
+      <c r="CX31" s="3"/>
+      <c r="CY31" s="3"/>
+      <c r="CZ31" s="3"/>
+      <c r="DA31" s="3"/>
+      <c r="DB31" s="3"/>
+      <c r="DC31" s="3"/>
+      <c r="DD31" s="3"/>
+      <c r="DE31" s="3"/>
+      <c r="DF31" s="3"/>
+      <c r="DG31" s="3"/>
+      <c r="DH31" s="3"/>
+      <c r="DI31" s="3"/>
+      <c r="DJ31" s="3"/>
+      <c r="DK31" s="3"/>
+      <c r="DL31" s="3"/>
+      <c r="DM31" s="3"/>
+      <c r="DN31" s="3"/>
+      <c r="DO31" s="3"/>
+      <c r="DP31" s="3"/>
+      <c r="DQ31" s="3"/>
     </row>
-    <row r="32" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>alunos!A31</f>
         <v>25129189</v>
@@ -7442,83 +6588,52 @@
       <c r="AP32" t="s">
         <v>36</v>
       </c>
-      <c r="AS32" s="2"/>
-      <c r="AT32" s="2"/>
-      <c r="AU32" s="2"/>
-      <c r="AX32" s="5"/>
-      <c r="AY32" s="5"/>
-      <c r="AZ32" s="5"/>
-      <c r="BA32" s="5"/>
-      <c r="BB32" s="5"/>
-      <c r="BC32" s="5"/>
-      <c r="BD32" s="5"/>
-      <c r="BE32" s="5"/>
-      <c r="BF32" s="5"/>
-      <c r="BG32" s="5"/>
-      <c r="BH32" s="5"/>
-      <c r="BI32" s="5"/>
-      <c r="BJ32" s="5"/>
-      <c r="BK32" s="5"/>
-      <c r="BL32" s="5"/>
-      <c r="BM32" s="5"/>
-      <c r="BN32" s="5"/>
-      <c r="BO32" s="5"/>
-      <c r="BP32" s="5"/>
-      <c r="BQ32" s="5"/>
-      <c r="BR32" s="5"/>
-      <c r="BS32" s="5"/>
-      <c r="BT32" s="5"/>
-      <c r="BU32" s="5"/>
-      <c r="BV32" s="5"/>
-      <c r="BW32" s="5"/>
-      <c r="BX32" s="5"/>
-      <c r="BY32" s="5"/>
-      <c r="BZ32" s="5"/>
-      <c r="CA32" s="5"/>
-      <c r="CB32" s="5"/>
-      <c r="CC32" s="5"/>
-      <c r="CD32" s="5"/>
-      <c r="CE32" s="5"/>
-      <c r="CF32" s="5"/>
-      <c r="CG32" s="5"/>
-      <c r="CH32" s="5"/>
-      <c r="CI32" s="5"/>
-      <c r="CJ32" s="5"/>
-      <c r="CK32" s="5"/>
-      <c r="CL32" s="5"/>
-      <c r="CM32" s="5"/>
-      <c r="CN32" s="5"/>
-      <c r="CO32" s="5"/>
-      <c r="CP32" s="5"/>
-      <c r="CQ32" s="5"/>
-      <c r="CR32" s="5"/>
-      <c r="CS32" s="5"/>
-      <c r="CT32" s="5"/>
-      <c r="CU32" s="5"/>
-      <c r="CV32" s="5"/>
-      <c r="CW32" s="5"/>
-      <c r="CX32" s="5"/>
-      <c r="CY32" s="5"/>
-      <c r="CZ32" s="5"/>
-      <c r="DA32" s="5"/>
-      <c r="DB32" s="5"/>
-      <c r="DC32" s="5"/>
-      <c r="DD32" s="5"/>
-      <c r="DE32" s="5"/>
-      <c r="DF32" s="5"/>
-      <c r="DG32" s="5"/>
-      <c r="DH32" s="5"/>
-      <c r="DI32" s="5"/>
-      <c r="DJ32" s="5"/>
-      <c r="DK32" s="5"/>
-      <c r="DL32" s="5"/>
-      <c r="DM32" s="5"/>
-      <c r="DN32" s="5"/>
-      <c r="DO32" s="5"/>
-      <c r="DP32" s="5"/>
-      <c r="DQ32" s="5"/>
+      <c r="AQ32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR32" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW32"/>
+      <c r="CJ32" s="3"/>
+      <c r="CK32" s="3"/>
+      <c r="CL32" s="3"/>
+      <c r="CM32" s="3"/>
+      <c r="CN32" s="3"/>
+      <c r="CO32" s="3"/>
+      <c r="CP32" s="3"/>
+      <c r="CQ32" s="3"/>
+      <c r="CR32" s="3"/>
+      <c r="CS32" s="3"/>
+      <c r="CT32" s="3"/>
+      <c r="CU32" s="3"/>
+      <c r="CV32" s="3"/>
+      <c r="CW32" s="3"/>
+      <c r="CX32" s="3"/>
+      <c r="CY32" s="3"/>
+      <c r="CZ32" s="3"/>
+      <c r="DA32" s="3"/>
+      <c r="DB32" s="3"/>
+      <c r="DC32" s="3"/>
+      <c r="DD32" s="3"/>
+      <c r="DE32" s="3"/>
+      <c r="DF32" s="3"/>
+      <c r="DG32" s="3"/>
+      <c r="DH32" s="3"/>
+      <c r="DI32" s="3"/>
+      <c r="DJ32" s="3"/>
+      <c r="DK32" s="3"/>
+      <c r="DL32" s="3"/>
+      <c r="DM32" s="3"/>
+      <c r="DN32" s="3"/>
+      <c r="DO32" s="3"/>
+      <c r="DP32" s="3"/>
+      <c r="DQ32" s="3"/>
     </row>
-    <row r="33" spans="1:121" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:121" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>alunos!A32</f>
         <v>25129069</v>
@@ -7647,88 +6762,57 @@
       <c r="AP33" t="s">
         <v>36</v>
       </c>
-      <c r="AS33" s="2"/>
-      <c r="AT33" s="2"/>
-      <c r="AU33" s="2"/>
-      <c r="AX33" s="5"/>
-      <c r="AY33" s="5"/>
-      <c r="AZ33" s="5"/>
-      <c r="BA33" s="5"/>
-      <c r="BB33" s="5"/>
-      <c r="BC33" s="5"/>
-      <c r="BD33" s="5"/>
-      <c r="BE33" s="5"/>
-      <c r="BF33" s="5"/>
-      <c r="BG33" s="5"/>
-      <c r="BH33" s="5"/>
-      <c r="BI33" s="5"/>
-      <c r="BJ33" s="5"/>
-      <c r="BK33" s="5"/>
-      <c r="BL33" s="5"/>
-      <c r="BM33" s="5"/>
-      <c r="BN33" s="5"/>
-      <c r="BO33" s="5"/>
-      <c r="BP33" s="5"/>
-      <c r="BQ33" s="5"/>
-      <c r="BR33" s="5"/>
-      <c r="BS33" s="5"/>
-      <c r="BT33" s="5"/>
-      <c r="BU33" s="5"/>
-      <c r="BV33" s="5"/>
-      <c r="BW33" s="5"/>
-      <c r="BX33" s="5"/>
-      <c r="BY33" s="5"/>
-      <c r="BZ33" s="5"/>
-      <c r="CA33" s="5"/>
-      <c r="CB33" s="5"/>
-      <c r="CC33" s="5"/>
-      <c r="CD33" s="5"/>
-      <c r="CE33" s="5"/>
-      <c r="CF33" s="5"/>
-      <c r="CG33" s="5"/>
-      <c r="CH33" s="5"/>
-      <c r="CI33" s="5"/>
-      <c r="CJ33" s="5"/>
-      <c r="CK33" s="5"/>
-      <c r="CL33" s="5"/>
-      <c r="CM33" s="5"/>
-      <c r="CN33" s="5"/>
-      <c r="CO33" s="5"/>
-      <c r="CP33" s="5"/>
-      <c r="CQ33" s="5"/>
-      <c r="CR33" s="5"/>
-      <c r="CS33" s="5"/>
-      <c r="CT33" s="5"/>
-      <c r="CU33" s="5"/>
-      <c r="CV33" s="5"/>
-      <c r="CW33" s="5"/>
-      <c r="CX33" s="5"/>
-      <c r="CY33" s="5"/>
-      <c r="CZ33" s="5"/>
-      <c r="DA33" s="5"/>
-      <c r="DB33" s="5"/>
-      <c r="DC33" s="5"/>
-      <c r="DD33" s="5"/>
-      <c r="DE33" s="5"/>
-      <c r="DF33" s="5"/>
-      <c r="DG33" s="5"/>
-      <c r="DH33" s="5"/>
-      <c r="DI33" s="5"/>
-      <c r="DJ33" s="5"/>
-      <c r="DK33" s="5"/>
-      <c r="DL33" s="5"/>
-      <c r="DM33" s="5"/>
-      <c r="DN33" s="5"/>
-      <c r="DO33" s="5"/>
-      <c r="DP33" s="5"/>
-      <c r="DQ33" s="5"/>
+      <c r="AQ33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR33" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW33"/>
+      <c r="CJ33" s="3"/>
+      <c r="CK33" s="3"/>
+      <c r="CL33" s="3"/>
+      <c r="CM33" s="3"/>
+      <c r="CN33" s="3"/>
+      <c r="CO33" s="3"/>
+      <c r="CP33" s="3"/>
+      <c r="CQ33" s="3"/>
+      <c r="CR33" s="3"/>
+      <c r="CS33" s="3"/>
+      <c r="CT33" s="3"/>
+      <c r="CU33" s="3"/>
+      <c r="CV33" s="3"/>
+      <c r="CW33" s="3"/>
+      <c r="CX33" s="3"/>
+      <c r="CY33" s="3"/>
+      <c r="CZ33" s="3"/>
+      <c r="DA33" s="3"/>
+      <c r="DB33" s="3"/>
+      <c r="DC33" s="3"/>
+      <c r="DD33" s="3"/>
+      <c r="DE33" s="3"/>
+      <c r="DF33" s="3"/>
+      <c r="DG33" s="3"/>
+      <c r="DH33" s="3"/>
+      <c r="DI33" s="3"/>
+      <c r="DJ33" s="3"/>
+      <c r="DK33" s="3"/>
+      <c r="DL33" s="3"/>
+      <c r="DM33" s="3"/>
+      <c r="DN33" s="3"/>
+      <c r="DO33" s="3"/>
+      <c r="DP33" s="3"/>
+      <c r="DQ33" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">
     <sortCondition ref="B3:B33"/>
   </sortState>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="AL3:AX3 BC3:DE3 AZ3:AZ22 D3:AK33 AO4:AX4 BC4:BH10 AL4:AN33 BI4:DE33 AP5:AX10 AO5:AO13 AP11:AY13 BA11:BH22 AO14:AY14 AP15:AY22 AO15:AO33 AP23:BH33">
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="D3:DE33">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -7741,15 +6825,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -7757,7 +6841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>25129175</v>
       </c>
@@ -7765,7 +6849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>25129085</v>
       </c>
@@ -7773,7 +6857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>25129021</v>
       </c>
@@ -7781,7 +6865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>25129019</v>
       </c>
@@ -7789,7 +6873,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>25129023</v>
       </c>
@@ -7797,7 +6881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>25129105</v>
       </c>
@@ -7805,7 +6889,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>25129083</v>
       </c>
@@ -7813,7 +6897,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>25129047</v>
       </c>
@@ -7821,7 +6905,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>25129101</v>
       </c>
@@ -7829,7 +6913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25129081</v>
       </c>
@@ -7837,7 +6921,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>25129160</v>
       </c>
@@ -7845,7 +6929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>25129079</v>
       </c>
@@ -7853,7 +6937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>25129208</v>
       </c>
@@ -7861,7 +6945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>25129025</v>
       </c>
@@ -7869,7 +6953,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>25129121</v>
       </c>
@@ -7877,7 +6961,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>25129073</v>
       </c>
@@ -7885,7 +6969,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>25129125</v>
       </c>
@@ -7893,7 +6977,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>25129027</v>
       </c>
@@ -7901,7 +6985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25129210</v>
       </c>
@@ -7909,7 +6993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>25129029</v>
       </c>
@@ -7917,7 +7001,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25129127</v>
       </c>
@@ -7925,7 +7009,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>25129235</v>
       </c>
@@ -7933,7 +7017,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25129031</v>
       </c>
@@ -7941,7 +7025,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25129033</v>
       </c>
@@ -7949,7 +7033,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25129162</v>
       </c>
@@ -7957,7 +7041,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25129035</v>
       </c>
@@ -7965,7 +7049,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>25129039</v>
       </c>
@@ -7973,7 +7057,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>25129041</v>
       </c>
@@ -7981,7 +7065,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>25129043</v>
       </c>
@@ -7989,7 +7073,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>25129189</v>
       </c>
@@ -7997,7 +7081,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>25129069</v>
       </c>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF5A711-86D3-43DC-B5A3-792427697A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921C5B1F-2324-4FC7-97C4-BE629EF1D0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -1013,7 +1013,9 @@
     <col min="38" max="38" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="40" max="43" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="48" width="7.7109375" customWidth="1"/>
+    <col min="44" max="44" width="7" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="48" width="7.7109375" customWidth="1"/>
     <col min="49" max="49" width="7.7109375" style="3" customWidth="1"/>
     <col min="50" max="104" width="7.7109375" customWidth="1"/>
   </cols>
@@ -1145,7 +1147,9 @@
       <c r="AS1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AT1" s="1"/>
+      <c r="AT1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AU1" s="1"/>
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
@@ -1326,7 +1330,9 @@
       <c r="AS2" s="1">
         <v>46227</v>
       </c>
-      <c r="AT2" s="1"/>
+      <c r="AT2" s="1">
+        <v>46232</v>
+      </c>
       <c r="AU2" s="1"/>
       <c r="AV2" s="1"/>
       <c r="AW2" s="1"/>
@@ -1508,6 +1514,9 @@
       </c>
       <c r="AS3" t="s">
         <v>37</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>36</v>
       </c>
       <c r="AW3"/>
       <c r="BV3" s="3"/>
@@ -1697,6 +1706,9 @@
       <c r="AS4" t="s">
         <v>37</v>
       </c>
+      <c r="AT4" t="s">
+        <v>36</v>
+      </c>
       <c r="AW4"/>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
@@ -1885,6 +1897,9 @@
       <c r="AS5" t="s">
         <v>37</v>
       </c>
+      <c r="AT5" t="s">
+        <v>36</v>
+      </c>
       <c r="AW5"/>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
@@ -2073,6 +2088,9 @@
       <c r="AS6" t="s">
         <v>36</v>
       </c>
+      <c r="AT6" t="s">
+        <v>36</v>
+      </c>
       <c r="AW6"/>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
@@ -2247,6 +2265,9 @@
       <c r="AS7" t="s">
         <v>36</v>
       </c>
+      <c r="AT7" t="s">
+        <v>36</v>
+      </c>
       <c r="AW7"/>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
@@ -2421,6 +2442,9 @@
       <c r="AS8" t="s">
         <v>36</v>
       </c>
+      <c r="AT8" t="s">
+        <v>36</v>
+      </c>
       <c r="AW8"/>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
@@ -2595,6 +2619,9 @@
       <c r="AS9" t="s">
         <v>36</v>
       </c>
+      <c r="AT9" t="s">
+        <v>36</v>
+      </c>
       <c r="AW9"/>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
@@ -2769,6 +2796,9 @@
       <c r="AS10" t="s">
         <v>36</v>
       </c>
+      <c r="AT10" t="s">
+        <v>36</v>
+      </c>
       <c r="AW10"/>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
@@ -2943,6 +2973,9 @@
       <c r="AS11" t="s">
         <v>36</v>
       </c>
+      <c r="AT11" t="s">
+        <v>36</v>
+      </c>
       <c r="AW11"/>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
@@ -3117,6 +3150,9 @@
       <c r="AS12" t="s">
         <v>36</v>
       </c>
+      <c r="AT12" t="s">
+        <v>36</v>
+      </c>
       <c r="AW12"/>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
@@ -3291,6 +3327,9 @@
       <c r="AS13" t="s">
         <v>36</v>
       </c>
+      <c r="AT13" t="s">
+        <v>36</v>
+      </c>
       <c r="AW13"/>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
@@ -3465,6 +3504,9 @@
       <c r="AS14" t="s">
         <v>37</v>
       </c>
+      <c r="AT14" t="s">
+        <v>36</v>
+      </c>
       <c r="AW14"/>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
@@ -3639,6 +3681,9 @@
       <c r="AS15" t="s">
         <v>37</v>
       </c>
+      <c r="AT15" t="s">
+        <v>36</v>
+      </c>
       <c r="AW15"/>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
@@ -3813,6 +3858,9 @@
       <c r="AS16" t="s">
         <v>37</v>
       </c>
+      <c r="AT16" t="s">
+        <v>36</v>
+      </c>
       <c r="AW16"/>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
@@ -3987,6 +4035,9 @@
       <c r="AS17" t="s">
         <v>37</v>
       </c>
+      <c r="AT17" t="s">
+        <v>36</v>
+      </c>
       <c r="AW17"/>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
@@ -4161,6 +4212,9 @@
       <c r="AS18" t="s">
         <v>36</v>
       </c>
+      <c r="AT18" t="s">
+        <v>36</v>
+      </c>
       <c r="AW18"/>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
@@ -4335,6 +4389,9 @@
       <c r="AS19" t="s">
         <v>36</v>
       </c>
+      <c r="AT19" t="s">
+        <v>36</v>
+      </c>
       <c r="AW19"/>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
@@ -4509,6 +4566,9 @@
       <c r="AS20" t="s">
         <v>36</v>
       </c>
+      <c r="AT20" t="s">
+        <v>36</v>
+      </c>
       <c r="AW20"/>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
@@ -4683,6 +4743,9 @@
       <c r="AS21" t="s">
         <v>36</v>
       </c>
+      <c r="AT21" t="s">
+        <v>36</v>
+      </c>
       <c r="AW21"/>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
@@ -4857,6 +4920,9 @@
       <c r="AS22" t="s">
         <v>36</v>
       </c>
+      <c r="AT22" t="s">
+        <v>36</v>
+      </c>
       <c r="AW22"/>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
@@ -5031,6 +5097,9 @@
       <c r="AS23" t="s">
         <v>37</v>
       </c>
+      <c r="AT23" t="s">
+        <v>37</v>
+      </c>
       <c r="AW23"/>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
@@ -5205,6 +5274,9 @@
       <c r="AS24" t="s">
         <v>36</v>
       </c>
+      <c r="AT24" t="s">
+        <v>36</v>
+      </c>
       <c r="AW24"/>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
@@ -5379,6 +5451,9 @@
       <c r="AS25" t="s">
         <v>36</v>
       </c>
+      <c r="AT25" t="s">
+        <v>36</v>
+      </c>
       <c r="AW25"/>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
@@ -5553,6 +5628,9 @@
       <c r="AS26" t="s">
         <v>36</v>
       </c>
+      <c r="AT26" t="s">
+        <v>36</v>
+      </c>
       <c r="AW26"/>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
@@ -5727,6 +5805,9 @@
       <c r="AS27" t="s">
         <v>37</v>
       </c>
+      <c r="AT27" t="s">
+        <v>36</v>
+      </c>
       <c r="AW27"/>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
@@ -5901,6 +5982,9 @@
       <c r="AS28" t="s">
         <v>36</v>
       </c>
+      <c r="AT28" t="s">
+        <v>36</v>
+      </c>
       <c r="AW28"/>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
@@ -6075,6 +6159,9 @@
       <c r="AS29" t="s">
         <v>36</v>
       </c>
+      <c r="AT29" t="s">
+        <v>36</v>
+      </c>
       <c r="AW29"/>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
@@ -6249,6 +6336,9 @@
       <c r="AS30" t="s">
         <v>36</v>
       </c>
+      <c r="AT30" t="s">
+        <v>36</v>
+      </c>
       <c r="AW30"/>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
@@ -6423,6 +6513,9 @@
       <c r="AS31" t="s">
         <v>37</v>
       </c>
+      <c r="AT31" t="s">
+        <v>36</v>
+      </c>
       <c r="AW31"/>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
@@ -6597,6 +6690,9 @@
       <c r="AS32" t="s">
         <v>36</v>
       </c>
+      <c r="AT32" t="s">
+        <v>36</v>
+      </c>
       <c r="AW32"/>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
@@ -6769,6 +6865,9 @@
         <v>43</v>
       </c>
       <c r="AS33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT33" t="s">
         <v>36</v>
       </c>
       <c r="AW33"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921C5B1F-2324-4FC7-97C4-BE629EF1D0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D4CCFB-46A2-4462-B9A6-DB25C1F746C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -662,11 +662,12 @@
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1150,9 +1151,15 @@
       <c r="AT1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AU1" s="1"/>
-      <c r="AV1" s="1"/>
-      <c r="AW1" s="1"/>
+      <c r="AU1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="AX1" s="1"/>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
@@ -1333,9 +1340,15 @@
       <c r="AT2" s="1">
         <v>46232</v>
       </c>
-      <c r="AU2" s="1"/>
-      <c r="AV2" s="1"/>
-      <c r="AW2" s="1"/>
+      <c r="AU2" s="1">
+        <v>46234</v>
+      </c>
+      <c r="AV2" s="1">
+        <v>46239</v>
+      </c>
+      <c r="AW2" s="1">
+        <v>46241</v>
+      </c>
       <c r="AX2" s="1"/>
       <c r="AY2" s="1"/>
       <c r="AZ2" s="1"/>
@@ -1516,6 +1529,12 @@
         <v>37</v>
       </c>
       <c r="AT3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV3" s="4" t="s">
         <v>36</v>
       </c>
       <c r="AW3"/>
@@ -1709,6 +1728,12 @@
       <c r="AT4" t="s">
         <v>36</v>
       </c>
+      <c r="AU4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>36</v>
+      </c>
       <c r="AW4"/>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
@@ -1900,6 +1925,12 @@
       <c r="AT5" t="s">
         <v>36</v>
       </c>
+      <c r="AU5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>36</v>
+      </c>
       <c r="AW5"/>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
@@ -2091,6 +2122,12 @@
       <c r="AT6" t="s">
         <v>36</v>
       </c>
+      <c r="AU6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>36</v>
+      </c>
       <c r="AW6"/>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
@@ -2268,6 +2305,12 @@
       <c r="AT7" t="s">
         <v>36</v>
       </c>
+      <c r="AU7" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>36</v>
+      </c>
       <c r="AW7"/>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
@@ -2445,6 +2488,12 @@
       <c r="AT8" t="s">
         <v>36</v>
       </c>
+      <c r="AU8" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>36</v>
+      </c>
       <c r="AW8"/>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
@@ -2622,6 +2671,12 @@
       <c r="AT9" t="s">
         <v>36</v>
       </c>
+      <c r="AU9" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>36</v>
+      </c>
       <c r="AW9"/>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
@@ -2799,6 +2854,12 @@
       <c r="AT10" t="s">
         <v>36</v>
       </c>
+      <c r="AU10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>36</v>
+      </c>
       <c r="AW10"/>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
@@ -2976,6 +3037,12 @@
       <c r="AT11" t="s">
         <v>36</v>
       </c>
+      <c r="AU11" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>36</v>
+      </c>
       <c r="AW11"/>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
@@ -3153,6 +3220,12 @@
       <c r="AT12" t="s">
         <v>36</v>
       </c>
+      <c r="AU12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>36</v>
+      </c>
       <c r="AW12"/>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
@@ -3330,6 +3403,12 @@
       <c r="AT13" t="s">
         <v>36</v>
       </c>
+      <c r="AU13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>36</v>
+      </c>
       <c r="AW13"/>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
@@ -3507,6 +3586,12 @@
       <c r="AT14" t="s">
         <v>36</v>
       </c>
+      <c r="AU14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>37</v>
+      </c>
       <c r="AW14"/>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
@@ -3684,6 +3769,12 @@
       <c r="AT15" t="s">
         <v>36</v>
       </c>
+      <c r="AU15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV15" t="s">
+        <v>36</v>
+      </c>
       <c r="AW15"/>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
@@ -3861,6 +3952,12 @@
       <c r="AT16" t="s">
         <v>36</v>
       </c>
+      <c r="AU16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>36</v>
+      </c>
       <c r="AW16"/>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
@@ -4038,6 +4135,12 @@
       <c r="AT17" t="s">
         <v>36</v>
       </c>
+      <c r="AU17" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>36</v>
+      </c>
       <c r="AW17"/>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
@@ -4215,6 +4318,12 @@
       <c r="AT18" t="s">
         <v>36</v>
       </c>
+      <c r="AU18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>36</v>
+      </c>
       <c r="AW18"/>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
@@ -4392,6 +4501,12 @@
       <c r="AT19" t="s">
         <v>36</v>
       </c>
+      <c r="AU19" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>36</v>
+      </c>
       <c r="AW19"/>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
@@ -4569,6 +4684,12 @@
       <c r="AT20" t="s">
         <v>36</v>
       </c>
+      <c r="AU20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV20" t="s">
+        <v>36</v>
+      </c>
       <c r="AW20"/>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
@@ -4746,6 +4867,12 @@
       <c r="AT21" t="s">
         <v>36</v>
       </c>
+      <c r="AU21" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV21" t="s">
+        <v>36</v>
+      </c>
       <c r="AW21"/>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
@@ -4923,6 +5050,12 @@
       <c r="AT22" t="s">
         <v>36</v>
       </c>
+      <c r="AU22" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV22" t="s">
+        <v>36</v>
+      </c>
       <c r="AW22"/>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
@@ -5100,6 +5233,12 @@
       <c r="AT23" t="s">
         <v>37</v>
       </c>
+      <c r="AU23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>36</v>
+      </c>
       <c r="AW23"/>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
@@ -5277,6 +5416,12 @@
       <c r="AT24" t="s">
         <v>36</v>
       </c>
+      <c r="AU24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>36</v>
+      </c>
       <c r="AW24"/>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
@@ -5454,6 +5599,12 @@
       <c r="AT25" t="s">
         <v>36</v>
       </c>
+      <c r="AU25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV25" t="s">
+        <v>36</v>
+      </c>
       <c r="AW25"/>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
@@ -5631,6 +5782,12 @@
       <c r="AT26" t="s">
         <v>36</v>
       </c>
+      <c r="AU26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV26" t="s">
+        <v>36</v>
+      </c>
       <c r="AW26"/>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
@@ -5808,6 +5965,12 @@
       <c r="AT27" t="s">
         <v>36</v>
       </c>
+      <c r="AU27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV27" t="s">
+        <v>36</v>
+      </c>
       <c r="AW27"/>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
@@ -5985,6 +6148,12 @@
       <c r="AT28" t="s">
         <v>36</v>
       </c>
+      <c r="AU28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV28" t="s">
+        <v>36</v>
+      </c>
       <c r="AW28"/>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
@@ -6162,6 +6331,12 @@
       <c r="AT29" t="s">
         <v>36</v>
       </c>
+      <c r="AU29" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV29" t="s">
+        <v>36</v>
+      </c>
       <c r="AW29"/>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
@@ -6339,6 +6514,12 @@
       <c r="AT30" t="s">
         <v>36</v>
       </c>
+      <c r="AU30" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV30" t="s">
+        <v>36</v>
+      </c>
       <c r="AW30"/>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
@@ -6516,6 +6697,12 @@
       <c r="AT31" t="s">
         <v>36</v>
       </c>
+      <c r="AU31" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV31" t="s">
+        <v>36</v>
+      </c>
       <c r="AW31"/>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
@@ -6693,6 +6880,12 @@
       <c r="AT32" t="s">
         <v>36</v>
       </c>
+      <c r="AU32" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV32" t="s">
+        <v>36</v>
+      </c>
       <c r="AW32"/>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
@@ -6868,6 +7061,12 @@
         <v>36</v>
       </c>
       <c r="AT33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV33" t="s">
         <v>36</v>
       </c>
       <c r="AW33"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D4CCFB-46A2-4462-B9A6-DB25C1F746C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB601BA-712E-4693-BC8F-DC09151A74C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -1537,7 +1537,9 @@
       <c r="AV3" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AW3"/>
+      <c r="AW3" t="s">
+        <v>36</v>
+      </c>
       <c r="BV3" s="3"/>
       <c r="BW3" s="3"/>
       <c r="BX3" s="3"/>
@@ -1734,7 +1736,9 @@
       <c r="AV4" t="s">
         <v>36</v>
       </c>
-      <c r="AW4"/>
+      <c r="AW4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -1931,7 +1935,9 @@
       <c r="AV5" t="s">
         <v>36</v>
       </c>
-      <c r="AW5"/>
+      <c r="AW5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2128,7 +2134,9 @@
       <c r="AV6" t="s">
         <v>36</v>
       </c>
-      <c r="AW6"/>
+      <c r="AW6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2311,7 +2319,9 @@
       <c r="AV7" t="s">
         <v>36</v>
       </c>
-      <c r="AW7"/>
+      <c r="AW7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2494,7 +2504,9 @@
       <c r="AV8" t="s">
         <v>36</v>
       </c>
-      <c r="AW8"/>
+      <c r="AW8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2677,7 +2689,9 @@
       <c r="AV9" t="s">
         <v>36</v>
       </c>
-      <c r="AW9"/>
+      <c r="AW9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -2860,7 +2874,9 @@
       <c r="AV10" t="s">
         <v>36</v>
       </c>
-      <c r="AW10"/>
+      <c r="AW10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3043,7 +3059,9 @@
       <c r="AV11" t="s">
         <v>36</v>
       </c>
-      <c r="AW11"/>
+      <c r="AW11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3226,7 +3244,9 @@
       <c r="AV12" t="s">
         <v>36</v>
       </c>
-      <c r="AW12"/>
+      <c r="AW12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3409,7 +3429,9 @@
       <c r="AV13" t="s">
         <v>36</v>
       </c>
-      <c r="AW13"/>
+      <c r="AW13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3592,7 +3614,9 @@
       <c r="AV14" t="s">
         <v>37</v>
       </c>
-      <c r="AW14"/>
+      <c r="AW14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -3775,7 +3799,9 @@
       <c r="AV15" t="s">
         <v>36</v>
       </c>
-      <c r="AW15"/>
+      <c r="AW15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -3958,7 +3984,9 @@
       <c r="AV16" t="s">
         <v>36</v>
       </c>
-      <c r="AW16"/>
+      <c r="AW16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4141,7 +4169,9 @@
       <c r="AV17" t="s">
         <v>36</v>
       </c>
-      <c r="AW17"/>
+      <c r="AW17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4324,7 +4354,9 @@
       <c r="AV18" t="s">
         <v>36</v>
       </c>
-      <c r="AW18"/>
+      <c r="AW18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -4507,7 +4539,9 @@
       <c r="AV19" t="s">
         <v>36</v>
       </c>
-      <c r="AW19"/>
+      <c r="AW19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -4690,7 +4724,9 @@
       <c r="AV20" t="s">
         <v>36</v>
       </c>
-      <c r="AW20"/>
+      <c r="AW20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -4873,7 +4909,9 @@
       <c r="AV21" t="s">
         <v>36</v>
       </c>
-      <c r="AW21"/>
+      <c r="AW21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5056,7 +5094,9 @@
       <c r="AV22" t="s">
         <v>36</v>
       </c>
-      <c r="AW22"/>
+      <c r="AW22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5239,7 +5279,9 @@
       <c r="AV23" t="s">
         <v>36</v>
       </c>
-      <c r="AW23"/>
+      <c r="AW23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -5422,7 +5464,9 @@
       <c r="AV24" t="s">
         <v>36</v>
       </c>
-      <c r="AW24"/>
+      <c r="AW24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -5605,7 +5649,9 @@
       <c r="AV25" t="s">
         <v>36</v>
       </c>
-      <c r="AW25"/>
+      <c r="AW25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -5788,7 +5834,9 @@
       <c r="AV26" t="s">
         <v>36</v>
       </c>
-      <c r="AW26"/>
+      <c r="AW26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -5971,7 +6019,9 @@
       <c r="AV27" t="s">
         <v>36</v>
       </c>
-      <c r="AW27"/>
+      <c r="AW27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6154,7 +6204,9 @@
       <c r="AV28" t="s">
         <v>36</v>
       </c>
-      <c r="AW28"/>
+      <c r="AW28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -6337,7 +6389,9 @@
       <c r="AV29" t="s">
         <v>36</v>
       </c>
-      <c r="AW29"/>
+      <c r="AW29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -6520,7 +6574,9 @@
       <c r="AV30" t="s">
         <v>36</v>
       </c>
-      <c r="AW30"/>
+      <c r="AW30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -6703,7 +6759,9 @@
       <c r="AV31" t="s">
         <v>36</v>
       </c>
-      <c r="AW31"/>
+      <c r="AW31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -6886,7 +6944,9 @@
       <c r="AV32" t="s">
         <v>36</v>
       </c>
-      <c r="AW32"/>
+      <c r="AW32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7069,7 +7129,9 @@
       <c r="AV33" t="s">
         <v>36</v>
       </c>
-      <c r="AW33"/>
+      <c r="AW33" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ33" s="3"/>
       <c r="CK33" s="3"/>
       <c r="CL33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB601BA-712E-4693-BC8F-DC09151A74C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AA862E-BA17-4D7D-9242-3371F6D5A237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -662,12 +662,15 @@
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1160,7 +1163,9 @@
       <c r="AW1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AX1" s="1"/>
+      <c r="AX1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="AY1" s="1"/>
       <c r="AZ1" s="1"/>
       <c r="BA1" s="1"/>
@@ -1349,7 +1354,9 @@
       <c r="AW2" s="1">
         <v>46241</v>
       </c>
-      <c r="AX2" s="1"/>
+      <c r="AX2" s="5">
+        <v>46246</v>
+      </c>
       <c r="AY2" s="1"/>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1"/>
@@ -1538,6 +1545,9 @@
         <v>36</v>
       </c>
       <c r="AW3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1739,6 +1749,9 @@
       <c r="AW4" t="s">
         <v>36</v>
       </c>
+      <c r="AX4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -1938,6 +1951,9 @@
       <c r="AW5" t="s">
         <v>36</v>
       </c>
+      <c r="AX5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2137,6 +2153,9 @@
       <c r="AW6" t="s">
         <v>36</v>
       </c>
+      <c r="AX6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2322,6 +2341,9 @@
       <c r="AW7" t="s">
         <v>36</v>
       </c>
+      <c r="AX7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2507,6 +2529,9 @@
       <c r="AW8" t="s">
         <v>36</v>
       </c>
+      <c r="AX8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2692,6 +2717,9 @@
       <c r="AW9" t="s">
         <v>36</v>
       </c>
+      <c r="AX9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -2877,6 +2905,9 @@
       <c r="AW10" t="s">
         <v>36</v>
       </c>
+      <c r="AX10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3062,6 +3093,9 @@
       <c r="AW11" t="s">
         <v>36</v>
       </c>
+      <c r="AX11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3247,6 +3281,9 @@
       <c r="AW12" t="s">
         <v>36</v>
       </c>
+      <c r="AX12" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3432,6 +3469,9 @@
       <c r="AW13" t="s">
         <v>36</v>
       </c>
+      <c r="AX13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3617,6 +3657,9 @@
       <c r="AW14" t="s">
         <v>36</v>
       </c>
+      <c r="AX14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -3802,6 +3845,9 @@
       <c r="AW15" t="s">
         <v>36</v>
       </c>
+      <c r="AX15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -3987,6 +4033,9 @@
       <c r="AW16" t="s">
         <v>36</v>
       </c>
+      <c r="AX16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4172,6 +4221,9 @@
       <c r="AW17" t="s">
         <v>36</v>
       </c>
+      <c r="AX17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4357,6 +4409,9 @@
       <c r="AW18" t="s">
         <v>36</v>
       </c>
+      <c r="AX18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -4542,6 +4597,9 @@
       <c r="AW19" t="s">
         <v>36</v>
       </c>
+      <c r="AX19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -4727,6 +4785,9 @@
       <c r="AW20" t="s">
         <v>36</v>
       </c>
+      <c r="AX20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -4912,6 +4973,9 @@
       <c r="AW21" t="s">
         <v>36</v>
       </c>
+      <c r="AX21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5097,6 +5161,9 @@
       <c r="AW22" t="s">
         <v>36</v>
       </c>
+      <c r="AX22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5282,6 +5349,9 @@
       <c r="AW23" t="s">
         <v>36</v>
       </c>
+      <c r="AX23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -5467,6 +5537,9 @@
       <c r="AW24" t="s">
         <v>36</v>
       </c>
+      <c r="AX24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -5652,6 +5725,9 @@
       <c r="AW25" t="s">
         <v>36</v>
       </c>
+      <c r="AX25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -5837,6 +5913,9 @@
       <c r="AW26" t="s">
         <v>36</v>
       </c>
+      <c r="AX26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6022,6 +6101,9 @@
       <c r="AW27" t="s">
         <v>36</v>
       </c>
+      <c r="AX27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6207,6 +6289,9 @@
       <c r="AW28" t="s">
         <v>36</v>
       </c>
+      <c r="AX28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -6392,6 +6477,9 @@
       <c r="AW29" t="s">
         <v>36</v>
       </c>
+      <c r="AX29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -6577,6 +6665,9 @@
       <c r="AW30" t="s">
         <v>36</v>
       </c>
+      <c r="AX30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -6762,6 +6853,9 @@
       <c r="AW31" t="s">
         <v>36</v>
       </c>
+      <c r="AX31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -6947,6 +7041,9 @@
       <c r="AW32" t="s">
         <v>36</v>
       </c>
+      <c r="AX32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7130,6 +7227,9 @@
         <v>36</v>
       </c>
       <c r="AW33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AA862E-BA17-4D7D-9242-3371F6D5A237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5006736C-F2B0-4D9A-952F-854E32BC75F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -1166,7 +1166,9 @@
       <c r="AX1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="AY1" s="1"/>
+      <c r="AY1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="AZ1" s="1"/>
       <c r="BA1" s="1"/>
       <c r="BB1" s="1"/>
@@ -1357,7 +1359,9 @@
       <c r="AX2" s="5">
         <v>46246</v>
       </c>
-      <c r="AY2" s="1"/>
+      <c r="AY2" s="1">
+        <v>46248</v>
+      </c>
       <c r="AZ2" s="1"/>
       <c r="BA2" s="1"/>
       <c r="BB2" s="1"/>
@@ -1548,6 +1552,9 @@
         <v>36</v>
       </c>
       <c r="AX3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1752,6 +1759,9 @@
       <c r="AX4" t="s">
         <v>36</v>
       </c>
+      <c r="AY4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -1954,6 +1964,9 @@
       <c r="AX5" t="s">
         <v>36</v>
       </c>
+      <c r="AY5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2156,6 +2169,9 @@
       <c r="AX6" t="s">
         <v>36</v>
       </c>
+      <c r="AY6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2344,6 +2360,9 @@
       <c r="AX7" t="s">
         <v>36</v>
       </c>
+      <c r="AY7" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2532,6 +2551,9 @@
       <c r="AX8" t="s">
         <v>36</v>
       </c>
+      <c r="AY8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2720,6 +2742,9 @@
       <c r="AX9" t="s">
         <v>36</v>
       </c>
+      <c r="AY9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -2908,6 +2933,9 @@
       <c r="AX10" t="s">
         <v>36</v>
       </c>
+      <c r="AY10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3096,6 +3124,9 @@
       <c r="AX11" t="s">
         <v>36</v>
       </c>
+      <c r="AY11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3284,6 +3315,9 @@
       <c r="AX12" t="s">
         <v>37</v>
       </c>
+      <c r="AY12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3472,6 +3506,9 @@
       <c r="AX13" t="s">
         <v>36</v>
       </c>
+      <c r="AY13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3660,6 +3697,9 @@
       <c r="AX14" t="s">
         <v>36</v>
       </c>
+      <c r="AY14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -3848,6 +3888,9 @@
       <c r="AX15" t="s">
         <v>36</v>
       </c>
+      <c r="AY15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4036,6 +4079,9 @@
       <c r="AX16" t="s">
         <v>36</v>
       </c>
+      <c r="AY16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4224,6 +4270,9 @@
       <c r="AX17" t="s">
         <v>36</v>
       </c>
+      <c r="AY17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4412,6 +4461,9 @@
       <c r="AX18" t="s">
         <v>36</v>
       </c>
+      <c r="AY18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -4600,6 +4652,9 @@
       <c r="AX19" t="s">
         <v>36</v>
       </c>
+      <c r="AY19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -4788,6 +4843,9 @@
       <c r="AX20" t="s">
         <v>36</v>
       </c>
+      <c r="AY20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -4976,6 +5034,9 @@
       <c r="AX21" t="s">
         <v>36</v>
       </c>
+      <c r="AY21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5164,6 +5225,9 @@
       <c r="AX22" t="s">
         <v>36</v>
       </c>
+      <c r="AY22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5352,6 +5416,9 @@
       <c r="AX23" t="s">
         <v>36</v>
       </c>
+      <c r="AY23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -5540,6 +5607,9 @@
       <c r="AX24" t="s">
         <v>36</v>
       </c>
+      <c r="AY24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -5728,6 +5798,9 @@
       <c r="AX25" t="s">
         <v>36</v>
       </c>
+      <c r="AY25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -5916,6 +5989,9 @@
       <c r="AX26" t="s">
         <v>36</v>
       </c>
+      <c r="AY26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6104,6 +6180,9 @@
       <c r="AX27" t="s">
         <v>36</v>
       </c>
+      <c r="AY27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6292,6 +6371,9 @@
       <c r="AX28" t="s">
         <v>36</v>
       </c>
+      <c r="AY28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -6480,6 +6562,9 @@
       <c r="AX29" t="s">
         <v>36</v>
       </c>
+      <c r="AY29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -6668,6 +6753,9 @@
       <c r="AX30" t="s">
         <v>36</v>
       </c>
+      <c r="AY30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -6856,6 +6944,9 @@
       <c r="AX31" t="s">
         <v>36</v>
       </c>
+      <c r="AY31" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7044,6 +7135,9 @@
       <c r="AX32" t="s">
         <v>36</v>
       </c>
+      <c r="AY32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7230,6 +7324,9 @@
         <v>36</v>
       </c>
       <c r="AX33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AY33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5006736C-F2B0-4D9A-952F-854E32BC75F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9FAAC8-9C20-4D24-8AEA-BDA9BA05A6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6563,7 +6563,7 @@
         <v>36</v>
       </c>
       <c r="AY29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9FAAC8-9C20-4D24-8AEA-BDA9BA05A6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162548E2-0166-4B78-BD87-CC46B69FB5C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="44">
   <si>
     <t>Aluno</t>
   </si>
@@ -1018,10 +1018,11 @@
     <col min="39" max="39" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="40" max="43" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="7" bestFit="1" customWidth="1"/>
-    <col min="45" max="46" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="47" max="48" width="7.7109375" customWidth="1"/>
-    <col min="49" max="49" width="7.7109375" style="3" customWidth="1"/>
-    <col min="50" max="104" width="7.7109375" customWidth="1"/>
+    <col min="45" max="47" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="7" style="3" bestFit="1" customWidth="1"/>
+    <col min="50" max="52" width="7" bestFit="1" customWidth="1"/>
+    <col min="53" max="104" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:121" x14ac:dyDescent="0.25">
@@ -1169,7 +1170,9 @@
       <c r="AY1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AZ1" s="1"/>
+      <c r="AZ1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BA1" s="1"/>
       <c r="BB1" s="1"/>
       <c r="BC1" s="1"/>
@@ -1362,7 +1365,9 @@
       <c r="AY2" s="1">
         <v>46248</v>
       </c>
-      <c r="AZ2" s="1"/>
+      <c r="AZ2" s="1">
+        <v>46253</v>
+      </c>
       <c r="BA2" s="1"/>
       <c r="BB2" s="1"/>
       <c r="BC2" s="1"/>
@@ -1555,6 +1560,9 @@
         <v>36</v>
       </c>
       <c r="AY3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1762,6 +1770,9 @@
       <c r="AY4" t="s">
         <v>36</v>
       </c>
+      <c r="AZ4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -1967,6 +1978,9 @@
       <c r="AY5" t="s">
         <v>36</v>
       </c>
+      <c r="AZ5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2172,6 +2186,9 @@
       <c r="AY6" t="s">
         <v>36</v>
       </c>
+      <c r="AZ6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2363,6 +2380,9 @@
       <c r="AY7" t="s">
         <v>37</v>
       </c>
+      <c r="AZ7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2554,6 +2574,9 @@
       <c r="AY8" t="s">
         <v>36</v>
       </c>
+      <c r="AZ8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2745,6 +2768,9 @@
       <c r="AY9" t="s">
         <v>36</v>
       </c>
+      <c r="AZ9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -2936,6 +2962,9 @@
       <c r="AY10" t="s">
         <v>36</v>
       </c>
+      <c r="AZ10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3127,6 +3156,9 @@
       <c r="AY11" t="s">
         <v>36</v>
       </c>
+      <c r="AZ11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3318,6 +3350,9 @@
       <c r="AY12" t="s">
         <v>36</v>
       </c>
+      <c r="AZ12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3509,6 +3544,9 @@
       <c r="AY13" t="s">
         <v>36</v>
       </c>
+      <c r="AZ13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3700,6 +3738,9 @@
       <c r="AY14" t="s">
         <v>36</v>
       </c>
+      <c r="AZ14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -3891,6 +3932,9 @@
       <c r="AY15" t="s">
         <v>36</v>
       </c>
+      <c r="AZ15" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4082,6 +4126,9 @@
       <c r="AY16" t="s">
         <v>36</v>
       </c>
+      <c r="AZ16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4273,6 +4320,9 @@
       <c r="AY17" t="s">
         <v>36</v>
       </c>
+      <c r="AZ17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4464,6 +4514,9 @@
       <c r="AY18" t="s">
         <v>36</v>
       </c>
+      <c r="AZ18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -4655,6 +4708,9 @@
       <c r="AY19" t="s">
         <v>36</v>
       </c>
+      <c r="AZ19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -4846,6 +4902,9 @@
       <c r="AY20" t="s">
         <v>36</v>
       </c>
+      <c r="AZ20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5037,6 +5096,9 @@
       <c r="AY21" t="s">
         <v>36</v>
       </c>
+      <c r="AZ21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5228,6 +5290,9 @@
       <c r="AY22" t="s">
         <v>36</v>
       </c>
+      <c r="AZ22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5419,6 +5484,9 @@
       <c r="AY23" t="s">
         <v>36</v>
       </c>
+      <c r="AZ23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -5610,6 +5678,9 @@
       <c r="AY24" t="s">
         <v>36</v>
       </c>
+      <c r="AZ24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -5801,6 +5872,9 @@
       <c r="AY25" t="s">
         <v>36</v>
       </c>
+      <c r="AZ25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -5992,6 +6066,9 @@
       <c r="AY26" t="s">
         <v>36</v>
       </c>
+      <c r="AZ26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6183,6 +6260,9 @@
       <c r="AY27" t="s">
         <v>36</v>
       </c>
+      <c r="AZ27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6374,6 +6454,9 @@
       <c r="AY28" t="s">
         <v>36</v>
       </c>
+      <c r="AZ28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -6565,6 +6648,9 @@
       <c r="AY29" t="s">
         <v>38</v>
       </c>
+      <c r="AZ29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -6756,6 +6842,9 @@
       <c r="AY30" t="s">
         <v>36</v>
       </c>
+      <c r="AZ30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -6947,6 +7036,9 @@
       <c r="AY31" t="s">
         <v>37</v>
       </c>
+      <c r="AZ31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7138,6 +7230,9 @@
       <c r="AY32" t="s">
         <v>36</v>
       </c>
+      <c r="AZ32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7327,6 +7422,9 @@
         <v>36</v>
       </c>
       <c r="AY33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AZ33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162548E2-0166-4B78-BD87-CC46B69FB5C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA13E60-6B3F-4354-953B-F1820FB83AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t>férias</t>
+  </si>
+  <si>
+    <t>5P | F</t>
   </si>
 </sst>
 </file>
@@ -716,7 +719,27 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5485,7 +5508,7 @@
         <v>36</v>
       </c>
       <c r="AZ23" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
@@ -5873,7 +5896,7 @@
         <v>36</v>
       </c>
       <c r="AZ25" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
@@ -7468,8 +7491,13 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D3:DE33">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AZ3:AZ33">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA13E60-6B3F-4354-953B-F1820FB83AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9476A25F-329C-4807-9807-4D8BB9D8D815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1605" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -719,17 +719,7 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1196,7 +1186,9 @@
       <c r="AZ1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BA1" s="1"/>
+      <c r="BA1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BB1" s="1"/>
       <c r="BC1" s="1"/>
       <c r="BD1" s="1"/>
@@ -1391,7 +1383,9 @@
       <c r="AZ2" s="1">
         <v>46253</v>
       </c>
-      <c r="BA2" s="1"/>
+      <c r="BA2" s="1">
+        <v>46255</v>
+      </c>
       <c r="BB2" s="1"/>
       <c r="BC2" s="1"/>
       <c r="BD2" s="1"/>
@@ -1586,6 +1580,9 @@
         <v>36</v>
       </c>
       <c r="AZ3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1796,6 +1793,9 @@
       <c r="AZ4" t="s">
         <v>36</v>
       </c>
+      <c r="BA4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2004,6 +2004,9 @@
       <c r="AZ5" t="s">
         <v>36</v>
       </c>
+      <c r="BA5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2212,6 +2215,9 @@
       <c r="AZ6" t="s">
         <v>36</v>
       </c>
+      <c r="BA6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2406,6 +2412,9 @@
       <c r="AZ7" t="s">
         <v>36</v>
       </c>
+      <c r="BA7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2600,6 +2609,9 @@
       <c r="AZ8" t="s">
         <v>36</v>
       </c>
+      <c r="BA8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2794,6 +2806,9 @@
       <c r="AZ9" t="s">
         <v>36</v>
       </c>
+      <c r="BA9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -2988,6 +3003,9 @@
       <c r="AZ10" t="s">
         <v>36</v>
       </c>
+      <c r="BA10" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3182,6 +3200,9 @@
       <c r="AZ11" t="s">
         <v>36</v>
       </c>
+      <c r="BA11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3376,6 +3397,9 @@
       <c r="AZ12" t="s">
         <v>36</v>
       </c>
+      <c r="BA12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3570,6 +3594,9 @@
       <c r="AZ13" t="s">
         <v>36</v>
       </c>
+      <c r="BA13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3764,6 +3791,9 @@
       <c r="AZ14" t="s">
         <v>36</v>
       </c>
+      <c r="BA14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -3958,6 +3988,9 @@
       <c r="AZ15" t="s">
         <v>37</v>
       </c>
+      <c r="BA15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4152,6 +4185,9 @@
       <c r="AZ16" t="s">
         <v>36</v>
       </c>
+      <c r="BA16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4346,6 +4382,9 @@
       <c r="AZ17" t="s">
         <v>36</v>
       </c>
+      <c r="BA17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4540,6 +4579,9 @@
       <c r="AZ18" t="s">
         <v>36</v>
       </c>
+      <c r="BA18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -4734,6 +4776,9 @@
       <c r="AZ19" t="s">
         <v>36</v>
       </c>
+      <c r="BA19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -4928,6 +4973,9 @@
       <c r="AZ20" t="s">
         <v>36</v>
       </c>
+      <c r="BA20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5122,6 +5170,9 @@
       <c r="AZ21" t="s">
         <v>36</v>
       </c>
+      <c r="BA21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5316,6 +5367,9 @@
       <c r="AZ22" t="s">
         <v>36</v>
       </c>
+      <c r="BA22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5510,6 +5564,9 @@
       <c r="AZ23" t="s">
         <v>44</v>
       </c>
+      <c r="BA23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -5704,6 +5761,9 @@
       <c r="AZ24" t="s">
         <v>36</v>
       </c>
+      <c r="BA24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -5898,6 +5958,9 @@
       <c r="AZ25" t="s">
         <v>44</v>
       </c>
+      <c r="BA25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6092,6 +6155,9 @@
       <c r="AZ26" t="s">
         <v>36</v>
       </c>
+      <c r="BA26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6286,6 +6352,9 @@
       <c r="AZ27" t="s">
         <v>36</v>
       </c>
+      <c r="BA27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6480,6 +6549,9 @@
       <c r="AZ28" t="s">
         <v>36</v>
       </c>
+      <c r="BA28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -6674,6 +6746,9 @@
       <c r="AZ29" t="s">
         <v>36</v>
       </c>
+      <c r="BA29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -6868,6 +6943,9 @@
       <c r="AZ30" t="s">
         <v>36</v>
       </c>
+      <c r="BA30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7062,6 +7140,9 @@
       <c r="AZ31" t="s">
         <v>36</v>
       </c>
+      <c r="BA31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7256,6 +7337,9 @@
       <c r="AZ32" t="s">
         <v>36</v>
       </c>
+      <c r="BA32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7448,6 +7532,9 @@
         <v>36</v>
       </c>
       <c r="AZ33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BA33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>
@@ -7491,7 +7578,7 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D3:DE33">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9476A25F-329C-4807-9807-4D8BB9D8D815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA71D2B-3043-49B9-8761-2136458CF1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -1019,23 +1019,21 @@
   <dimension ref="A1:DQ33"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="37" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="28" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="37" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="7" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="40" max="43" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="7" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="7" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="50" max="52" width="7" bestFit="1" customWidth="1"/>
-    <col min="53" max="104" width="7.7109375" customWidth="1"/>
+    <col min="40" max="44" width="7" bestFit="1" customWidth="1"/>
+    <col min="45" max="47" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="7.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="50" max="54" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="55" max="104" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:121" x14ac:dyDescent="0.25">
@@ -1189,7 +1187,9 @@
       <c r="BA1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BB1" s="1"/>
+      <c r="BB1" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="BC1" s="1"/>
       <c r="BD1" s="1"/>
       <c r="BE1" s="1"/>
@@ -1386,7 +1386,9 @@
       <c r="BA2" s="1">
         <v>46255</v>
       </c>
-      <c r="BB2" s="1"/>
+      <c r="BB2" s="1">
+        <v>46260</v>
+      </c>
       <c r="BC2" s="1"/>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
@@ -1583,6 +1585,9 @@
         <v>36</v>
       </c>
       <c r="BA3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1796,6 +1801,9 @@
       <c r="BA4" t="s">
         <v>36</v>
       </c>
+      <c r="BB4" t="s">
+        <v>37</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2007,6 +2015,9 @@
       <c r="BA5" t="s">
         <v>36</v>
       </c>
+      <c r="BB5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2218,6 +2229,9 @@
       <c r="BA6" t="s">
         <v>36</v>
       </c>
+      <c r="BB6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2415,6 +2429,9 @@
       <c r="BA7" t="s">
         <v>36</v>
       </c>
+      <c r="BB7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2612,6 +2629,9 @@
       <c r="BA8" t="s">
         <v>36</v>
       </c>
+      <c r="BB8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2809,6 +2829,9 @@
       <c r="BA9" t="s">
         <v>36</v>
       </c>
+      <c r="BB9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3006,6 +3029,9 @@
       <c r="BA10" t="s">
         <v>37</v>
       </c>
+      <c r="BB10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3203,6 +3229,9 @@
       <c r="BA11" t="s">
         <v>36</v>
       </c>
+      <c r="BB11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3400,6 +3429,9 @@
       <c r="BA12" t="s">
         <v>36</v>
       </c>
+      <c r="BB12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3597,6 +3629,9 @@
       <c r="BA13" t="s">
         <v>36</v>
       </c>
+      <c r="BB13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3794,6 +3829,9 @@
       <c r="BA14" t="s">
         <v>36</v>
       </c>
+      <c r="BB14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -3991,6 +4029,9 @@
       <c r="BA15" t="s">
         <v>36</v>
       </c>
+      <c r="BB15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4188,6 +4229,9 @@
       <c r="BA16" t="s">
         <v>36</v>
       </c>
+      <c r="BB16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4385,6 +4429,9 @@
       <c r="BA17" t="s">
         <v>36</v>
       </c>
+      <c r="BB17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4582,6 +4629,9 @@
       <c r="BA18" t="s">
         <v>36</v>
       </c>
+      <c r="BB18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -4779,6 +4829,9 @@
       <c r="BA19" t="s">
         <v>36</v>
       </c>
+      <c r="BB19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -4976,6 +5029,9 @@
       <c r="BA20" t="s">
         <v>36</v>
       </c>
+      <c r="BB20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5173,6 +5229,9 @@
       <c r="BA21" t="s">
         <v>36</v>
       </c>
+      <c r="BB21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5370,6 +5429,9 @@
       <c r="BA22" t="s">
         <v>36</v>
       </c>
+      <c r="BB22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5567,6 +5629,9 @@
       <c r="BA23" t="s">
         <v>36</v>
       </c>
+      <c r="BB23" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -5764,6 +5829,9 @@
       <c r="BA24" t="s">
         <v>36</v>
       </c>
+      <c r="BB24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -5961,6 +6029,9 @@
       <c r="BA25" t="s">
         <v>36</v>
       </c>
+      <c r="BB25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6158,6 +6229,9 @@
       <c r="BA26" t="s">
         <v>36</v>
       </c>
+      <c r="BB26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6355,6 +6429,9 @@
       <c r="BA27" t="s">
         <v>36</v>
       </c>
+      <c r="BB27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6552,6 +6629,9 @@
       <c r="BA28" t="s">
         <v>36</v>
       </c>
+      <c r="BB28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -6749,6 +6829,9 @@
       <c r="BA29" t="s">
         <v>36</v>
       </c>
+      <c r="BB29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -6946,6 +7029,9 @@
       <c r="BA30" t="s">
         <v>36</v>
       </c>
+      <c r="BB30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7143,6 +7229,9 @@
       <c r="BA31" t="s">
         <v>36</v>
       </c>
+      <c r="BB31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7340,6 +7429,9 @@
       <c r="BA32" t="s">
         <v>36</v>
       </c>
+      <c r="BB32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7535,6 +7627,9 @@
         <v>36</v>
       </c>
       <c r="BA33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BB33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA71D2B-3043-49B9-8761-2136458CF1C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CB09EA-076A-41C5-90C0-15FCD7A2B5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1669" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="45">
   <si>
     <t>Aluno</t>
   </si>
@@ -1190,7 +1190,9 @@
       <c r="BB1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="BC1" s="1"/>
+      <c r="BC1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BD1" s="1"/>
       <c r="BE1" s="1"/>
       <c r="BF1" s="1"/>
@@ -1389,7 +1391,9 @@
       <c r="BB2" s="1">
         <v>46260</v>
       </c>
-      <c r="BC2" s="1"/>
+      <c r="BC2" s="1">
+        <v>46262</v>
+      </c>
       <c r="BD2" s="1"/>
       <c r="BE2" s="1"/>
       <c r="BF2" s="1"/>
@@ -1588,6 +1592,9 @@
         <v>36</v>
       </c>
       <c r="BB3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BC3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1804,6 +1811,9 @@
       <c r="BB4" t="s">
         <v>37</v>
       </c>
+      <c r="BC4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2018,6 +2028,9 @@
       <c r="BB5" t="s">
         <v>36</v>
       </c>
+      <c r="BC5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2232,6 +2245,9 @@
       <c r="BB6" t="s">
         <v>36</v>
       </c>
+      <c r="BC6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2432,6 +2448,9 @@
       <c r="BB7" t="s">
         <v>36</v>
       </c>
+      <c r="BC7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2632,6 +2651,9 @@
       <c r="BB8" t="s">
         <v>36</v>
       </c>
+      <c r="BC8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2832,6 +2854,9 @@
       <c r="BB9" t="s">
         <v>36</v>
       </c>
+      <c r="BC9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3032,6 +3057,9 @@
       <c r="BB10" t="s">
         <v>36</v>
       </c>
+      <c r="BC10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3232,6 +3260,9 @@
       <c r="BB11" t="s">
         <v>36</v>
       </c>
+      <c r="BC11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3432,6 +3463,9 @@
       <c r="BB12" t="s">
         <v>36</v>
       </c>
+      <c r="BC12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3632,6 +3666,9 @@
       <c r="BB13" t="s">
         <v>36</v>
       </c>
+      <c r="BC13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3832,6 +3869,9 @@
       <c r="BB14" t="s">
         <v>36</v>
       </c>
+      <c r="BC14" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4032,6 +4072,9 @@
       <c r="BB15" t="s">
         <v>36</v>
       </c>
+      <c r="BC15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4232,6 +4275,9 @@
       <c r="BB16" t="s">
         <v>36</v>
       </c>
+      <c r="BC16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4432,6 +4478,9 @@
       <c r="BB17" t="s">
         <v>36</v>
       </c>
+      <c r="BC17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4632,6 +4681,9 @@
       <c r="BB18" t="s">
         <v>36</v>
       </c>
+      <c r="BC18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -4832,6 +4884,9 @@
       <c r="BB19" t="s">
         <v>36</v>
       </c>
+      <c r="BC19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5032,6 +5087,9 @@
       <c r="BB20" t="s">
         <v>36</v>
       </c>
+      <c r="BC20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5232,6 +5290,9 @@
       <c r="BB21" t="s">
         <v>36</v>
       </c>
+      <c r="BC21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5432,6 +5493,9 @@
       <c r="BB22" t="s">
         <v>36</v>
       </c>
+      <c r="BC22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5632,6 +5696,9 @@
       <c r="BB23" t="s">
         <v>37</v>
       </c>
+      <c r="BC23" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -5832,6 +5899,9 @@
       <c r="BB24" t="s">
         <v>36</v>
       </c>
+      <c r="BC24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6032,6 +6102,9 @@
       <c r="BB25" t="s">
         <v>36</v>
       </c>
+      <c r="BC25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6232,6 +6305,9 @@
       <c r="BB26" t="s">
         <v>36</v>
       </c>
+      <c r="BC26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6432,6 +6508,9 @@
       <c r="BB27" t="s">
         <v>36</v>
       </c>
+      <c r="BC27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6632,6 +6711,9 @@
       <c r="BB28" t="s">
         <v>36</v>
       </c>
+      <c r="BC28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -6832,6 +6914,9 @@
       <c r="BB29" t="s">
         <v>36</v>
       </c>
+      <c r="BC29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -7032,6 +7117,9 @@
       <c r="BB30" t="s">
         <v>36</v>
       </c>
+      <c r="BC30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7232,6 +7320,9 @@
       <c r="BB31" t="s">
         <v>36</v>
       </c>
+      <c r="BC31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7432,6 +7523,9 @@
       <c r="BB32" t="s">
         <v>36</v>
       </c>
+      <c r="BC32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7630,6 +7724,9 @@
         <v>36</v>
       </c>
       <c r="BB33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BC33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4CB09EA-076A-41C5-90C0-15FCD7A2B5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D05274E-A7D9-4893-9AE2-C763D5828601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -170,6 +170,9 @@
   </si>
   <si>
     <t>5P | F</t>
+  </si>
+  <si>
+    <t>5P|F</t>
   </si>
 </sst>
 </file>
@@ -719,7 +722,37 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4073,7 +4106,7 @@
         <v>36</v>
       </c>
       <c r="BC15" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
@@ -7770,13 +7803,18 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D3:DE33">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ33">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BC5:BC33">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BC5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D05274E-A7D9-4893-9AE2-C763D5828601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5FCA6D-1507-45BE-AA35-77D00A7CDA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -722,27 +722,7 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1226,8 +1206,12 @@
       <c r="BC1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BD1" s="1"/>
-      <c r="BE1" s="1"/>
+      <c r="BD1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BF1" s="1"/>
       <c r="BG1" s="1"/>
       <c r="BH1" s="1"/>
@@ -1427,8 +1411,12 @@
       <c r="BC2" s="1">
         <v>46262</v>
       </c>
-      <c r="BD2" s="1"/>
-      <c r="BE2" s="1"/>
+      <c r="BD2" s="1">
+        <v>46267</v>
+      </c>
+      <c r="BE2" s="1">
+        <v>46269</v>
+      </c>
       <c r="BF2" s="1"/>
       <c r="BG2" s="1"/>
       <c r="BH2" s="1"/>
@@ -1628,6 +1616,9 @@
         <v>36</v>
       </c>
       <c r="BC3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1847,6 +1838,9 @@
       <c r="BC4" t="s">
         <v>36</v>
       </c>
+      <c r="BD4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2064,6 +2058,9 @@
       <c r="BC5" t="s">
         <v>36</v>
       </c>
+      <c r="BD5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2281,6 +2278,9 @@
       <c r="BC6" t="s">
         <v>36</v>
       </c>
+      <c r="BD6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2484,6 +2484,9 @@
       <c r="BC7" t="s">
         <v>36</v>
       </c>
+      <c r="BD7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2687,6 +2690,9 @@
       <c r="BC8" t="s">
         <v>36</v>
       </c>
+      <c r="BD8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2890,6 +2896,9 @@
       <c r="BC9" t="s">
         <v>36</v>
       </c>
+      <c r="BD9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3093,6 +3102,9 @@
       <c r="BC10" t="s">
         <v>36</v>
       </c>
+      <c r="BD10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3296,6 +3308,9 @@
       <c r="BC11" t="s">
         <v>36</v>
       </c>
+      <c r="BD11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3499,6 +3514,9 @@
       <c r="BC12" t="s">
         <v>36</v>
       </c>
+      <c r="BD12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3702,6 +3720,9 @@
       <c r="BC13" t="s">
         <v>36</v>
       </c>
+      <c r="BD13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3905,6 +3926,9 @@
       <c r="BC14" t="s">
         <v>37</v>
       </c>
+      <c r="BD14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4108,6 +4132,9 @@
       <c r="BC15" t="s">
         <v>45</v>
       </c>
+      <c r="BD15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4311,6 +4338,9 @@
       <c r="BC16" t="s">
         <v>36</v>
       </c>
+      <c r="BD16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4514,6 +4544,9 @@
       <c r="BC17" t="s">
         <v>36</v>
       </c>
+      <c r="BD17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4717,6 +4750,9 @@
       <c r="BC18" t="s">
         <v>36</v>
       </c>
+      <c r="BD18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -4920,6 +4956,9 @@
       <c r="BC19" t="s">
         <v>36</v>
       </c>
+      <c r="BD19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5123,6 +5162,9 @@
       <c r="BC20" t="s">
         <v>36</v>
       </c>
+      <c r="BD20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5326,6 +5368,9 @@
       <c r="BC21" t="s">
         <v>36</v>
       </c>
+      <c r="BD21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5529,6 +5574,9 @@
       <c r="BC22" t="s">
         <v>36</v>
       </c>
+      <c r="BD22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5732,6 +5780,9 @@
       <c r="BC23" t="s">
         <v>37</v>
       </c>
+      <c r="BD23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -5935,6 +5986,9 @@
       <c r="BC24" t="s">
         <v>36</v>
       </c>
+      <c r="BD24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6138,6 +6192,9 @@
       <c r="BC25" t="s">
         <v>36</v>
       </c>
+      <c r="BD25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6341,6 +6398,9 @@
       <c r="BC26" t="s">
         <v>36</v>
       </c>
+      <c r="BD26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6544,6 +6604,9 @@
       <c r="BC27" t="s">
         <v>36</v>
       </c>
+      <c r="BD27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6747,6 +6810,9 @@
       <c r="BC28" t="s">
         <v>36</v>
       </c>
+      <c r="BD28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -6950,6 +7016,9 @@
       <c r="BC29" t="s">
         <v>36</v>
       </c>
+      <c r="BD29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -7153,6 +7222,9 @@
       <c r="BC30" t="s">
         <v>36</v>
       </c>
+      <c r="BD30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7356,6 +7428,9 @@
       <c r="BC31" t="s">
         <v>36</v>
       </c>
+      <c r="BD31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7559,6 +7634,9 @@
       <c r="BC32" t="s">
         <v>36</v>
       </c>
+      <c r="BD32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7760,6 +7838,9 @@
         <v>36</v>
       </c>
       <c r="BC33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BD33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>
@@ -7803,12 +7884,12 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D3:DE33">
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ33">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5FCA6D-1507-45BE-AA35-77D00A7CDA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC610C01-3303-4620-82FE-C04C63EC6E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -179,7 +179,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -322,6 +322,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -668,7 +676,7 @@
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -677,6 +685,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1029,7 +1038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DQ33"/>
+  <dimension ref="A1:DQ34"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -1619,6 +1628,9 @@
         <v>36</v>
       </c>
       <c r="BD3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BE3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1841,6 +1853,9 @@
       <c r="BD4" t="s">
         <v>36</v>
       </c>
+      <c r="BE4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2061,6 +2076,9 @@
       <c r="BD5" t="s">
         <v>36</v>
       </c>
+      <c r="BE5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2281,6 +2299,9 @@
       <c r="BD6" t="s">
         <v>36</v>
       </c>
+      <c r="BE6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2487,6 +2508,9 @@
       <c r="BD7" t="s">
         <v>36</v>
       </c>
+      <c r="BE7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2693,6 +2717,9 @@
       <c r="BD8" t="s">
         <v>36</v>
       </c>
+      <c r="BE8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2899,6 +2926,9 @@
       <c r="BD9" t="s">
         <v>36</v>
       </c>
+      <c r="BE9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3105,6 +3135,9 @@
       <c r="BD10" t="s">
         <v>36</v>
       </c>
+      <c r="BE10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3311,6 +3344,9 @@
       <c r="BD11" t="s">
         <v>36</v>
       </c>
+      <c r="BE11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3517,6 +3553,9 @@
       <c r="BD12" t="s">
         <v>36</v>
       </c>
+      <c r="BE12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3723,6 +3762,9 @@
       <c r="BD13" t="s">
         <v>36</v>
       </c>
+      <c r="BE13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3929,6 +3971,9 @@
       <c r="BD14" t="s">
         <v>36</v>
       </c>
+      <c r="BE14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4135,6 +4180,9 @@
       <c r="BD15" t="s">
         <v>36</v>
       </c>
+      <c r="BE15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4341,6 +4389,9 @@
       <c r="BD16" t="s">
         <v>36</v>
       </c>
+      <c r="BE16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4547,6 +4598,9 @@
       <c r="BD17" t="s">
         <v>36</v>
       </c>
+      <c r="BE17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4753,6 +4807,9 @@
       <c r="BD18" t="s">
         <v>36</v>
       </c>
+      <c r="BE18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -4959,6 +5016,9 @@
       <c r="BD19" t="s">
         <v>36</v>
       </c>
+      <c r="BE19" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5165,6 +5225,9 @@
       <c r="BD20" t="s">
         <v>36</v>
       </c>
+      <c r="BE20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5371,6 +5434,9 @@
       <c r="BD21" t="s">
         <v>36</v>
       </c>
+      <c r="BE21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5577,6 +5643,9 @@
       <c r="BD22" t="s">
         <v>36</v>
       </c>
+      <c r="BE22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5783,6 +5852,9 @@
       <c r="BD23" t="s">
         <v>36</v>
       </c>
+      <c r="BE23" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -5989,6 +6061,9 @@
       <c r="BD24" t="s">
         <v>36</v>
       </c>
+      <c r="BE24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6195,6 +6270,9 @@
       <c r="BD25" t="s">
         <v>36</v>
       </c>
+      <c r="BE25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6401,6 +6479,9 @@
       <c r="BD26" t="s">
         <v>36</v>
       </c>
+      <c r="BE26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6607,6 +6688,9 @@
       <c r="BD27" t="s">
         <v>36</v>
       </c>
+      <c r="BE27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6813,6 +6897,9 @@
       <c r="BD28" t="s">
         <v>36</v>
       </c>
+      <c r="BE28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7019,6 +7106,9 @@
       <c r="BD29" t="s">
         <v>36</v>
       </c>
+      <c r="BE29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -7225,6 +7315,9 @@
       <c r="BD30" t="s">
         <v>36</v>
       </c>
+      <c r="BE30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7431,6 +7524,9 @@
       <c r="BD31" t="s">
         <v>36</v>
       </c>
+      <c r="BE31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7637,6 +7733,9 @@
       <c r="BD32" t="s">
         <v>36</v>
       </c>
+      <c r="BE32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7843,6 +7942,9 @@
       <c r="BD33" t="s">
         <v>36</v>
       </c>
+      <c r="BE33" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ33" s="3"/>
       <c r="CK33" s="3"/>
       <c r="CL33" s="3"/>
@@ -7877,6 +7979,9 @@
       <c r="DO33" s="3"/>
       <c r="DP33" s="3"/>
       <c r="DQ33" s="3"/>
+    </row>
+    <row r="34" spans="1:121" x14ac:dyDescent="0.25">
+      <c r="BE34" s="6"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:B33">

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC610C01-3303-4620-82FE-C04C63EC6E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D677A65-EB1B-4681-9549-3BA67B431401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -1221,8 +1221,12 @@
       <c r="BE1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BF1" s="1"/>
-      <c r="BG1" s="1"/>
+      <c r="BF1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
       <c r="BJ1" s="1"/>
@@ -1426,8 +1430,12 @@
       <c r="BE2" s="1">
         <v>46269</v>
       </c>
-      <c r="BF2" s="1"/>
-      <c r="BG2" s="1"/>
+      <c r="BF2" s="1">
+        <v>46274</v>
+      </c>
+      <c r="BG2" s="1">
+        <v>46276</v>
+      </c>
       <c r="BH2" s="1"/>
       <c r="BI2" s="1"/>
       <c r="BJ2" s="1"/>
@@ -1631,6 +1639,9 @@
         <v>36</v>
       </c>
       <c r="BE3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BF3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1856,6 +1867,9 @@
       <c r="BE4" t="s">
         <v>36</v>
       </c>
+      <c r="BF4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2079,6 +2093,9 @@
       <c r="BE5" t="s">
         <v>36</v>
       </c>
+      <c r="BF5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2302,6 +2319,9 @@
       <c r="BE6" t="s">
         <v>36</v>
       </c>
+      <c r="BF6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2511,6 +2531,9 @@
       <c r="BE7" t="s">
         <v>36</v>
       </c>
+      <c r="BF7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2720,6 +2743,9 @@
       <c r="BE8" t="s">
         <v>36</v>
       </c>
+      <c r="BF8" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2929,6 +2955,9 @@
       <c r="BE9" t="s">
         <v>36</v>
       </c>
+      <c r="BF9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3138,6 +3167,9 @@
       <c r="BE10" t="s">
         <v>36</v>
       </c>
+      <c r="BF10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3347,6 +3379,9 @@
       <c r="BE11" t="s">
         <v>36</v>
       </c>
+      <c r="BF11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3556,6 +3591,9 @@
       <c r="BE12" t="s">
         <v>36</v>
       </c>
+      <c r="BF12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3765,6 +3803,9 @@
       <c r="BE13" t="s">
         <v>36</v>
       </c>
+      <c r="BF13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3974,6 +4015,9 @@
       <c r="BE14" t="s">
         <v>36</v>
       </c>
+      <c r="BF14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4183,6 +4227,9 @@
       <c r="BE15" t="s">
         <v>36</v>
       </c>
+      <c r="BF15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4392,6 +4439,9 @@
       <c r="BE16" t="s">
         <v>36</v>
       </c>
+      <c r="BF16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4601,6 +4651,9 @@
       <c r="BE17" t="s">
         <v>36</v>
       </c>
+      <c r="BF17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4810,6 +4863,9 @@
       <c r="BE18" t="s">
         <v>36</v>
       </c>
+      <c r="BF18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5019,6 +5075,9 @@
       <c r="BE19" t="s">
         <v>37</v>
       </c>
+      <c r="BF19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5228,6 +5287,9 @@
       <c r="BE20" t="s">
         <v>36</v>
       </c>
+      <c r="BF20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5437,6 +5499,9 @@
       <c r="BE21" t="s">
         <v>36</v>
       </c>
+      <c r="BF21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5646,6 +5711,9 @@
       <c r="BE22" t="s">
         <v>36</v>
       </c>
+      <c r="BF22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5855,6 +5923,9 @@
       <c r="BE23" t="s">
         <v>37</v>
       </c>
+      <c r="BF23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6064,6 +6135,9 @@
       <c r="BE24" t="s">
         <v>36</v>
       </c>
+      <c r="BF24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6273,6 +6347,9 @@
       <c r="BE25" t="s">
         <v>36</v>
       </c>
+      <c r="BF25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6482,6 +6559,9 @@
       <c r="BE26" t="s">
         <v>36</v>
       </c>
+      <c r="BF26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6691,6 +6771,9 @@
       <c r="BE27" t="s">
         <v>36</v>
       </c>
+      <c r="BF27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6900,6 +6983,9 @@
       <c r="BE28" t="s">
         <v>36</v>
       </c>
+      <c r="BF28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7109,6 +7195,9 @@
       <c r="BE29" t="s">
         <v>36</v>
       </c>
+      <c r="BF29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -7318,6 +7407,9 @@
       <c r="BE30" t="s">
         <v>36</v>
       </c>
+      <c r="BF30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7527,6 +7619,9 @@
       <c r="BE31" t="s">
         <v>36</v>
       </c>
+      <c r="BF31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7736,6 +7831,9 @@
       <c r="BE32" t="s">
         <v>36</v>
       </c>
+      <c r="BF32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7944,6 +8042,9 @@
       </c>
       <c r="BE33" t="s">
         <v>36</v>
+      </c>
+      <c r="BF33" t="s">
+        <v>37</v>
       </c>
       <c r="CJ33" s="3"/>
       <c r="CK33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5FCA6D-1507-45BE-AA35-77D00A7CDA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F03C34B-F792-47DC-81D1-3D79E0FC6633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="46">
   <si>
     <t>Aluno</t>
   </si>
@@ -1621,6 +1621,9 @@
       <c r="BD3" t="s">
         <v>36</v>
       </c>
+      <c r="BE3" t="s">
+        <v>36</v>
+      </c>
       <c r="BV3" s="3"/>
       <c r="BW3" s="3"/>
       <c r="BX3" s="3"/>
@@ -1841,6 +1844,9 @@
       <c r="BD4" t="s">
         <v>36</v>
       </c>
+      <c r="BE4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2061,6 +2067,9 @@
       <c r="BD5" t="s">
         <v>36</v>
       </c>
+      <c r="BE5" t="s">
+        <v>36</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2281,6 +2290,9 @@
       <c r="BD6" t="s">
         <v>36</v>
       </c>
+      <c r="BE6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2487,6 +2499,9 @@
       <c r="BD7" t="s">
         <v>36</v>
       </c>
+      <c r="BE7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2693,6 +2708,9 @@
       <c r="BD8" t="s">
         <v>36</v>
       </c>
+      <c r="BE8" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2899,6 +2917,9 @@
       <c r="BD9" t="s">
         <v>36</v>
       </c>
+      <c r="BE9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3105,6 +3126,9 @@
       <c r="BD10" t="s">
         <v>36</v>
       </c>
+      <c r="BE10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3311,6 +3335,9 @@
       <c r="BD11" t="s">
         <v>36</v>
       </c>
+      <c r="BE11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3517,6 +3544,9 @@
       <c r="BD12" t="s">
         <v>36</v>
       </c>
+      <c r="BE12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3723,6 +3753,9 @@
       <c r="BD13" t="s">
         <v>36</v>
       </c>
+      <c r="BE13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3929,6 +3962,9 @@
       <c r="BD14" t="s">
         <v>36</v>
       </c>
+      <c r="BE14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4135,6 +4171,9 @@
       <c r="BD15" t="s">
         <v>36</v>
       </c>
+      <c r="BE15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4341,6 +4380,9 @@
       <c r="BD16" t="s">
         <v>36</v>
       </c>
+      <c r="BE16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4547,6 +4589,9 @@
       <c r="BD17" t="s">
         <v>36</v>
       </c>
+      <c r="BE17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4753,6 +4798,9 @@
       <c r="BD18" t="s">
         <v>36</v>
       </c>
+      <c r="BE18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -4959,6 +5007,9 @@
       <c r="BD19" t="s">
         <v>36</v>
       </c>
+      <c r="BE19" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5165,6 +5216,9 @@
       <c r="BD20" t="s">
         <v>36</v>
       </c>
+      <c r="BE20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5371,6 +5425,9 @@
       <c r="BD21" t="s">
         <v>36</v>
       </c>
+      <c r="BE21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5577,6 +5634,9 @@
       <c r="BD22" t="s">
         <v>36</v>
       </c>
+      <c r="BE22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5783,6 +5843,9 @@
       <c r="BD23" t="s">
         <v>36</v>
       </c>
+      <c r="BE23" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -5989,6 +6052,9 @@
       <c r="BD24" t="s">
         <v>36</v>
       </c>
+      <c r="BE24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6195,6 +6261,9 @@
       <c r="BD25" t="s">
         <v>36</v>
       </c>
+      <c r="BE25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6401,6 +6470,9 @@
       <c r="BD26" t="s">
         <v>36</v>
       </c>
+      <c r="BE26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6607,6 +6679,9 @@
       <c r="BD27" t="s">
         <v>36</v>
       </c>
+      <c r="BE27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6813,6 +6888,9 @@
       <c r="BD28" t="s">
         <v>36</v>
       </c>
+      <c r="BE28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7019,6 +7097,9 @@
       <c r="BD29" t="s">
         <v>36</v>
       </c>
+      <c r="BE29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -7225,6 +7306,9 @@
       <c r="BD30" t="s">
         <v>36</v>
       </c>
+      <c r="BE30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7431,6 +7515,9 @@
       <c r="BD31" t="s">
         <v>36</v>
       </c>
+      <c r="BE31" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7637,6 +7724,9 @@
       <c r="BD32" t="s">
         <v>36</v>
       </c>
+      <c r="BE32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7841,6 +7931,9 @@
         <v>36</v>
       </c>
       <c r="BD33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BE33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F03C34B-F792-47DC-81D1-3D79E0FC6633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054D1713-22CF-4A37-8AAE-B74FFBB00007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="47">
   <si>
     <t>Aluno</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>5P|F</t>
+  </si>
+  <si>
+    <t>5F | P</t>
   </si>
 </sst>
 </file>
@@ -722,7 +725,47 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1212,8 +1255,12 @@
       <c r="BE1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="BF1" s="1"/>
-      <c r="BG1" s="1"/>
+      <c r="BF1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="BH1" s="1"/>
       <c r="BI1" s="1"/>
       <c r="BJ1" s="1"/>
@@ -1417,8 +1464,12 @@
       <c r="BE2" s="1">
         <v>46269</v>
       </c>
-      <c r="BF2" s="1"/>
-      <c r="BG2" s="1"/>
+      <c r="BF2" s="1">
+        <v>46274</v>
+      </c>
+      <c r="BG2" s="1">
+        <v>46276</v>
+      </c>
       <c r="BH2" s="1"/>
       <c r="BI2" s="1"/>
       <c r="BJ2" s="1"/>
@@ -1622,6 +1673,12 @@
         <v>36</v>
       </c>
       <c r="BE3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG3" t="s">
         <v>36</v>
       </c>
       <c r="BV3" s="3"/>
@@ -1847,6 +1904,12 @@
       <c r="BE4" t="s">
         <v>36</v>
       </c>
+      <c r="BF4" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>36</v>
+      </c>
       <c r="BV4" s="3"/>
       <c r="BW4" s="3"/>
       <c r="BX4" s="3"/>
@@ -2070,6 +2133,12 @@
       <c r="BE5" t="s">
         <v>36</v>
       </c>
+      <c r="BF5" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>37</v>
+      </c>
       <c r="BV5" s="3"/>
       <c r="BW5" s="3"/>
       <c r="BX5" s="3"/>
@@ -2293,6 +2362,12 @@
       <c r="BE6" t="s">
         <v>36</v>
       </c>
+      <c r="BF6" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ6" s="3"/>
       <c r="CK6" s="3"/>
       <c r="CL6" s="3"/>
@@ -2502,6 +2577,12 @@
       <c r="BE7" t="s">
         <v>36</v>
       </c>
+      <c r="BF7" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ7" s="3"/>
       <c r="CK7" s="3"/>
       <c r="CL7" s="3"/>
@@ -2711,6 +2792,12 @@
       <c r="BE8" t="s">
         <v>36</v>
       </c>
+      <c r="BF8" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ8" s="3"/>
       <c r="CK8" s="3"/>
       <c r="CL8" s="3"/>
@@ -2920,6 +3007,12 @@
       <c r="BE9" t="s">
         <v>36</v>
       </c>
+      <c r="BF9" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" s="3"/>
@@ -3129,6 +3222,12 @@
       <c r="BE10" t="s">
         <v>36</v>
       </c>
+      <c r="BF10" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ10" s="3"/>
       <c r="CK10" s="3"/>
       <c r="CL10" s="3"/>
@@ -3338,6 +3437,12 @@
       <c r="BE11" t="s">
         <v>36</v>
       </c>
+      <c r="BF11" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ11" s="3"/>
       <c r="CK11" s="3"/>
       <c r="CL11" s="3"/>
@@ -3547,6 +3652,12 @@
       <c r="BE12" t="s">
         <v>36</v>
       </c>
+      <c r="BF12" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ12" s="3"/>
       <c r="CK12" s="3"/>
       <c r="CL12" s="3"/>
@@ -3756,6 +3867,12 @@
       <c r="BE13" t="s">
         <v>36</v>
       </c>
+      <c r="BF13" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" s="3"/>
@@ -3965,6 +4082,12 @@
       <c r="BE14" t="s">
         <v>36</v>
       </c>
+      <c r="BF14" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" s="3"/>
@@ -4174,6 +4297,12 @@
       <c r="BE15" t="s">
         <v>36</v>
       </c>
+      <c r="BF15" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG15" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ15" s="3"/>
       <c r="CK15" s="3"/>
       <c r="CL15" s="3"/>
@@ -4383,6 +4512,12 @@
       <c r="BE16" t="s">
         <v>36</v>
       </c>
+      <c r="BF16" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ16" s="3"/>
       <c r="CK16" s="3"/>
       <c r="CL16" s="3"/>
@@ -4592,6 +4727,12 @@
       <c r="BE17" t="s">
         <v>36</v>
       </c>
+      <c r="BF17" t="s">
+        <v>37</v>
+      </c>
+      <c r="BG17" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" s="3"/>
@@ -4801,6 +4942,12 @@
       <c r="BE18" t="s">
         <v>36</v>
       </c>
+      <c r="BF18" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ18" s="3"/>
       <c r="CK18" s="3"/>
       <c r="CL18" s="3"/>
@@ -5010,6 +5157,12 @@
       <c r="BE19" t="s">
         <v>37</v>
       </c>
+      <c r="BF19" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG19" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" s="3"/>
@@ -5219,6 +5372,12 @@
       <c r="BE20" t="s">
         <v>36</v>
       </c>
+      <c r="BF20" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG20" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ20" s="3"/>
       <c r="CK20" s="3"/>
       <c r="CL20" s="3"/>
@@ -5428,6 +5587,12 @@
       <c r="BE21" t="s">
         <v>36</v>
       </c>
+      <c r="BF21" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG21" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" s="3"/>
@@ -5637,6 +5802,12 @@
       <c r="BE22" t="s">
         <v>36</v>
       </c>
+      <c r="BF22" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG22" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ22" s="3"/>
       <c r="CK22" s="3"/>
       <c r="CL22" s="3"/>
@@ -5846,6 +6017,12 @@
       <c r="BE23" t="s">
         <v>37</v>
       </c>
+      <c r="BF23" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG23" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ23" s="3"/>
       <c r="CK23" s="3"/>
       <c r="CL23" s="3"/>
@@ -6055,6 +6232,12 @@
       <c r="BE24" t="s">
         <v>36</v>
       </c>
+      <c r="BF24" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG24" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ24" s="3"/>
       <c r="CK24" s="3"/>
       <c r="CL24" s="3"/>
@@ -6264,6 +6447,12 @@
       <c r="BE25" t="s">
         <v>36</v>
       </c>
+      <c r="BF25" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG25" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ25" s="3"/>
       <c r="CK25" s="3"/>
       <c r="CL25" s="3"/>
@@ -6473,6 +6662,12 @@
       <c r="BE26" t="s">
         <v>36</v>
       </c>
+      <c r="BF26" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG26" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ26" s="3"/>
       <c r="CK26" s="3"/>
       <c r="CL26" s="3"/>
@@ -6682,6 +6877,12 @@
       <c r="BE27" t="s">
         <v>36</v>
       </c>
+      <c r="BF27" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG27" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" s="3"/>
@@ -6891,6 +7092,12 @@
       <c r="BE28" t="s">
         <v>36</v>
       </c>
+      <c r="BF28" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG28" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ28" s="3"/>
       <c r="CK28" s="3"/>
       <c r="CL28" s="3"/>
@@ -7100,6 +7307,12 @@
       <c r="BE29" t="s">
         <v>36</v>
       </c>
+      <c r="BF29" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG29" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" s="3"/>
@@ -7309,6 +7522,12 @@
       <c r="BE30" t="s">
         <v>36</v>
       </c>
+      <c r="BF30" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG30" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ30" s="3"/>
       <c r="CK30" s="3"/>
       <c r="CL30" s="3"/>
@@ -7518,6 +7737,12 @@
       <c r="BE31" t="s">
         <v>36</v>
       </c>
+      <c r="BF31" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG31" t="s">
+        <v>37</v>
+      </c>
       <c r="CJ31" s="3"/>
       <c r="CK31" s="3"/>
       <c r="CL31" s="3"/>
@@ -7727,6 +7952,12 @@
       <c r="BE32" t="s">
         <v>36</v>
       </c>
+      <c r="BF32" t="s">
+        <v>36</v>
+      </c>
+      <c r="BG32" t="s">
+        <v>36</v>
+      </c>
       <c r="CJ32" s="3"/>
       <c r="CK32" s="3"/>
       <c r="CL32" s="3"/>
@@ -7934,6 +8165,12 @@
         <v>36</v>
       </c>
       <c r="BE33" t="s">
+        <v>36</v>
+      </c>
+      <c r="BF33" t="s">
+        <v>46</v>
+      </c>
+      <c r="BG33" t="s">
         <v>36</v>
       </c>
       <c r="CJ33" s="3"/>
@@ -7977,18 +8214,23 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D3:DE33">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ33">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC5:BC33">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="F">
+      <formula>NOT(ISERROR(SEARCH("F",BC5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BF3:BF33">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="F">
-      <formula>NOT(ISERROR(SEARCH("F",BC5)))</formula>
+      <formula>NOT(ISERROR(SEARCH("F",BF3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/ds/turmas/2DES_B/frequencia-3-B.xlsx
+++ b/ds/turmas/2DES_B/frequencia-3-B.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\2DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\2DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054D1713-22CF-4A37-8AAE-B74FFBB00007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37D53EC-5DC2-4FEB-9010-EA794BBFDB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -725,37 +725,7 @@
     <cellStyle name="Título 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4086,7 +4056,7 @@
         <v>36</v>
       </c>
       <c r="BG14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CJ14" s="3"/>
       <c r="CK14" s="3"/>
@@ -8214,17 +8184,17 @@
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="D3:DE33">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AZ3:AZ33">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",AZ3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BC5:BC33">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BC5)))</formula>
     </cfRule>
   </conditionalFormatting>
